--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\modelX\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\data\prod_parameters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="13" r:id="rId1"/>
@@ -56,13 +56,13 @@
   </definedNames>
   <calcPr calcId="162913" iterate="1"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="435">
   <si>
     <t>value</t>
   </si>
@@ -1371,6 +1371,15 @@
   <si>
     <t>breeding bulls</t>
   </si>
+  <si>
+    <t>Maximum share of grazing in semi-natural grasslands</t>
+  </si>
+  <si>
+    <t>max_sng_grazing</t>
+  </si>
+  <si>
+    <t>This parameter specifies the maximum share of grazing demand that can be met from grazing in semi-natural grasslands</t>
+  </si>
 </sst>
 </file>
 
@@ -1383,7 +1392,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1628,6 +1637,13 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -2220,7 +2236,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2333,7 +2349,6 @@
     <xf numFmtId="2" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2473,6 +2488,8 @@
     <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -13985,7 +14002,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="L3:O43" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0">
@@ -14477,7 +14494,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="109" t="s">
         <v>331</v>
       </c>
     </row>
@@ -14498,48 +14515,48 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="140" t="s">
+      <c r="A3" s="139" t="s">
         <v>359</v>
       </c>
-      <c r="B3" s="140"/>
+      <c r="B3" s="139"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="136" t="s">
         <v>360</v>
       </c>
-      <c r="B4" s="137">
+      <c r="B4" s="136">
         <v>0.99434308508956182</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="136" t="s">
         <v>361</v>
       </c>
-      <c r="B5" s="137">
+      <c r="B5" s="136">
         <v>0.98871817086542757</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="136" t="s">
         <v>362</v>
       </c>
-      <c r="B6" s="142">
+      <c r="B6" s="141">
         <v>0.9876437109478492</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="136" t="s">
         <v>363</v>
       </c>
-      <c r="B7" s="137">
+      <c r="B7" s="136">
         <v>0.64295634155271764</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="137" t="s">
         <v>364</v>
       </c>
-      <c r="B8" s="138">
+      <c r="B8" s="137">
         <v>24</v>
       </c>
     </row>
@@ -14549,185 +14566,185 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="139"/>
-      <c r="B11" s="139" t="s">
+      <c r="A11" s="138"/>
+      <c r="B11" s="138" t="s">
         <v>369</v>
       </c>
-      <c r="C11" s="139" t="s">
+      <c r="C11" s="138" t="s">
         <v>370</v>
       </c>
-      <c r="D11" s="139" t="s">
+      <c r="D11" s="138" t="s">
         <v>371</v>
       </c>
-      <c r="E11" s="139" t="s">
+      <c r="E11" s="138" t="s">
         <v>372</v>
       </c>
-      <c r="F11" s="139" t="s">
+      <c r="F11" s="138" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="137" t="s">
+      <c r="A12" s="136" t="s">
         <v>366</v>
       </c>
-      <c r="B12" s="137">
+      <c r="B12" s="136">
         <v>2</v>
       </c>
-      <c r="C12" s="137">
+      <c r="C12" s="136">
         <v>760.80833333333317</v>
       </c>
-      <c r="D12" s="137">
+      <c r="D12" s="136">
         <v>380.40416666666658</v>
       </c>
-      <c r="E12" s="137">
+      <c r="E12" s="136">
         <v>920.20014398848559</v>
       </c>
-      <c r="F12" s="137">
+      <c r="F12" s="136">
         <v>3.5480108451103033E-21</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="136" t="s">
         <v>367</v>
       </c>
-      <c r="B13" s="137">
+      <c r="B13" s="136">
         <v>21</v>
       </c>
-      <c r="C13" s="137">
+      <c r="C13" s="136">
         <v>8.6812499999999542</v>
       </c>
-      <c r="D13" s="137">
+      <c r="D13" s="136">
         <v>0.41339285714285495</v>
       </c>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="136"/>
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="138" t="s">
+      <c r="A14" s="137" t="s">
         <v>317</v>
       </c>
-      <c r="B14" s="138">
+      <c r="B14" s="137">
         <v>23</v>
       </c>
-      <c r="C14" s="138">
+      <c r="C14" s="137">
         <v>769.48958333333314</v>
       </c>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="139"/>
-      <c r="B16" s="139" t="s">
+      <c r="A16" s="138"/>
+      <c r="B16" s="138" t="s">
         <v>374</v>
       </c>
-      <c r="C16" s="139" t="s">
+      <c r="C16" s="138" t="s">
         <v>363</v>
       </c>
-      <c r="D16" s="139" t="s">
+      <c r="D16" s="138" t="s">
         <v>375</v>
       </c>
-      <c r="E16" s="139" t="s">
+      <c r="E16" s="138" t="s">
         <v>376</v>
       </c>
-      <c r="F16" s="139" t="s">
+      <c r="F16" s="138" t="s">
         <v>377</v>
       </c>
-      <c r="G16" s="139" t="s">
+      <c r="G16" s="138" t="s">
         <v>378</v>
       </c>
-      <c r="H16" s="139" t="s">
+      <c r="H16" s="138" t="s">
         <v>379</v>
       </c>
-      <c r="I16" s="139" t="s">
+      <c r="I16" s="138" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="137" t="s">
+      <c r="A17" s="136" t="s">
         <v>368</v>
       </c>
-      <c r="B17" s="137">
+      <c r="B17" s="136">
         <v>-0.40773809523810023</v>
       </c>
-      <c r="C17" s="137">
+      <c r="C17" s="136">
         <v>0.46902457944381531</v>
       </c>
-      <c r="D17" s="137">
+      <c r="D17" s="136">
         <v>-0.86933204166316702</v>
       </c>
-      <c r="E17" s="137">
+      <c r="E17" s="136">
         <v>0.3944933503705087</v>
       </c>
-      <c r="F17" s="137">
+      <c r="F17" s="136">
         <v>-1.383128104167036</v>
       </c>
-      <c r="G17" s="137">
+      <c r="G17" s="136">
         <v>0.56765191369083567</v>
       </c>
-      <c r="H17" s="137">
+      <c r="H17" s="136">
         <v>-1.383128104167036</v>
       </c>
-      <c r="I17" s="137">
+      <c r="I17" s="136">
         <v>0.56765191369083567</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="137" t="s">
+      <c r="A18" s="136" t="s">
         <v>349</v>
       </c>
-      <c r="B18" s="137">
+      <c r="B18" s="136">
         <v>0.16892857142857148</v>
       </c>
-      <c r="C18" s="137">
+      <c r="C18" s="136">
         <v>7.6847981397678419E-3</v>
       </c>
-      <c r="D18" s="137">
+      <c r="D18" s="136">
         <v>21.982174203690253</v>
       </c>
-      <c r="E18" s="137">
+      <c r="E18" s="136">
         <v>5.622260089430527E-16</v>
       </c>
-      <c r="F18" s="137">
+      <c r="F18" s="136">
         <v>0.15294715882317275</v>
       </c>
-      <c r="G18" s="137">
+      <c r="G18" s="136">
         <v>0.18490998403397021</v>
       </c>
-      <c r="H18" s="137">
+      <c r="H18" s="136">
         <v>0.15294715882317275</v>
       </c>
-      <c r="I18" s="137">
+      <c r="I18" s="136">
         <v>0.18490998403397021</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="138" t="s">
+      <c r="A19" s="137" t="s">
         <v>356</v>
       </c>
-      <c r="B19" s="138">
+      <c r="B19" s="137">
         <v>1.3076190476190479E-2</v>
       </c>
-      <c r="C19" s="138">
+      <c r="C19" s="137">
         <v>3.549456219730319E-4</v>
       </c>
-      <c r="D19" s="138">
+      <c r="D19" s="137">
         <v>36.839982427460349</v>
       </c>
-      <c r="E19" s="138">
+      <c r="E19" s="137">
         <v>1.4430475578158989E-20</v>
       </c>
-      <c r="F19" s="138">
+      <c r="F19" s="137">
         <v>1.2338040646609885E-2</v>
       </c>
-      <c r="G19" s="138">
+      <c r="G19" s="137">
         <v>1.3814340305771073E-2</v>
       </c>
-      <c r="H19" s="138">
+      <c r="H19" s="137">
         <v>1.2338040646609885E-2</v>
       </c>
-      <c r="I19" s="138">
+      <c r="I19" s="137">
         <v>1.3814340305771073E-2</v>
       </c>
     </row>
@@ -14738,352 +14755,352 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="139" t="s">
+      <c r="A25" s="138" t="s">
         <v>382</v>
       </c>
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="138" t="s">
         <v>383</v>
       </c>
-      <c r="C25" s="139" t="s">
+      <c r="C25" s="138" t="s">
         <v>384</v>
       </c>
-      <c r="D25" s="139" t="s">
+      <c r="D25" s="138" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="137">
+      <c r="A26" s="136">
         <v>1</v>
       </c>
-      <c r="B26" s="137">
+      <c r="B26" s="136">
         <v>4.6601190476190446</v>
       </c>
-      <c r="C26" s="137">
+      <c r="C26" s="136">
         <v>1.3398809523809554</v>
       </c>
-      <c r="D26" s="137">
+      <c r="D26" s="136">
         <v>2.1809163068088218</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="137">
+      <c r="A27" s="136">
         <v>2</v>
       </c>
-      <c r="B27" s="137">
+      <c r="B27" s="136">
         <v>6.3494047619047596</v>
       </c>
-      <c r="C27" s="137">
+      <c r="C27" s="136">
         <v>0.65059523809524045</v>
       </c>
-      <c r="D27" s="137">
+      <c r="D27" s="136">
         <v>1.0589700236970436</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="137">
+      <c r="A28" s="136">
         <v>3</v>
       </c>
-      <c r="B28" s="137">
+      <c r="B28" s="136">
         <v>8.0386904761904745</v>
       </c>
-      <c r="C28" s="137">
+      <c r="C28" s="136">
         <v>0.4613095238095255</v>
       </c>
-      <c r="D28" s="137">
+      <c r="D28" s="136">
         <v>0.75087078532955975</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="137">
+      <c r="A29" s="136">
         <v>4</v>
       </c>
-      <c r="B29" s="137">
+      <c r="B29" s="136">
         <v>9.7279761904761894</v>
       </c>
-      <c r="C29" s="137">
+      <c r="C29" s="136">
         <v>0.27202380952381056</v>
       </c>
-      <c r="D29" s="137">
+      <c r="D29" s="136">
         <v>0.44277154696207599</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="137">
+      <c r="A30" s="136">
         <v>5</v>
       </c>
-      <c r="B30" s="137">
+      <c r="B30" s="136">
         <v>11.417261904761904</v>
       </c>
-      <c r="C30" s="137">
+      <c r="C30" s="136">
         <v>8.273809523809561E-2</v>
       </c>
-      <c r="D30" s="137">
+      <c r="D30" s="136">
         <v>0.13467230859459212</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="137">
+      <c r="A31" s="136">
         <v>6</v>
       </c>
-      <c r="B31" s="137">
+      <c r="B31" s="136">
         <v>13.106547619047619</v>
       </c>
-      <c r="C31" s="137">
+      <c r="C31" s="136">
         <v>-0.10654761904761934</v>
       </c>
-      <c r="D31" s="137">
+      <c r="D31" s="136">
         <v>-0.1734269297728917</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="137">
+      <c r="A32" s="136">
         <v>7</v>
       </c>
-      <c r="B32" s="137">
+      <c r="B32" s="136">
         <v>7.9291666666666645</v>
       </c>
-      <c r="C32" s="137">
+      <c r="C32" s="136">
         <v>7.0833333333335524E-2</v>
       </c>
-      <c r="D32" s="137">
+      <c r="D32" s="136">
         <v>0.11529499800544522</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="137">
+      <c r="A33" s="136">
         <v>8</v>
       </c>
-      <c r="B33" s="137">
+      <c r="B33" s="136">
         <v>9.6184523809523803</v>
       </c>
-      <c r="C33" s="137">
+      <c r="C33" s="136">
         <v>-0.11845238095238031</v>
       </c>
-      <c r="D33" s="137">
+      <c r="D33" s="136">
         <v>-0.19280424036204005</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="137">
+      <c r="A34" s="136">
         <v>9</v>
       </c>
-      <c r="B34" s="137">
+      <c r="B34" s="136">
         <v>11.307738095238093</v>
       </c>
-      <c r="C34" s="137">
+      <c r="C34" s="136">
         <v>-0.30773809523809348</v>
       </c>
-      <c r="D34" s="137">
+      <c r="D34" s="136">
         <v>-0.50090347872952101</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="137">
+      <c r="A35" s="136">
         <v>10</v>
       </c>
-      <c r="B35" s="137">
+      <c r="B35" s="136">
         <v>12.99702380952381</v>
       </c>
-      <c r="C35" s="137">
+      <c r="C35" s="136">
         <v>-0.4970238095238102</v>
       </c>
-      <c r="D35" s="137">
+      <c r="D35" s="136">
         <v>-0.80900271709700777</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="137">
+      <c r="A36" s="136">
         <v>11</v>
       </c>
-      <c r="B36" s="137">
+      <c r="B36" s="136">
         <v>14.686309523809523</v>
       </c>
-      <c r="C36" s="137">
+      <c r="C36" s="136">
         <v>-0.68630952380952337</v>
       </c>
-      <c r="D36" s="137">
+      <c r="D36" s="136">
         <v>-1.1171019554644888</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="137">
+      <c r="A37" s="136">
         <v>12</v>
       </c>
-      <c r="B37" s="137">
+      <c r="B37" s="136">
         <v>16.37559523809524</v>
       </c>
-      <c r="C37" s="137">
+      <c r="C37" s="136">
         <v>-0.37559523809524009</v>
       </c>
-      <c r="D37" s="137">
+      <c r="D37" s="136">
         <v>-0.61135414908768126</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="137">
+      <c r="A38" s="136">
         <v>13</v>
       </c>
-      <c r="B38" s="137">
+      <c r="B38" s="136">
         <v>11.198214285714284</v>
       </c>
-      <c r="C38" s="137">
+      <c r="C38" s="136">
         <v>-0.19821428571428434</v>
       </c>
-      <c r="D38" s="137">
+      <c r="D38" s="136">
         <v>-0.32263222130934294</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="137">
+      <c r="A39" s="136">
         <v>14</v>
       </c>
-      <c r="B39" s="137">
+      <c r="B39" s="136">
         <v>12.887499999999999</v>
       </c>
-      <c r="C39" s="137">
+      <c r="C39" s="136">
         <v>-0.38749999999999929</v>
       </c>
-      <c r="D39" s="137">
+      <c r="D39" s="136">
         <v>-0.63073145967682676</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="137">
+      <c r="A40" s="136">
         <v>15</v>
       </c>
-      <c r="B40" s="137">
+      <c r="B40" s="136">
         <v>14.576785714285714</v>
       </c>
-      <c r="C40" s="137">
+      <c r="C40" s="136">
         <v>-0.57678571428571423</v>
       </c>
-      <c r="D40" s="137">
+      <c r="D40" s="136">
         <v>-0.93883069804431063</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="137">
+      <c r="A41" s="136">
         <v>16</v>
       </c>
-      <c r="B41" s="137">
+      <c r="B41" s="136">
         <v>16.266071428571429</v>
       </c>
-      <c r="C41" s="137">
+      <c r="C41" s="136">
         <v>-0.76607142857142918</v>
       </c>
-      <c r="D41" s="137">
+      <c r="D41" s="136">
         <v>-1.2469299364117945</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="137">
+      <c r="A42" s="136">
         <v>17</v>
       </c>
-      <c r="B42" s="137">
+      <c r="B42" s="136">
         <v>17.955357142857146</v>
       </c>
-      <c r="C42" s="137">
+      <c r="C42" s="136">
         <v>-0.4553571428571459</v>
       </c>
-      <c r="D42" s="137">
+      <c r="D42" s="136">
         <v>-0.74118213003498712</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="137">
+      <c r="A43" s="136">
         <v>18</v>
       </c>
-      <c r="B43" s="137">
+      <c r="B43" s="136">
         <v>19.644642857142859</v>
       </c>
-      <c r="C43" s="137">
+      <c r="C43" s="136">
         <v>-0.14464285714285907</v>
       </c>
-      <c r="D43" s="137">
+      <c r="D43" s="136">
         <v>-0.23543432365817393</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="137">
+      <c r="A44" s="136">
         <v>19</v>
       </c>
-      <c r="B44" s="137">
+      <c r="B44" s="136">
         <v>17.736309523809524</v>
       </c>
-      <c r="C44" s="137">
+      <c r="C44" s="136">
         <v>-0.23630952380952408</v>
       </c>
-      <c r="D44" s="137">
+      <c r="D44" s="136">
         <v>-0.38463961519462514</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="137">
+      <c r="A45" s="136">
         <v>20</v>
       </c>
-      <c r="B45" s="137">
+      <c r="B45" s="136">
         <v>19.425595238095241</v>
       </c>
-      <c r="C45" s="137">
+      <c r="C45" s="136">
         <v>-0.4255952380952408</v>
       </c>
-      <c r="D45" s="137">
+      <c r="D45" s="136">
         <v>-0.69273885356211184</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="137">
+      <c r="A46" s="136">
         <v>21</v>
       </c>
-      <c r="B46" s="137">
+      <c r="B46" s="136">
         <v>21.114880952380954</v>
       </c>
-      <c r="C46" s="137">
+      <c r="C46" s="136">
         <v>-0.11488095238095397</v>
       </c>
-      <c r="D46" s="137">
+      <c r="D46" s="136">
         <v>-0.18699104718529874</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="137">
+      <c r="A47" s="136">
         <v>22</v>
       </c>
-      <c r="B47" s="137">
+      <c r="B47" s="136">
         <v>22.804166666666667</v>
       </c>
-      <c r="C47" s="137">
+      <c r="C47" s="136">
         <v>0.19583333333333286</v>
       </c>
-      <c r="D47" s="137">
+      <c r="D47" s="136">
         <v>0.31875675919151442</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="137">
+      <c r="A48" s="136">
         <v>23</v>
       </c>
-      <c r="B48" s="137">
+      <c r="B48" s="136">
         <v>24.493452380952384</v>
       </c>
-      <c r="C48" s="137">
+      <c r="C48" s="136">
         <v>0.50654761904761614</v>
       </c>
-      <c r="D48" s="137">
+      <c r="D48" s="136">
         <v>0.82450456556832175</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="138">
+      <c r="A49" s="137">
         <v>24</v>
       </c>
-      <c r="B49" s="138">
+      <c r="B49" s="137">
         <v>26.182738095238101</v>
       </c>
-      <c r="C49" s="138">
+      <c r="C49" s="137">
         <v>1.8172619047618994</v>
       </c>
-      <c r="D49" s="138">
+      <c r="D49" s="137">
         <v>2.9579464614337172</v>
       </c>
     </row>
@@ -15105,48 +15122,48 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="140" t="s">
+      <c r="A3" s="139" t="s">
         <v>359</v>
       </c>
-      <c r="B3" s="140"/>
+      <c r="B3" s="139"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="136" t="s">
         <v>360</v>
       </c>
-      <c r="B4" s="137">
+      <c r="B4" s="136">
         <v>0.99923601209082613</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="136" t="s">
         <v>361</v>
       </c>
-      <c r="B5" s="137">
+      <c r="B5" s="136">
         <v>0.99847260785917769</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="136" t="s">
         <v>362</v>
       </c>
-      <c r="B6" s="142">
+      <c r="B6" s="141">
         <v>0.95294863548914033</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="136" t="s">
         <v>363</v>
       </c>
-      <c r="B7" s="137">
+      <c r="B7" s="136">
         <v>0.63937706804773409</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="137" t="s">
         <v>364</v>
       </c>
-      <c r="B8" s="138">
+      <c r="B8" s="137">
         <v>24</v>
       </c>
     </row>
@@ -15156,185 +15173,185 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="139"/>
-      <c r="B11" s="139" t="s">
+      <c r="A11" s="138"/>
+      <c r="B11" s="138" t="s">
         <v>369</v>
       </c>
-      <c r="C11" s="139" t="s">
+      <c r="C11" s="138" t="s">
         <v>370</v>
       </c>
-      <c r="D11" s="139" t="s">
+      <c r="D11" s="138" t="s">
         <v>371</v>
       </c>
-      <c r="E11" s="139" t="s">
+      <c r="E11" s="138" t="s">
         <v>372</v>
       </c>
-      <c r="F11" s="139" t="s">
+      <c r="F11" s="138" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="137" t="s">
+      <c r="A12" s="136" t="s">
         <v>366</v>
       </c>
-      <c r="B12" s="137">
+      <c r="B12" s="136">
         <v>2</v>
       </c>
-      <c r="C12" s="137">
+      <c r="C12" s="136">
         <v>5879.2563332268028</v>
       </c>
-      <c r="D12" s="137">
+      <c r="D12" s="136">
         <v>2939.6281666134014</v>
       </c>
-      <c r="E12" s="137">
+      <c r="E12" s="136">
         <v>7190.8178606561842</v>
       </c>
-      <c r="F12" s="137">
+      <c r="F12" s="136">
         <v>1.658295194250544E-30</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="136" t="s">
         <v>367</v>
       </c>
-      <c r="B13" s="137">
+      <c r="B13" s="136">
         <v>22</v>
       </c>
-      <c r="C13" s="137">
+      <c r="C13" s="136">
         <v>8.9936667731969688</v>
       </c>
-      <c r="D13" s="137">
+      <c r="D13" s="136">
         <v>0.40880303514531674</v>
       </c>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="136"/>
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="138" t="s">
+      <c r="A14" s="137" t="s">
         <v>317</v>
       </c>
-      <c r="B14" s="138">
+      <c r="B14" s="137">
         <v>24</v>
       </c>
-      <c r="C14" s="138">
+      <c r="C14" s="137">
         <v>5888.25</v>
       </c>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="139"/>
-      <c r="B16" s="139" t="s">
+      <c r="A16" s="138"/>
+      <c r="B16" s="138" t="s">
         <v>374</v>
       </c>
-      <c r="C16" s="139" t="s">
+      <c r="C16" s="138" t="s">
         <v>363</v>
       </c>
-      <c r="D16" s="139" t="s">
+      <c r="D16" s="138" t="s">
         <v>375</v>
       </c>
-      <c r="E16" s="139" t="s">
+      <c r="E16" s="138" t="s">
         <v>376</v>
       </c>
-      <c r="F16" s="139" t="s">
+      <c r="F16" s="138" t="s">
         <v>377</v>
       </c>
-      <c r="G16" s="139" t="s">
+      <c r="G16" s="138" t="s">
         <v>378</v>
       </c>
-      <c r="H16" s="139" t="s">
+      <c r="H16" s="138" t="s">
         <v>379</v>
       </c>
-      <c r="I16" s="139" t="s">
+      <c r="I16" s="138" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="137" t="s">
+      <c r="A17" s="136" t="s">
         <v>368</v>
       </c>
-      <c r="B17" s="137">
+      <c r="B17" s="136">
         <v>0</v>
       </c>
-      <c r="C17" s="137" t="e">
+      <c r="C17" s="136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D17" s="137" t="e">
+      <c r="D17" s="136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="E17" s="137" t="e">
+      <c r="E17" s="136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F17" s="137" t="e">
+      <c r="F17" s="136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G17" s="137" t="e">
+      <c r="G17" s="136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H17" s="137" t="e">
+      <c r="H17" s="136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="I17" s="137" t="e">
+      <c r="I17" s="136" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="137" t="s">
+      <c r="A18" s="136" t="s">
         <v>349</v>
       </c>
-      <c r="B18" s="137">
+      <c r="B18" s="136">
         <v>0.1629082774049217</v>
       </c>
-      <c r="C18" s="137">
+      <c r="C18" s="136">
         <v>3.3127900815938349E-3</v>
       </c>
-      <c r="D18" s="137">
+      <c r="D18" s="136">
         <v>49.175550938181992</v>
       </c>
-      <c r="E18" s="137">
+      <c r="E18" s="136">
         <v>5.4013091173267767E-24</v>
       </c>
-      <c r="F18" s="137">
+      <c r="F18" s="136">
         <v>0.15603797127508467</v>
       </c>
-      <c r="G18" s="137">
+      <c r="G18" s="136">
         <v>0.16977858353475872</v>
       </c>
-      <c r="H18" s="137">
+      <c r="H18" s="136">
         <v>0.15603797127508467</v>
       </c>
-      <c r="I18" s="137">
+      <c r="I18" s="136">
         <v>0.16977858353475872</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="138" t="s">
+      <c r="A19" s="137" t="s">
         <v>356</v>
       </c>
-      <c r="B19" s="138">
+      <c r="B19" s="137">
         <v>1.2974027910940667E-2</v>
       </c>
-      <c r="C19" s="138">
+      <c r="C19" s="137">
         <v>3.330620646154739E-4</v>
       </c>
-      <c r="D19" s="138">
+      <c r="D19" s="137">
         <v>38.953784562404053</v>
       </c>
-      <c r="E19" s="138">
+      <c r="E19" s="137">
         <v>8.5990489859870578E-22</v>
       </c>
-      <c r="F19" s="138">
+      <c r="F19" s="137">
         <v>1.2283299465194126E-2</v>
       </c>
-      <c r="G19" s="138">
+      <c r="G19" s="137">
         <v>1.3664756356687209E-2</v>
       </c>
-      <c r="H19" s="138">
+      <c r="H19" s="137">
         <v>1.2283299465194126E-2</v>
       </c>
-      <c r="I19" s="138">
+      <c r="I19" s="137">
         <v>1.3664756356687209E-2</v>
       </c>
     </row>
@@ -15345,352 +15362,352 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="139" t="s">
+      <c r="A25" s="138" t="s">
         <v>382</v>
       </c>
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="138" t="s">
         <v>383</v>
       </c>
-      <c r="C25" s="139" t="s">
+      <c r="C25" s="138" t="s">
         <v>384</v>
       </c>
-      <c r="D25" s="139" t="s">
+      <c r="D25" s="138" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="137">
+      <c r="A26" s="136">
         <v>1</v>
       </c>
-      <c r="B26" s="137">
+      <c r="B26" s="136">
         <v>4.8872483221476513</v>
       </c>
-      <c r="C26" s="137">
+      <c r="C26" s="136">
         <v>1.1127516778523487</v>
       </c>
-      <c r="D26" s="137">
+      <c r="D26" s="136">
         <v>1.8177555632337312</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="137">
+      <c r="A27" s="136">
         <v>2</v>
       </c>
-      <c r="B27" s="137">
+      <c r="B27" s="136">
         <v>6.5163310961968683</v>
       </c>
-      <c r="C27" s="137">
+      <c r="C27" s="136">
         <v>0.48366890380313166</v>
       </c>
-      <c r="D27" s="137">
+      <c r="D27" s="136">
         <v>0.79010605703886705</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="137">
+      <c r="A28" s="136">
         <v>3</v>
       </c>
-      <c r="B28" s="137">
+      <c r="B28" s="136">
         <v>8.1454138702460845</v>
       </c>
-      <c r="C28" s="137">
+      <c r="C28" s="136">
         <v>0.35458612975391546</v>
       </c>
-      <c r="D28" s="137">
+      <c r="D28" s="136">
         <v>0.57924056448039174</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="137">
+      <c r="A29" s="136">
         <v>4</v>
       </c>
-      <c r="B29" s="137">
+      <c r="B29" s="136">
         <v>9.7744966442953025</v>
       </c>
-      <c r="C29" s="137">
+      <c r="C29" s="136">
         <v>0.22550335570469748</v>
       </c>
-      <c r="D29" s="137">
+      <c r="D29" s="136">
         <v>0.36837507192191343</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="137">
+      <c r="A30" s="136">
         <v>5</v>
       </c>
-      <c r="B30" s="137">
+      <c r="B30" s="136">
         <v>11.403579418344519</v>
       </c>
-      <c r="C30" s="137">
+      <c r="C30" s="136">
         <v>9.6420581655481286E-2</v>
       </c>
-      <c r="D30" s="137">
+      <c r="D30" s="136">
         <v>0.15750957936343804</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="137">
+      <c r="A31" s="136">
         <v>6</v>
       </c>
-      <c r="B31" s="137">
+      <c r="B31" s="136">
         <v>13.032662192393737</v>
       </c>
-      <c r="C31" s="137">
+      <c r="C31" s="136">
         <v>-3.2662192393736689E-2</v>
       </c>
-      <c r="D31" s="137">
+      <c r="D31" s="136">
         <v>-5.335591319504026E-2</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="137">
+      <c r="A32" s="136">
         <v>7</v>
       </c>
-      <c r="B32" s="137">
+      <c r="B32" s="136">
         <v>8.1307552998828179</v>
       </c>
-      <c r="C32" s="137">
+      <c r="C32" s="136">
         <v>-0.13075529988281787</v>
       </c>
-      <c r="D32" s="137">
+      <c r="D32" s="136">
         <v>-0.21359767728503481</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="137">
+      <c r="A33" s="136">
         <v>8</v>
       </c>
-      <c r="B33" s="137">
+      <c r="B33" s="136">
         <v>9.7598380739320358</v>
       </c>
-      <c r="C33" s="137">
+      <c r="C33" s="136">
         <v>-0.25983807393203584</v>
       </c>
-      <c r="D33" s="137">
+      <c r="D33" s="136">
         <v>-0.42446316984351312</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="137">
+      <c r="A34" s="136">
         <v>9</v>
       </c>
-      <c r="B34" s="137">
+      <c r="B34" s="136">
         <v>11.388920847981252</v>
       </c>
-      <c r="C34" s="137">
+      <c r="C34" s="136">
         <v>-0.38892084798125204</v>
       </c>
-      <c r="D34" s="137">
+      <c r="D34" s="136">
         <v>-0.63532866240198849</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="137">
+      <c r="A35" s="136">
         <v>10</v>
       </c>
-      <c r="B35" s="137">
+      <c r="B35" s="136">
         <v>13.01800362203047</v>
       </c>
-      <c r="C35" s="137">
+      <c r="C35" s="136">
         <v>-0.51800362203047001</v>
       </c>
-      <c r="D35" s="137">
+      <c r="D35" s="136">
         <v>-0.84619415496046679</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="137">
+      <c r="A36" s="136">
         <v>11</v>
       </c>
-      <c r="B36" s="137">
+      <c r="B36" s="136">
         <v>14.647086396079686</v>
       </c>
-      <c r="C36" s="137">
+      <c r="C36" s="136">
         <v>-0.64708639607968621</v>
       </c>
-      <c r="D36" s="137">
+      <c r="D36" s="136">
         <v>-1.0570596475189422</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="137">
+      <c r="A37" s="136">
         <v>12</v>
       </c>
-      <c r="B37" s="137">
+      <c r="B37" s="136">
         <v>16.276169170128902</v>
       </c>
-      <c r="C37" s="137">
+      <c r="C37" s="136">
         <v>-0.27616917012890241</v>
       </c>
-      <c r="D37" s="137">
+      <c r="D37" s="136">
         <v>-0.45114112644103033</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="137">
+      <c r="A38" s="136">
         <v>13</v>
       </c>
-      <c r="B38" s="137">
+      <c r="B38" s="136">
         <v>11.374262277617985</v>
       </c>
-      <c r="C38" s="137">
+      <c r="C38" s="136">
         <v>-0.37426227761798536</v>
       </c>
-      <c r="D38" s="137">
+      <c r="D38" s="136">
         <v>-0.61138289053102779</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="137">
+      <c r="A39" s="136">
         <v>14</v>
       </c>
-      <c r="B39" s="137">
+      <c r="B39" s="136">
         <v>13.003345051667203</v>
       </c>
-      <c r="C39" s="137">
+      <c r="C39" s="136">
         <v>-0.50334505166720334</v>
       </c>
-      <c r="D39" s="137">
+      <c r="D39" s="136">
         <v>-0.8222483830895061</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="137">
+      <c r="A40" s="136">
         <v>15</v>
       </c>
-      <c r="B40" s="137">
+      <c r="B40" s="136">
         <v>14.63242782571642</v>
       </c>
-      <c r="C40" s="137">
+      <c r="C40" s="136">
         <v>-0.63242782571641953</v>
       </c>
-      <c r="D40" s="137">
+      <c r="D40" s="136">
         <v>-1.0331138756479814</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="137">
+      <c r="A41" s="136">
         <v>16</v>
       </c>
-      <c r="B41" s="137">
+      <c r="B41" s="136">
         <v>16.261510599765636</v>
       </c>
-      <c r="C41" s="137">
+      <c r="C41" s="136">
         <v>-0.76151059976563573</v>
       </c>
-      <c r="D41" s="137">
+      <c r="D41" s="136">
         <v>-1.2439793682064568</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="137">
+      <c r="A42" s="136">
         <v>17</v>
       </c>
-      <c r="B42" s="137">
+      <c r="B42" s="136">
         <v>17.890593373814852</v>
       </c>
-      <c r="C42" s="137">
+      <c r="C42" s="136">
         <v>-0.39059337381485193</v>
       </c>
-      <c r="D42" s="137">
+      <c r="D42" s="136">
         <v>-0.63806084712854505</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="137">
+      <c r="A43" s="136">
         <v>18</v>
       </c>
-      <c r="B43" s="137">
+      <c r="B43" s="136">
         <v>19.519676147864072</v>
       </c>
-      <c r="C43" s="137">
+      <c r="C43" s="136">
         <v>-1.967614786407168E-2</v>
       </c>
-      <c r="D43" s="137">
+      <c r="D43" s="136">
         <v>-3.2142326050638992E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="137">
+      <c r="A44" s="136">
         <v>19</v>
       </c>
-      <c r="B44" s="137">
+      <c r="B44" s="136">
         <v>17.861276233088319</v>
       </c>
-      <c r="C44" s="137">
+      <c r="C44" s="136">
         <v>-0.36127623308831858</v>
       </c>
-      <c r="D44" s="137">
+      <c r="D44" s="136">
         <v>-0.59016930338662366</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="137">
+      <c r="A45" s="136">
         <v>20</v>
       </c>
-      <c r="B45" s="137">
+      <c r="B45" s="136">
         <v>19.490359007137535</v>
       </c>
-      <c r="C45" s="137">
+      <c r="C45" s="136">
         <v>-0.49035900713753477</v>
       </c>
-      <c r="D45" s="137">
+      <c r="D45" s="136">
         <v>-0.80103479594509897</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="137">
+      <c r="A46" s="136">
         <v>21</v>
       </c>
-      <c r="B46" s="137">
+      <c r="B46" s="136">
         <v>21.119441781186751</v>
       </c>
-      <c r="C46" s="137">
+      <c r="C46" s="136">
         <v>-0.11944178118675097</v>
       </c>
-      <c r="D46" s="137">
+      <c r="D46" s="136">
         <v>-0.19511627486718716</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="137">
+      <c r="A47" s="136">
         <v>22</v>
       </c>
-      <c r="B47" s="137">
+      <c r="B47" s="136">
         <v>22.748524555235971</v>
       </c>
-      <c r="C47" s="137">
+      <c r="C47" s="136">
         <v>0.25147544476402928</v>
       </c>
-      <c r="D47" s="137">
+      <c r="D47" s="136">
         <v>0.41080224621071887</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="137">
+      <c r="A48" s="136">
         <v>23</v>
       </c>
-      <c r="B48" s="137">
+      <c r="B48" s="136">
         <v>24.377607329285187</v>
       </c>
-      <c r="C48" s="137">
+      <c r="C48" s="136">
         <v>0.62239267071481308</v>
       </c>
-      <c r="D48" s="137">
+      <c r="D48" s="136">
         <v>1.0167207672886307</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="138">
+      <c r="A49" s="137">
         <v>24</v>
       </c>
-      <c r="B49" s="138">
+      <c r="B49" s="137">
         <v>26.006690103334407</v>
       </c>
-      <c r="C49" s="138">
+      <c r="C49" s="137">
         <v>1.9933098966655933</v>
       </c>
-      <c r="D49" s="138">
+      <c r="D49" s="137">
         <v>3.2562073156393114</v>
       </c>
     </row>
@@ -15705,7 +15722,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L184"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -15964,7 +15981,7 @@
       <c r="H12" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="112">
+      <c r="I12" s="111">
         <v>0</v>
       </c>
       <c r="J12" t="s">
@@ -15981,7 +15998,7 @@
       <c r="H13" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="158">
+      <c r="I13" s="157">
         <v>0</v>
       </c>
       <c r="J13" t="s">
@@ -15995,7 +16012,7 @@
       <c r="H14" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="158">
+      <c r="I14" s="157">
         <v>0</v>
       </c>
       <c r="J14" t="s">
@@ -16470,13 +16487,13 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="111" t="s">
+      <c r="D46" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="E46" s="111"/>
-      <c r="F46" s="111"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="111" t="s">
+      <c r="E46" s="110"/>
+      <c r="F46" s="110"/>
+      <c r="G46" s="110"/>
+      <c r="H46" s="110" t="s">
         <v>301</v>
       </c>
       <c r="I46" s="2">
@@ -16486,7 +16503,7 @@
       <c r="J46" t="s">
         <v>134</v>
       </c>
-      <c r="K46" s="110" t="s">
+      <c r="K46" s="109" t="s">
         <v>334</v>
       </c>
       <c r="L46" t="s">
@@ -16497,13 +16514,13 @@
       <c r="A47" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="111" t="s">
+      <c r="D47" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111" t="s">
+      <c r="E47" s="110"/>
+      <c r="F47" s="110"/>
+      <c r="G47" s="110"/>
+      <c r="H47" s="110" t="s">
         <v>344</v>
       </c>
       <c r="I47" s="93">
@@ -16520,16 +16537,16 @@
       <c r="A48" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="111" t="s">
+      <c r="D48" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="111"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111" t="s">
+      <c r="E48" s="110"/>
+      <c r="F48" s="110"/>
+      <c r="G48" s="110"/>
+      <c r="H48" s="110" t="s">
         <v>389</v>
       </c>
-      <c r="I48" s="112">
+      <c r="I48" s="111">
         <f>I47+(I95/0.5-I47)/(I90*30.4)*I29</f>
         <v>130.26609162869005</v>
       </c>
@@ -16544,16 +16561,16 @@
       <c r="A49" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="111" t="s">
+      <c r="D49" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="111"/>
-      <c r="F49" s="111"/>
-      <c r="G49" s="111"/>
-      <c r="H49" s="111" t="s">
+      <c r="E49" s="110"/>
+      <c r="F49" s="110"/>
+      <c r="G49" s="110"/>
+      <c r="H49" s="110" t="s">
         <v>330</v>
       </c>
-      <c r="I49" s="112">
+      <c r="I49" s="111">
         <f>I$50</f>
         <v>339.02685500000001</v>
       </c>
@@ -16568,13 +16585,13 @@
       <c r="A50" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="111" t="s">
+      <c r="D50" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="111"/>
-      <c r="F50" s="111"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111" t="s">
+      <c r="E50" s="110"/>
+      <c r="F50" s="110"/>
+      <c r="G50" s="110"/>
+      <c r="H50" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I50" s="2">
@@ -16584,7 +16601,7 @@
       <c r="J50" t="s">
         <v>134</v>
       </c>
-      <c r="K50" s="110" t="s">
+      <c r="K50" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L50" t="s">
@@ -16595,13 +16612,13 @@
       <c r="A51" t="s">
         <v>2</v>
       </c>
-      <c r="D51" s="111" t="s">
+      <c r="D51" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="E51" s="111"/>
-      <c r="F51" s="111"/>
-      <c r="G51" s="111"/>
-      <c r="H51" s="111" t="s">
+      <c r="E51" s="110"/>
+      <c r="F51" s="110"/>
+      <c r="G51" s="110"/>
+      <c r="H51" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I51" s="2">
@@ -16611,7 +16628,7 @@
       <c r="J51" t="s">
         <v>134</v>
       </c>
-      <c r="K51" s="110" t="s">
+      <c r="K51" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L51" t="s">
@@ -16622,13 +16639,13 @@
       <c r="A52" t="s">
         <v>2</v>
       </c>
-      <c r="D52" s="111" t="s">
+      <c r="D52" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="111"/>
-      <c r="F52" s="111"/>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111" t="s">
+      <c r="E52" s="110"/>
+      <c r="F52" s="110"/>
+      <c r="G52" s="110"/>
+      <c r="H52" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I52" s="2">
@@ -16638,7 +16655,7 @@
       <c r="J52" t="s">
         <v>134</v>
       </c>
-      <c r="K52" s="110" t="s">
+      <c r="K52" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L52" t="s">
@@ -16649,13 +16666,13 @@
       <c r="A53" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="111" t="s">
+      <c r="D53" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="E53" s="111"/>
-      <c r="F53" s="111"/>
-      <c r="G53" s="111"/>
-      <c r="H53" s="111" t="s">
+      <c r="E53" s="110"/>
+      <c r="F53" s="110"/>
+      <c r="G53" s="110"/>
+      <c r="H53" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I53" s="2">
@@ -16665,7 +16682,7 @@
       <c r="J53" t="s">
         <v>134</v>
       </c>
-      <c r="K53" s="110" t="s">
+      <c r="K53" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L53" t="s">
@@ -16694,13 +16711,13 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="111" t="s">
+      <c r="D55" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="111"/>
-      <c r="F55" s="111"/>
-      <c r="G55" s="111"/>
-      <c r="H55" s="111" t="s">
+      <c r="E55" s="110"/>
+      <c r="F55" s="110"/>
+      <c r="G55" s="110"/>
+      <c r="H55" s="110" t="s">
         <v>301</v>
       </c>
       <c r="I55" s="2">
@@ -16710,7 +16727,7 @@
       <c r="J55" t="s">
         <v>134</v>
       </c>
-      <c r="K55" s="110" t="s">
+      <c r="K55" s="109" t="s">
         <v>334</v>
       </c>
       <c r="L55" t="s">
@@ -16721,13 +16738,13 @@
       <c r="A56" t="s">
         <v>39</v>
       </c>
-      <c r="D56" s="111" t="s">
+      <c r="D56" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E56" s="111"/>
-      <c r="F56" s="111"/>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111" t="s">
+      <c r="E56" s="110"/>
+      <c r="F56" s="110"/>
+      <c r="G56" s="110"/>
+      <c r="H56" s="110" t="s">
         <v>344</v>
       </c>
       <c r="I56" s="93">
@@ -16744,16 +16761,16 @@
       <c r="A57" t="s">
         <v>39</v>
       </c>
-      <c r="D57" s="111" t="s">
+      <c r="D57" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E57" s="111"/>
-      <c r="F57" s="111"/>
-      <c r="G57" s="111"/>
-      <c r="H57" s="111" t="s">
+      <c r="E57" s="110"/>
+      <c r="F57" s="110"/>
+      <c r="G57" s="110"/>
+      <c r="H57" s="110" t="s">
         <v>389</v>
       </c>
-      <c r="I57" s="112">
+      <c r="I57" s="111">
         <f>I56+(I115/0.5-I56)/(I110*30.4)*I40</f>
         <v>215.80423925763492</v>
       </c>
@@ -16768,16 +16785,16 @@
       <c r="A58" t="s">
         <v>39</v>
       </c>
-      <c r="D58" s="111" t="s">
+      <c r="D58" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E58" s="111"/>
-      <c r="F58" s="111"/>
-      <c r="G58" s="111"/>
-      <c r="H58" s="111" t="s">
+      <c r="E58" s="110"/>
+      <c r="F58" s="110"/>
+      <c r="G58" s="110"/>
+      <c r="H58" s="110" t="s">
         <v>330</v>
       </c>
-      <c r="I58" s="112">
+      <c r="I58" s="111">
         <f>I$59</f>
         <v>314.63230679999998</v>
       </c>
@@ -16792,13 +16809,13 @@
       <c r="A59" t="s">
         <v>39</v>
       </c>
-      <c r="D59" s="111" t="s">
+      <c r="D59" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="111"/>
-      <c r="F59" s="111"/>
-      <c r="G59" s="111"/>
-      <c r="H59" s="111" t="s">
+      <c r="E59" s="110"/>
+      <c r="F59" s="110"/>
+      <c r="G59" s="110"/>
+      <c r="H59" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I59" s="2">
@@ -16808,7 +16825,7 @@
       <c r="J59" t="s">
         <v>134</v>
       </c>
-      <c r="K59" s="110" t="s">
+      <c r="K59" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L59" t="s">
@@ -16819,13 +16836,13 @@
       <c r="A60" t="s">
         <v>39</v>
       </c>
-      <c r="D60" s="111" t="s">
+      <c r="D60" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111" t="s">
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I60" s="2">
@@ -16835,7 +16852,7 @@
       <c r="J60" t="s">
         <v>134</v>
       </c>
-      <c r="K60" s="110" t="s">
+      <c r="K60" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L60" t="s">
@@ -16846,13 +16863,13 @@
       <c r="A61" t="s">
         <v>39</v>
       </c>
-      <c r="D61" s="111" t="s">
+      <c r="D61" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="E61" s="111"/>
-      <c r="F61" s="111"/>
-      <c r="G61" s="111"/>
-      <c r="H61" s="111" t="s">
+      <c r="E61" s="110"/>
+      <c r="F61" s="110"/>
+      <c r="G61" s="110"/>
+      <c r="H61" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I61" s="2">
@@ -16862,7 +16879,7 @@
       <c r="J61" t="s">
         <v>134</v>
       </c>
-      <c r="K61" s="110" t="s">
+      <c r="K61" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L61" t="s">
@@ -16873,13 +16890,13 @@
       <c r="A62" t="s">
         <v>39</v>
       </c>
-      <c r="D62" s="111" t="s">
+      <c r="D62" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="E62" s="111"/>
-      <c r="F62" s="111"/>
-      <c r="G62" s="111"/>
-      <c r="H62" s="111" t="s">
+      <c r="E62" s="110"/>
+      <c r="F62" s="110"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="110" t="s">
         <v>297</v>
       </c>
       <c r="I62" s="2">
@@ -16889,7 +16906,7 @@
       <c r="J62" t="s">
         <v>134</v>
       </c>
-      <c r="K62" s="110" t="s">
+      <c r="K62" s="109" t="s">
         <v>332</v>
       </c>
       <c r="L62" t="s">
@@ -17539,7 +17556,7 @@
       <c r="H99" t="s">
         <v>36</v>
       </c>
-      <c r="I99" s="159">
+      <c r="I99" s="158">
         <v>0</v>
       </c>
       <c r="J99" s="93" t="s">
@@ -17926,7 +17943,7 @@
       <c r="H119" t="s">
         <v>36</v>
       </c>
-      <c r="I119" s="159">
+      <c r="I119" s="158">
         <v>0</v>
       </c>
       <c r="J119" s="93" t="s">
@@ -18877,163 +18894,398 @@
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H176" s="93" t="s">
+      <c r="H176" s="160" t="s">
         <v>327</v>
       </c>
-      <c r="I176" s="93">
+      <c r="I176" s="160">
         <v>0</v>
       </c>
-      <c r="J176" s="93" t="s">
+      <c r="J176" s="160" t="s">
         <v>328</v>
       </c>
-      <c r="K176" s="93" t="s">
+      <c r="K176" s="160" t="s">
         <v>430</v>
       </c>
     </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H177" s="93"/>
+      <c r="I177" s="93"/>
+      <c r="J177" s="93"/>
+      <c r="K177" s="93"/>
+    </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="102" t="s">
+      <c r="A178" s="94" t="s">
+        <v>432</v>
+      </c>
+      <c r="B178" s="94"/>
+      <c r="C178" s="94"/>
+      <c r="D178" s="95"/>
+      <c r="E178" s="95"/>
+      <c r="F178" s="95"/>
+      <c r="G178" s="95"/>
+      <c r="H178" s="95"/>
+      <c r="I178" s="95"/>
+      <c r="J178" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="K178" s="95" t="s">
+        <v>434</v>
+      </c>
+      <c r="L178" s="95"/>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" s="97" t="s">
+        <v>304</v>
+      </c>
+      <c r="B179" s="97"/>
+      <c r="C179" s="97"/>
+      <c r="D179" s="98"/>
+      <c r="E179" s="98"/>
+      <c r="F179" s="98"/>
+      <c r="G179" s="98"/>
+      <c r="H179" s="98"/>
+      <c r="I179" s="99"/>
+      <c r="J179" s="98"/>
+      <c r="K179" s="98"/>
+      <c r="L179" s="98"/>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>2</v>
+      </c>
+      <c r="D180" t="s">
+        <v>18</v>
+      </c>
+      <c r="H180" t="s">
+        <v>433</v>
+      </c>
+      <c r="J180" s="93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>2</v>
+      </c>
+      <c r="D181" t="s">
+        <v>20</v>
+      </c>
+      <c r="H181" t="s">
+        <v>433</v>
+      </c>
+      <c r="J181" s="93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>2</v>
+      </c>
+      <c r="D182" t="s">
+        <v>35</v>
+      </c>
+      <c r="H182" t="s">
+        <v>433</v>
+      </c>
+      <c r="J182" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>2</v>
+      </c>
+      <c r="D183" t="s">
+        <v>33</v>
+      </c>
+      <c r="H183" t="s">
+        <v>433</v>
+      </c>
+      <c r="J183" s="93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>2</v>
+      </c>
+      <c r="D184" t="s">
+        <v>34</v>
+      </c>
+      <c r="H184" t="s">
+        <v>433</v>
+      </c>
+      <c r="J184" s="93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>2</v>
+      </c>
+      <c r="D185" t="s">
+        <v>431</v>
+      </c>
+      <c r="H185" t="s">
+        <v>433</v>
+      </c>
+      <c r="J185" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" s="100" t="s">
+        <v>305</v>
+      </c>
+      <c r="B187" s="100"/>
+      <c r="C187" s="100"/>
+      <c r="D187" s="101"/>
+      <c r="E187" s="101"/>
+      <c r="F187" s="101"/>
+      <c r="G187" s="101"/>
+      <c r="H187" s="101"/>
+      <c r="I187" s="101"/>
+      <c r="J187" s="101"/>
+      <c r="K187" s="101"/>
+      <c r="L187" s="101"/>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>39</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="H188" t="s">
+        <v>433</v>
+      </c>
+      <c r="J188" s="93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>39</v>
+      </c>
+      <c r="D189" t="s">
+        <v>20</v>
+      </c>
+      <c r="H189" t="s">
+        <v>433</v>
+      </c>
+      <c r="J189" s="93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>39</v>
+      </c>
+      <c r="D190" t="s">
+        <v>35</v>
+      </c>
+      <c r="H190" t="s">
+        <v>433</v>
+      </c>
+      <c r="J190" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>39</v>
+      </c>
+      <c r="D191" t="s">
+        <v>33</v>
+      </c>
+      <c r="H191" t="s">
+        <v>433</v>
+      </c>
+      <c r="J191" s="93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>39</v>
+      </c>
+      <c r="D192" t="s">
+        <v>34</v>
+      </c>
+      <c r="H192" t="s">
+        <v>433</v>
+      </c>
+      <c r="J192" s="93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>39</v>
+      </c>
+      <c r="D193" t="s">
+        <v>431</v>
+      </c>
+      <c r="H193" t="s">
+        <v>433</v>
+      </c>
+      <c r="J193" s="93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" s="159" t="s">
         <v>306</v>
       </c>
-      <c r="B178" s="102"/>
-      <c r="C178" s="102"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="93" t="s">
+      <c r="B195" s="159"/>
+      <c r="C195" s="159"/>
+      <c r="D195" s="95"/>
+      <c r="E195" s="95"/>
+      <c r="F195" s="95"/>
+      <c r="G195" s="95"/>
+      <c r="H195" s="95"/>
+      <c r="I195" s="95"/>
+      <c r="J195" s="95"/>
+      <c r="K195" s="95"/>
+      <c r="L195" s="95"/>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="D179" s="93" t="s">
+      <c r="D196" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="E179" s="93"/>
-      <c r="F179" s="93"/>
-      <c r="G179" s="93"/>
-      <c r="H179" s="93" t="s">
+      <c r="E196" s="93"/>
+      <c r="F196" s="93"/>
+      <c r="G196" s="93"/>
+      <c r="H196" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I179" s="93">
+      <c r="I196" s="93">
         <v>7.1</v>
       </c>
-      <c r="J179" s="93" t="s">
+      <c r="J196" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K179" s="93"/>
-      <c r="L179" s="93" t="s">
+      <c r="K196" s="93"/>
+      <c r="L196" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="93" t="s">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="D180" s="93" t="s">
+      <c r="D197" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="E180" s="93"/>
-      <c r="F180" s="93"/>
-      <c r="G180" s="93"/>
-      <c r="H180" s="93" t="s">
+      <c r="E197" s="93"/>
+      <c r="F197" s="93"/>
+      <c r="G197" s="93"/>
+      <c r="H197" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I180" s="93">
+      <c r="I197" s="93">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J180" s="93" t="s">
+      <c r="J197" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K180" s="93"/>
-      <c r="L180" s="93" t="s">
+      <c r="K197" s="93"/>
+      <c r="L197" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="93"/>
-      <c r="D181" s="93" t="s">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" s="93"/>
+      <c r="D198" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="E181" s="93"/>
-      <c r="F181" s="93"/>
-      <c r="G181" s="93"/>
-      <c r="H181" s="93" t="s">
+      <c r="E198" s="93"/>
+      <c r="F198" s="93"/>
+      <c r="G198" s="93"/>
+      <c r="H198" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I181" s="93">
+      <c r="I198" s="93">
         <v>5.7</v>
       </c>
-      <c r="J181" s="93" t="s">
+      <c r="J198" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K181" s="93"/>
-      <c r="L181" s="93" t="s">
+      <c r="K198" s="93"/>
+      <c r="L198" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="93"/>
-      <c r="D182" s="93" t="s">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" s="93"/>
+      <c r="D199" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="E182" s="93"/>
-      <c r="F182" s="93"/>
-      <c r="G182" s="93"/>
-      <c r="H182" s="93" t="s">
+      <c r="E199" s="93"/>
+      <c r="F199" s="93"/>
+      <c r="G199" s="93"/>
+      <c r="H199" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I182" s="93">
+      <c r="I199" s="93">
         <v>7.7</v>
       </c>
-      <c r="J182" s="93" t="s">
+      <c r="J199" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K182" s="93"/>
-      <c r="L182" s="93" t="s">
+      <c r="K199" s="93"/>
+      <c r="L199" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" s="93"/>
-      <c r="D183" s="93" t="s">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" s="93"/>
+      <c r="D200" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="E183" s="93"/>
-      <c r="F183" s="93"/>
-      <c r="G183" s="93"/>
-      <c r="H183" s="93" t="s">
+      <c r="E200" s="93"/>
+      <c r="F200" s="93"/>
+      <c r="G200" s="93"/>
+      <c r="H200" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I183" s="93">
+      <c r="I200" s="93">
         <v>9.1</v>
       </c>
-      <c r="J183" s="93" t="s">
+      <c r="J200" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K183" s="93" t="s">
+      <c r="K200" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="L183" s="93" t="s">
+      <c r="L200" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" s="93"/>
-      <c r="D184" s="93" t="s">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" s="93"/>
+      <c r="D201" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="E184" s="93"/>
-      <c r="F184" s="93"/>
-      <c r="G184" s="93"/>
-      <c r="H184" s="93" t="s">
+      <c r="E201" s="93"/>
+      <c r="F201" s="93"/>
+      <c r="G201" s="93"/>
+      <c r="H201" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I184" s="93">
+      <c r="I201" s="93">
         <v>9.1</v>
       </c>
-      <c r="J184" s="93" t="s">
+      <c r="J201" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K184" s="93" t="s">
+      <c r="K201" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="L184" s="93" t="s">
+      <c r="L201" s="93" t="s">
         <v>42</v>
       </c>
     </row>
@@ -21625,7 +21877,7 @@
       <c r="J40" s="15"/>
       <c r="K40" s="21"/>
       <c r="L40" s="22"/>
-      <c r="M40" s="104" t="s">
+      <c r="M40" s="103" t="s">
         <v>318</v>
       </c>
       <c r="N40" s="15"/>
@@ -21637,7 +21889,7 @@
       <c r="T40" s="15"/>
       <c r="U40" s="15"/>
       <c r="V40" s="15"/>
-      <c r="W40" s="107"/>
+      <c r="W40" s="106"/>
       <c r="X40" s="26"/>
       <c r="AA40" s="15"/>
       <c r="AB40" s="21"/>
@@ -21648,7 +21900,7 @@
       <c r="AG40" s="15"/>
       <c r="AH40" s="15"/>
       <c r="AI40" s="15"/>
-      <c r="AJ40" s="104" t="s">
+      <c r="AJ40" s="103" t="s">
         <v>318</v>
       </c>
       <c r="AK40" s="15"/>
@@ -21660,7 +21912,7 @@
       <c r="AQ40" s="15"/>
       <c r="AR40" s="15"/>
       <c r="AS40" s="15"/>
-      <c r="AT40" s="107"/>
+      <c r="AT40" s="106"/>
     </row>
     <row r="41" spans="2:46" x14ac:dyDescent="0.25">
       <c r="D41" s="12"/>
@@ -21668,7 +21920,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="21"/>
       <c r="L41" s="22"/>
-      <c r="M41" s="105" t="s">
+      <c r="M41" s="104" t="s">
         <v>319</v>
       </c>
       <c r="N41" s="15"/>
@@ -21677,7 +21929,7 @@
         <v>89</v>
       </c>
       <c r="Q41" s="15"/>
-      <c r="R41" s="109" t="s">
+      <c r="R41" s="108" t="s">
         <v>9</v>
       </c>
       <c r="S41" s="15"/>
@@ -21686,7 +21938,7 @@
       </c>
       <c r="U41" s="15"/>
       <c r="V41" s="15"/>
-      <c r="W41" s="107"/>
+      <c r="W41" s="106"/>
       <c r="X41" s="26"/>
       <c r="AA41" s="15"/>
       <c r="AB41" s="21"/>
@@ -21697,7 +21949,7 @@
       <c r="AG41" s="15"/>
       <c r="AH41" s="15"/>
       <c r="AI41" s="15"/>
-      <c r="AJ41" s="105" t="s">
+      <c r="AJ41" s="104" t="s">
         <v>319</v>
       </c>
       <c r="AK41" s="15"/>
@@ -21706,14 +21958,14 @@
         <v>14</v>
       </c>
       <c r="AN41" s="15"/>
-      <c r="AO41" s="109" t="s">
+      <c r="AO41" s="108" t="s">
         <v>9</v>
       </c>
       <c r="AP41" s="15"/>
       <c r="AQ41" s="15"/>
       <c r="AR41" s="15"/>
       <c r="AS41" s="15"/>
-      <c r="AT41" s="107"/>
+      <c r="AT41" s="106"/>
     </row>
     <row r="42" spans="2:46" x14ac:dyDescent="0.25">
       <c r="D42" s="12"/>
@@ -21721,7 +21973,7 @@
       <c r="J42" s="15"/>
       <c r="K42" s="21"/>
       <c r="L42" s="22"/>
-      <c r="M42" s="106" t="s">
+      <c r="M42" s="105" t="s">
         <v>320</v>
       </c>
       <c r="N42" s="47"/>
@@ -21739,7 +21991,7 @@
       </c>
       <c r="U42" s="47"/>
       <c r="V42" s="47"/>
-      <c r="W42" s="108"/>
+      <c r="W42" s="107"/>
       <c r="X42" s="26"/>
       <c r="AA42" s="15"/>
       <c r="AB42" s="21"/>
@@ -21750,7 +22002,7 @@
       <c r="AG42" s="15"/>
       <c r="AH42" s="15"/>
       <c r="AI42" s="15"/>
-      <c r="AJ42" s="106" t="s">
+      <c r="AJ42" s="105" t="s">
         <v>320</v>
       </c>
       <c r="AK42" s="47"/>
@@ -21766,7 +22018,7 @@
       <c r="AQ42" s="47"/>
       <c r="AR42" s="47"/>
       <c r="AS42" s="47"/>
-      <c r="AT42" s="108"/>
+      <c r="AT42" s="107"/>
     </row>
     <row r="43" spans="2:46" x14ac:dyDescent="0.25">
       <c r="D43" s="12"/>
@@ -21862,7 +22114,7 @@
         <f>SUM(D5:E5)</f>
         <v>316238</v>
       </c>
-      <c r="E46" s="103">
+      <c r="E46" s="102">
         <f>E5</f>
         <v>55025.411999999997</v>
       </c>
@@ -21908,7 +22160,7 @@
         <f>SUM(AA5:AB5)</f>
         <v>206514</v>
       </c>
-      <c r="E47" s="103">
+      <c r="E47" s="102">
         <f>AB5</f>
         <v>72692.928000000014</v>
       </c>
@@ -21954,7 +22206,7 @@
         <f>SUM(D9:E9,AA9:AB9)</f>
         <v>462203.76921728684</v>
       </c>
-      <c r="E48" s="103">
+      <c r="E48" s="102">
         <f>SUM(E9,AB9)</f>
         <v>85658.04919782767</v>
       </c>
@@ -22002,7 +22254,7 @@
         <f>SUM(D6:E8,AA6:AB8)</f>
         <v>491678.55122292211</v>
       </c>
-      <c r="E49" s="103">
+      <c r="E49" s="102">
         <f>SUM(E6:E8,AB6:AB8)</f>
         <v>97115.906082827161</v>
       </c>
@@ -22096,7 +22348,7 @@
         <f>SUM(F5:G5,AC5:AD5)</f>
         <v>143608.72911893675</v>
       </c>
-      <c r="E50" s="103">
+      <c r="E50" s="102">
         <f>SUM(G5,AD5)</f>
         <v>33025.146960105732</v>
       </c>
@@ -22215,7 +22467,7 @@
         <f>SUM(F6:G6,AC6:AD6)</f>
         <v>56446.350672823188</v>
       </c>
-      <c r="E51" s="103">
+      <c r="E51" s="102">
         <f>SUM(G6,AD6)</f>
         <v>13122.812032834503</v>
       </c>
@@ -22334,7 +22586,7 @@
         <f>SUM(F7:G7,AC7:AD7)</f>
         <v>35750.513487991702</v>
       </c>
-      <c r="E52" s="103">
+      <c r="E52" s="102">
         <f>SUM(G7,AD7)</f>
         <v>11903.310295425101</v>
       </c>
@@ -22385,7 +22637,7 @@
         <f>SUM(F8:G8,AC8:AD8)</f>
         <v>183108.40482051656</v>
       </c>
-      <c r="E53" s="103">
+      <c r="E53" s="102">
         <f>SUM(G8,AD8)</f>
         <v>19474.403024226824</v>
       </c>
@@ -25121,7 +25373,7 @@
       </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B105" s="156" t="s">
+      <c r="B105" s="155" t="s">
         <v>400</v>
       </c>
       <c r="C105" s="2">
@@ -25162,18 +25414,18 @@
       </c>
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D106" s="156" t="s">
+      <c r="D106" s="155" t="s">
         <v>405</v>
       </c>
-      <c r="E106" s="157">
+      <c r="E106" s="156">
         <f>1/E105</f>
         <v>4.9969493593654671E-2</v>
       </c>
-      <c r="H106" s="157">
+      <c r="H106" s="156">
         <f>1/H105</f>
         <v>3.1568577532293592E-2</v>
       </c>
-      <c r="K106" s="157">
+      <c r="K106" s="156">
         <f>1/K105</f>
         <v>5.9876519298329253E-2</v>
       </c>
@@ -47026,16 +47278,16 @@
         <f>SUM(G4:I4)</f>
         <v>28</v>
       </c>
-      <c r="R4" s="141" t="s">
+      <c r="R4" s="140" t="s">
         <v>353</v>
       </c>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119"/>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
       <c r="AB4" t="s">
         <v>349</v>
       </c>
@@ -47082,29 +47334,29 @@
         <f t="shared" ref="N5:N7" si="0">SUM(G5:I5)</f>
         <v>37</v>
       </c>
-      <c r="R5" s="120" t="s">
+      <c r="R5" s="119" t="s">
         <v>355</v>
       </c>
-      <c r="S5" s="120" t="s">
+      <c r="S5" s="119" t="s">
         <v>354</v>
       </c>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="119"/>
-      <c r="W5" s="119"/>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="AB5" s="134">
+      <c r="T5" s="118"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="118"/>
+      <c r="X5" s="118"/>
+      <c r="Y5" s="118"/>
+      <c r="AB5" s="133">
         <v>30</v>
       </c>
-      <c r="AC5" s="134">
+      <c r="AC5" s="133">
         <f t="shared" ref="AC5:AC28" si="1">AB5^0.75</f>
         <v>12.818610191887021</v>
       </c>
-      <c r="AD5" s="134">
+      <c r="AD5" s="133">
         <v>0</v>
       </c>
-      <c r="AE5" s="126">
+      <c r="AE5" s="125">
         <v>6</v>
       </c>
     </row>
@@ -47141,35 +47393,35 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="R6" s="121" t="s">
+      <c r="R6" s="120" t="s">
         <v>134</v>
       </c>
-      <c r="S6" s="122">
+      <c r="S6" s="121">
         <v>0</v>
       </c>
-      <c r="T6" s="123">
+      <c r="T6" s="122">
         <v>250</v>
       </c>
-      <c r="U6" s="123">
+      <c r="U6" s="122">
         <v>500</v>
       </c>
-      <c r="V6" s="124">
+      <c r="V6" s="123">
         <v>1000</v>
       </c>
-      <c r="W6" s="116"/>
-      <c r="X6" s="116"/>
-      <c r="Y6" s="116"/>
-      <c r="AB6" s="135">
+      <c r="W6" s="115"/>
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="AB6" s="134">
         <v>40</v>
       </c>
-      <c r="AC6" s="135">
+      <c r="AC6" s="134">
         <f t="shared" si="1"/>
         <v>15.905414575341014</v>
       </c>
-      <c r="AD6" s="135">
+      <c r="AD6" s="134">
         <v>0</v>
       </c>
-      <c r="AE6" s="129">
+      <c r="AE6" s="128">
         <v>7</v>
       </c>
     </row>
@@ -47206,754 +47458,754 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="R7" s="115">
+      <c r="R7" s="114">
         <v>30</v>
       </c>
-      <c r="S7" s="125">
+      <c r="S7" s="124">
         <v>6</v>
       </c>
-      <c r="T7" s="126">
+      <c r="T7" s="125">
         <v>8</v>
       </c>
-      <c r="U7" s="126">
+      <c r="U7" s="125">
         <v>11</v>
       </c>
-      <c r="V7" s="127">
+      <c r="V7" s="126">
         <v>17.5</v>
       </c>
-      <c r="W7" s="114"/>
-      <c r="X7" s="155" t="s">
+      <c r="W7" s="113"/>
+      <c r="X7" s="154" t="s">
         <v>390</v>
       </c>
-      <c r="Y7" s="114"/>
-      <c r="AB7" s="135">
+      <c r="Y7" s="113"/>
+      <c r="AB7" s="134">
         <v>50</v>
       </c>
-      <c r="AC7" s="135">
+      <c r="AC7" s="134">
         <f t="shared" si="1"/>
         <v>18.803015465431965</v>
       </c>
-      <c r="AD7" s="135">
+      <c r="AD7" s="134">
         <v>0</v>
       </c>
-      <c r="AE7" s="129">
+      <c r="AE7" s="128">
         <v>8.5</v>
       </c>
     </row>
     <row r="8" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="R8" s="117">
+      <c r="R8" s="116">
         <v>40</v>
       </c>
-      <c r="S8" s="128">
+      <c r="S8" s="127">
         <v>7</v>
       </c>
-      <c r="T8" s="129">
+      <c r="T8" s="128">
         <v>9.5</v>
       </c>
-      <c r="U8" s="129">
+      <c r="U8" s="128">
         <v>12.5</v>
       </c>
-      <c r="V8" s="130">
+      <c r="V8" s="129">
         <v>19</v>
       </c>
-      <c r="W8" s="114"/>
+      <c r="W8" s="113"/>
       <c r="X8" t="s">
         <v>387</v>
       </c>
       <c r="Y8">
         <v>0</v>
       </c>
-      <c r="AB8" s="135">
+      <c r="AB8" s="134">
         <v>60</v>
       </c>
-      <c r="AC8" s="135">
+      <c r="AC8" s="134">
         <f t="shared" si="1"/>
         <v>21.558246717785043</v>
       </c>
-      <c r="AD8" s="135">
+      <c r="AD8" s="134">
         <v>0</v>
       </c>
-      <c r="AE8" s="129">
+      <c r="AE8" s="128">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="R9" s="117">
+      <c r="R9" s="116">
         <v>50</v>
       </c>
-      <c r="S9" s="128">
+      <c r="S9" s="127">
         <v>8.5</v>
       </c>
-      <c r="T9" s="129">
+      <c r="T9" s="128">
         <v>11</v>
       </c>
-      <c r="U9" s="129">
+      <c r="U9" s="128">
         <v>14</v>
       </c>
-      <c r="V9" s="130">
+      <c r="V9" s="129">
         <v>21</v>
       </c>
-      <c r="W9" s="114"/>
+      <c r="W9" s="113"/>
       <c r="X9" t="s">
         <v>349</v>
       </c>
-      <c r="Y9" s="137">
+      <c r="Y9" s="136">
         <v>0.16</v>
       </c>
-      <c r="AB9" s="135">
+      <c r="AB9" s="134">
         <v>70</v>
       </c>
-      <c r="AC9" s="135">
+      <c r="AC9" s="134">
         <f t="shared" si="1"/>
         <v>24.200454924935883</v>
       </c>
-      <c r="AD9" s="135">
+      <c r="AD9" s="134">
         <v>0</v>
       </c>
-      <c r="AE9" s="129">
+      <c r="AE9" s="128">
         <v>11.5</v>
       </c>
     </row>
     <row r="10" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="R10" s="117">
+      <c r="R10" s="116">
         <v>60</v>
       </c>
-      <c r="S10" s="128">
+      <c r="S10" s="127">
         <v>10</v>
       </c>
-      <c r="T10" s="129">
+      <c r="T10" s="128">
         <v>12.5</v>
       </c>
-      <c r="U10" s="129">
+      <c r="U10" s="128">
         <v>15.5</v>
       </c>
-      <c r="V10" s="130">
+      <c r="V10" s="129">
         <v>23</v>
       </c>
-      <c r="W10" s="114"/>
+      <c r="W10" s="113"/>
       <c r="X10" t="s">
         <v>356</v>
       </c>
       <c r="Y10">
         <v>12.5</v>
       </c>
-      <c r="AB10" s="136">
+      <c r="AB10" s="135">
         <v>80</v>
       </c>
-      <c r="AC10" s="136">
+      <c r="AC10" s="135">
         <f t="shared" si="1"/>
         <v>26.749612199056873</v>
       </c>
-      <c r="AD10" s="136">
+      <c r="AD10" s="135">
         <v>0</v>
       </c>
-      <c r="AE10" s="132">
+      <c r="AE10" s="131">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="R11" s="117">
+      <c r="R11" s="116">
         <v>70</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="127">
         <v>11.5</v>
       </c>
-      <c r="T11" s="129">
+      <c r="T11" s="128">
         <v>14</v>
       </c>
-      <c r="U11" s="129">
+      <c r="U11" s="128">
         <v>17.5</v>
       </c>
-      <c r="V11" s="130">
+      <c r="V11" s="129">
         <v>25</v>
       </c>
-      <c r="W11" s="116"/>
-      <c r="X11" s="116"/>
-      <c r="Y11" s="116"/>
-      <c r="AB11" s="134">
+      <c r="W11" s="115"/>
+      <c r="X11" s="115"/>
+      <c r="Y11" s="115"/>
+      <c r="AB11" s="133">
         <v>30</v>
       </c>
-      <c r="AC11" s="134">
+      <c r="AC11" s="133">
         <f t="shared" si="1"/>
         <v>12.818610191887021</v>
       </c>
-      <c r="AD11" s="134">
+      <c r="AD11" s="133">
         <v>250</v>
       </c>
-      <c r="AE11" s="126">
+      <c r="AE11" s="125">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="R12" s="118">
+      <c r="R12" s="117">
         <v>80</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="130">
         <v>13</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="131">
         <v>16</v>
       </c>
-      <c r="U12" s="132">
+      <c r="U12" s="131">
         <v>19.5</v>
       </c>
-      <c r="V12" s="133">
+      <c r="V12" s="132">
         <v>28</v>
       </c>
-      <c r="AB12" s="135">
+      <c r="AB12" s="134">
         <v>40</v>
       </c>
-      <c r="AC12" s="135">
+      <c r="AC12" s="134">
         <f t="shared" si="1"/>
         <v>15.905414575341014</v>
       </c>
-      <c r="AD12" s="135">
+      <c r="AD12" s="134">
         <v>250</v>
       </c>
-      <c r="AE12" s="129">
+      <c r="AE12" s="128">
         <v>9.5</v>
       </c>
     </row>
     <row r="13" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="AB13" s="135">
+      <c r="AB13" s="134">
         <v>50</v>
       </c>
-      <c r="AC13" s="135">
+      <c r="AC13" s="134">
         <f t="shared" si="1"/>
         <v>18.803015465431965</v>
       </c>
-      <c r="AD13" s="135">
+      <c r="AD13" s="134">
         <v>250</v>
       </c>
-      <c r="AE13" s="129">
+      <c r="AE13" s="128">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="6:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="R14" s="141" t="s">
+      <c r="R14" s="140" t="s">
         <v>394</v>
       </c>
-      <c r="S14" s="119"/>
-      <c r="T14" s="119"/>
-      <c r="U14" s="119"/>
-      <c r="V14" s="119"/>
-      <c r="AB14" s="135">
+      <c r="S14" s="118"/>
+      <c r="T14" s="118"/>
+      <c r="U14" s="118"/>
+      <c r="V14" s="118"/>
+      <c r="AB14" s="134">
         <v>60</v>
       </c>
-      <c r="AC14" s="135">
+      <c r="AC14" s="134">
         <f t="shared" si="1"/>
         <v>21.558246717785043</v>
       </c>
-      <c r="AD14" s="135">
+      <c r="AD14" s="134">
         <v>250</v>
       </c>
-      <c r="AE14" s="129">
+      <c r="AE14" s="128">
         <v>12.5</v>
       </c>
     </row>
     <row r="15" spans="6:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="R15" s="120" t="s">
+      <c r="R15" s="119" t="s">
         <v>355</v>
       </c>
-      <c r="S15" s="120" t="s">
+      <c r="S15" s="119" t="s">
         <v>388</v>
       </c>
-      <c r="T15" s="119"/>
-      <c r="U15" s="119"/>
-      <c r="V15" s="119"/>
-      <c r="AB15" s="135">
+      <c r="T15" s="118"/>
+      <c r="U15" s="118"/>
+      <c r="V15" s="118"/>
+      <c r="AB15" s="134">
         <v>70</v>
       </c>
-      <c r="AC15" s="135">
+      <c r="AC15" s="134">
         <f t="shared" si="1"/>
         <v>24.200454924935883</v>
       </c>
-      <c r="AD15" s="135">
+      <c r="AD15" s="134">
         <v>250</v>
       </c>
-      <c r="AE15" s="129">
+      <c r="AE15" s="128">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="R16" s="121" t="s">
+      <c r="R16" s="120" t="s">
         <v>134</v>
       </c>
-      <c r="S16" s="152">
+      <c r="S16" s="151">
         <v>0</v>
       </c>
-      <c r="T16" s="153">
+      <c r="T16" s="152">
         <v>0.25</v>
       </c>
-      <c r="U16" s="153">
+      <c r="U16" s="152">
         <v>0.5</v>
       </c>
-      <c r="V16" s="154">
+      <c r="V16" s="153">
         <v>1</v>
       </c>
-      <c r="AB16" s="136">
+      <c r="AB16" s="135">
         <v>80</v>
       </c>
-      <c r="AC16" s="136">
+      <c r="AC16" s="135">
         <f t="shared" si="1"/>
         <v>26.749612199056873</v>
       </c>
-      <c r="AD16" s="136">
+      <c r="AD16" s="135">
         <v>250</v>
       </c>
-      <c r="AE16" s="132">
+      <c r="AE16" s="131">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R17" s="115">
+      <c r="R17" s="114">
         <v>30</v>
       </c>
-      <c r="S17" s="143">
+      <c r="S17" s="142">
         <f t="shared" ref="S17:V22" si="2">($Y$8+$R17*$Y$9+S$16*$Y$10)/S7</f>
         <v>0.79999999999999993</v>
       </c>
-      <c r="T17" s="144">
+      <c r="T17" s="143">
         <f t="shared" si="2"/>
         <v>0.99062499999999998</v>
       </c>
-      <c r="U17" s="144">
+      <c r="U17" s="143">
         <f t="shared" si="2"/>
         <v>1.0045454545454546</v>
       </c>
-      <c r="V17" s="145">
+      <c r="V17" s="144">
         <f t="shared" si="2"/>
         <v>0.98857142857142866</v>
       </c>
-      <c r="AB17" s="134">
+      <c r="AB17" s="133">
         <v>30</v>
       </c>
-      <c r="AC17" s="134">
+      <c r="AC17" s="133">
         <f t="shared" si="1"/>
         <v>12.818610191887021</v>
       </c>
-      <c r="AD17" s="134">
+      <c r="AD17" s="133">
         <v>500</v>
       </c>
-      <c r="AE17" s="126">
+      <c r="AE17" s="125">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R18" s="117">
+      <c r="R18" s="116">
         <v>40</v>
       </c>
-      <c r="S18" s="146">
+      <c r="S18" s="145">
         <f t="shared" si="2"/>
         <v>0.91428571428571437</v>
       </c>
-      <c r="T18" s="147">
+      <c r="T18" s="146">
         <f>($Y$8+$R18*$Y$9+T$16*$Y$10)/T8</f>
         <v>1.0026315789473685</v>
       </c>
-      <c r="U18" s="147">
+      <c r="U18" s="146">
         <f t="shared" si="2"/>
         <v>1.012</v>
       </c>
-      <c r="V18" s="148">
+      <c r="V18" s="147">
         <f t="shared" si="2"/>
         <v>0.99473684210526303</v>
       </c>
-      <c r="AB18" s="135">
+      <c r="AB18" s="134">
         <v>40</v>
       </c>
-      <c r="AC18" s="135">
+      <c r="AC18" s="134">
         <f t="shared" si="1"/>
         <v>15.905414575341014</v>
       </c>
-      <c r="AD18" s="135">
+      <c r="AD18" s="134">
         <v>500</v>
       </c>
-      <c r="AE18" s="129">
+      <c r="AE18" s="128">
         <v>12.5</v>
       </c>
     </row>
     <row r="19" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R19" s="117">
+      <c r="R19" s="116">
         <v>50</v>
       </c>
-      <c r="S19" s="146">
+      <c r="S19" s="145">
         <f t="shared" si="2"/>
         <v>0.94117647058823528</v>
       </c>
-      <c r="T19" s="147">
+      <c r="T19" s="146">
         <f t="shared" si="2"/>
         <v>1.0113636363636365</v>
       </c>
-      <c r="U19" s="147">
+      <c r="U19" s="146">
         <f t="shared" si="2"/>
         <v>1.0178571428571428</v>
       </c>
-      <c r="V19" s="148">
+      <c r="V19" s="147">
         <f t="shared" si="2"/>
         <v>0.97619047619047616</v>
       </c>
-      <c r="AB19" s="135">
+      <c r="AB19" s="134">
         <v>50</v>
       </c>
-      <c r="AC19" s="135">
+      <c r="AC19" s="134">
         <f t="shared" si="1"/>
         <v>18.803015465431965</v>
       </c>
-      <c r="AD19" s="135">
+      <c r="AD19" s="134">
         <v>500</v>
       </c>
-      <c r="AE19" s="129">
+      <c r="AE19" s="128">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R20" s="117">
+      <c r="R20" s="116">
         <v>60</v>
       </c>
-      <c r="S20" s="146">
+      <c r="S20" s="145">
         <f t="shared" si="2"/>
         <v>0.96</v>
       </c>
-      <c r="T20" s="147">
+      <c r="T20" s="146">
         <f t="shared" si="2"/>
         <v>1.018</v>
       </c>
-      <c r="U20" s="147">
+      <c r="U20" s="146">
         <f t="shared" si="2"/>
         <v>1.0225806451612902</v>
       </c>
-      <c r="V20" s="148">
+      <c r="V20" s="147">
         <f t="shared" si="2"/>
         <v>0.96086956521739142</v>
       </c>
-      <c r="AB20" s="135">
+      <c r="AB20" s="134">
         <v>60</v>
       </c>
-      <c r="AC20" s="135">
+      <c r="AC20" s="134">
         <f t="shared" si="1"/>
         <v>21.558246717785043</v>
       </c>
-      <c r="AD20" s="135">
+      <c r="AD20" s="134">
         <v>500</v>
       </c>
-      <c r="AE20" s="129">
+      <c r="AE20" s="128">
         <v>15.5</v>
       </c>
     </row>
     <row r="21" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R21" s="117">
+      <c r="R21" s="116">
         <v>70</v>
       </c>
-      <c r="S21" s="146">
+      <c r="S21" s="145">
         <f t="shared" si="2"/>
         <v>0.97391304347826091</v>
       </c>
-      <c r="T21" s="147">
+      <c r="T21" s="146">
         <f t="shared" si="2"/>
         <v>1.0232142857142859</v>
       </c>
-      <c r="U21" s="147">
+      <c r="U21" s="146">
         <f t="shared" si="2"/>
         <v>0.99714285714285733</v>
       </c>
-      <c r="V21" s="148">
+      <c r="V21" s="147">
         <f t="shared" si="2"/>
         <v>0.94800000000000006</v>
       </c>
-      <c r="AB21" s="135">
+      <c r="AB21" s="134">
         <v>70</v>
       </c>
-      <c r="AC21" s="135">
+      <c r="AC21" s="134">
         <f t="shared" si="1"/>
         <v>24.200454924935883</v>
       </c>
-      <c r="AD21" s="135">
+      <c r="AD21" s="134">
         <v>500</v>
       </c>
-      <c r="AE21" s="129">
+      <c r="AE21" s="128">
         <v>17.5</v>
       </c>
     </row>
     <row r="22" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R22" s="118">
+      <c r="R22" s="117">
         <v>80</v>
       </c>
-      <c r="S22" s="149">
+      <c r="S22" s="148">
         <f t="shared" si="2"/>
         <v>0.98461538461538467</v>
       </c>
-      <c r="T22" s="150">
+      <c r="T22" s="149">
         <f t="shared" si="2"/>
         <v>0.99531250000000004</v>
       </c>
-      <c r="U22" s="150">
+      <c r="U22" s="149">
         <f t="shared" si="2"/>
         <v>0.97692307692307701</v>
       </c>
-      <c r="V22" s="151">
+      <c r="V22" s="150">
         <f t="shared" si="2"/>
         <v>0.90357142857142858</v>
       </c>
-      <c r="AB22" s="136">
+      <c r="AB22" s="135">
         <v>80</v>
       </c>
-      <c r="AC22" s="136">
+      <c r="AC22" s="135">
         <f t="shared" si="1"/>
         <v>26.749612199056873</v>
       </c>
-      <c r="AD22" s="136">
+      <c r="AD22" s="135">
         <v>500</v>
       </c>
-      <c r="AE22" s="132">
+      <c r="AE22" s="131">
         <v>19.5</v>
       </c>
     </row>
     <row r="23" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="AB23" s="134">
+      <c r="AB23" s="133">
         <v>30</v>
       </c>
-      <c r="AC23" s="134">
+      <c r="AC23" s="133">
         <f t="shared" si="1"/>
         <v>12.818610191887021</v>
       </c>
-      <c r="AD23" s="134">
+      <c r="AD23" s="133">
         <v>1000</v>
       </c>
-      <c r="AE23" s="126">
+      <c r="AE23" s="125">
         <v>17.5</v>
       </c>
     </row>
     <row r="24" spans="18:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="R24" s="141" t="s">
+      <c r="R24" s="140" t="s">
         <v>393</v>
       </c>
-      <c r="S24" s="119"/>
-      <c r="T24" s="119"/>
-      <c r="U24" s="119"/>
-      <c r="V24" s="119"/>
-      <c r="AB24" s="135">
+      <c r="S24" s="118"/>
+      <c r="T24" s="118"/>
+      <c r="U24" s="118"/>
+      <c r="V24" s="118"/>
+      <c r="AB24" s="134">
         <v>40</v>
       </c>
-      <c r="AC24" s="135">
+      <c r="AC24" s="134">
         <f t="shared" si="1"/>
         <v>15.905414575341014</v>
       </c>
-      <c r="AD24" s="135">
+      <c r="AD24" s="134">
         <v>1000</v>
       </c>
-      <c r="AE24" s="129">
+      <c r="AE24" s="128">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="18:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="R25" s="120" t="s">
+      <c r="R25" s="119" t="s">
         <v>355</v>
       </c>
-      <c r="S25" s="120" t="s">
+      <c r="S25" s="119" t="s">
         <v>388</v>
       </c>
-      <c r="T25" s="119"/>
-      <c r="U25" s="119"/>
-      <c r="V25" s="119"/>
-      <c r="AB25" s="135">
+      <c r="T25" s="118"/>
+      <c r="U25" s="118"/>
+      <c r="V25" s="118"/>
+      <c r="AB25" s="134">
         <v>50</v>
       </c>
-      <c r="AC25" s="135">
+      <c r="AC25" s="134">
         <f t="shared" si="1"/>
         <v>18.803015465431965</v>
       </c>
-      <c r="AD25" s="135">
+      <c r="AD25" s="134">
         <v>1000</v>
       </c>
-      <c r="AE25" s="129">
+      <c r="AE25" s="128">
         <v>21</v>
       </c>
     </row>
     <row r="26" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R26" s="121" t="s">
+      <c r="R26" s="120" t="s">
         <v>134</v>
       </c>
-      <c r="S26" s="152">
+      <c r="S26" s="151">
         <v>0</v>
       </c>
-      <c r="T26" s="153">
+      <c r="T26" s="152">
         <v>0.25</v>
       </c>
-      <c r="U26" s="153">
+      <c r="U26" s="152">
         <v>0.5</v>
       </c>
-      <c r="V26" s="154">
+      <c r="V26" s="153">
         <v>1</v>
       </c>
-      <c r="AB26" s="135">
+      <c r="AB26" s="134">
         <v>60</v>
       </c>
-      <c r="AC26" s="135">
+      <c r="AC26" s="134">
         <f t="shared" si="1"/>
         <v>21.558246717785043</v>
       </c>
-      <c r="AD26" s="135">
+      <c r="AD26" s="134">
         <v>1000</v>
       </c>
-      <c r="AE26" s="129">
+      <c r="AE26" s="128">
         <v>23</v>
       </c>
     </row>
     <row r="27" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R27" s="115">
+      <c r="R27" s="114">
         <v>30</v>
       </c>
-      <c r="S27" s="143">
+      <c r="S27" s="142">
         <f>(0.475*$R27^0.75 + S$26*$X$27)/S7</f>
         <v>1.0148066401910558</v>
       </c>
-      <c r="T27" s="144">
+      <c r="T27" s="143">
         <f t="shared" ref="T27:V27" si="3">(0.475*$R27^0.75 + T$26*$X$27)/T7</f>
         <v>1.1361049801432919</v>
       </c>
-      <c r="U27" s="144">
+      <c r="U27" s="143">
         <f t="shared" si="3"/>
         <v>1.0989854401042123</v>
       </c>
-      <c r="V27" s="145">
+      <c r="V27" s="144">
         <f t="shared" si="3"/>
         <v>1.0336479909226477</v>
       </c>
       <c r="X27">
         <v>12</v>
       </c>
-      <c r="AB27" s="135">
+      <c r="AB27" s="134">
         <v>70</v>
       </c>
-      <c r="AC27" s="135">
+      <c r="AC27" s="134">
         <f t="shared" si="1"/>
         <v>24.200454924935883</v>
       </c>
-      <c r="AD27" s="135">
+      <c r="AD27" s="134">
         <v>1000</v>
       </c>
-      <c r="AE27" s="129">
+      <c r="AE27" s="128">
         <v>25</v>
       </c>
     </row>
     <row r="28" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R28" s="117">
+      <c r="R28" s="116">
         <v>40</v>
       </c>
-      <c r="S28" s="146">
+      <c r="S28" s="145">
         <f t="shared" ref="S28:V28" si="4">(0.475*$R28^0.75 + S$26*$X$27)/S8</f>
         <v>1.0792959890409974</v>
       </c>
-      <c r="T28" s="147">
+      <c r="T28" s="146">
         <f t="shared" si="4"/>
         <v>1.1110602024512612</v>
       </c>
-      <c r="U28" s="147">
+      <c r="U28" s="146">
         <f t="shared" si="4"/>
         <v>1.0844057538629586</v>
       </c>
-      <c r="V28" s="148">
+      <c r="V28" s="147">
         <f t="shared" si="4"/>
         <v>1.0292143117519463</v>
       </c>
       <c r="X28">
         <v>0.2</v>
       </c>
-      <c r="AB28" s="136">
+      <c r="AB28" s="135">
         <v>80</v>
       </c>
-      <c r="AC28" s="136">
+      <c r="AC28" s="135">
         <f t="shared" si="1"/>
         <v>26.749612199056873</v>
       </c>
-      <c r="AD28" s="136">
+      <c r="AD28" s="135">
         <v>1000</v>
       </c>
-      <c r="AE28" s="132">
+      <c r="AE28" s="131">
         <v>28</v>
       </c>
     </row>
     <row r="29" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R29" s="117">
+      <c r="R29" s="116">
         <v>50</v>
       </c>
-      <c r="S29" s="146">
+      <c r="S29" s="145">
         <f t="shared" ref="S29:V29" si="5">(0.475*$R29^0.75 + S$26*$X$27)/S9</f>
         <v>1.0507567465976686</v>
       </c>
-      <c r="T29" s="147">
+      <c r="T29" s="146">
         <f t="shared" si="5"/>
         <v>1.0846756678254712</v>
       </c>
-      <c r="U29" s="147">
+      <c r="U29" s="146">
         <f t="shared" si="5"/>
         <v>1.0665308818628703</v>
       </c>
-      <c r="V29" s="148">
+      <c r="V29" s="147">
         <f t="shared" si="5"/>
         <v>0.99673487362286584</v>
       </c>
     </row>
     <row r="30" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R30" s="117">
+      <c r="R30" s="116">
         <v>60</v>
       </c>
-      <c r="S30" s="146">
+      <c r="S30" s="145">
         <f t="shared" ref="S30:V30" si="6">(0.475*$R30^0.75 + S$26*$X$27)/S10</f>
         <v>1.0240167190947895</v>
       </c>
-      <c r="T30" s="147">
+      <c r="T30" s="146">
         <f t="shared" si="6"/>
         <v>1.0592133752758317</v>
       </c>
-      <c r="U30" s="147">
+      <c r="U30" s="146">
         <f t="shared" si="6"/>
         <v>1.0477527219966383</v>
       </c>
-      <c r="V30" s="148">
+      <c r="V30" s="147">
         <f t="shared" si="6"/>
         <v>0.966963790910778</v>
       </c>
     </row>
     <row r="31" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R31" s="117">
+      <c r="R31" s="116">
         <v>70</v>
       </c>
-      <c r="S31" s="146">
+      <c r="S31" s="145">
         <f t="shared" ref="S31:V31" si="7">(0.475*$R31^0.75 + S$26*$X$27)/S11</f>
         <v>0.99958400776909073</v>
       </c>
-      <c r="T31" s="147">
+      <c r="T31" s="146">
         <f t="shared" si="7"/>
         <v>1.0353725778103244</v>
       </c>
-      <c r="U31" s="147">
+      <c r="U31" s="146">
         <f t="shared" si="7"/>
         <v>0.99972663367683112</v>
       </c>
-      <c r="V31" s="148">
+      <c r="V31" s="147">
         <f t="shared" si="7"/>
         <v>0.9398086435737818</v>
       </c>
     </row>
     <row r="32" spans="18:31" x14ac:dyDescent="0.25">
-      <c r="R32" s="118">
+      <c r="R32" s="117">
         <v>80</v>
       </c>
-      <c r="S32" s="149">
+      <c r="S32" s="148">
         <f t="shared" ref="S32:V32" si="8">(0.475*$R32^0.75 + S$26*$X$27)/S12</f>
         <v>0.9773896765040011</v>
       </c>
-      <c r="T32" s="150">
+      <c r="T32" s="149">
         <f t="shared" si="8"/>
         <v>0.98162911215950088</v>
       </c>
-      <c r="U32" s="150">
+      <c r="U32" s="149">
         <f t="shared" si="8"/>
         <v>0.95928542536164174</v>
       </c>
-      <c r="V32" s="151">
+      <c r="V32" s="150">
         <f t="shared" si="8"/>
         <v>0.88235949266257196</v>
       </c>

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -56,13 +56,13 @@
   </definedNames>
   <calcPr calcId="162913" iterate="1"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId12"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="435">
   <si>
     <t>value</t>
   </si>
@@ -2236,7 +2236,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2490,6 +2490,7 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -14002,7 +14003,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="L3:O43" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0">
@@ -16280,7 +16281,7 @@
       <c r="H30" t="s">
         <v>407</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="93">
         <v>0</v>
       </c>
       <c r="J30" t="s">
@@ -16297,7 +16298,7 @@
       <c r="H31" t="s">
         <v>407</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="93">
         <v>0</v>
       </c>
       <c r="J31" t="s">
@@ -16440,6 +16441,15 @@
       <c r="B41" t="s">
         <v>1</v>
       </c>
+      <c r="H41" t="s">
+        <v>407</v>
+      </c>
+      <c r="I41" s="93">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -16447,6 +16457,15 @@
       </c>
       <c r="B42" t="s">
         <v>5</v>
+      </c>
+      <c r="H42" t="s">
+        <v>407</v>
+      </c>
+      <c r="I42" s="93">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -16911,6 +16930,18 @@
       </c>
       <c r="L62" t="s">
         <v>333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H63" s="160" t="s">
+        <v>301</v>
+      </c>
+      <c r="I63" s="160">
+        <v>0</v>
+      </c>
+      <c r="J63" s="160"/>
+      <c r="K63" s="161" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -54,7 +54,7 @@
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913" iterate="1" calcCompleted="0"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId12"/>
   </pivotCaches>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="435">
   <si>
     <t>value</t>
   </si>
@@ -18590,37 +18590,32 @@
       <c r="L153" s="95"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="97" t="s">
+      <c r="H154" s="160" t="s">
+        <v>327</v>
+      </c>
+      <c r="I154" s="160">
+        <v>0</v>
+      </c>
+      <c r="J154" s="160"/>
+      <c r="K154" s="160" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" s="97" t="s">
         <v>304</v>
       </c>
-      <c r="B154" s="97"/>
-      <c r="C154" s="97"/>
-      <c r="D154" s="98"/>
-      <c r="E154" s="98"/>
-      <c r="F154" s="98"/>
-      <c r="G154" s="98"/>
-      <c r="H154" s="98"/>
-      <c r="I154" s="99"/>
-      <c r="J154" s="98"/>
-      <c r="K154" s="98"/>
-      <c r="L154" s="98"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>2</v>
-      </c>
-      <c r="D155" t="s">
-        <v>18</v>
-      </c>
-      <c r="E155" t="s">
-        <v>329</v>
-      </c>
-      <c r="H155" t="s">
-        <v>327</v>
-      </c>
-      <c r="I155">
-        <v>40</v>
-      </c>
+      <c r="B155" s="97"/>
+      <c r="C155" s="97"/>
+      <c r="D155" s="98"/>
+      <c r="E155" s="98"/>
+      <c r="F155" s="98"/>
+      <c r="G155" s="98"/>
+      <c r="H155" s="98"/>
+      <c r="I155" s="99"/>
+      <c r="J155" s="98"/>
+      <c r="K155" s="98"/>
+      <c r="L155" s="98"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
@@ -18630,13 +18625,13 @@
         <v>18</v>
       </c>
       <c r="E156" t="s">
-        <v>429</v>
+        <v>329</v>
       </c>
       <c r="H156" t="s">
         <v>327</v>
       </c>
       <c r="I156">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -18647,13 +18642,13 @@
         <v>18</v>
       </c>
       <c r="E157" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="H157" t="s">
         <v>327</v>
       </c>
       <c r="I157">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -18664,27 +18659,30 @@
         <v>18</v>
       </c>
       <c r="E158" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H158" t="s">
         <v>327</v>
       </c>
       <c r="I158">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>2</v>
       </c>
+      <c r="D159" t="s">
+        <v>18</v>
+      </c>
       <c r="E159" t="s">
-        <v>329</v>
+        <v>397</v>
       </c>
       <c r="H159" t="s">
         <v>327</v>
       </c>
       <c r="I159">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -18692,13 +18690,13 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>429</v>
+        <v>329</v>
       </c>
       <c r="H160" t="s">
         <v>327</v>
       </c>
       <c r="I160">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -18706,7 +18704,7 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="H161" t="s">
         <v>327</v>
@@ -18720,30 +18718,27 @@
         <v>2</v>
       </c>
       <c r="E162" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H162" t="s">
         <v>327</v>
       </c>
       <c r="I162">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>2</v>
       </c>
-      <c r="D163" t="s">
-        <v>35</v>
-      </c>
       <c r="E163" t="s">
-        <v>329</v>
+        <v>397</v>
       </c>
       <c r="H163" t="s">
         <v>327</v>
       </c>
       <c r="I163">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -18754,13 +18749,13 @@
         <v>35</v>
       </c>
       <c r="E164" t="s">
-        <v>429</v>
+        <v>329</v>
       </c>
       <c r="H164" t="s">
         <v>327</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -18771,13 +18766,13 @@
         <v>35</v>
       </c>
       <c r="E165" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="H165" t="s">
         <v>327</v>
       </c>
       <c r="I165">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -18788,63 +18783,60 @@
         <v>35</v>
       </c>
       <c r="E166" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H166" t="s">
         <v>327</v>
       </c>
       <c r="I166">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" t="s">
+        <v>397</v>
+      </c>
+      <c r="H167" t="s">
+        <v>327</v>
+      </c>
+      <c r="I167">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="100" t="s">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" s="100" t="s">
         <v>305</v>
       </c>
-      <c r="B168" s="100"/>
-      <c r="C168" s="100"/>
-      <c r="D168" s="101"/>
-      <c r="E168" s="101"/>
-      <c r="F168" s="101"/>
-      <c r="G168" s="101"/>
-      <c r="H168" s="101"/>
-      <c r="I168" s="101"/>
-      <c r="J168" s="101"/>
-      <c r="K168" s="101"/>
-      <c r="L168" s="101"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>39</v>
-      </c>
-      <c r="E169" t="s">
-        <v>329</v>
-      </c>
-      <c r="H169" t="s">
-        <v>327</v>
-      </c>
-      <c r="I169">
-        <v>60</v>
-      </c>
-      <c r="J169" t="s">
-        <v>328</v>
-      </c>
+      <c r="B169" s="100"/>
+      <c r="C169" s="100"/>
+      <c r="D169" s="101"/>
+      <c r="E169" s="101"/>
+      <c r="F169" s="101"/>
+      <c r="G169" s="101"/>
+      <c r="H169" s="101"/>
+      <c r="I169" s="101"/>
+      <c r="J169" s="101"/>
+      <c r="K169" s="101"/>
+      <c r="L169" s="101"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>429</v>
+        <v>329</v>
       </c>
       <c r="H170" t="s">
         <v>327</v>
       </c>
       <c r="I170">
-        <v>30</v>
-      </c>
-      <c r="J170" t="s">
-        <v>328</v>
+        <v>60</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -18852,36 +18844,27 @@
         <v>39</v>
       </c>
       <c r="E171" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="H171" t="s">
         <v>327</v>
       </c>
       <c r="I171">
-        <v>10</v>
-      </c>
-      <c r="J171" t="s">
-        <v>328</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>39</v>
       </c>
-      <c r="D172" t="s">
-        <v>35</v>
-      </c>
       <c r="E172" t="s">
-        <v>329</v>
+        <v>399</v>
       </c>
       <c r="H172" t="s">
         <v>327</v>
       </c>
       <c r="I172">
-        <v>50</v>
-      </c>
-      <c r="J172" t="s">
-        <v>328</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -18892,16 +18875,13 @@
         <v>35</v>
       </c>
       <c r="E173" t="s">
-        <v>429</v>
+        <v>329</v>
       </c>
       <c r="H173" t="s">
         <v>327</v>
       </c>
       <c r="I173">
-        <v>0</v>
-      </c>
-      <c r="J173" t="s">
-        <v>328</v>
+        <v>50</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -18912,30 +18892,30 @@
         <v>35</v>
       </c>
       <c r="E174" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="H174" t="s">
         <v>327</v>
       </c>
       <c r="I174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>39</v>
+      </c>
+      <c r="D175" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" t="s">
+        <v>399</v>
+      </c>
+      <c r="H175" t="s">
+        <v>327</v>
+      </c>
+      <c r="I175">
         <v>50</v>
-      </c>
-      <c r="J174" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H176" s="160" t="s">
-        <v>327</v>
-      </c>
-      <c r="I176" s="160">
-        <v>0</v>
-      </c>
-      <c r="J176" s="160" t="s">
-        <v>328</v>
-      </c>
-      <c r="K176" s="160" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -18990,9 +18970,10 @@
       <c r="H180" t="s">
         <v>433</v>
       </c>
-      <c r="J180" s="93">
+      <c r="I180" s="93">
         <v>5</v>
       </c>
+      <c r="J180" s="93"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
@@ -19004,9 +18985,10 @@
       <c r="H181" t="s">
         <v>433</v>
       </c>
-      <c r="J181" s="93">
+      <c r="I181" s="93">
         <v>5</v>
       </c>
+      <c r="J181" s="93"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
@@ -19018,9 +19000,10 @@
       <c r="H182" t="s">
         <v>433</v>
       </c>
-      <c r="J182" s="93">
+      <c r="I182" s="93">
         <v>0</v>
       </c>
+      <c r="J182" s="93"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
@@ -19032,9 +19015,10 @@
       <c r="H183" t="s">
         <v>433</v>
       </c>
-      <c r="J183" s="93">
+      <c r="I183" s="93">
         <v>100</v>
       </c>
+      <c r="J183" s="93"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
@@ -19046,9 +19030,10 @@
       <c r="H184" t="s">
         <v>433</v>
       </c>
-      <c r="J184" s="93">
+      <c r="I184" s="93">
         <v>100</v>
       </c>
+      <c r="J184" s="93"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
@@ -19060,9 +19045,10 @@
       <c r="H185" t="s">
         <v>433</v>
       </c>
-      <c r="J185" s="93">
+      <c r="I185" s="93">
         <v>0</v>
       </c>
+      <c r="J185" s="93"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="100" t="s">
@@ -19090,9 +19076,10 @@
       <c r="H188" t="s">
         <v>433</v>
       </c>
-      <c r="J188" s="93">
+      <c r="I188" s="93">
         <v>100</v>
       </c>
+      <c r="J188" s="93"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
@@ -19104,9 +19091,10 @@
       <c r="H189" t="s">
         <v>433</v>
       </c>
-      <c r="J189" s="93">
+      <c r="I189" s="93">
         <v>100</v>
       </c>
+      <c r="J189" s="93"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
@@ -19118,9 +19106,10 @@
       <c r="H190" t="s">
         <v>433</v>
       </c>
-      <c r="J190" s="93">
+      <c r="I190" s="93">
         <v>0</v>
       </c>
+      <c r="J190" s="93"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
@@ -19132,9 +19121,10 @@
       <c r="H191" t="s">
         <v>433</v>
       </c>
-      <c r="J191" s="93">
+      <c r="I191" s="93">
         <v>100</v>
       </c>
+      <c r="J191" s="93"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
@@ -19146,9 +19136,10 @@
       <c r="H192" t="s">
         <v>433</v>
       </c>
-      <c r="J192" s="93">
+      <c r="I192" s="93">
         <v>100</v>
       </c>
+      <c r="J192" s="93"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
@@ -19160,9 +19151,10 @@
       <c r="H193" t="s">
         <v>433</v>
       </c>
-      <c r="J193" s="93">
+      <c r="I193" s="93">
         <v>100</v>
       </c>
+      <c r="J193" s="93"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="159" t="s">

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -54,7 +54,7 @@
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterate="1" calcCompleted="0"/>
+  <calcPr calcId="162913" iterate="1"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId12"/>
   </pivotCaches>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="442">
   <si>
     <t>value</t>
   </si>
@@ -1267,13 +1267,7 @@
     <t>Total incl. for calves</t>
   </si>
   <si>
-    <t>rapeseed meal/cake</t>
-  </si>
-  <si>
     <t>f_sub_system</t>
-  </si>
-  <si>
-    <t>wheat</t>
   </si>
   <si>
     <t>Avg</t>
@@ -1379,6 +1373,33 @@
   </si>
   <si>
     <t>This parameter specifies the maximum share of grazing demand that can be met from grazing in semi-natural grasslands</t>
+  </si>
+  <si>
+    <t>straw</t>
+  </si>
+  <si>
+    <t>barley</t>
+  </si>
+  <si>
+    <t>rapeseed meal</t>
+  </si>
+  <si>
+    <t>wheat distillers grain, dry</t>
+  </si>
+  <si>
+    <t>maize based</t>
+  </si>
+  <si>
+    <t>maize silage</t>
+  </si>
+  <si>
+    <t>sugar beet pulp</t>
+  </si>
+  <si>
+    <t>wheat bran</t>
+  </si>
+  <si>
+    <t>Mikaela Lindberg (SLU) pers. com. 2023-04-21</t>
   </si>
 </sst>
 </file>
@@ -15723,7 +15744,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L213"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -15748,7 +15769,7 @@
         <v>296</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>53</v>
@@ -16279,13 +16300,13 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I30" s="93">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -16296,13 +16317,13 @@
         <v>5</v>
       </c>
       <c r="H31" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I31" s="93">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -16442,13 +16463,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I41" s="93">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -16459,13 +16480,13 @@
         <v>5</v>
       </c>
       <c r="H42" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I42" s="93">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -16941,7 +16962,7 @@
       </c>
       <c r="J63" s="160"/>
       <c r="K63" s="161" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -17582,7 +17603,7 @@
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H99" t="s">
         <v>36</v>
@@ -17614,7 +17635,7 @@
         <v>9</v>
       </c>
       <c r="K100" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -17637,7 +17658,7 @@
         <v>9</v>
       </c>
       <c r="K101" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -17660,7 +17681,7 @@
         <v>9</v>
       </c>
       <c r="K102" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -17683,7 +17704,7 @@
         <v>9</v>
       </c>
       <c r="K103" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -17706,7 +17727,7 @@
         <v>9</v>
       </c>
       <c r="K104" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -17729,7 +17750,7 @@
         <v>9</v>
       </c>
       <c r="K105" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -17752,7 +17773,7 @@
         <v>9</v>
       </c>
       <c r="K106" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -17775,7 +17796,7 @@
         <v>9</v>
       </c>
       <c r="K107" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -17969,7 +17990,7 @@
         <v>39</v>
       </c>
       <c r="D119" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H119" t="s">
         <v>36</v>
@@ -18001,7 +18022,7 @@
         <v>9</v>
       </c>
       <c r="K120" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -18024,7 +18045,7 @@
         <v>9</v>
       </c>
       <c r="K121" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -18047,7 +18068,7 @@
         <v>9</v>
       </c>
       <c r="K122" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -18070,7 +18091,7 @@
         <v>9</v>
       </c>
       <c r="K123" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -18093,7 +18114,7 @@
         <v>9</v>
       </c>
       <c r="K124" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -18116,7 +18137,7 @@
         <v>9</v>
       </c>
       <c r="K125" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -18139,7 +18160,7 @@
         <v>9</v>
       </c>
       <c r="K126" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -18162,7 +18183,7 @@
         <v>9</v>
       </c>
       <c r="K127" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -18307,7 +18328,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="94" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B137" s="94"/>
       <c r="C137" s="94"/>
@@ -18326,30 +18347,30 @@
         <v>18</v>
       </c>
       <c r="H138" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I138">
         <v>0.50700000000000001</v>
       </c>
       <c r="J138" t="s">
+        <v>411</v>
+      </c>
+      <c r="L138" t="s">
         <v>413</v>
-      </c>
-      <c r="L138" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H139" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I139">
         <v>0.47499999999999998</v>
       </c>
       <c r="J139" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L139" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -18357,16 +18378,16 @@
         <v>18</v>
       </c>
       <c r="H140" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I140" s="13">
         <v>5</v>
       </c>
       <c r="J140" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L140" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -18377,20 +18398,20 @@
         <v>18</v>
       </c>
       <c r="H141" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I141" s="13">
         <f>(0.013+0.021+0.038) * 30.4</f>
         <v>2.1888000000000001</v>
       </c>
       <c r="J141" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K141" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L141" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -18401,31 +18422,31 @@
         <v>18</v>
       </c>
       <c r="H142" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I142" s="13">
         <f>(8 * 7 * 3.6)/100</f>
         <v>2.016</v>
       </c>
       <c r="J142" t="s">
+        <v>416</v>
+      </c>
+      <c r="K142" t="s">
         <v>418</v>
       </c>
-      <c r="K142" t="s">
-        <v>420</v>
-      </c>
       <c r="L142" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H143" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I143" s="1">
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -18436,16 +18457,16 @@
         <v>18</v>
       </c>
       <c r="H144" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I144" s="1">
         <v>1.1100000000000001</v>
       </c>
       <c r="J144" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L144" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -18456,19 +18477,19 @@
         <v>35</v>
       </c>
       <c r="H145" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I145" s="1">
         <v>0.9</v>
       </c>
       <c r="J145" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K145" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L145" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -18476,16 +18497,16 @@
         <v>33</v>
       </c>
       <c r="H146" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I146" s="1">
         <v>1.05</v>
       </c>
       <c r="J146" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L146" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -18496,27 +18517,27 @@
         <v>34</v>
       </c>
       <c r="H147" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I147" s="1">
         <v>1.05</v>
       </c>
       <c r="J147" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L147" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H148" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I148" s="13">
         <v>0</v>
       </c>
       <c r="J148" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -18527,16 +18548,16 @@
         <v>18</v>
       </c>
       <c r="H149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I149" s="13">
         <v>-13.6</v>
       </c>
       <c r="J149" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L149" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -18573,7 +18594,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="94" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B153" s="94"/>
       <c r="C153" s="94"/>
@@ -18598,7 +18619,7 @@
       </c>
       <c r="J154" s="160"/>
       <c r="K154" s="160" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -18631,7 +18652,10 @@
         <v>327</v>
       </c>
       <c r="I156">
-        <v>40</v>
+        <v>48</v>
+      </c>
+      <c r="L156" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -18642,13 +18666,16 @@
         <v>18</v>
       </c>
       <c r="E157" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H157" t="s">
         <v>327</v>
       </c>
       <c r="I157">
         <v>10</v>
+      </c>
+      <c r="L157" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -18659,13 +18686,16 @@
         <v>18</v>
       </c>
       <c r="E158" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="H158" t="s">
         <v>327</v>
       </c>
       <c r="I158">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="L158" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -18676,639 +18706,889 @@
         <v>18</v>
       </c>
       <c r="E159" t="s">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="H159" t="s">
         <v>327</v>
       </c>
       <c r="I159">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="L159" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>2</v>
       </c>
+      <c r="D160" t="s">
+        <v>18</v>
+      </c>
       <c r="E160" t="s">
-        <v>329</v>
+        <v>435</v>
       </c>
       <c r="H160" t="s">
         <v>327</v>
       </c>
       <c r="I160">
-        <v>50</v>
+        <v>6</v>
+      </c>
+      <c r="L160" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>2</v>
       </c>
+      <c r="D161" t="s">
+        <v>18</v>
+      </c>
       <c r="E161" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="H161" t="s">
         <v>327</v>
       </c>
       <c r="I161">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="L161" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>2</v>
       </c>
+      <c r="C162" t="s">
+        <v>437</v>
+      </c>
+      <c r="D162" t="s">
+        <v>18</v>
+      </c>
       <c r="E162" t="s">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="H162" t="s">
         <v>327</v>
       </c>
       <c r="I162">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="L162" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>2</v>
       </c>
+      <c r="C163" t="s">
+        <v>437</v>
+      </c>
+      <c r="D163" t="s">
+        <v>18</v>
+      </c>
       <c r="E163" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="H163" t="s">
         <v>327</v>
       </c>
       <c r="I163">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="L163" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>2</v>
       </c>
+      <c r="C164" t="s">
+        <v>437</v>
+      </c>
       <c r="D164" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E164" t="s">
-        <v>329</v>
+        <v>427</v>
       </c>
       <c r="H164" t="s">
         <v>327</v>
       </c>
       <c r="I164">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="L164" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>2</v>
       </c>
+      <c r="C165" t="s">
+        <v>437</v>
+      </c>
       <c r="D165" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E165" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="H165" t="s">
         <v>327</v>
       </c>
       <c r="I165">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="L165" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>2</v>
       </c>
+      <c r="C166" t="s">
+        <v>437</v>
+      </c>
       <c r="D166" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E166" t="s">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="H166" t="s">
         <v>327</v>
       </c>
       <c r="I166">
-        <v>50</v>
+        <v>17</v>
+      </c>
+      <c r="L166" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>2</v>
       </c>
+      <c r="C167" t="s">
+        <v>437</v>
+      </c>
       <c r="D167" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E167" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="H167" t="s">
         <v>327</v>
       </c>
       <c r="I167">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="L167" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>2</v>
+      </c>
+      <c r="C168" t="s">
+        <v>437</v>
+      </c>
+      <c r="D168" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" t="s">
+        <v>436</v>
+      </c>
+      <c r="H168" t="s">
+        <v>327</v>
+      </c>
+      <c r="I168">
+        <v>9</v>
+      </c>
+      <c r="L168" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="B169" s="100"/>
-      <c r="C169" s="100"/>
-      <c r="D169" s="101"/>
-      <c r="E169" s="101"/>
-      <c r="F169" s="101"/>
-      <c r="G169" s="101"/>
-      <c r="H169" s="101"/>
-      <c r="I169" s="101"/>
-      <c r="J169" s="101"/>
-      <c r="K169" s="101"/>
-      <c r="L169" s="101"/>
+      <c r="A169" t="s">
+        <v>2</v>
+      </c>
+      <c r="C169" t="s">
+        <v>437</v>
+      </c>
+      <c r="D169" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169" t="s">
+        <v>439</v>
+      </c>
+      <c r="H169" t="s">
+        <v>327</v>
+      </c>
+      <c r="I169">
+        <v>5</v>
+      </c>
+      <c r="L169" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>39</v>
+        <v>2</v>
+      </c>
+      <c r="C170" t="s">
+        <v>437</v>
+      </c>
+      <c r="D170" t="s">
+        <v>18</v>
       </c>
       <c r="E170" t="s">
-        <v>329</v>
+        <v>440</v>
       </c>
       <c r="H170" t="s">
         <v>327</v>
       </c>
       <c r="I170">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>39</v>
-      </c>
-      <c r="E171" t="s">
-        <v>429</v>
-      </c>
-      <c r="H171" t="s">
-        <v>327</v>
-      </c>
-      <c r="I171">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="L170" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="E172" t="s">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="H172" t="s">
         <v>327</v>
       </c>
       <c r="I172">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>39</v>
-      </c>
-      <c r="D173" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>329</v>
+        <v>427</v>
       </c>
       <c r="H173" t="s">
         <v>327</v>
       </c>
       <c r="I173">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>39</v>
-      </c>
-      <c r="D174" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="H174" t="s">
         <v>327</v>
       </c>
       <c r="I174">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>39</v>
-      </c>
-      <c r="D175" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="H175" t="s">
         <v>327</v>
       </c>
       <c r="I175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>2</v>
+      </c>
+      <c r="D176" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" t="s">
+        <v>329</v>
+      </c>
+      <c r="H176" t="s">
+        <v>327</v>
+      </c>
+      <c r="I176">
         <v>50</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H177" s="93"/>
-      <c r="I177" s="93"/>
-      <c r="J177" s="93"/>
-      <c r="K177" s="93"/>
+      <c r="A177" t="s">
+        <v>2</v>
+      </c>
+      <c r="D177" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" t="s">
+        <v>427</v>
+      </c>
+      <c r="H177" t="s">
+        <v>327</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="94" t="s">
-        <v>432</v>
-      </c>
-      <c r="B178" s="94"/>
-      <c r="C178" s="94"/>
-      <c r="D178" s="95"/>
-      <c r="E178" s="95"/>
-      <c r="F178" s="95"/>
-      <c r="G178" s="95"/>
-      <c r="H178" s="95"/>
-      <c r="I178" s="95"/>
-      <c r="J178" s="95" t="s">
-        <v>9</v>
-      </c>
-      <c r="K178" s="95" t="s">
+      <c r="A178" t="s">
+        <v>2</v>
+      </c>
+      <c r="D178" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" t="s">
         <v>434</v>
       </c>
-      <c r="L178" s="95"/>
+      <c r="H178" t="s">
+        <v>327</v>
+      </c>
+      <c r="I178">
+        <v>50</v>
+      </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="97" t="s">
-        <v>304</v>
-      </c>
-      <c r="B179" s="97"/>
-      <c r="C179" s="97"/>
-      <c r="D179" s="98"/>
-      <c r="E179" s="98"/>
-      <c r="F179" s="98"/>
-      <c r="G179" s="98"/>
-      <c r="H179" s="98"/>
-      <c r="I179" s="99"/>
-      <c r="J179" s="98"/>
-      <c r="K179" s="98"/>
-      <c r="L179" s="98"/>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A179" t="s">
         <v>2</v>
       </c>
-      <c r="D180" t="s">
-        <v>18</v>
-      </c>
-      <c r="H180" t="s">
-        <v>433</v>
-      </c>
-      <c r="I180" s="93">
-        <v>5</v>
-      </c>
-      <c r="J180" s="93"/>
+      <c r="D179" t="s">
+        <v>35</v>
+      </c>
+      <c r="E179" t="s">
+        <v>435</v>
+      </c>
+      <c r="H179" t="s">
+        <v>327</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>2</v>
-      </c>
-      <c r="D181" t="s">
-        <v>20</v>
-      </c>
-      <c r="H181" t="s">
-        <v>433</v>
-      </c>
-      <c r="I181" s="93">
-        <v>5</v>
-      </c>
-      <c r="J181" s="93"/>
+      <c r="A181" s="100" t="s">
+        <v>305</v>
+      </c>
+      <c r="B181" s="100"/>
+      <c r="C181" s="100"/>
+      <c r="D181" s="101"/>
+      <c r="E181" s="101"/>
+      <c r="F181" s="101"/>
+      <c r="G181" s="101"/>
+      <c r="H181" s="101"/>
+      <c r="I181" s="101"/>
+      <c r="J181" s="101"/>
+      <c r="K181" s="101"/>
+      <c r="L181" s="101"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>2</v>
-      </c>
-      <c r="D182" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="E182" t="s">
+        <v>329</v>
       </c>
       <c r="H182" t="s">
-        <v>433</v>
-      </c>
-      <c r="I182" s="93">
-        <v>0</v>
-      </c>
-      <c r="J182" s="93"/>
+        <v>327</v>
+      </c>
+      <c r="I182">
+        <v>60</v>
+      </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>2</v>
-      </c>
-      <c r="D183" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="E183" t="s">
+        <v>427</v>
       </c>
       <c r="H183" t="s">
-        <v>433</v>
-      </c>
-      <c r="I183" s="93">
-        <v>100</v>
-      </c>
-      <c r="J183" s="93"/>
+        <v>327</v>
+      </c>
+      <c r="I183">
+        <v>30</v>
+      </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>2</v>
-      </c>
-      <c r="D184" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="E184" t="s">
+        <v>434</v>
       </c>
       <c r="H184" t="s">
-        <v>433</v>
-      </c>
-      <c r="I184" s="93">
-        <v>100</v>
-      </c>
-      <c r="J184" s="93"/>
+        <v>327</v>
+      </c>
+      <c r="I184">
+        <v>10</v>
+      </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D185" t="s">
-        <v>431</v>
+        <v>35</v>
+      </c>
+      <c r="E185" t="s">
+        <v>329</v>
       </c>
       <c r="H185" t="s">
-        <v>433</v>
-      </c>
-      <c r="I185" s="93">
+        <v>327</v>
+      </c>
+      <c r="I185">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>39</v>
+      </c>
+      <c r="D186" t="s">
+        <v>35</v>
+      </c>
+      <c r="E186" t="s">
+        <v>427</v>
+      </c>
+      <c r="H186" t="s">
+        <v>327</v>
+      </c>
+      <c r="I186">
         <v>0</v>
       </c>
-      <c r="J185" s="93"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="B187" s="100"/>
-      <c r="C187" s="100"/>
-      <c r="D187" s="101"/>
-      <c r="E187" s="101"/>
-      <c r="F187" s="101"/>
-      <c r="G187" s="101"/>
-      <c r="H187" s="101"/>
-      <c r="I187" s="101"/>
-      <c r="J187" s="101"/>
-      <c r="K187" s="101"/>
-      <c r="L187" s="101"/>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="A187" t="s">
         <v>39</v>
       </c>
-      <c r="D188" t="s">
-        <v>18</v>
-      </c>
-      <c r="H188" t="s">
-        <v>433</v>
-      </c>
-      <c r="I188" s="93">
-        <v>100</v>
-      </c>
-      <c r="J188" s="93"/>
+      <c r="D187" t="s">
+        <v>35</v>
+      </c>
+      <c r="E187" t="s">
+        <v>434</v>
+      </c>
+      <c r="H187" t="s">
+        <v>327</v>
+      </c>
+      <c r="I187">
+        <v>50</v>
+      </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>39</v>
-      </c>
-      <c r="D189" t="s">
-        <v>20</v>
-      </c>
-      <c r="H189" t="s">
-        <v>433</v>
-      </c>
-      <c r="I189" s="93">
-        <v>100</v>
-      </c>
+      <c r="H189" s="93"/>
+      <c r="I189" s="93"/>
       <c r="J189" s="93"/>
+      <c r="K189" s="93"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>39</v>
-      </c>
-      <c r="D190" t="s">
-        <v>35</v>
-      </c>
-      <c r="H190" t="s">
-        <v>433</v>
-      </c>
-      <c r="I190" s="93">
-        <v>0</v>
-      </c>
-      <c r="J190" s="93"/>
+      <c r="A190" s="94" t="s">
+        <v>430</v>
+      </c>
+      <c r="B190" s="94"/>
+      <c r="C190" s="94"/>
+      <c r="D190" s="95"/>
+      <c r="E190" s="95"/>
+      <c r="F190" s="95"/>
+      <c r="G190" s="95"/>
+      <c r="H190" s="95"/>
+      <c r="I190" s="95"/>
+      <c r="J190" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="K190" s="95" t="s">
+        <v>432</v>
+      </c>
+      <c r="L190" s="95"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>39</v>
-      </c>
-      <c r="D191" t="s">
-        <v>33</v>
-      </c>
-      <c r="H191" t="s">
-        <v>433</v>
-      </c>
-      <c r="I191" s="93">
-        <v>100</v>
-      </c>
-      <c r="J191" s="93"/>
+      <c r="A191" s="97" t="s">
+        <v>304</v>
+      </c>
+      <c r="B191" s="97"/>
+      <c r="C191" s="97"/>
+      <c r="D191" s="98"/>
+      <c r="E191" s="98"/>
+      <c r="F191" s="98"/>
+      <c r="G191" s="98"/>
+      <c r="H191" s="98"/>
+      <c r="I191" s="99"/>
+      <c r="J191" s="98"/>
+      <c r="K191" s="98"/>
+      <c r="L191" s="98"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D192" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H192" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I192" s="93">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J192" s="93"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>2</v>
+      </c>
+      <c r="D193" t="s">
+        <v>20</v>
+      </c>
+      <c r="H193" t="s">
+        <v>431</v>
+      </c>
+      <c r="I193" s="93">
+        <v>5</v>
+      </c>
+      <c r="J193" s="93"/>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>2</v>
+      </c>
+      <c r="D194" t="s">
+        <v>35</v>
+      </c>
+      <c r="H194" t="s">
+        <v>431</v>
+      </c>
+      <c r="I194" s="93">
+        <v>0</v>
+      </c>
+      <c r="J194" s="93"/>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>33</v>
+      </c>
+      <c r="H195" t="s">
+        <v>431</v>
+      </c>
+      <c r="I195" s="93">
+        <v>100</v>
+      </c>
+      <c r="J195" s="93"/>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>2</v>
+      </c>
+      <c r="D196" t="s">
+        <v>34</v>
+      </c>
+      <c r="H196" t="s">
+        <v>431</v>
+      </c>
+      <c r="I196" s="93">
+        <v>100</v>
+      </c>
+      <c r="J196" s="93"/>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>2</v>
+      </c>
+      <c r="D197" t="s">
+        <v>429</v>
+      </c>
+      <c r="H197" t="s">
+        <v>431</v>
+      </c>
+      <c r="I197" s="93">
+        <v>0</v>
+      </c>
+      <c r="J197" s="93"/>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" s="100" t="s">
+        <v>305</v>
+      </c>
+      <c r="B199" s="100"/>
+      <c r="C199" s="100"/>
+      <c r="D199" s="101"/>
+      <c r="E199" s="101"/>
+      <c r="F199" s="101"/>
+      <c r="G199" s="101"/>
+      <c r="H199" s="101"/>
+      <c r="I199" s="101"/>
+      <c r="J199" s="101"/>
+      <c r="K199" s="101"/>
+      <c r="L199" s="101"/>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
         <v>39</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D200" t="s">
+        <v>18</v>
+      </c>
+      <c r="H200" t="s">
         <v>431</v>
       </c>
-      <c r="H193" t="s">
-        <v>433</v>
-      </c>
-      <c r="I193" s="93">
+      <c r="I200" s="93">
         <v>100</v>
       </c>
-      <c r="J193" s="93"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="159" t="s">
+      <c r="J200" s="93"/>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>39</v>
+      </c>
+      <c r="D201" t="s">
+        <v>20</v>
+      </c>
+      <c r="H201" t="s">
+        <v>431</v>
+      </c>
+      <c r="I201" s="93">
+        <v>100</v>
+      </c>
+      <c r="J201" s="93"/>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>39</v>
+      </c>
+      <c r="D202" t="s">
+        <v>35</v>
+      </c>
+      <c r="H202" t="s">
+        <v>431</v>
+      </c>
+      <c r="I202" s="93">
+        <v>0</v>
+      </c>
+      <c r="J202" s="93"/>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>39</v>
+      </c>
+      <c r="D203" t="s">
+        <v>33</v>
+      </c>
+      <c r="H203" t="s">
+        <v>431</v>
+      </c>
+      <c r="I203" s="93">
+        <v>100</v>
+      </c>
+      <c r="J203" s="93"/>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>39</v>
+      </c>
+      <c r="D204" t="s">
+        <v>34</v>
+      </c>
+      <c r="H204" t="s">
+        <v>431</v>
+      </c>
+      <c r="I204" s="93">
+        <v>100</v>
+      </c>
+      <c r="J204" s="93"/>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>39</v>
+      </c>
+      <c r="D205" t="s">
+        <v>429</v>
+      </c>
+      <c r="H205" t="s">
+        <v>431</v>
+      </c>
+      <c r="I205" s="93">
+        <v>100</v>
+      </c>
+      <c r="J205" s="93"/>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" s="159" t="s">
         <v>306</v>
       </c>
-      <c r="B195" s="159"/>
-      <c r="C195" s="159"/>
-      <c r="D195" s="95"/>
-      <c r="E195" s="95"/>
-      <c r="F195" s="95"/>
-      <c r="G195" s="95"/>
-      <c r="H195" s="95"/>
-      <c r="I195" s="95"/>
-      <c r="J195" s="95"/>
-      <c r="K195" s="95"/>
-      <c r="L195" s="95"/>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="93" t="s">
+      <c r="B207" s="159"/>
+      <c r="C207" s="159"/>
+      <c r="D207" s="95"/>
+      <c r="E207" s="95"/>
+      <c r="F207" s="95"/>
+      <c r="G207" s="95"/>
+      <c r="H207" s="95"/>
+      <c r="I207" s="95"/>
+      <c r="J207" s="95"/>
+      <c r="K207" s="95"/>
+      <c r="L207" s="95"/>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A208" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="D196" s="93" t="s">
+      <c r="D208" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="E196" s="93"/>
-      <c r="F196" s="93"/>
-      <c r="G196" s="93"/>
-      <c r="H196" s="93" t="s">
+      <c r="E208" s="93"/>
+      <c r="F208" s="93"/>
+      <c r="G208" s="93"/>
+      <c r="H208" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I196" s="93">
+      <c r="I208" s="93">
         <v>7.1</v>
       </c>
-      <c r="J196" s="93" t="s">
+      <c r="J208" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K196" s="93"/>
-      <c r="L196" s="93" t="s">
+      <c r="K208" s="93"/>
+      <c r="L208" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="93" t="s">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="D197" s="93" t="s">
+      <c r="D209" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="E197" s="93"/>
-      <c r="F197" s="93"/>
-      <c r="G197" s="93"/>
-      <c r="H197" s="93" t="s">
+      <c r="E209" s="93"/>
+      <c r="F209" s="93"/>
+      <c r="G209" s="93"/>
+      <c r="H209" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I197" s="93">
+      <c r="I209" s="93">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J197" s="93" t="s">
+      <c r="J209" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K197" s="93"/>
-      <c r="L197" s="93" t="s">
+      <c r="K209" s="93"/>
+      <c r="L209" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="93"/>
-      <c r="D198" s="93" t="s">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" s="93"/>
+      <c r="D210" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="E198" s="93"/>
-      <c r="F198" s="93"/>
-      <c r="G198" s="93"/>
-      <c r="H198" s="93" t="s">
+      <c r="E210" s="93"/>
+      <c r="F210" s="93"/>
+      <c r="G210" s="93"/>
+      <c r="H210" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I198" s="93">
+      <c r="I210" s="93">
         <v>5.7</v>
       </c>
-      <c r="J198" s="93" t="s">
+      <c r="J210" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K198" s="93"/>
-      <c r="L198" s="93" t="s">
+      <c r="K210" s="93"/>
+      <c r="L210" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="93"/>
-      <c r="D199" s="93" t="s">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" s="93"/>
+      <c r="D211" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="E199" s="93"/>
-      <c r="F199" s="93"/>
-      <c r="G199" s="93"/>
-      <c r="H199" s="93" t="s">
+      <c r="E211" s="93"/>
+      <c r="F211" s="93"/>
+      <c r="G211" s="93"/>
+      <c r="H211" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I199" s="93">
+      <c r="I211" s="93">
         <v>7.7</v>
       </c>
-      <c r="J199" s="93" t="s">
+      <c r="J211" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K199" s="93"/>
-      <c r="L199" s="93" t="s">
+      <c r="K211" s="93"/>
+      <c r="L211" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="93"/>
-      <c r="D200" s="93" t="s">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" s="93"/>
+      <c r="D212" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="E200" s="93"/>
-      <c r="F200" s="93"/>
-      <c r="G200" s="93"/>
-      <c r="H200" s="93" t="s">
+      <c r="E212" s="93"/>
+      <c r="F212" s="93"/>
+      <c r="G212" s="93"/>
+      <c r="H212" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I200" s="93">
+      <c r="I212" s="93">
         <v>9.1</v>
       </c>
-      <c r="J200" s="93" t="s">
+      <c r="J212" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K200" s="93" t="s">
+      <c r="K212" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="L200" s="93" t="s">
+      <c r="L212" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="93"/>
-      <c r="D201" s="93" t="s">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" s="93"/>
+      <c r="D213" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="E201" s="93"/>
-      <c r="F201" s="93"/>
-      <c r="G201" s="93"/>
-      <c r="H201" s="93" t="s">
+      <c r="E213" s="93"/>
+      <c r="F213" s="93"/>
+      <c r="G213" s="93"/>
+      <c r="H213" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="I201" s="93">
+      <c r="I213" s="93">
         <v>9.1</v>
       </c>
-      <c r="J201" s="93" t="s">
+      <c r="J213" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K201" s="93" t="s">
+      <c r="K213" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="L201" s="93" t="s">
+      <c r="L213" s="93" t="s">
         <v>42</v>
       </c>
     </row>
@@ -25167,7 +25447,7 @@
     </row>
     <row r="96" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
@@ -25175,10 +25455,10 @@
         <v>317</v>
       </c>
       <c r="F98" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I98" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
@@ -25186,28 +25466,28 @@
         <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E99" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F99" t="s">
         <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H99" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K99" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
@@ -25397,7 +25677,7 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" s="155" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C105" s="2">
         <f>AVERAGE(C100:C104)</f>
@@ -25438,7 +25718,7 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D106" s="155" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E106" s="156">
         <f>1/E105</f>

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -55,7 +55,7 @@
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId13"/>
   </pivotCaches>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3702" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3661" uniqueCount="533">
   <si>
     <t>value</t>
   </si>
@@ -1423,15 +1423,6 @@
   </si>
   <si>
     <t>breeding bulls</t>
-  </si>
-  <si>
-    <t>Maximum share of grazing in semi-natural grasslands</t>
-  </si>
-  <si>
-    <t>max_sng_grazing</t>
-  </si>
-  <si>
-    <t>This parameter specifies the maximum share of grazing demand that can be met from grazing in semi-natural grasslands</t>
   </si>
   <si>
     <t>straw</t>
@@ -17269,7 +17260,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L456"/>
+  <dimension ref="A1:L439"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -20207,7 +20198,7 @@
         <v>18</v>
       </c>
       <c r="E158" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H158" t="s">
         <v>327</v>
@@ -20227,7 +20218,7 @@
         <v>18</v>
       </c>
       <c r="E159" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H159" t="s">
         <v>327</v>
@@ -20247,7 +20238,7 @@
         <v>18</v>
       </c>
       <c r="E160" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H160" t="s">
         <v>327</v>
@@ -20267,7 +20258,7 @@
         <v>18</v>
       </c>
       <c r="E161" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H161" t="s">
         <v>327</v>
@@ -20287,7 +20278,7 @@
         <v>18</v>
       </c>
       <c r="E162" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H162" t="s">
         <v>327</v>
@@ -20347,7 +20338,7 @@
         <v>18</v>
       </c>
       <c r="E165" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H165" t="s">
         <v>327</v>
@@ -20367,7 +20358,7 @@
         <v>18</v>
       </c>
       <c r="E166" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H166" t="s">
         <v>327</v>
@@ -20387,7 +20378,7 @@
         <v>18</v>
       </c>
       <c r="E167" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H167" t="s">
         <v>327</v>
@@ -20407,7 +20398,7 @@
         <v>18</v>
       </c>
       <c r="E168" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H168" t="s">
         <v>327</v>
@@ -20427,7 +20418,7 @@
         <v>18</v>
       </c>
       <c r="E169" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H169" t="s">
         <v>327</v>
@@ -20447,7 +20438,7 @@
         <v>18</v>
       </c>
       <c r="E170" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H170" t="s">
         <v>327</v>
@@ -20467,7 +20458,7 @@
         <v>18</v>
       </c>
       <c r="E171" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H171" t="s">
         <v>327</v>
@@ -20487,7 +20478,7 @@
         <v>18</v>
       </c>
       <c r="E172" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H172" t="s">
         <v>327</v>
@@ -20507,7 +20498,7 @@
         <v>18</v>
       </c>
       <c r="E173" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H173" t="s">
         <v>327</v>
@@ -20527,7 +20518,7 @@
         <v>18</v>
       </c>
       <c r="E174" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H174" t="s">
         <v>327</v>
@@ -20547,7 +20538,7 @@
         <v>18</v>
       </c>
       <c r="E175" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H175" t="s">
         <v>327</v>
@@ -20567,7 +20558,7 @@
         <v>18</v>
       </c>
       <c r="E176" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H176" t="s">
         <v>327</v>
@@ -20587,7 +20578,7 @@
         <v>18</v>
       </c>
       <c r="E177" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H177" t="s">
         <v>327</v>
@@ -20607,7 +20598,7 @@
         <v>18</v>
       </c>
       <c r="E178" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H178" t="s">
         <v>327</v>
@@ -20627,7 +20618,7 @@
         <v>18</v>
       </c>
       <c r="E179" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H179" t="s">
         <v>327</v>
@@ -20645,7 +20636,7 @@
         <v>18</v>
       </c>
       <c r="E180" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H180" t="s">
         <v>327</v>
@@ -20663,7 +20654,7 @@
         <v>18</v>
       </c>
       <c r="E181" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H181" t="s">
         <v>327</v>
@@ -20681,7 +20672,7 @@
         <v>18</v>
       </c>
       <c r="E182" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H182" t="s">
         <v>327</v>
@@ -20699,7 +20690,7 @@
         <v>18</v>
       </c>
       <c r="E183" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H183" t="s">
         <v>327</v>
@@ -20717,7 +20708,7 @@
         <v>18</v>
       </c>
       <c r="E184" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H184" t="s">
         <v>327</v>
@@ -20735,7 +20726,7 @@
         <v>18</v>
       </c>
       <c r="E185" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H185" t="s">
         <v>327</v>
@@ -20751,7 +20742,7 @@
       </c>
       <c r="B187" s="160"/>
       <c r="C187" s="160" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D187" s="160" t="s">
         <v>18</v>
@@ -20772,13 +20763,13 @@
         <v>2</v>
       </c>
       <c r="C188" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D188" t="s">
         <v>18</v>
       </c>
       <c r="E188" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H188" t="s">
         <v>327</v>
@@ -20795,13 +20786,13 @@
         <v>2</v>
       </c>
       <c r="C189" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D189" t="s">
         <v>18</v>
       </c>
       <c r="E189" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H189" t="s">
         <v>327</v>
@@ -20818,13 +20809,13 @@
         <v>2</v>
       </c>
       <c r="C190" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D190" t="s">
         <v>18</v>
       </c>
       <c r="E190" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H190" t="s">
         <v>327</v>
@@ -20841,13 +20832,13 @@
         <v>2</v>
       </c>
       <c r="C191" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D191" t="s">
         <v>18</v>
       </c>
       <c r="E191" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H191" t="s">
         <v>327</v>
@@ -20864,13 +20855,13 @@
         <v>2</v>
       </c>
       <c r="C192" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D192" t="s">
         <v>18</v>
       </c>
       <c r="E192" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H192" t="s">
         <v>327</v>
@@ -20887,7 +20878,7 @@
         <v>2</v>
       </c>
       <c r="C193" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D193" t="s">
         <v>18</v>
@@ -20910,7 +20901,7 @@
         <v>2</v>
       </c>
       <c r="C194" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D194" t="s">
         <v>18</v>
@@ -20933,13 +20924,13 @@
         <v>2</v>
       </c>
       <c r="C195" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D195" t="s">
         <v>18</v>
       </c>
       <c r="E195" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H195" t="s">
         <v>327</v>
@@ -20956,13 +20947,13 @@
         <v>2</v>
       </c>
       <c r="C196" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D196" t="s">
         <v>18</v>
       </c>
       <c r="E196" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H196" t="s">
         <v>327</v>
@@ -20979,13 +20970,13 @@
         <v>2</v>
       </c>
       <c r="C197" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D197" t="s">
         <v>18</v>
       </c>
       <c r="E197" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H197" t="s">
         <v>327</v>
@@ -21002,13 +20993,13 @@
         <v>2</v>
       </c>
       <c r="C198" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D198" t="s">
         <v>18</v>
       </c>
       <c r="E198" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H198" t="s">
         <v>327</v>
@@ -21025,13 +21016,13 @@
         <v>2</v>
       </c>
       <c r="C199" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D199" t="s">
         <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H199" t="s">
         <v>327</v>
@@ -21048,13 +21039,13 @@
         <v>2</v>
       </c>
       <c r="C200" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D200" t="s">
         <v>18</v>
       </c>
       <c r="E200" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H200" t="s">
         <v>327</v>
@@ -21071,13 +21062,13 @@
         <v>2</v>
       </c>
       <c r="C201" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D201" t="s">
         <v>18</v>
       </c>
       <c r="E201" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H201" t="s">
         <v>327</v>
@@ -21094,13 +21085,13 @@
         <v>2</v>
       </c>
       <c r="C202" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D202" t="s">
         <v>18</v>
       </c>
       <c r="E202" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H202" t="s">
         <v>327</v>
@@ -21117,13 +21108,13 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D203" t="s">
         <v>18</v>
       </c>
       <c r="E203" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H203" t="s">
         <v>327</v>
@@ -21140,13 +21131,13 @@
         <v>2</v>
       </c>
       <c r="C204" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D204" t="s">
         <v>18</v>
       </c>
       <c r="E204" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H204" t="s">
         <v>327</v>
@@ -21163,13 +21154,13 @@
         <v>2</v>
       </c>
       <c r="C205" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D205" t="s">
         <v>18</v>
       </c>
       <c r="E205" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H205" t="s">
         <v>327</v>
@@ -21186,13 +21177,13 @@
         <v>2</v>
       </c>
       <c r="C206" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D206" t="s">
         <v>18</v>
       </c>
       <c r="E206" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H206" t="s">
         <v>327</v>
@@ -21209,13 +21200,13 @@
         <v>2</v>
       </c>
       <c r="C207" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D207" t="s">
         <v>18</v>
       </c>
       <c r="E207" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H207" t="s">
         <v>327</v>
@@ -21232,13 +21223,13 @@
         <v>2</v>
       </c>
       <c r="C208" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D208" t="s">
         <v>18</v>
       </c>
       <c r="E208" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H208" t="s">
         <v>327</v>
@@ -21255,13 +21246,13 @@
         <v>2</v>
       </c>
       <c r="C209" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D209" t="s">
         <v>18</v>
       </c>
       <c r="E209" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H209" t="s">
         <v>327</v>
@@ -21276,13 +21267,13 @@
         <v>2</v>
       </c>
       <c r="C210" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D210" t="s">
         <v>18</v>
       </c>
       <c r="E210" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H210" t="s">
         <v>327</v>
@@ -21297,13 +21288,13 @@
         <v>2</v>
       </c>
       <c r="C211" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D211" t="s">
         <v>18</v>
       </c>
       <c r="E211" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H211" t="s">
         <v>327</v>
@@ -21318,13 +21309,13 @@
         <v>2</v>
       </c>
       <c r="C212" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D212" t="s">
         <v>18</v>
       </c>
       <c r="E212" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H212" t="s">
         <v>327</v>
@@ -21339,13 +21330,13 @@
         <v>2</v>
       </c>
       <c r="C213" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D213" t="s">
         <v>18</v>
       </c>
       <c r="E213" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H213" t="s">
         <v>327</v>
@@ -21360,13 +21351,13 @@
         <v>2</v>
       </c>
       <c r="C214" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D214" t="s">
         <v>18</v>
       </c>
       <c r="E214" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H214" t="s">
         <v>327</v>
@@ -21381,13 +21372,13 @@
         <v>2</v>
       </c>
       <c r="C215" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D215" t="s">
         <v>18</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H215" t="s">
         <v>327</v>
@@ -21399,7 +21390,7 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="81" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B217" s="48"/>
       <c r="C217" s="48"/>
@@ -21436,7 +21427,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H219" t="s">
         <v>327</v>
@@ -21453,7 +21444,7 @@
         <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H220" t="s">
         <v>327</v>
@@ -21470,7 +21461,7 @@
         <v>2</v>
       </c>
       <c r="E221" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H221" t="s">
         <v>327</v>
@@ -21487,7 +21478,7 @@
         <v>2</v>
       </c>
       <c r="E222" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H222" t="s">
         <v>327</v>
@@ -21504,7 +21495,7 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H223" t="s">
         <v>327</v>
@@ -21555,7 +21546,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H226" t="s">
         <v>327</v>
@@ -21572,7 +21563,7 @@
         <v>2</v>
       </c>
       <c r="E227" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H227" t="s">
         <v>327</v>
@@ -21589,7 +21580,7 @@
         <v>2</v>
       </c>
       <c r="E228" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H228" t="s">
         <v>327</v>
@@ -21606,7 +21597,7 @@
         <v>2</v>
       </c>
       <c r="E229" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H229" t="s">
         <v>327</v>
@@ -21623,7 +21614,7 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H230" t="s">
         <v>327</v>
@@ -21640,7 +21631,7 @@
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H231" t="s">
         <v>327</v>
@@ -21657,7 +21648,7 @@
         <v>2</v>
       </c>
       <c r="E232" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H232" t="s">
         <v>327</v>
@@ -21674,7 +21665,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H233" t="s">
         <v>327</v>
@@ -21691,7 +21682,7 @@
         <v>2</v>
       </c>
       <c r="E234" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H234" t="s">
         <v>327</v>
@@ -21708,7 +21699,7 @@
         <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H235" t="s">
         <v>327</v>
@@ -21725,7 +21716,7 @@
         <v>2</v>
       </c>
       <c r="E236" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H236" t="s">
         <v>327</v>
@@ -21742,7 +21733,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H237" t="s">
         <v>327</v>
@@ -21759,7 +21750,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H238" t="s">
         <v>327</v>
@@ -21776,7 +21767,7 @@
         <v>2</v>
       </c>
       <c r="E239" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H239" t="s">
         <v>327</v>
@@ -21793,7 +21784,7 @@
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H240" t="s">
         <v>327</v>
@@ -21808,7 +21799,7 @@
         <v>2</v>
       </c>
       <c r="E241" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H241" t="s">
         <v>327</v>
@@ -21823,7 +21814,7 @@
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H242" t="s">
         <v>327</v>
@@ -21838,7 +21829,7 @@
         <v>2</v>
       </c>
       <c r="E243" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H243" t="s">
         <v>327</v>
@@ -21853,7 +21844,7 @@
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H244" t="s">
         <v>327</v>
@@ -21868,7 +21859,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H245" t="s">
         <v>327</v>
@@ -21883,7 +21874,7 @@
         <v>2</v>
       </c>
       <c r="E246" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H246" t="s">
         <v>327</v>
@@ -21937,7 +21928,7 @@
         <v>35</v>
       </c>
       <c r="E250" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H250" t="s">
         <v>327</v>
@@ -21957,7 +21948,7 @@
         <v>35</v>
       </c>
       <c r="E251" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H251" t="s">
         <v>327</v>
@@ -21977,7 +21968,7 @@
         <v>35</v>
       </c>
       <c r="E252" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H252" t="s">
         <v>327</v>
@@ -21997,7 +21988,7 @@
         <v>35</v>
       </c>
       <c r="E253" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H253" t="s">
         <v>327</v>
@@ -22017,7 +22008,7 @@
         <v>35</v>
       </c>
       <c r="E254" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H254" t="s">
         <v>327</v>
@@ -22077,7 +22068,7 @@
         <v>35</v>
       </c>
       <c r="E257" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H257" t="s">
         <v>327</v>
@@ -22097,7 +22088,7 @@
         <v>35</v>
       </c>
       <c r="E258" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H258" t="s">
         <v>327</v>
@@ -22117,7 +22108,7 @@
         <v>35</v>
       </c>
       <c r="E259" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H259" t="s">
         <v>327</v>
@@ -22137,7 +22128,7 @@
         <v>35</v>
       </c>
       <c r="E260" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H260" t="s">
         <v>327</v>
@@ -22157,7 +22148,7 @@
         <v>35</v>
       </c>
       <c r="E261" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H261" t="s">
         <v>327</v>
@@ -22177,7 +22168,7 @@
         <v>35</v>
       </c>
       <c r="E262" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H262" t="s">
         <v>327</v>
@@ -22197,7 +22188,7 @@
         <v>35</v>
       </c>
       <c r="E263" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H263" t="s">
         <v>327</v>
@@ -22217,7 +22208,7 @@
         <v>35</v>
       </c>
       <c r="E264" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H264" t="s">
         <v>327</v>
@@ -22237,7 +22228,7 @@
         <v>35</v>
       </c>
       <c r="E265" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H265" t="s">
         <v>327</v>
@@ -22257,7 +22248,7 @@
         <v>35</v>
       </c>
       <c r="E266" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H266" t="s">
         <v>327</v>
@@ -22277,7 +22268,7 @@
         <v>35</v>
       </c>
       <c r="E267" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H267" t="s">
         <v>327</v>
@@ -22297,7 +22288,7 @@
         <v>35</v>
       </c>
       <c r="E268" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H268" t="s">
         <v>327</v>
@@ -22317,7 +22308,7 @@
         <v>35</v>
       </c>
       <c r="E269" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H269" t="s">
         <v>327</v>
@@ -22337,7 +22328,7 @@
         <v>35</v>
       </c>
       <c r="E270" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H270" t="s">
         <v>327</v>
@@ -22357,7 +22348,7 @@
         <v>35</v>
       </c>
       <c r="E271" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H271" t="s">
         <v>327</v>
@@ -22375,7 +22366,7 @@
         <v>35</v>
       </c>
       <c r="E272" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H272" t="s">
         <v>327</v>
@@ -22393,7 +22384,7 @@
         <v>35</v>
       </c>
       <c r="E273" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H273" t="s">
         <v>327</v>
@@ -22411,7 +22402,7 @@
         <v>35</v>
       </c>
       <c r="E274" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H274" t="s">
         <v>327</v>
@@ -22429,7 +22420,7 @@
         <v>35</v>
       </c>
       <c r="E275" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H275" t="s">
         <v>327</v>
@@ -22447,7 +22438,7 @@
         <v>35</v>
       </c>
       <c r="E276" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H276" t="s">
         <v>327</v>
@@ -22465,7 +22456,7 @@
         <v>35</v>
       </c>
       <c r="E277" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H277" t="s">
         <v>327</v>
@@ -22491,7 +22482,7 @@
       </c>
       <c r="B279" s="160"/>
       <c r="C279" s="160" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D279" s="160" t="s">
         <v>35</v>
@@ -22512,13 +22503,13 @@
         <v>2</v>
       </c>
       <c r="C280" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D280" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E280" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H280" t="s">
         <v>327</v>
@@ -22535,13 +22526,13 @@
         <v>2</v>
       </c>
       <c r="C281" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D281" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E281" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H281" t="s">
         <v>327</v>
@@ -22558,13 +22549,13 @@
         <v>2</v>
       </c>
       <c r="C282" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D282" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E282" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H282" t="s">
         <v>327</v>
@@ -22581,13 +22572,13 @@
         <v>2</v>
       </c>
       <c r="C283" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D283" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E283" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H283" t="s">
         <v>327</v>
@@ -22604,13 +22595,13 @@
         <v>2</v>
       </c>
       <c r="C284" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D284" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E284" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H284" t="s">
         <v>327</v>
@@ -22627,7 +22618,7 @@
         <v>2</v>
       </c>
       <c r="C285" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D285" s="110" t="s">
         <v>35</v>
@@ -22650,7 +22641,7 @@
         <v>2</v>
       </c>
       <c r="C286" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D286" s="110" t="s">
         <v>35</v>
@@ -22673,13 +22664,13 @@
         <v>2</v>
       </c>
       <c r="C287" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D287" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E287" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H287" t="s">
         <v>327</v>
@@ -22696,13 +22687,13 @@
         <v>2</v>
       </c>
       <c r="C288" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D288" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E288" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H288" t="s">
         <v>327</v>
@@ -22719,13 +22710,13 @@
         <v>2</v>
       </c>
       <c r="C289" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D289" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E289" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H289" t="s">
         <v>327</v>
@@ -22742,13 +22733,13 @@
         <v>2</v>
       </c>
       <c r="C290" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D290" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E290" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H290" t="s">
         <v>327</v>
@@ -22765,13 +22756,13 @@
         <v>2</v>
       </c>
       <c r="C291" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D291" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E291" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H291" t="s">
         <v>327</v>
@@ -22788,13 +22779,13 @@
         <v>2</v>
       </c>
       <c r="C292" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D292" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E292" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H292" t="s">
         <v>327</v>
@@ -22811,13 +22802,13 @@
         <v>2</v>
       </c>
       <c r="C293" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D293" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E293" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H293" t="s">
         <v>327</v>
@@ -22834,13 +22825,13 @@
         <v>2</v>
       </c>
       <c r="C294" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D294" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E294" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H294" t="s">
         <v>327</v>
@@ -22857,13 +22848,13 @@
         <v>2</v>
       </c>
       <c r="C295" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D295" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E295" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H295" t="s">
         <v>327</v>
@@ -22880,13 +22871,13 @@
         <v>2</v>
       </c>
       <c r="C296" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D296" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E296" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H296" t="s">
         <v>327</v>
@@ -22903,13 +22894,13 @@
         <v>2</v>
       </c>
       <c r="C297" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D297" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E297" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H297" t="s">
         <v>327</v>
@@ -22926,13 +22917,13 @@
         <v>2</v>
       </c>
       <c r="C298" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D298" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E298" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H298" t="s">
         <v>327</v>
@@ -22949,13 +22940,13 @@
         <v>2</v>
       </c>
       <c r="C299" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D299" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E299" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H299" t="s">
         <v>327</v>
@@ -22972,13 +22963,13 @@
         <v>2</v>
       </c>
       <c r="C300" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D300" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E300" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H300" t="s">
         <v>327</v>
@@ -22995,13 +22986,13 @@
         <v>2</v>
       </c>
       <c r="C301" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D301" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E301" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H301" t="s">
         <v>327</v>
@@ -23016,13 +23007,13 @@
         <v>2</v>
       </c>
       <c r="C302" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D302" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E302" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H302" t="s">
         <v>327</v>
@@ -23037,13 +23028,13 @@
         <v>2</v>
       </c>
       <c r="C303" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D303" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E303" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H303" t="s">
         <v>327</v>
@@ -23058,13 +23049,13 @@
         <v>2</v>
       </c>
       <c r="C304" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D304" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E304" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H304" t="s">
         <v>327</v>
@@ -23079,13 +23070,13 @@
         <v>2</v>
       </c>
       <c r="C305" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D305" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E305" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H305" t="s">
         <v>327</v>
@@ -23100,13 +23091,13 @@
         <v>2</v>
       </c>
       <c r="C306" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D306" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E306" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H306" t="s">
         <v>327</v>
@@ -23121,13 +23112,13 @@
         <v>2</v>
       </c>
       <c r="C307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D307" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E307" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H307" t="s">
         <v>327</v>
@@ -23197,7 +23188,7 @@
         <v>18</v>
       </c>
       <c r="E312" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H312" t="s">
         <v>327</v>
@@ -23217,7 +23208,7 @@
         <v>18</v>
       </c>
       <c r="E313" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H313" t="s">
         <v>327</v>
@@ -23237,7 +23228,7 @@
         <v>18</v>
       </c>
       <c r="E314" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H314" t="s">
         <v>327</v>
@@ -23257,7 +23248,7 @@
         <v>18</v>
       </c>
       <c r="E315" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H315" t="s">
         <v>327</v>
@@ -23277,7 +23268,7 @@
         <v>18</v>
       </c>
       <c r="E316" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H316" t="s">
         <v>327</v>
@@ -23337,7 +23328,7 @@
         <v>18</v>
       </c>
       <c r="E319" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H319" t="s">
         <v>327</v>
@@ -23357,7 +23348,7 @@
         <v>18</v>
       </c>
       <c r="E320" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H320" t="s">
         <v>327</v>
@@ -23377,7 +23368,7 @@
         <v>18</v>
       </c>
       <c r="E321" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H321" t="s">
         <v>327</v>
@@ -23397,7 +23388,7 @@
         <v>18</v>
       </c>
       <c r="E322" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H322" t="s">
         <v>327</v>
@@ -23417,7 +23408,7 @@
         <v>18</v>
       </c>
       <c r="E323" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H323" t="s">
         <v>327</v>
@@ -23437,7 +23428,7 @@
         <v>18</v>
       </c>
       <c r="E324" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H324" t="s">
         <v>327</v>
@@ -23457,7 +23448,7 @@
         <v>18</v>
       </c>
       <c r="E325" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H325" t="s">
         <v>327</v>
@@ -23477,7 +23468,7 @@
         <v>18</v>
       </c>
       <c r="E326" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H326" t="s">
         <v>327</v>
@@ -23497,7 +23488,7 @@
         <v>18</v>
       </c>
       <c r="E327" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H327" t="s">
         <v>327</v>
@@ -23517,7 +23508,7 @@
         <v>18</v>
       </c>
       <c r="E328" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H328" t="s">
         <v>327</v>
@@ -23537,7 +23528,7 @@
         <v>18</v>
       </c>
       <c r="E329" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H329" t="s">
         <v>327</v>
@@ -23557,7 +23548,7 @@
         <v>18</v>
       </c>
       <c r="E330" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H330" t="s">
         <v>327</v>
@@ -23577,7 +23568,7 @@
         <v>18</v>
       </c>
       <c r="E331" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H331" t="s">
         <v>327</v>
@@ -23597,7 +23588,7 @@
         <v>18</v>
       </c>
       <c r="E332" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H332" t="s">
         <v>327</v>
@@ -23617,7 +23608,7 @@
         <v>18</v>
       </c>
       <c r="E333" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H333" t="s">
         <v>327</v>
@@ -23635,7 +23626,7 @@
         <v>18</v>
       </c>
       <c r="E334" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H334" t="s">
         <v>327</v>
@@ -23653,7 +23644,7 @@
         <v>18</v>
       </c>
       <c r="E335" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H335" t="s">
         <v>327</v>
@@ -23671,7 +23662,7 @@
         <v>18</v>
       </c>
       <c r="E336" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H336" t="s">
         <v>327</v>
@@ -23689,7 +23680,7 @@
         <v>18</v>
       </c>
       <c r="E337" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H337" t="s">
         <v>327</v>
@@ -23707,7 +23698,7 @@
         <v>18</v>
       </c>
       <c r="E338" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H338" t="s">
         <v>327</v>
@@ -23725,7 +23716,7 @@
         <v>18</v>
       </c>
       <c r="E339" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H339" t="s">
         <v>327</v>
@@ -23737,7 +23728,7 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" s="91" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B341" s="164"/>
       <c r="C341" s="164"/>
@@ -23774,7 +23765,7 @@
         <v>39</v>
       </c>
       <c r="E343" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H343" t="s">
         <v>327</v>
@@ -23791,7 +23782,7 @@
         <v>39</v>
       </c>
       <c r="E344" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H344" t="s">
         <v>327</v>
@@ -23808,7 +23799,7 @@
         <v>39</v>
       </c>
       <c r="E345" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H345" t="s">
         <v>327</v>
@@ -23825,7 +23816,7 @@
         <v>39</v>
       </c>
       <c r="E346" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H346" t="s">
         <v>327</v>
@@ -23842,7 +23833,7 @@
         <v>39</v>
       </c>
       <c r="E347" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H347" t="s">
         <v>327</v>
@@ -23893,7 +23884,7 @@
         <v>39</v>
       </c>
       <c r="E350" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H350" t="s">
         <v>327</v>
@@ -23910,7 +23901,7 @@
         <v>39</v>
       </c>
       <c r="E351" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H351" t="s">
         <v>327</v>
@@ -23927,7 +23918,7 @@
         <v>39</v>
       </c>
       <c r="E352" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H352" t="s">
         <v>327</v>
@@ -23944,7 +23935,7 @@
         <v>39</v>
       </c>
       <c r="E353" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H353" t="s">
         <v>327</v>
@@ -23961,7 +23952,7 @@
         <v>39</v>
       </c>
       <c r="E354" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H354" t="s">
         <v>327</v>
@@ -23978,7 +23969,7 @@
         <v>39</v>
       </c>
       <c r="E355" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H355" t="s">
         <v>327</v>
@@ -23995,7 +23986,7 @@
         <v>39</v>
       </c>
       <c r="E356" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H356" t="s">
         <v>327</v>
@@ -24012,7 +24003,7 @@
         <v>39</v>
       </c>
       <c r="E357" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H357" t="s">
         <v>327</v>
@@ -24029,7 +24020,7 @@
         <v>39</v>
       </c>
       <c r="E358" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H358" t="s">
         <v>327</v>
@@ -24046,7 +24037,7 @@
         <v>39</v>
       </c>
       <c r="E359" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H359" t="s">
         <v>327</v>
@@ -24063,7 +24054,7 @@
         <v>39</v>
       </c>
       <c r="E360" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H360" t="s">
         <v>327</v>
@@ -24080,7 +24071,7 @@
         <v>39</v>
       </c>
       <c r="E361" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H361" t="s">
         <v>327</v>
@@ -24097,7 +24088,7 @@
         <v>39</v>
       </c>
       <c r="E362" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H362" t="s">
         <v>327</v>
@@ -24114,7 +24105,7 @@
         <v>39</v>
       </c>
       <c r="E363" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H363" t="s">
         <v>327</v>
@@ -24131,7 +24122,7 @@
         <v>39</v>
       </c>
       <c r="E364" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H364" t="s">
         <v>327</v>
@@ -24146,7 +24137,7 @@
         <v>39</v>
       </c>
       <c r="E365" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H365" t="s">
         <v>327</v>
@@ -24161,7 +24152,7 @@
         <v>39</v>
       </c>
       <c r="E366" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H366" t="s">
         <v>327</v>
@@ -24176,7 +24167,7 @@
         <v>39</v>
       </c>
       <c r="E367" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H367" t="s">
         <v>327</v>
@@ -24191,7 +24182,7 @@
         <v>39</v>
       </c>
       <c r="E368" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H368" t="s">
         <v>327</v>
@@ -24206,7 +24197,7 @@
         <v>39</v>
       </c>
       <c r="E369" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H369" t="s">
         <v>327</v>
@@ -24221,7 +24212,7 @@
         <v>39</v>
       </c>
       <c r="E370" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H370" t="s">
         <v>327</v>
@@ -24275,7 +24266,7 @@
         <v>35</v>
       </c>
       <c r="E374" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H374" t="s">
         <v>327</v>
@@ -24295,7 +24286,7 @@
         <v>35</v>
       </c>
       <c r="E375" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H375" t="s">
         <v>327</v>
@@ -24315,7 +24306,7 @@
         <v>35</v>
       </c>
       <c r="E376" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H376" t="s">
         <v>327</v>
@@ -24335,7 +24326,7 @@
         <v>35</v>
       </c>
       <c r="E377" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H377" t="s">
         <v>327</v>
@@ -24355,7 +24346,7 @@
         <v>35</v>
       </c>
       <c r="E378" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H378" t="s">
         <v>327</v>
@@ -24415,7 +24406,7 @@
         <v>35</v>
       </c>
       <c r="E381" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H381" t="s">
         <v>327</v>
@@ -24435,7 +24426,7 @@
         <v>35</v>
       </c>
       <c r="E382" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H382" t="s">
         <v>327</v>
@@ -24455,7 +24446,7 @@
         <v>35</v>
       </c>
       <c r="E383" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H383" t="s">
         <v>327</v>
@@ -24475,7 +24466,7 @@
         <v>35</v>
       </c>
       <c r="E384" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H384" t="s">
         <v>327</v>
@@ -24495,7 +24486,7 @@
         <v>35</v>
       </c>
       <c r="E385" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H385" t="s">
         <v>327</v>
@@ -24515,7 +24506,7 @@
         <v>35</v>
       </c>
       <c r="E386" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H386" t="s">
         <v>327</v>
@@ -24535,7 +24526,7 @@
         <v>35</v>
       </c>
       <c r="E387" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H387" t="s">
         <v>327</v>
@@ -24555,7 +24546,7 @@
         <v>35</v>
       </c>
       <c r="E388" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H388" t="s">
         <v>327</v>
@@ -24575,7 +24566,7 @@
         <v>35</v>
       </c>
       <c r="E389" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H389" t="s">
         <v>327</v>
@@ -24595,7 +24586,7 @@
         <v>35</v>
       </c>
       <c r="E390" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H390" t="s">
         <v>327</v>
@@ -24615,7 +24606,7 @@
         <v>35</v>
       </c>
       <c r="E391" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H391" t="s">
         <v>327</v>
@@ -24635,7 +24626,7 @@
         <v>35</v>
       </c>
       <c r="E392" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H392" t="s">
         <v>327</v>
@@ -24655,7 +24646,7 @@
         <v>35</v>
       </c>
       <c r="E393" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H393" t="s">
         <v>327</v>
@@ -24675,7 +24666,7 @@
         <v>35</v>
       </c>
       <c r="E394" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H394" t="s">
         <v>327</v>
@@ -24695,7 +24686,7 @@
         <v>35</v>
       </c>
       <c r="E395" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H395" t="s">
         <v>327</v>
@@ -24713,7 +24704,7 @@
         <v>35</v>
       </c>
       <c r="E396" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H396" t="s">
         <v>327</v>
@@ -24731,7 +24722,7 @@
         <v>35</v>
       </c>
       <c r="E397" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H397" t="s">
         <v>327</v>
@@ -24749,7 +24740,7 @@
         <v>35</v>
       </c>
       <c r="E398" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H398" t="s">
         <v>327</v>
@@ -24767,7 +24758,7 @@
         <v>35</v>
       </c>
       <c r="E399" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H399" t="s">
         <v>327</v>
@@ -24785,7 +24776,7 @@
         <v>35</v>
       </c>
       <c r="E400" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H400" t="s">
         <v>327</v>
@@ -24803,7 +24794,7 @@
         <v>35</v>
       </c>
       <c r="E401" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H401" t="s">
         <v>327</v>
@@ -24823,7 +24814,7 @@
       </c>
       <c r="B403" s="160"/>
       <c r="C403" s="160" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D403" s="160" t="s">
         <v>35</v>
@@ -24844,13 +24835,13 @@
         <v>39</v>
       </c>
       <c r="C404" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D404" t="s">
         <v>35</v>
       </c>
       <c r="E404" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H404" t="s">
         <v>327</v>
@@ -24867,13 +24858,13 @@
         <v>39</v>
       </c>
       <c r="C405" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D405" t="s">
         <v>35</v>
       </c>
       <c r="E405" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H405" t="s">
         <v>327</v>
@@ -24890,13 +24881,13 @@
         <v>39</v>
       </c>
       <c r="C406" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D406" t="s">
         <v>35</v>
       </c>
       <c r="E406" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H406" t="s">
         <v>327</v>
@@ -24913,13 +24904,13 @@
         <v>39</v>
       </c>
       <c r="C407" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D407" t="s">
         <v>35</v>
       </c>
       <c r="E407" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H407" t="s">
         <v>327</v>
@@ -24936,13 +24927,13 @@
         <v>39</v>
       </c>
       <c r="C408" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D408" t="s">
         <v>35</v>
       </c>
       <c r="E408" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H408" t="s">
         <v>327</v>
@@ -24959,7 +24950,7 @@
         <v>39</v>
       </c>
       <c r="C409" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D409" t="s">
         <v>35</v>
@@ -24982,7 +24973,7 @@
         <v>39</v>
       </c>
       <c r="C410" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D410" t="s">
         <v>35</v>
@@ -25005,13 +24996,13 @@
         <v>39</v>
       </c>
       <c r="C411" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D411" t="s">
         <v>35</v>
       </c>
       <c r="E411" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H411" t="s">
         <v>327</v>
@@ -25028,13 +25019,13 @@
         <v>39</v>
       </c>
       <c r="C412" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D412" t="s">
         <v>35</v>
       </c>
       <c r="E412" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H412" t="s">
         <v>327</v>
@@ -25051,13 +25042,13 @@
         <v>39</v>
       </c>
       <c r="C413" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D413" t="s">
         <v>35</v>
       </c>
       <c r="E413" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H413" t="s">
         <v>327</v>
@@ -25074,13 +25065,13 @@
         <v>39</v>
       </c>
       <c r="C414" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D414" t="s">
         <v>35</v>
       </c>
       <c r="E414" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H414" t="s">
         <v>327</v>
@@ -25097,13 +25088,13 @@
         <v>39</v>
       </c>
       <c r="C415" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D415" t="s">
         <v>35</v>
       </c>
       <c r="E415" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H415" t="s">
         <v>327</v>
@@ -25120,13 +25111,13 @@
         <v>39</v>
       </c>
       <c r="C416" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D416" t="s">
         <v>35</v>
       </c>
       <c r="E416" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H416" t="s">
         <v>327</v>
@@ -25143,13 +25134,13 @@
         <v>39</v>
       </c>
       <c r="C417" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D417" t="s">
         <v>35</v>
       </c>
       <c r="E417" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H417" t="s">
         <v>327</v>
@@ -25166,13 +25157,13 @@
         <v>39</v>
       </c>
       <c r="C418" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D418" t="s">
         <v>35</v>
       </c>
       <c r="E418" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H418" t="s">
         <v>327</v>
@@ -25189,13 +25180,13 @@
         <v>39</v>
       </c>
       <c r="C419" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D419" t="s">
         <v>35</v>
       </c>
       <c r="E419" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H419" t="s">
         <v>327</v>
@@ -25212,13 +25203,13 @@
         <v>39</v>
       </c>
       <c r="C420" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D420" t="s">
         <v>35</v>
       </c>
       <c r="E420" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H420" t="s">
         <v>327</v>
@@ -25235,13 +25226,13 @@
         <v>39</v>
       </c>
       <c r="C421" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D421" t="s">
         <v>35</v>
       </c>
       <c r="E421" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H421" t="s">
         <v>327</v>
@@ -25258,13 +25249,13 @@
         <v>39</v>
       </c>
       <c r="C422" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D422" t="s">
         <v>35</v>
       </c>
       <c r="E422" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H422" t="s">
         <v>327</v>
@@ -25281,13 +25272,13 @@
         <v>39</v>
       </c>
       <c r="C423" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D423" t="s">
         <v>35</v>
       </c>
       <c r="E423" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H423" t="s">
         <v>327</v>
@@ -25304,13 +25295,13 @@
         <v>39</v>
       </c>
       <c r="C424" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D424" t="s">
         <v>35</v>
       </c>
       <c r="E424" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H424" t="s">
         <v>327</v>
@@ -25327,13 +25318,13 @@
         <v>39</v>
       </c>
       <c r="C425" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D425" t="s">
         <v>35</v>
       </c>
       <c r="E425" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H425" t="s">
         <v>327</v>
@@ -25348,13 +25339,13 @@
         <v>39</v>
       </c>
       <c r="C426" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D426" t="s">
         <v>35</v>
       </c>
       <c r="E426" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H426" t="s">
         <v>327</v>
@@ -25369,13 +25360,13 @@
         <v>39</v>
       </c>
       <c r="C427" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D427" t="s">
         <v>35</v>
       </c>
       <c r="E427" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H427" t="s">
         <v>327</v>
@@ -25390,13 +25381,13 @@
         <v>39</v>
       </c>
       <c r="C428" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D428" t="s">
         <v>35</v>
       </c>
       <c r="E428" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H428" t="s">
         <v>327</v>
@@ -25411,13 +25402,13 @@
         <v>39</v>
       </c>
       <c r="C429" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D429" t="s">
         <v>35</v>
       </c>
       <c r="E429" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H429" t="s">
         <v>327</v>
@@ -25432,13 +25423,13 @@
         <v>39</v>
       </c>
       <c r="C430" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D430" t="s">
         <v>35</v>
       </c>
       <c r="E430" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H430" t="s">
         <v>327</v>
@@ -25453,13 +25444,13 @@
         <v>39</v>
       </c>
       <c r="C431" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D431" t="s">
         <v>35</v>
       </c>
       <c r="E431" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H431" t="s">
         <v>327</v>
@@ -25469,395 +25460,159 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J432" s="160"/>
-      <c r="K432" s="160"/>
-    </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A433" s="94" t="s">
-        <v>430</v>
-      </c>
-      <c r="B433" s="94"/>
-      <c r="C433" s="94"/>
+      <c r="A433" s="159" t="s">
+        <v>306</v>
+      </c>
+      <c r="B433" s="159"/>
+      <c r="C433" s="159"/>
       <c r="D433" s="95"/>
       <c r="E433" s="95"/>
       <c r="F433" s="95"/>
       <c r="G433" s="95"/>
       <c r="H433" s="95"/>
       <c r="I433" s="95"/>
-      <c r="J433" s="95" t="s">
-        <v>9</v>
-      </c>
-      <c r="K433" s="95" t="s">
-        <v>432</v>
-      </c>
+      <c r="J433" s="95"/>
+      <c r="K433" s="95"/>
       <c r="L433" s="95"/>
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A434" s="97" t="s">
-        <v>304</v>
-      </c>
-      <c r="B434" s="97"/>
-      <c r="C434" s="97"/>
-      <c r="D434" s="98"/>
-      <c r="E434" s="98"/>
-      <c r="F434" s="98"/>
-      <c r="G434" s="98"/>
-      <c r="H434" s="98"/>
-      <c r="I434" s="99"/>
-      <c r="J434" s="98"/>
-      <c r="K434" s="98"/>
-      <c r="L434" s="98"/>
+      <c r="A434" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D434" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E434" s="93"/>
+      <c r="F434" s="93"/>
+      <c r="G434" s="93"/>
+      <c r="H434" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="I434" s="93">
+        <v>7.1</v>
+      </c>
+      <c r="J434" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="K434" s="93"/>
+      <c r="L434" s="93" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
-        <v>2</v>
-      </c>
-      <c r="D435" t="s">
+      <c r="A435" s="93" t="s">
+        <v>39</v>
+      </c>
+      <c r="D435" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="H435" t="s">
-        <v>431</v>
+      <c r="E435" s="93"/>
+      <c r="F435" s="93"/>
+      <c r="G435" s="93"/>
+      <c r="H435" s="93" t="s">
+        <v>41</v>
       </c>
       <c r="I435" s="93">
-        <v>5</v>
-      </c>
-      <c r="J435" s="93"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J435" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="K435" s="93"/>
+      <c r="L435" s="93" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
-        <v>2</v>
-      </c>
-      <c r="D436" t="s">
+      <c r="A436" s="93"/>
+      <c r="D436" s="93" t="s">
+        <v>33</v>
+      </c>
+      <c r="E436" s="93"/>
+      <c r="F436" s="93"/>
+      <c r="G436" s="93"/>
+      <c r="H436" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="I436" s="93">
+        <v>5.7</v>
+      </c>
+      <c r="J436" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="K436" s="93"/>
+      <c r="L436" s="93" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A437" s="93"/>
+      <c r="D437" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="H436" t="s">
-        <v>431</v>
-      </c>
-      <c r="I436" s="93">
-        <v>5</v>
-      </c>
-      <c r="J436" s="93"/>
-    </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A437" t="s">
-        <v>2</v>
-      </c>
-      <c r="D437" t="s">
+      <c r="E437" s="93"/>
+      <c r="F437" s="93"/>
+      <c r="G437" s="93"/>
+      <c r="H437" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="I437" s="93">
+        <v>7.7</v>
+      </c>
+      <c r="J437" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="K437" s="93"/>
+      <c r="L437" s="93" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A438" s="93"/>
+      <c r="D438" s="93" t="s">
+        <v>34</v>
+      </c>
+      <c r="E438" s="93"/>
+      <c r="F438" s="93"/>
+      <c r="G438" s="93"/>
+      <c r="H438" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="I438" s="93">
+        <v>9.1</v>
+      </c>
+      <c r="J438" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="K438" s="93" t="s">
+        <v>43</v>
+      </c>
+      <c r="L438" s="93" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A439" s="93"/>
+      <c r="D439" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="H437" t="s">
-        <v>431</v>
-      </c>
-      <c r="I437" s="93">
-        <v>0</v>
-      </c>
-      <c r="J437" s="93"/>
-    </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
-        <v>2</v>
-      </c>
-      <c r="D438" t="s">
-        <v>33</v>
-      </c>
-      <c r="H438" t="s">
-        <v>431</v>
-      </c>
-      <c r="I438" s="93">
-        <v>100</v>
-      </c>
-      <c r="J438" s="93"/>
-    </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
-        <v>2</v>
-      </c>
-      <c r="D439" t="s">
-        <v>34</v>
-      </c>
-      <c r="H439" t="s">
-        <v>431</v>
+      <c r="E439" s="93"/>
+      <c r="F439" s="93"/>
+      <c r="G439" s="93"/>
+      <c r="H439" s="93" t="s">
+        <v>41</v>
       </c>
       <c r="I439" s="93">
-        <v>100</v>
-      </c>
-      <c r="J439" s="93"/>
-    </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
-        <v>2</v>
-      </c>
-      <c r="D440" t="s">
-        <v>429</v>
-      </c>
-      <c r="H440" t="s">
-        <v>431</v>
-      </c>
-      <c r="I440" s="93">
-        <v>0</v>
-      </c>
-      <c r="J440" s="93"/>
-    </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A442" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="B442" s="100"/>
-      <c r="C442" s="100"/>
-      <c r="D442" s="101"/>
-      <c r="E442" s="101"/>
-      <c r="F442" s="101"/>
-      <c r="G442" s="101"/>
-      <c r="H442" s="101"/>
-      <c r="I442" s="101"/>
-      <c r="J442" s="101"/>
-      <c r="K442" s="101"/>
-      <c r="L442" s="101"/>
-    </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
-        <v>39</v>
-      </c>
-      <c r="D443" t="s">
-        <v>18</v>
-      </c>
-      <c r="H443" t="s">
-        <v>431</v>
-      </c>
-      <c r="I443" s="93">
-        <v>100</v>
-      </c>
-      <c r="J443" s="93"/>
-    </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A444" t="s">
-        <v>39</v>
-      </c>
-      <c r="D444" t="s">
-        <v>20</v>
-      </c>
-      <c r="H444" t="s">
-        <v>431</v>
-      </c>
-      <c r="I444" s="93">
-        <v>100</v>
-      </c>
-      <c r="J444" s="93"/>
-    </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
-        <v>39</v>
-      </c>
-      <c r="D445" t="s">
-        <v>35</v>
-      </c>
-      <c r="H445" t="s">
-        <v>431</v>
-      </c>
-      <c r="I445" s="93">
-        <v>0</v>
-      </c>
-      <c r="J445" s="93"/>
-    </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A446" t="s">
-        <v>39</v>
-      </c>
-      <c r="D446" t="s">
-        <v>33</v>
-      </c>
-      <c r="H446" t="s">
-        <v>431</v>
-      </c>
-      <c r="I446" s="93">
-        <v>100</v>
-      </c>
-      <c r="J446" s="93"/>
-    </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
-        <v>39</v>
-      </c>
-      <c r="D447" t="s">
-        <v>34</v>
-      </c>
-      <c r="H447" t="s">
-        <v>431</v>
-      </c>
-      <c r="I447" s="93">
-        <v>100</v>
-      </c>
-      <c r="J447" s="93"/>
-    </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
-        <v>39</v>
-      </c>
-      <c r="D448" t="s">
-        <v>429</v>
-      </c>
-      <c r="H448" t="s">
-        <v>431</v>
-      </c>
-      <c r="I448" s="93">
-        <v>100</v>
-      </c>
-      <c r="J448" s="93"/>
-    </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A450" s="159" t="s">
-        <v>306</v>
-      </c>
-      <c r="B450" s="159"/>
-      <c r="C450" s="159"/>
-      <c r="D450" s="95"/>
-      <c r="E450" s="95"/>
-      <c r="F450" s="95"/>
-      <c r="G450" s="95"/>
-      <c r="H450" s="95"/>
-      <c r="I450" s="95"/>
-      <c r="J450" s="95"/>
-      <c r="K450" s="95"/>
-      <c r="L450" s="95"/>
-    </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A451" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="D451" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="E451" s="93"/>
-      <c r="F451" s="93"/>
-      <c r="G451" s="93"/>
-      <c r="H451" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="I451" s="93">
-        <v>7.1</v>
-      </c>
-      <c r="J451" s="93" t="s">
+        <v>9.1</v>
+      </c>
+      <c r="J439" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K451" s="93"/>
-      <c r="L451" s="93" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A452" s="93" t="s">
-        <v>39</v>
-      </c>
-      <c r="D452" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="E452" s="93"/>
-      <c r="F452" s="93"/>
-      <c r="G452" s="93"/>
-      <c r="H452" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="I452" s="93">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="J452" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="K452" s="93"/>
-      <c r="L452" s="93" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A453" s="93"/>
-      <c r="D453" s="93" t="s">
-        <v>33</v>
-      </c>
-      <c r="E453" s="93"/>
-      <c r="F453" s="93"/>
-      <c r="G453" s="93"/>
-      <c r="H453" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="I453" s="93">
-        <v>5.7</v>
-      </c>
-      <c r="J453" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="K453" s="93"/>
-      <c r="L453" s="93" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A454" s="93"/>
-      <c r="D454" s="93" t="s">
-        <v>20</v>
-      </c>
-      <c r="E454" s="93"/>
-      <c r="F454" s="93"/>
-      <c r="G454" s="93"/>
-      <c r="H454" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="I454" s="93">
-        <v>7.7</v>
-      </c>
-      <c r="J454" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="K454" s="93"/>
-      <c r="L454" s="93" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A455" s="93"/>
-      <c r="D455" s="93" t="s">
-        <v>34</v>
-      </c>
-      <c r="E455" s="93"/>
-      <c r="F455" s="93"/>
-      <c r="G455" s="93"/>
-      <c r="H455" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="I455" s="93">
-        <v>9.1</v>
-      </c>
-      <c r="J455" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="K455" s="93" t="s">
+      <c r="K439" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="L455" s="93" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A456" s="93"/>
-      <c r="D456" s="93" t="s">
-        <v>35</v>
-      </c>
-      <c r="E456" s="93"/>
-      <c r="F456" s="93"/>
-      <c r="G456" s="93"/>
-      <c r="H456" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="I456" s="93">
-        <v>9.1</v>
-      </c>
-      <c r="J456" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="K456" s="93" t="s">
-        <v>43</v>
-      </c>
-      <c r="L456" s="93" t="s">
+      <c r="L439" s="93" t="s">
         <v>42</v>
       </c>
     </row>
@@ -32046,10 +31801,10 @@
   <sheetData>
     <row r="2" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B2" s="179" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C2" s="179" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D2" s="179"/>
       <c r="E2" s="179"/>
@@ -32072,7 +31827,7 @@
       <c r="V2" s="179"/>
       <c r="W2" s="179"/>
       <c r="X2" s="179" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="Y2" s="179"/>
       <c r="AA2" s="191"/>
@@ -32080,7 +31835,7 @@
     <row r="3" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B3" s="179"/>
       <c r="C3" s="83" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D3" s="172"/>
       <c r="E3" s="172"/>
@@ -32091,7 +31846,7 @@
       <c r="J3" s="172"/>
       <c r="K3" s="172"/>
       <c r="L3" s="83" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="M3" s="172"/>
       <c r="N3" s="172"/>
@@ -32099,7 +31854,7 @@
       <c r="P3" s="172"/>
       <c r="Q3" s="172"/>
       <c r="R3" s="83" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="S3" s="172"/>
       <c r="T3" s="172"/>
@@ -32107,7 +31862,7 @@
       <c r="V3" s="172"/>
       <c r="W3" s="172"/>
       <c r="X3" s="194" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="Y3" s="83"/>
       <c r="AA3" s="192"/>
@@ -32115,127 +31870,127 @@
     <row r="4" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B4" s="172"/>
       <c r="C4" s="101" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D4" s="101"/>
       <c r="E4" s="101"/>
       <c r="F4" s="169" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G4" s="169"/>
       <c r="H4" s="169"/>
       <c r="I4" s="101" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J4" s="101"/>
       <c r="K4" s="101"/>
       <c r="L4" s="169" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M4" s="169"/>
       <c r="N4" s="169"/>
       <c r="O4" s="101" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="P4" s="101"/>
       <c r="Q4" s="101"/>
       <c r="R4" s="169" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="S4" s="169"/>
       <c r="T4" s="169"/>
       <c r="U4" s="101" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="V4" s="101"/>
       <c r="W4" s="101"/>
       <c r="X4" s="169" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="Y4" s="101" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AA4" s="32"/>
     </row>
     <row r="5" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="172"/>
       <c r="C5" s="101" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D5" s="101" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E5" s="101" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F5" s="169" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G5" s="169" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H5" s="169" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I5" s="101" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J5" s="101" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K5" s="101" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L5" s="169" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="M5" s="169" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N5" s="169" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="O5" s="101" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="P5" s="101" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q5" s="101" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="R5" s="169" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="S5" s="169" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="T5" s="169" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="U5" s="101" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V5" s="101" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="W5" s="101" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="X5" s="169" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="Y5" s="101" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AA5" s="32"/>
       <c r="AF5" s="173" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="172" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C6" s="169"/>
       <c r="D6" s="169"/>
@@ -32279,7 +32034,7 @@
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B7" s="172" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C7" s="169"/>
       <c r="D7" s="169"/>
@@ -32333,7 +32088,7 @@
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B8" s="172" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C8" s="169">
         <v>659</v>
@@ -32373,7 +32128,7 @@
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B9" s="172" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C9" s="169"/>
       <c r="D9" s="169"/>
@@ -32409,7 +32164,7 @@
     </row>
     <row r="10" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B10" s="172" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C10" s="169"/>
       <c r="D10" s="169"/>
@@ -32447,7 +32202,7 @@
     </row>
     <row r="11" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B11" s="172" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C11" s="169">
         <v>977</v>
@@ -32487,7 +32242,7 @@
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B12" s="172" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C12" s="169"/>
       <c r="D12" s="169">
@@ -32527,7 +32282,7 @@
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B13" s="172" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C13" s="169">
         <v>1953</v>
@@ -32589,7 +32344,7 @@
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B14" s="172" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C14" s="169">
         <v>345</v>
@@ -32655,7 +32410,7 @@
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B15" s="172" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C15" s="169"/>
       <c r="D15" s="169"/>
@@ -32703,7 +32458,7 @@
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B16" s="172" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C16" s="169"/>
       <c r="D16" s="169"/>
@@ -32747,7 +32502,7 @@
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B17" s="172" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C17" s="169"/>
       <c r="D17" s="169"/>
@@ -32797,7 +32552,7 @@
     </row>
     <row r="18" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B18" s="172" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C18" s="169">
         <v>34</v>
@@ -32910,66 +32665,66 @@
         <v>3100</v>
       </c>
       <c r="L19" s="170">
-        <f>SUM(L6:L18)</f>
+        <f t="shared" ref="L19:Y19" si="1">SUM(L6:L18)</f>
         <v>3429</v>
       </c>
       <c r="M19" s="170">
-        <f>SUM(M6:M18)</f>
+        <f t="shared" si="1"/>
         <v>3451</v>
       </c>
       <c r="N19" s="170">
-        <f>SUM(N6:N18)</f>
+        <f t="shared" si="1"/>
         <v>3430</v>
       </c>
       <c r="O19" s="171">
-        <f>SUM(O6:O18)</f>
+        <f t="shared" si="1"/>
         <v>4830</v>
       </c>
       <c r="P19" s="171">
-        <f>SUM(P6:P18)</f>
+        <f t="shared" si="1"/>
         <v>4857</v>
       </c>
       <c r="Q19" s="171">
-        <f>SUM(Q6:Q18)</f>
+        <f t="shared" si="1"/>
         <v>4840</v>
       </c>
       <c r="R19" s="170">
-        <f>SUM(R6:R18)</f>
+        <f t="shared" si="1"/>
         <v>3691</v>
       </c>
       <c r="S19" s="170">
-        <f>SUM(S6:S18)</f>
+        <f t="shared" si="1"/>
         <v>3699</v>
       </c>
       <c r="T19" s="170">
-        <f>SUM(T6:T18)</f>
+        <f t="shared" si="1"/>
         <v>3544</v>
       </c>
       <c r="U19" s="171">
-        <f>SUM(U6:U18)</f>
+        <f t="shared" si="1"/>
         <v>3621</v>
       </c>
       <c r="V19" s="171">
-        <f>SUM(V6:V18)</f>
+        <f t="shared" si="1"/>
         <v>3636</v>
       </c>
       <c r="W19" s="171">
-        <f>SUM(W6:W18)</f>
+        <f t="shared" si="1"/>
         <v>3544</v>
       </c>
       <c r="X19" s="170">
-        <f>SUM(X6:X18)</f>
+        <f t="shared" si="1"/>
         <v>7692.9025000000001</v>
       </c>
       <c r="Y19" s="171">
-        <f>SUM(Y6:Y18)</f>
+        <f t="shared" si="1"/>
         <v>7692.3894999999993</v>
       </c>
       <c r="AA19" s="193"/>
     </row>
     <row r="21" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B21" s="172" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C21" s="185">
         <v>103131</v>
@@ -33003,7 +32758,7 @@
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B22" s="172" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C22" s="185">
         <v>87632</v>
@@ -33037,10 +32792,10 @@
     </row>
     <row r="24" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B24" s="179" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C24" s="83" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D24" s="172"/>
       <c r="E24" s="172"/>
@@ -33049,12 +32804,12 @@
       <c r="H24" s="172"/>
       <c r="I24" s="172"/>
       <c r="M24" s="179" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N24" s="83"/>
       <c r="O24" s="83"/>
       <c r="P24" s="83" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="Q24" s="172"/>
       <c r="R24" s="172"/>
@@ -33064,25 +32819,25 @@
     </row>
     <row r="25" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B25" s="179" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C25" s="169"/>
       <c r="D25" s="169" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E25" s="101"/>
       <c r="F25" s="101" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G25" s="169"/>
       <c r="H25" s="169" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I25" s="101" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M25" s="179" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N25" s="172"/>
       <c r="O25" s="172"/>
@@ -33090,51 +32845,51 @@
         <v>304</v>
       </c>
       <c r="Q25" s="169" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="R25" s="101" t="s">
         <v>305</v>
       </c>
       <c r="S25" s="101" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="T25" s="169" t="s">
         <v>317</v>
       </c>
       <c r="U25" s="169" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B26" s="83" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C26" s="169" t="s">
         <v>304</v>
       </c>
       <c r="D26" s="169" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E26" s="101" t="s">
         <v>305</v>
       </c>
       <c r="F26" s="101" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G26" s="169" t="s">
         <v>317</v>
       </c>
       <c r="H26" s="169" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="I26" s="101" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="K26" s="173" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="M26" s="172" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N26" s="172"/>
       <c r="O26" s="172"/>
@@ -33163,7 +32918,7 @@
     </row>
     <row r="27" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B27" s="172" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C27" s="92">
         <f>G27*H27</f>
@@ -33194,12 +32949,12 @@
         <v>0.87</v>
       </c>
       <c r="M27" s="172" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="N27" s="172"/>
       <c r="O27" s="172"/>
       <c r="P27" s="92">
-        <f t="shared" ref="P27:P29" si="1">T27*U27</f>
+        <f t="shared" ref="P27:P29" si="2">T27*U27</f>
         <v>61792.549779753324</v>
       </c>
       <c r="Q27" s="175">
@@ -33207,7 +32962,7 @@
         <v>0.18593732139754057</v>
       </c>
       <c r="R27" s="176">
-        <f t="shared" ref="R27:R29" si="2">T27-P27</f>
+        <f t="shared" ref="R27:R29" si="3">T27-P27</f>
         <v>37795.451708713757</v>
       </c>
       <c r="S27" s="177">
@@ -33223,22 +32978,22 @@
     </row>
     <row r="28" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B28" s="172" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C28" s="92">
-        <f t="shared" ref="C28:C33" si="3">G28*H28</f>
+        <f t="shared" ref="C28:C33" si="4">G28*H28</f>
         <v>38739.785795838885</v>
       </c>
       <c r="D28" s="175">
-        <f t="shared" ref="D28:D33" si="4">C28*K28/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" ref="D28:D33" si="5">C28*K28/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
         <v>5.140953744803383E-2</v>
       </c>
       <c r="E28" s="176">
-        <f t="shared" ref="E28:E33" si="5">G28-C28</f>
+        <f t="shared" ref="E28:E33" si="6">G28-C28</f>
         <v>23695.214204161115</v>
       </c>
       <c r="F28" s="177">
-        <f t="shared" ref="F28:F33" si="6">E28*$K28/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" ref="F28:F33" si="7">E28*$K28/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
         <v>0.17513002162161409</v>
       </c>
       <c r="G28" s="92">
@@ -33254,12 +33009,12 @@
         <v>0.87</v>
       </c>
       <c r="M28" s="172" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="N28" s="172"/>
       <c r="O28" s="172"/>
       <c r="P28" s="92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>159717.72580047889</v>
       </c>
       <c r="Q28" s="175">
@@ -33267,7 +33022,7 @@
         <v>0.48059978461640451</v>
       </c>
       <c r="R28" s="176">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>97691.446849722182</v>
       </c>
       <c r="S28" s="177">
@@ -33283,22 +33038,22 @@
     </row>
     <row r="29" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B29" s="172" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C29" s="92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21059.030703189121</v>
       </c>
       <c r="D29" s="175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.7946334893549748E-2</v>
       </c>
       <c r="E29" s="176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12880.769296810882</v>
       </c>
       <c r="F29" s="177">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.5201055623180236E-2</v>
       </c>
       <c r="G29" s="92">
@@ -33314,12 +33069,12 @@
         <v>0.87</v>
       </c>
       <c r="M29" s="172" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="N29" s="172"/>
       <c r="O29" s="172"/>
       <c r="P29" s="92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33007.100971752872</v>
       </c>
       <c r="Q29" s="175">
@@ -33327,7 +33082,7 @@
         <v>9.9320257274717494E-2</v>
       </c>
       <c r="R29" s="176">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20188.81394713511</v>
       </c>
       <c r="S29" s="177">
@@ -33343,22 +33098,22 @@
     </row>
     <row r="30" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B30" s="172" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C30" s="92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>68413.87639421731</v>
       </c>
       <c r="D30" s="175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.0788466384123717E-2</v>
       </c>
       <c r="E30" s="176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>41845.390272449687</v>
       </c>
       <c r="F30" s="177">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.30927697213608885</v>
       </c>
       <c r="G30" s="92">
@@ -33376,22 +33131,22 @@
     </row>
     <row r="31" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B31" s="172" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C31" s="92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14138.341343739448</v>
       </c>
       <c r="D31" s="175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8762251102641098E-2</v>
       </c>
       <c r="E31" s="176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8647.7253229272501</v>
       </c>
       <c r="F31" s="177">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.3914861023542546E-2</v>
       </c>
       <c r="G31" s="92">
@@ -33409,22 +33164,22 @@
     </row>
     <row r="32" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B32" s="172" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C32" s="92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4095.4809354661024</v>
       </c>
       <c r="D32" s="175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.4348979013241839E-3</v>
       </c>
       <c r="E32" s="176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>323.18573120056726</v>
       </c>
       <c r="F32" s="177">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.3886479187435693E-3</v>
       </c>
       <c r="G32" s="92">
@@ -33440,12 +33195,12 @@
         <v>0.87</v>
       </c>
       <c r="M32" s="179" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N32" s="83"/>
       <c r="O32" s="83"/>
       <c r="P32" s="83" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="Q32" s="172"/>
       <c r="R32" s="172"/>
@@ -33455,22 +33210,22 @@
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B33" s="172" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C33" s="92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11613.017957647857</v>
       </c>
       <c r="D33" s="175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.5411026914932346E-2</v>
       </c>
       <c r="E33" s="176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>916.415375685443</v>
       </c>
       <c r="F33" s="177">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.7731755102676929E-3</v>
       </c>
       <c r="G33" s="92">
@@ -33486,7 +33241,7 @@
         <v>0.87</v>
       </c>
       <c r="M33" s="179" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N33" s="172"/>
       <c r="O33" s="172"/>
@@ -33494,39 +33249,39 @@
         <v>304</v>
       </c>
       <c r="Q33" s="169" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="R33" s="101" t="s">
         <v>305</v>
       </c>
       <c r="S33" s="101" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="T33" s="169" t="s">
         <v>317</v>
       </c>
       <c r="U33" s="169" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B34" s="172" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C34" s="92">
-        <f>G34*H34</f>
+        <f t="shared" ref="C34:C47" si="8">G34*H34</f>
         <v>125972.18626629541</v>
       </c>
       <c r="D34" s="175">
-        <f>C34*K34/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" ref="D34:D47" si="9">C34*K34/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
         <v>0.1787001199119426</v>
       </c>
       <c r="E34" s="176">
-        <f>G34-C34</f>
+        <f t="shared" ref="E34:E47" si="10">G34-C34</f>
         <v>9940.8137337045919</v>
       </c>
       <c r="F34" s="177">
-        <f>E34*$K34/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" ref="F34:F47" si="11">E34*$K34/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
         <v>7.8539041074329657E-2</v>
       </c>
       <c r="G34" s="92">
@@ -33542,12 +33297,12 @@
         <v>0.93</v>
       </c>
       <c r="M34" s="172" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="N34" s="172"/>
       <c r="O34" s="172"/>
       <c r="P34" s="92">
-        <f t="shared" ref="P34:P35" si="7">T34*U34</f>
+        <f t="shared" ref="P34:P35" si="12">T34*U34</f>
         <v>18331.527857478479</v>
       </c>
       <c r="Q34" s="175">
@@ -33555,7 +33310,7 @@
         <v>0.51302572087399856</v>
       </c>
       <c r="R34" s="176">
-        <f t="shared" ref="R34:R35" si="8">T34-P34</f>
+        <f t="shared" ref="R34:R35" si="13">T34-P34</f>
         <v>11212.490475854818</v>
       </c>
       <c r="S34" s="177">
@@ -33571,22 +33326,22 @@
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B35" s="172" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C35" s="92">
-        <f>G35*H35</f>
+        <f t="shared" si="8"/>
         <v>36603.206384229525</v>
       </c>
       <c r="D35" s="175">
-        <f>C35*K35/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>5.024916723664883E-2</v>
       </c>
       <c r="E35" s="176">
-        <f>G35-C35</f>
+        <f t="shared" si="10"/>
         <v>2888.4602824371759</v>
       </c>
       <c r="F35" s="177">
-        <f>E35*$K35/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>2.2084604148529564E-2</v>
       </c>
       <c r="G35" s="92">
@@ -33602,12 +33357,12 @@
         <v>0.9</v>
       </c>
       <c r="M35" s="172" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N35" s="172"/>
       <c r="O35" s="172"/>
       <c r="P35" s="92">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>17400.653028596018</v>
       </c>
       <c r="Q35" s="175">
@@ -33615,7 +33370,7 @@
         <v>0.48697427912600155</v>
       </c>
       <c r="R35" s="176">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>10643.120304737324</v>
       </c>
       <c r="S35" s="177">
@@ -33631,22 +33386,22 @@
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B36" s="172" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C36" s="92">
-        <f>G36*H36</f>
+        <f t="shared" si="8"/>
         <v>90204.110729731736</v>
       </c>
       <c r="D36" s="175">
-        <f>C36*K36/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>0.11970514325933213</v>
       </c>
       <c r="E36" s="176">
-        <f>G36-C36</f>
+        <f t="shared" si="10"/>
         <v>7118.2559369349037</v>
       </c>
       <c r="F36" s="177">
-        <f>E36*$K36/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>5.2610637127081708E-2</v>
       </c>
       <c r="G36" s="92">
@@ -33667,22 +33422,22 @@
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B37" s="172" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C37" s="92">
-        <f>G37*H37</f>
+        <f t="shared" si="8"/>
         <v>29382.974831585889</v>
       </c>
       <c r="D37" s="175">
-        <f>C37*K37/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>4.0785367897941328E-2</v>
       </c>
       <c r="E37" s="176">
-        <f>G37-C37</f>
+        <f t="shared" si="10"/>
         <v>2318.69183508071</v>
       </c>
       <c r="F37" s="177">
-        <f>E37*$K37/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>1.7925246419233029E-2</v>
       </c>
       <c r="G37" s="92">
@@ -33703,22 +33458,22 @@
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B38" s="172" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C38" s="92">
-        <f>G38*H38</f>
+        <f t="shared" si="8"/>
         <v>15543.487097124786</v>
       </c>
       <c r="D38" s="175">
-        <f>C38*K38/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>2.0626946318286005E-2</v>
       </c>
       <c r="E38" s="176">
-        <f>G38-C38</f>
+        <f t="shared" si="10"/>
         <v>1226.5795695418474</v>
       </c>
       <c r="F38" s="177">
-        <f>E38*$K38/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>9.0655819645120948E-3</v>
       </c>
       <c r="G38" s="92">
@@ -33736,22 +33491,22 @@
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B39" s="172" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C39" s="92">
-        <f>G39*H39</f>
+        <f t="shared" si="8"/>
         <v>39489.568868500683</v>
       </c>
       <c r="D39" s="175">
-        <f>C39*K39/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>5.2404535230289213E-2</v>
       </c>
       <c r="E39" s="176">
-        <f>G39-C39</f>
+        <f t="shared" si="10"/>
         <v>3116.2311314993494</v>
       </c>
       <c r="F39" s="177">
-        <f>E39*$K39/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>2.3031892462976329E-2</v>
       </c>
       <c r="G39" s="92">
@@ -33769,22 +33524,22 @@
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B40" s="172" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C40" s="92">
-        <f>G40*H40</f>
+        <f t="shared" si="8"/>
         <v>103581.4047798645</v>
       </c>
       <c r="D40" s="175">
-        <f>C40*K40/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>0.14219736043760764</v>
       </c>
       <c r="E40" s="176">
-        <f>G40-C40</f>
+        <f t="shared" si="10"/>
         <v>8173.8952201354987</v>
       </c>
       <c r="F40" s="177">
-        <f>E40*$K40/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>6.2496009166494983E-2</v>
       </c>
       <c r="G40" s="92">
@@ -33802,22 +33557,22 @@
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B41" s="172" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C41" s="92">
-        <f>G41*H41</f>
+        <f t="shared" si="8"/>
         <v>3649.7235506071347</v>
       </c>
       <c r="D41" s="175">
-        <f>C41*K41/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>5.1217104912708407E-3</v>
       </c>
       <c r="E41" s="176">
-        <f>G41-C41</f>
+        <f t="shared" si="10"/>
         <v>288.0097827262025</v>
       </c>
       <c r="F41" s="177">
-        <f>E41*$K41/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>2.2510014589971318E-3</v>
       </c>
       <c r="G41" s="92">
@@ -33835,22 +33590,22 @@
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B42" s="172" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C42" s="92">
-        <f>G42*H42</f>
+        <f t="shared" si="8"/>
         <v>2313.4678513921531</v>
       </c>
       <c r="D42" s="175">
-        <f>C42*K42/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>3.175946711906122E-3</v>
       </c>
       <c r="E42" s="176">
-        <f>G42-C42</f>
+        <f t="shared" si="10"/>
         <v>182.56214860784985</v>
       </c>
       <c r="F42" s="177">
-        <f>E42*$K42/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>1.3958345936152176E-3</v>
       </c>
       <c r="G42" s="92">
@@ -33869,22 +33624,22 @@
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B43" s="172" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C43" s="92">
-        <f>G43*H43</f>
+        <f t="shared" si="8"/>
         <v>257.05198348801702</v>
       </c>
       <c r="D43" s="175">
-        <f>C43*K43/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>3.5288296798956909E-4</v>
       </c>
       <c r="E43" s="176">
-        <f>G43-C43</f>
+        <f t="shared" si="10"/>
         <v>20.284683178649971</v>
       </c>
       <c r="F43" s="177">
-        <f>E43*$K43/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>1.5509273262391299E-4</v>
       </c>
       <c r="G43" s="92">
@@ -33903,22 +33658,22 @@
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B44" s="172" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C44" s="92">
-        <f>G44*H44</f>
+        <f t="shared" si="8"/>
         <v>19145.662781409661</v>
       </c>
       <c r="D44" s="175">
-        <f>C44*K44/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>2.9203683562603517E-2</v>
       </c>
       <c r="E44" s="176">
-        <f>G44-C44</f>
+        <f t="shared" si="10"/>
         <v>1510.837218590339</v>
       </c>
       <c r="F44" s="177">
-        <f>E44*$K44/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>1.2835074223650576E-2</v>
       </c>
       <c r="G44" s="92">
@@ -33936,22 +33691,22 @@
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B45" s="172" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C45" s="92">
-        <f>G45*H45</f>
+        <f t="shared" si="8"/>
         <v>35644.185384547847</v>
       </c>
       <c r="D45" s="175">
-        <f>C45*K45/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>5.4369573030809949E-2</v>
       </c>
       <c r="E45" s="176">
-        <f>G45-C45</f>
+        <f t="shared" si="10"/>
         <v>2812.7812821188563</v>
       </c>
       <c r="F45" s="177">
-        <f>E45*$K45/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>2.3895530297152162E-2</v>
       </c>
       <c r="G45" s="92">
@@ -33969,22 +33724,22 @@
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B46" s="172" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C46" s="92">
-        <f>G46*H46</f>
+        <f t="shared" si="8"/>
         <v>38744.652296118176</v>
       </c>
       <c r="D46" s="175">
-        <f>C46*K46/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>5.3188960888198779E-2</v>
       </c>
       <c r="E46" s="176">
-        <f>G46-C46</f>
+        <f t="shared" si="10"/>
         <v>3057.4477038818441</v>
       </c>
       <c r="F46" s="177">
-        <f>E46*$K46/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>2.3376649024956703E-2</v>
       </c>
       <c r="G46" s="92">
@@ -34003,22 +33758,22 @@
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B47" s="172" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C47" s="92">
-        <f>G47*H47</f>
+        <f t="shared" si="8"/>
         <v>25829.768197412119</v>
       </c>
       <c r="D47" s="175">
-        <f>C47*K47/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
+        <f t="shared" si="9"/>
         <v>2.9549422715665987E-2</v>
       </c>
       <c r="E47" s="176">
-        <f>G47-C47</f>
+        <f t="shared" si="10"/>
         <v>2038.2984692545615</v>
       </c>
       <c r="F47" s="177">
-        <f>E47*$K47/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
+        <f t="shared" si="11"/>
         <v>1.2987027236087049E-2</v>
       </c>
       <c r="G47" s="92">
@@ -34037,7 +33792,7 @@
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B48" s="180" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C48" s="181">
         <v>692.67262049750991</v>
@@ -34058,7 +33813,7 @@
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C52" t="s">
         <v>39</v>
@@ -34093,24 +33848,24 @@
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="G53" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="K53" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="L53" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N53" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
@@ -34143,12 +33898,12 @@
         <v>35</v>
       </c>
       <c r="N54" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="U55" s="110" t="str">
         <f>C52&amp;C53&amp;C54</f>
@@ -34179,21 +33934,21 @@
         <v>dairy</v>
       </c>
       <c r="AB55" s="110" t="str">
-        <f t="shared" ref="AA55:AD55" si="9">J52&amp;J53&amp;J54</f>
+        <f t="shared" ref="AB55:AD55" si="14">J52&amp;J53&amp;J54</f>
         <v>dairybulls</v>
       </c>
       <c r="AC55" s="110" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>dairymaize basedcows</v>
       </c>
       <c r="AD55" s="110" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>dairymaize basedbulls</v>
       </c>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
@@ -34228,26 +33983,26 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" s="110" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="U56" s="13">
-        <f>C56/C$94*100</f>
+        <f t="shared" ref="U56:U61" si="15">C56/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V56" s="13">
-        <f t="shared" ref="V56:AD61" si="10">D56/D$94*100</f>
+        <f t="shared" ref="V56:Z61" si="16">D56/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W56" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X56" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>60.249501023299892</v>
       </c>
       <c r="Y56" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>56.175982718049596</v>
       </c>
       <c r="Z56" s="13">
@@ -34255,25 +34010,25 @@
         <v>38.655760943285067</v>
       </c>
       <c r="AA56" s="13">
-        <f t="shared" ref="AA56:AD61" si="11">I56/I$94*100</f>
+        <f t="shared" ref="AA56:AD61" si="17">I56/I$94*100</f>
         <v>0</v>
       </c>
       <c r="AB56" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>65.282988689132509</v>
       </c>
       <c r="AC56" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>21.053926091496013</v>
       </c>
       <c r="AD56" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>56.862458601207877</v>
       </c>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C57" s="12">
         <f>SUMPRODUCT(C8:E8,C22:E22)/SUM(C22:E22)*AF8</f>
@@ -34307,52 +34062,52 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="110" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U57" s="13">
-        <f>C57/C$94*100</f>
+        <f t="shared" si="15"/>
         <v>16.595954764760993</v>
       </c>
       <c r="V57" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>69.353683256124697</v>
       </c>
       <c r="W57" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>69.504158295923276</v>
       </c>
       <c r="X57" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Y57" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z57" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>9.2487848377124262</v>
       </c>
       <c r="AA57" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>55.413619478612851</v>
       </c>
       <c r="AB57" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC57" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>9.7648461508611888</v>
       </c>
       <c r="AD57" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C58" s="12">
         <f>SUMPRODUCT(C11:E11,C22:E22)/SUM(C22:E22)*AF11</f>
@@ -34370,52 +34125,52 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="110" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="U58" s="13">
-        <f>C58/C$94*100</f>
+        <f t="shared" si="15"/>
         <v>17.173343787959137</v>
       </c>
       <c r="V58" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="W58" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X58" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Y58" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z58" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AA58" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB58" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC58" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD58" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C59" s="12"/>
       <c r="D59" s="12"/>
@@ -34440,52 +34195,52 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="110" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="U59" s="13">
-        <f>C59/C$94*100</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V59" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="W59" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X59" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Y59" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>13.115765922154072</v>
       </c>
       <c r="Z59" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AA59" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB59" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC59" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>16.256327113961142</v>
       </c>
       <c r="AD59" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>13.271965712059227</v>
       </c>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C60" s="12">
         <f>SUMPRODUCT(C11:E11,C22:E22)/SUM(C22:E22)*AF11</f>
@@ -34509,46 +34264,46 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="110" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="U60" s="13">
-        <f>C60/C$94*100</f>
+        <f t="shared" si="15"/>
         <v>17.173343787959137</v>
       </c>
       <c r="V60" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="W60" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X60" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Y60" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z60" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>2.6959915324547534</v>
       </c>
       <c r="AA60" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB60" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC60" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>2.6961713262179456</v>
       </c>
       <c r="AD60" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -34590,50 +34345,50 @@
         <v>427</v>
       </c>
       <c r="U61" s="13">
-        <f>C61/C$94*100</f>
+        <f t="shared" si="15"/>
         <v>49.057357659320729</v>
       </c>
       <c r="V61" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>30.646316743875307</v>
       </c>
       <c r="W61" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>30.495841704076721</v>
       </c>
       <c r="X61" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Y61" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z61" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>10.178212969682118</v>
       </c>
       <c r="AA61" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>38.884638191900635</v>
       </c>
       <c r="AB61" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC61" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>10.178891747486265</v>
       </c>
       <c r="AD61" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="155"/>
       <c r="B62" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C62" s="167"/>
       <c r="D62" s="167"/>
@@ -34676,39 +34431,39 @@
         <v>0</v>
       </c>
       <c r="V62" s="13">
-        <f t="shared" ref="V62:AD62" si="12">(D63+D73)/D$94*100</f>
+        <f t="shared" ref="V62:Z62" si="18">(D63+D73)/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W62" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X62" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>8.3580433504262022</v>
       </c>
       <c r="Y62" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>6.4239515794862037</v>
       </c>
       <c r="Z62" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>6.522978613065411</v>
       </c>
       <c r="AA62" s="13">
-        <f t="shared" ref="AA62:AA65" si="13">(I63+I73)/I$94*100</f>
+        <f t="shared" ref="AA62:AA65" si="19">(I63+I73)/I$94*100</f>
         <v>1.1628177607947425</v>
       </c>
       <c r="AB62" s="13">
-        <f t="shared" ref="AB62:AB65" si="14">(J63+J73)/J$94*100</f>
+        <f t="shared" ref="AB62:AB65" si="20">(J63+J73)/J$94*100</f>
         <v>7.0130888477159132</v>
       </c>
       <c r="AC62" s="13">
-        <f t="shared" ref="AC62:AC65" si="15">(K63+K73)/K$94*100</f>
+        <f t="shared" ref="AC62:AC65" si="21">(K63+K73)/K$94*100</f>
         <v>5.1917347110499525</v>
       </c>
       <c r="AD62" s="13">
-        <f t="shared" ref="AD62:AD65" si="16">(L63+L73)/L$94*100</f>
+        <f t="shared" ref="AD62:AD65" si="22">(L63+L73)/L$94*100</f>
         <v>6.6666574064662587</v>
       </c>
     </row>
@@ -34732,11 +34487,11 @@
         <v>444.22770285717644</v>
       </c>
       <c r="I63" s="12">
-        <f>I$62*$S26</f>
+        <f t="shared" ref="I63:J66" si="23">I$62*$S26</f>
         <v>33.021486832051707</v>
       </c>
       <c r="J63" s="12">
-        <f>J$62*$S26</f>
+        <f t="shared" si="23"/>
         <v>182.09576437404189</v>
       </c>
       <c r="K63" s="12">
@@ -34752,74 +34507,74 @@
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="110" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="U63" s="13">
         <f>(C64+C74)/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V63" s="13">
-        <f t="shared" ref="V63:AD63" si="17">(D64+D74)/D$94*100</f>
+        <f t="shared" ref="V63:Z63" si="24">(D64+D74)/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W63" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="X63" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>6.3565169401541155</v>
       </c>
       <c r="Y63" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>5.1013876253121104</v>
       </c>
       <c r="Z63" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>4.992523211434996</v>
       </c>
       <c r="AA63" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>0.80563895711258293</v>
       </c>
       <c r="AB63" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>5.2164760725210764</v>
       </c>
       <c r="AC63" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>3.8278564703417133</v>
       </c>
       <c r="AD63" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>5.1991702356471148</v>
       </c>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B64" s="168" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C64" s="12"/>
       <c r="D64" s="12"/>
       <c r="E64" s="12"/>
       <c r="F64" s="12">
-        <f t="shared" ref="F64:G66" si="18">F$62*$S27</f>
+        <f t="shared" ref="F64:G66" si="25">F$62*$S27</f>
         <v>118.64869287778419</v>
       </c>
       <c r="G64" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>105.79461712877267</v>
       </c>
       <c r="H64" s="12">
-        <f t="shared" ref="H64:H66" si="19">H$62*$Q27</f>
+        <f t="shared" ref="H64:H66" si="26">H$62*$Q27</f>
         <v>352.77004786478733</v>
       </c>
       <c r="I64" s="12">
-        <f>I$62*$S27</f>
+        <f t="shared" si="23"/>
         <v>26.22301899540604</v>
       </c>
       <c r="J64" s="12">
-        <f>J$62*$S27</f>
+        <f t="shared" si="23"/>
         <v>144.60586564287038</v>
       </c>
       <c r="K64" s="12">
@@ -34835,74 +34590,74 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" s="110" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="U64" s="13">
         <f>(C65+C75)/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V64" s="13">
-        <f t="shared" ref="V64:AD64" si="20">(D65+D75)/D$94*100</f>
+        <f t="shared" ref="V64:Z64" si="27">(D65+D75)/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W64" s="13">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="X64" s="13">
+        <f t="shared" si="27"/>
+        <v>16.834448704037197</v>
+      </c>
+      <c r="Y64" s="13">
+        <f t="shared" si="27"/>
+        <v>13.185764834849451</v>
+      </c>
+      <c r="Z64" s="13">
+        <f t="shared" si="27"/>
+        <v>13.174510208769105</v>
+      </c>
+      <c r="AA64" s="13">
+        <f t="shared" si="19"/>
+        <v>2.2520471552888917</v>
+      </c>
+      <c r="AB64" s="13">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="X64" s="13">
-        <f t="shared" si="20"/>
-        <v>16.834448704037197</v>
-      </c>
-      <c r="Y64" s="13">
-        <f t="shared" si="20"/>
-        <v>13.185764834849451</v>
-      </c>
-      <c r="Z64" s="13">
-        <f t="shared" si="20"/>
-        <v>13.174510208769105</v>
-      </c>
-      <c r="AA64" s="13">
-        <f t="shared" si="13"/>
-        <v>2.2520471552888917</v>
-      </c>
-      <c r="AB64" s="13">
-        <f t="shared" si="14"/>
         <v>13.991446516700695</v>
       </c>
       <c r="AC64" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>10.319020213721652</v>
       </c>
       <c r="AD64" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>13.575306555370148</v>
       </c>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B65" s="168" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C65" s="12"/>
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
       <c r="F65" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>306.67611974556092</v>
       </c>
       <c r="G65" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>273.45166545104189</v>
       </c>
       <c r="H65" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>911.819142862935</v>
       </c>
       <c r="I65" s="12">
-        <f>I$62*$S28</f>
+        <f t="shared" si="23"/>
         <v>67.779707626522381</v>
       </c>
       <c r="J65" s="12">
-        <f>J$62*$S28</f>
+        <f t="shared" si="23"/>
         <v>373.76868376867714</v>
       </c>
       <c r="K65" s="12">
@@ -34918,74 +34673,74 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="110" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="U65" s="13">
         <f>(C66+C76)/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V65" s="13">
-        <f t="shared" ref="V65:AD65" si="21">(D66+D76)/D$94*100</f>
+        <f t="shared" ref="V65:Z65" si="28">(D66+D76)/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W65" s="13">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="X65" s="13">
+        <f t="shared" si="28"/>
+        <v>3.4789898578450962</v>
+      </c>
+      <c r="Y65" s="13">
+        <f t="shared" si="28"/>
+        <v>2.7249566014817326</v>
+      </c>
+      <c r="Z65" s="13">
+        <f t="shared" si="28"/>
+        <v>2.7226307320294127</v>
+      </c>
+      <c r="AA65" s="13">
+        <f t="shared" si="19"/>
+        <v>0.46540574926935496</v>
+      </c>
+      <c r="AB65" s="13">
+        <f t="shared" si="20"/>
+        <v>2.8914579493482573</v>
+      </c>
+      <c r="AC65" s="13">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="X65" s="13">
-        <f t="shared" si="21"/>
-        <v>3.4789898578450962</v>
-      </c>
-      <c r="Y65" s="13">
-        <f t="shared" si="21"/>
-        <v>2.7249566014817326</v>
-      </c>
-      <c r="Z65" s="13">
-        <f t="shared" si="21"/>
-        <v>2.7226307320294127</v>
-      </c>
-      <c r="AA65" s="13">
-        <f t="shared" si="13"/>
-        <v>0.46540574926935496</v>
-      </c>
-      <c r="AB65" s="13">
-        <f t="shared" si="14"/>
-        <v>2.8914579493482573</v>
-      </c>
-      <c r="AC65" s="13">
-        <f t="shared" si="15"/>
         <v>2.1325181060325882</v>
       </c>
       <c r="AD65" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.8054588928679678</v>
       </c>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B66" s="168" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
       <c r="E66" s="12"/>
       <c r="F66" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>63.377371543044816</v>
       </c>
       <c r="G66" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>56.511239984168768</v>
       </c>
       <c r="H66" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>188.43560641510095</v>
       </c>
       <c r="I66" s="12">
-        <f>I$62*$S29</f>
+        <f t="shared" si="23"/>
         <v>14.007284678340973</v>
       </c>
       <c r="J66" s="12">
-        <f>J$62*$S29</f>
+        <f t="shared" si="23"/>
         <v>77.242651830914724</v>
       </c>
       <c r="K66" s="12">
@@ -35001,52 +34756,52 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" s="110" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="U66" s="13">
         <f>C67/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V66" s="13">
-        <f t="shared" ref="V66:AD66" si="22">D67/D$94*100</f>
+        <f t="shared" ref="V66:Z66" si="29">D67/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W66" s="13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X66" s="13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y66" s="13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Z66" s="13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AA66" s="13">
-        <f t="shared" ref="AA66" si="23">I67/I$94*100</f>
+        <f t="shared" ref="AA66" si="30">I67/I$94*100</f>
         <v>0</v>
       </c>
       <c r="AB66" s="13">
-        <f t="shared" ref="AB66" si="24">J67/J$94*100</f>
+        <f t="shared" ref="AB66" si="31">J67/J$94*100</f>
         <v>0</v>
       </c>
       <c r="AC66" s="13">
-        <f t="shared" ref="AC66" si="25">K67/K$94*100</f>
+        <f t="shared" ref="AC66" si="32">K67/K$94*100</f>
         <v>0</v>
       </c>
       <c r="AD66" s="13">
-        <f t="shared" ref="AD66" si="26">L67/L$94*100</f>
+        <f t="shared" ref="AD66" si="33">L67/L$94*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B67" s="110" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C67" s="12"/>
       <c r="D67" s="12"/>
@@ -35062,53 +34817,53 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="110" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="U67" s="13">
         <f>C72/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V67" s="13">
-        <f t="shared" ref="V67:AD67" si="27">D72/D$94*100</f>
+        <f t="shared" ref="V67:Z67" si="34">D72/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W67" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="X67" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>2.9860883502482297E-2</v>
       </c>
       <c r="Y67" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Z67" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0.15456668608878038</v>
       </c>
       <c r="AA67" s="13">
-        <f t="shared" ref="AA67" si="28">I72/I$94*100</f>
+        <f t="shared" ref="AA67" si="35">I72/I$94*100</f>
         <v>1.2526016891559834E-2</v>
       </c>
       <c r="AB67" s="13">
-        <f t="shared" ref="AB67" si="29">J72/J$94*100</f>
+        <f t="shared" ref="AB67" si="36">J72/J$94*100</f>
         <v>3.7516786382972102E-2</v>
       </c>
       <c r="AC67" s="13">
-        <f t="shared" ref="AC67" si="30">K72/K$94*100</f>
+        <f t="shared" ref="AC67" si="37">K72/K$94*100</f>
         <v>0.24318273525305006</v>
       </c>
       <c r="AD67" s="13">
-        <f t="shared" ref="AD67" si="31">L72/L$94*100</f>
+        <f t="shared" ref="AD67" si="38">L72/L$94*100</f>
         <v>1.0098740539236407E-2</v>
       </c>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="155"/>
       <c r="B68" s="6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C68" s="167"/>
       <c r="D68" s="167"/>
@@ -35137,52 +34892,52 @@
       <c r="N68" s="72"/>
       <c r="Q68" s="72"/>
       <c r="R68" s="110" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="U68" s="13">
         <f>(C69+C77)/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V68" s="13">
-        <f t="shared" ref="V68:AD68" si="32">(D69+D77)/D$94*100</f>
+        <f t="shared" ref="V68:Z68" si="39">(D69+D77)/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W68" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="X68" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v>1.2676767287415975</v>
       </c>
       <c r="Y68" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v>1.6787180022812531</v>
       </c>
       <c r="Z68" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v>7.9125995025714754E-2</v>
       </c>
       <c r="AA68" s="13">
-        <f t="shared" ref="AA68:AA69" si="33">(I69+I77)/I$94*100</f>
+        <f t="shared" ref="AA68:AA69" si="40">(I69+I77)/I$94*100</f>
         <v>3.6613311294760156E-2</v>
       </c>
       <c r="AB68" s="13">
-        <f t="shared" ref="AB68:AB69" si="34">(J69+J77)/J$94*100</f>
+        <f t="shared" ref="AB68:AB69" si="41">(J69+J77)/J$94*100</f>
         <v>1.4240390174797204</v>
       </c>
       <c r="AC68" s="13">
-        <f t="shared" ref="AC68:AC69" si="35">(K69+K77)/K$94*100</f>
+        <f t="shared" ref="AC68:AC69" si="42">(K69+K77)/K$94*100</f>
         <v>0.12449044737182395</v>
       </c>
       <c r="AD68" s="13">
-        <f t="shared" ref="AD68:AD69" si="36">(L69+L77)/L$94*100</f>
+        <f t="shared" ref="AD68:AD69" si="43">(L69+L77)/L$94*100</f>
         <v>0.43993732150286113</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B69" s="168" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C69" s="12"/>
       <c r="D69" s="12"/>
@@ -35213,52 +34968,52 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="110" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="U69" s="13">
         <f>(C70+C78)/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V69" s="13">
-        <f t="shared" ref="V69:AD69" si="37">(D70+D78)/D$94*100</f>
+        <f t="shared" ref="V69:Z69" si="44">(D70+D78)/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W69" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="X69" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v>1.2321396453293407</v>
       </c>
       <c r="Y69" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v>1.5934727163855678</v>
       </c>
       <c r="Z69" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v>0.22436720268746718</v>
       </c>
       <c r="AA69" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v>4.6849990217144546E-2</v>
       </c>
       <c r="AB69" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v>1.38795487532739</v>
       </c>
       <c r="AC69" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="42"/>
         <v>0.35300122834537684</v>
       </c>
       <c r="AD69" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>0.42734928129407507</v>
       </c>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B70" s="168" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C70" s="12"/>
       <c r="D70" s="12"/>
@@ -35289,52 +35044,52 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="110" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="U70" s="13">
-        <f>C79/C$94*100</f>
+        <f t="shared" ref="U70:U83" si="45">C79/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V70" s="13">
-        <f t="shared" ref="V70:AD70" si="38">D79/D$94*100</f>
+        <f t="shared" ref="V70:Z70" si="46">D79/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W70" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="X70" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="46"/>
         <v>0.50261957176929339</v>
       </c>
       <c r="Y70" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="Z70" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="46"/>
         <v>2.6016725715862865</v>
       </c>
       <c r="AA70" s="13">
-        <f t="shared" ref="AA70:AA83" si="39">I79/I$94*100</f>
+        <f t="shared" ref="AA70:AA83" si="47">I79/I$94*100</f>
         <v>0.2108384115790605</v>
       </c>
       <c r="AB70" s="13">
-        <f t="shared" ref="AB70:AB83" si="40">J79/J$94*100</f>
+        <f t="shared" ref="AB70:AB83" si="48">J79/J$94*100</f>
         <v>0.63148403175686241</v>
       </c>
       <c r="AC70" s="13">
-        <f t="shared" ref="AC70:AC83" si="41">K79/K$94*100</f>
+        <f t="shared" ref="AC70:AC83" si="49">K79/K$94*100</f>
         <v>4.0932614148678095</v>
       </c>
       <c r="AD70" s="13">
-        <f t="shared" ref="AD70:AD83" si="42">L79/L$94*100</f>
+        <f t="shared" ref="AD70:AD83" si="50">L79/L$94*100</f>
         <v>0.16998240004580778</v>
       </c>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C71" s="167"/>
       <c r="D71" s="167"/>
@@ -35367,55 +35122,55 @@
       <c r="N71" s="72"/>
       <c r="Q71" s="72"/>
       <c r="R71" s="110" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="U71" s="13">
-        <f>C80/C$94*100</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="V71" s="13">
-        <f t="shared" ref="V71:AD71" si="43">D80/D$94*100</f>
+        <f t="shared" ref="V71:Z71" si="51">D80/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W71" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="X71" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0.14133294891292425</v>
       </c>
       <c r="Y71" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="Z71" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0.73157130621435396</v>
       </c>
       <c r="AA71" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>5.9286219889310578E-2</v>
       </c>
       <c r="AB71" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.17756869292902569</v>
       </c>
       <c r="AC71" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>1.1509951838888972</v>
       </c>
       <c r="AD71" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>4.7797808145834932E-2</v>
       </c>
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F72" s="13">
-        <f>F$71*$F27</f>
+        <f t="shared" ref="F72:F92" si="52">F$71*$F27</f>
         <v>0.61645906766781788</v>
       </c>
       <c r="G72" s="13"/>
@@ -35424,11 +35179,11 @@
         <v>11.890664458290937</v>
       </c>
       <c r="I72" s="13">
-        <f>I$71*$F27</f>
+        <f t="shared" ref="I72:J92" si="53">I$71*$F27</f>
         <v>0.5971407409667594</v>
       </c>
       <c r="J72" s="13">
-        <f>J$71*$F27</f>
+        <f t="shared" si="53"/>
         <v>1.2188540277094801</v>
       </c>
       <c r="K72" s="13">
@@ -35436,7 +35191,7 @@
         <v>18.706563192418422</v>
       </c>
       <c r="L72" s="13">
-        <f>L$71*$F27</f>
+        <f t="shared" ref="L72:L92" si="54">L$71*$F27</f>
         <v>0.33175574520256301</v>
       </c>
       <c r="N72" s="2">
@@ -35444,46 +35199,46 @@
         <v>27.270318402958633</v>
       </c>
       <c r="R72" s="110" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="U72" s="13">
-        <f>C81/C$94*100</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="V72" s="13">
-        <f t="shared" ref="V72:AD72" si="44">D81/D$94*100</f>
+        <f t="shared" ref="V72:Z72" si="55">D81/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W72" s="13">
-        <f t="shared" si="44"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="X72" s="13">
-        <f t="shared" si="44"/>
+        <f t="shared" si="55"/>
         <v>0.33668778662955168</v>
       </c>
       <c r="Y72" s="13">
-        <f t="shared" si="44"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="Z72" s="13">
-        <f t="shared" si="44"/>
+        <f t="shared" si="55"/>
         <v>1.7427721260012328</v>
       </c>
       <c r="AA72" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>0.14123349371605412</v>
       </c>
       <c r="AB72" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.42300971328214537</v>
       </c>
       <c r="AC72" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>2.7419368509998514</v>
       </c>
       <c r="AD72" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>0.11386543869738427</v>
       </c>
     </row>
@@ -35492,484 +35247,484 @@
         <v>397</v>
       </c>
       <c r="F73" s="13">
-        <f>F$71*$F28</f>
+        <f t="shared" si="52"/>
         <v>23.13747671080424</v>
       </c>
       <c r="H73" s="13">
-        <f t="shared" ref="H73:H92" si="45">H$71*$D28</f>
+        <f t="shared" ref="H73:H92" si="56">H$71*$D28</f>
         <v>57.578681941797889</v>
       </c>
       <c r="I73" s="13">
-        <f>I$71*$F28</f>
+        <f t="shared" si="53"/>
         <v>22.412404507992054</v>
       </c>
       <c r="J73" s="13">
-        <f>J$71*$F28</f>
+        <f t="shared" si="53"/>
         <v>45.747087128896617</v>
       </c>
       <c r="K73" s="13">
-        <f t="shared" ref="K73:K92" si="46">K$71*$D28</f>
+        <f t="shared" ref="K73:K92" si="57">K$71*$D28</f>
         <v>90.583604983435606</v>
       </c>
       <c r="L73" s="13">
-        <f>L$71*$F28</f>
+        <f t="shared" si="54"/>
         <v>12.451744537296763</v>
       </c>
       <c r="N73" s="2">
-        <f t="shared" ref="N73:N78" si="47">I28*100</f>
+        <f t="shared" ref="N73:N78" si="58">I28*100</f>
         <v>0</v>
       </c>
       <c r="R73" s="110" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="U73" s="13">
-        <f>C82/C$94*100</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="V73" s="13">
-        <f t="shared" ref="V73:AD73" si="48">D82/D$94*100</f>
+        <f t="shared" ref="V73:Z73" si="59">D82/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W73" s="13">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="X73" s="13">
+        <f t="shared" si="59"/>
+        <v>0.11471466363546844</v>
+      </c>
+      <c r="Y73" s="13">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="Z73" s="13">
+        <f t="shared" si="59"/>
+        <v>0.59378904185636427</v>
+      </c>
+      <c r="AA73" s="13">
+        <f t="shared" si="47"/>
+        <v>4.8120405221367048E-2</v>
+      </c>
+      <c r="AB73" s="13">
         <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X73" s="13">
-        <f t="shared" si="48"/>
-        <v>0.11471466363546844</v>
-      </c>
-      <c r="Y73" s="13">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="Z73" s="13">
-        <f t="shared" si="48"/>
-        <v>0.59378904185636427</v>
-      </c>
-      <c r="AA73" s="13">
-        <f t="shared" si="39"/>
-        <v>4.8120405221367048E-2</v>
-      </c>
-      <c r="AB73" s="13">
-        <f t="shared" si="40"/>
         <v>0.14412586051744264</v>
       </c>
       <c r="AC73" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>0.93421970164371715</v>
       </c>
       <c r="AD73" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>3.879569149399318E-2</v>
       </c>
     </row>
     <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B74" s="168" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F74" s="13">
-        <f>F$71*$F29</f>
+        <f t="shared" si="52"/>
         <v>12.577581998387982</v>
       </c>
       <c r="H74" s="13">
+        <f t="shared" si="56"/>
+        <v>31.299895080775716</v>
+      </c>
+      <c r="I74" s="13">
+        <f t="shared" si="53"/>
+        <v>12.183431192766058</v>
+      </c>
+      <c r="J74" s="13">
+        <f t="shared" si="53"/>
+        <v>24.868214747134228</v>
+      </c>
+      <c r="K74" s="13">
+        <f t="shared" si="57"/>
+        <v>49.241442082434652</v>
+      </c>
+      <c r="L74" s="13">
+        <f t="shared" si="54"/>
+        <v>6.7687950548081153</v>
+      </c>
+      <c r="N74" s="2">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="R74" s="110" t="s">
+        <v>503</v>
+      </c>
+      <c r="U74" s="13">
         <f t="shared" si="45"/>
-        <v>31.299895080775716</v>
-      </c>
-      <c r="I74" s="13">
-        <f>I$71*$F29</f>
-        <v>12.183431192766058</v>
-      </c>
-      <c r="J74" s="13">
-        <f>J$71*$F29</f>
-        <v>24.868214747134228</v>
-      </c>
-      <c r="K74" s="13">
-        <f t="shared" si="46"/>
-        <v>49.241442082434652</v>
-      </c>
-      <c r="L74" s="13">
-        <f>L$71*$F29</f>
-        <v>6.7687950548081153</v>
-      </c>
-      <c r="N74" s="2">
+        <v>0</v>
+      </c>
+      <c r="V74" s="13">
+        <f t="shared" ref="V74:Z74" si="60">D83/D$94*100</f>
+        <v>0</v>
+      </c>
+      <c r="W74" s="13">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="X74" s="13">
+        <f t="shared" si="60"/>
+        <v>5.8016228139711724E-2</v>
+      </c>
+      <c r="Y74" s="13">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="Z74" s="13">
+        <f t="shared" si="60"/>
+        <v>0.30030511730104892</v>
+      </c>
+      <c r="AA74" s="13">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="R74" s="110" t="s">
-        <v>506</v>
-      </c>
-      <c r="U74" s="13">
-        <f>C83/C$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="V74" s="13">
-        <f t="shared" ref="V74:AD74" si="49">D83/D$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="13">
+        <v>2.4336595854647348E-2</v>
+      </c>
+      <c r="AB74" s="13">
+        <f t="shared" si="48"/>
+        <v>7.2890758161338512E-2</v>
+      </c>
+      <c r="AC74" s="13">
         <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="X74" s="13">
-        <f t="shared" si="49"/>
-        <v>5.8016228139711724E-2</v>
-      </c>
-      <c r="Y74" s="13">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="Z74" s="13">
-        <f t="shared" si="49"/>
-        <v>0.30030511730104892</v>
-      </c>
-      <c r="AA74" s="13">
-        <f t="shared" si="39"/>
-        <v>2.4336595854647348E-2</v>
-      </c>
-      <c r="AB74" s="13">
-        <f t="shared" si="40"/>
-        <v>7.2890758161338512E-2</v>
-      </c>
-      <c r="AC74" s="13">
-        <f t="shared" si="41"/>
         <v>0.47247580758644553</v>
       </c>
       <c r="AD74" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>1.9620679843561577E-2</v>
       </c>
     </row>
     <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B75" s="168" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F75" s="13">
-        <f>F$71*$F30</f>
+        <f t="shared" si="52"/>
         <v>40.860434286063295</v>
       </c>
       <c r="H75" s="13">
+        <f t="shared" si="56"/>
+        <v>101.68308235021857</v>
+      </c>
+      <c r="I75" s="13">
+        <f t="shared" si="53"/>
+        <v>39.579967731046786</v>
+      </c>
+      <c r="J75" s="13">
+        <f t="shared" si="53"/>
+        <v>80.788664674753946</v>
+      </c>
+      <c r="K75" s="13">
+        <f t="shared" si="57"/>
+        <v>159.969277768826</v>
+      </c>
+      <c r="L75" s="13">
+        <f t="shared" si="54"/>
+        <v>21.989592718875919</v>
+      </c>
+      <c r="N75" s="2">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="R75" s="110" t="s">
+        <v>505</v>
+      </c>
+      <c r="U75" s="13">
         <f t="shared" si="45"/>
-        <v>101.68308235021857</v>
-      </c>
-      <c r="I75" s="13">
-        <f>I$71*$F30</f>
-        <v>39.579967731046786</v>
-      </c>
-      <c r="J75" s="13">
-        <f>J$71*$F30</f>
-        <v>80.788664674753946</v>
-      </c>
-      <c r="K75" s="13">
-        <f t="shared" si="46"/>
-        <v>159.969277768826</v>
-      </c>
-      <c r="L75" s="13">
-        <f>L$71*$F30</f>
-        <v>21.989592718875919</v>
-      </c>
-      <c r="N75" s="2">
+        <v>0</v>
+      </c>
+      <c r="V75" s="13">
+        <f t="shared" ref="V75:Z75" si="61">D84/D$94*100</f>
+        <v>0</v>
+      </c>
+      <c r="W75" s="13">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="X75" s="13">
+        <f t="shared" si="61"/>
+        <v>0.14739522877318739</v>
+      </c>
+      <c r="Y75" s="13">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="Z75" s="13">
+        <f t="shared" si="61"/>
+        <v>0.76295103776401596</v>
+      </c>
+      <c r="AA75" s="13">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="R75" s="110" t="s">
-        <v>508</v>
-      </c>
-      <c r="U75" s="13">
-        <f>C84/C$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="V75" s="13">
-        <f t="shared" ref="V75:AD75" si="50">D84/D$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="W75" s="13">
+        <v>6.1829219661059011E-2</v>
+      </c>
+      <c r="AB75" s="13">
+        <f t="shared" si="48"/>
+        <v>0.18518525452514792</v>
+      </c>
+      <c r="AC75" s="13">
+        <f t="shared" si="49"/>
+        <v>1.2003655180977197</v>
+      </c>
+      <c r="AD75" s="13">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="X75" s="13">
-        <f t="shared" si="50"/>
-        <v>0.14739522877318739</v>
-      </c>
-      <c r="Y75" s="13">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="Z75" s="13">
-        <f t="shared" si="50"/>
-        <v>0.76295103776401596</v>
-      </c>
-      <c r="AA75" s="13">
-        <f t="shared" si="39"/>
-        <v>6.1829219661059011E-2</v>
-      </c>
-      <c r="AB75" s="13">
-        <f t="shared" si="40"/>
-        <v>0.18518525452514792</v>
-      </c>
-      <c r="AC75" s="13">
-        <f t="shared" si="41"/>
-        <v>1.2003655180977197</v>
-      </c>
-      <c r="AD75" s="13">
-        <f t="shared" si="42"/>
         <v>4.98480285078663E-2</v>
       </c>
     </row>
     <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B76" s="168" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F76" s="13">
-        <f>F$71*$F31</f>
+        <f t="shared" si="52"/>
         <v>8.44417533163824</v>
       </c>
       <c r="H76" s="13">
+        <f t="shared" si="56"/>
+        <v>21.01372123495803</v>
+      </c>
+      <c r="I76" s="13">
+        <f t="shared" si="53"/>
+        <v>8.1795554301178548</v>
+      </c>
+      <c r="J76" s="13">
+        <f t="shared" si="53"/>
+        <v>16.695702364456608</v>
+      </c>
+      <c r="K76" s="13">
+        <f t="shared" si="57"/>
+        <v>33.059086442853612</v>
+      </c>
+      <c r="L76" s="13">
+        <f t="shared" si="54"/>
+        <v>4.5443466187738757</v>
+      </c>
+      <c r="N76" s="2">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="R76" s="110" t="s">
+        <v>432</v>
+      </c>
+      <c r="U76" s="13">
         <f t="shared" si="45"/>
-        <v>21.01372123495803</v>
-      </c>
-      <c r="I76" s="13">
-        <f>I$71*$F31</f>
-        <v>8.1795554301178548</v>
-      </c>
-      <c r="J76" s="13">
-        <f>J$71*$F31</f>
-        <v>16.695702364456608</v>
-      </c>
-      <c r="K76" s="13">
-        <f t="shared" si="46"/>
-        <v>33.059086442853612</v>
-      </c>
-      <c r="L76" s="13">
-        <f>L$71*$F31</f>
-        <v>4.5443466187738757</v>
-      </c>
-      <c r="N76" s="2">
+        <v>0</v>
+      </c>
+      <c r="V76" s="13">
+        <f t="shared" ref="V76:Z76" si="62">D85/D$94*100</f>
+        <v>0</v>
+      </c>
+      <c r="W76" s="13">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="X76" s="13">
+        <f t="shared" si="62"/>
+        <v>0.3999503550702303</v>
+      </c>
+      <c r="Y76" s="13">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Z76" s="13">
+        <f t="shared" si="62"/>
+        <v>2.0702334871671719</v>
+      </c>
+      <c r="AA76" s="13">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="R76" s="110" t="s">
-        <v>435</v>
-      </c>
-      <c r="U76" s="13">
-        <f>C85/C$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="V76" s="13">
-        <f t="shared" ref="V76:AD76" si="51">D85/D$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="13">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X76" s="13">
-        <f t="shared" si="51"/>
-        <v>0.3999503550702303</v>
-      </c>
-      <c r="Y76" s="13">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="Z76" s="13">
-        <f t="shared" si="51"/>
-        <v>2.0702334871671719</v>
-      </c>
-      <c r="AA76" s="13">
-        <f t="shared" si="39"/>
         <v>0.16777081974076891</v>
       </c>
       <c r="AB76" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.50249189826270002</v>
       </c>
       <c r="AC76" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>3.2571380985201626</v>
       </c>
       <c r="AD76" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>0.13526039388934941</v>
       </c>
     </row>
     <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B77" s="168" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F77" s="13">
-        <f>F$71*$F32</f>
+        <f t="shared" si="52"/>
         <v>0.31557859171427982</v>
       </c>
       <c r="H77" s="13">
+        <f t="shared" si="56"/>
+        <v>6.0870856494830861</v>
+      </c>
+      <c r="I77" s="13">
+        <f t="shared" si="53"/>
+        <v>0.30568912677760457</v>
+      </c>
+      <c r="J77" s="13">
+        <f t="shared" si="53"/>
+        <v>0.62395746570006339</v>
+      </c>
+      <c r="K77" s="13">
+        <f t="shared" si="57"/>
+        <v>9.5762901021332123</v>
+      </c>
+      <c r="L77" s="13">
+        <f t="shared" si="54"/>
+        <v>0.16983286702266781</v>
+      </c>
+      <c r="N77" s="2">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="R77" s="110" t="s">
+        <v>507</v>
+      </c>
+      <c r="U77" s="13">
         <f t="shared" si="45"/>
-        <v>6.0870856494830861</v>
-      </c>
-      <c r="I77" s="13">
-        <f>I$71*$F32</f>
-        <v>0.30568912677760457</v>
-      </c>
-      <c r="J77" s="13">
-        <f>J$71*$F32</f>
-        <v>0.62395746570006339</v>
-      </c>
-      <c r="K77" s="13">
-        <f t="shared" si="46"/>
-        <v>9.5762901021332123</v>
-      </c>
-      <c r="L77" s="13">
-        <f>L$71*$F32</f>
-        <v>0.16983286702266781</v>
-      </c>
-      <c r="N77" s="2">
+        <v>0</v>
+      </c>
+      <c r="V77" s="13">
+        <f t="shared" ref="V77:Z77" si="63">D86/D$94*100</f>
+        <v>0</v>
+      </c>
+      <c r="W77" s="13">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="X77" s="13">
+        <f t="shared" si="63"/>
+        <v>1.440554116649367E-2</v>
+      </c>
+      <c r="Y77" s="13">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="Z77" s="13">
+        <f t="shared" si="63"/>
+        <v>7.4566338910747182E-2</v>
+      </c>
+      <c r="AA77" s="13">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="110" t="s">
-        <v>510</v>
-      </c>
-      <c r="U77" s="13">
-        <f>C86/C$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="V77" s="13">
-        <f t="shared" ref="V77:AD77" si="52">D86/D$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="W77" s="13">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="X77" s="13">
-        <f t="shared" si="52"/>
-        <v>1.440554116649367E-2</v>
-      </c>
-      <c r="Y77" s="13">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z77" s="13">
-        <f t="shared" si="52"/>
-        <v>7.4566338910747182E-2</v>
-      </c>
-      <c r="AA77" s="13">
-        <f t="shared" si="39"/>
         <v>6.0428236146649909E-3</v>
       </c>
       <c r="AB77" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>1.8098915614118617E-2</v>
       </c>
       <c r="AC77" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>0.1173166528504468</v>
       </c>
       <c r="AD77" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>4.8718525878718617E-3</v>
       </c>
     </row>
     <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B78" s="168" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F78" s="13">
-        <f>F$71*$F33</f>
+        <f t="shared" si="52"/>
         <v>0.89484480830822388</v>
       </c>
       <c r="H78" s="13">
+        <f t="shared" si="56"/>
+        <v>17.260350144724228</v>
+      </c>
+      <c r="I78" s="13">
+        <f t="shared" si="53"/>
+        <v>0.8668025500946428</v>
+      </c>
+      <c r="J78" s="13">
+        <f t="shared" si="53"/>
+        <v>1.769274321663669</v>
+      </c>
+      <c r="K78" s="13">
+        <f t="shared" si="57"/>
+        <v>27.154229424110795</v>
+      </c>
+      <c r="L78" s="13">
+        <f t="shared" si="54"/>
+        <v>0.48157277878003302</v>
+      </c>
+      <c r="N78" s="2">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="R78" s="110" t="s">
+        <v>508</v>
+      </c>
+      <c r="U78" s="13">
         <f t="shared" si="45"/>
-        <v>17.260350144724228</v>
-      </c>
-      <c r="I78" s="13">
-        <f>I$71*$F33</f>
-        <v>0.8668025500946428</v>
-      </c>
-      <c r="J78" s="13">
-        <f>J$71*$F33</f>
-        <v>1.769274321663669</v>
-      </c>
-      <c r="K78" s="13">
-        <f t="shared" si="46"/>
-        <v>27.154229424110795</v>
-      </c>
-      <c r="L78" s="13">
-        <f>L$71*$F33</f>
-        <v>0.48157277878003302</v>
-      </c>
-      <c r="N78" s="2">
+        <v>0</v>
+      </c>
+      <c r="V78" s="13">
+        <f t="shared" ref="V78:Z78" si="64">D87/D$94*100</f>
+        <v>0</v>
+      </c>
+      <c r="W78" s="13">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="X78" s="13">
+        <f t="shared" si="64"/>
+        <v>8.9328030506468023E-3</v>
+      </c>
+      <c r="Y78" s="13">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="13">
+        <f t="shared" si="64"/>
+        <v>4.6238208755861092E-2</v>
+      </c>
+      <c r="AA78" s="13">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="R78" s="110" t="s">
-        <v>511</v>
-      </c>
-      <c r="U78" s="13">
-        <f>C87/C$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="V78" s="13">
-        <f t="shared" ref="V78:AD78" si="53">D87/D$94*100</f>
-        <v>0</v>
-      </c>
-      <c r="W78" s="13">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="X78" s="13">
-        <f t="shared" si="53"/>
-        <v>8.9328030506468023E-3</v>
-      </c>
-      <c r="Y78" s="13">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="Z78" s="13">
-        <f t="shared" si="53"/>
-        <v>4.6238208755861092E-2</v>
-      </c>
-      <c r="AA78" s="13">
-        <f t="shared" si="39"/>
         <v>3.7471242902802114E-3</v>
       </c>
       <c r="AB78" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>1.1223045822620041E-2</v>
       </c>
       <c r="AC78" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>7.2747461713666306E-2</v>
       </c>
       <c r="AD78" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>3.0210110926249881E-3</v>
       </c>
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F79" s="13">
-        <f>F$71*$F34</f>
+        <f t="shared" si="52"/>
         <v>10.376263400871563</v>
       </c>
       <c r="G79" s="13"/>
       <c r="H79" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>200.14413430137571</v>
       </c>
       <c r="I79" s="13">
-        <f>I$71*$F34</f>
+        <f t="shared" si="53"/>
         <v>10.05109656202106</v>
       </c>
       <c r="J79" s="13">
-        <f>J$71*$F34</f>
+        <f t="shared" si="53"/>
         <v>20.5157991861055</v>
       </c>
       <c r="K79" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>314.86961128484285</v>
       </c>
       <c r="L79" s="13">
-        <f>L$71*$F34</f>
+        <f t="shared" si="54"/>
         <v>5.5841258203848394</v>
       </c>
       <c r="N79" s="2">
@@ -35977,76 +35732,76 @@
         <v>19.88391208330204</v>
       </c>
       <c r="R79" s="110" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="U79" s="13">
-        <f>C88/C$94*100</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="V79" s="13">
-        <f t="shared" ref="V79:AD79" si="54">D88/D$94*100</f>
+        <f t="shared" ref="V79:Z79" si="65">D88/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W79" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="X79" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="65"/>
         <v>9.9253367229408854E-4</v>
       </c>
       <c r="Y79" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="Z79" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="65"/>
         <v>5.1375787506512324E-3</v>
       </c>
       <c r="AA79" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>4.1634714336446778E-4</v>
       </c>
       <c r="AB79" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>1.2470050914022261E-3</v>
       </c>
       <c r="AC79" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>8.0830513015184777E-3</v>
       </c>
       <c r="AD79" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>3.3566789918055401E-4</v>
       </c>
     </row>
     <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F80" s="13">
-        <f>F$71*$F35</f>
+        <f t="shared" si="52"/>
         <v>2.917729407114225</v>
       </c>
       <c r="G80" s="13"/>
       <c r="H80" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>56.279067305046688</v>
       </c>
       <c r="I80" s="13">
-        <f>I$71*$F35</f>
+        <f t="shared" si="53"/>
         <v>2.8262948693351628</v>
       </c>
       <c r="J80" s="13">
-        <f>J$71*$F35</f>
+        <f t="shared" si="53"/>
         <v>5.7688927394347127</v>
       </c>
       <c r="K80" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>88.539032670975232</v>
       </c>
       <c r="L80" s="13">
-        <f>L$71*$F35</f>
+        <f t="shared" si="54"/>
         <v>1.5702153549604523</v>
       </c>
       <c r="N80" s="2">
@@ -36054,153 +35809,153 @@
         <v>0</v>
       </c>
       <c r="R80" s="110" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="U80" s="13">
-        <f>C89/C$94*100</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="V80" s="13">
-        <f t="shared" ref="V80:AD80" si="55">D89/D$94*100</f>
+        <f t="shared" ref="V80:Z80" si="66">D89/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W80" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="X80" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v>8.213952477230968E-2</v>
       </c>
       <c r="Y80" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="Z80" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v>0.42517275618813499</v>
       </c>
       <c r="AA80" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>3.4455814901696358E-2</v>
       </c>
       <c r="AB80" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.10319892257124332</v>
       </c>
       <c r="AC80" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>0.66893246158826714</v>
       </c>
       <c r="AD80" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>2.7779008903831705E-2</v>
       </c>
     </row>
     <row r="81" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B81" s="93" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F81" s="13">
-        <f>F$71*$F36</f>
+        <f t="shared" si="52"/>
         <v>6.9507065664530963</v>
       </c>
       <c r="G81" s="13"/>
       <c r="H81" s="13">
+        <f t="shared" si="56"/>
+        <v>134.06976045045198</v>
+      </c>
+      <c r="I81" s="13">
+        <f t="shared" si="53"/>
+        <v>6.732888340886352</v>
+      </c>
+      <c r="J81" s="13">
+        <f t="shared" si="53"/>
+        <v>13.742837340358847</v>
+      </c>
+      <c r="K81" s="13">
+        <f t="shared" si="57"/>
+        <v>210.92046242294322</v>
+      </c>
+      <c r="L81" s="13">
+        <f t="shared" si="54"/>
+        <v>3.7406162997355099</v>
+      </c>
+      <c r="N81" s="2">
+        <f t="shared" ref="N81" si="67">I36*100</f>
+        <v>0</v>
+      </c>
+      <c r="R81" s="110" t="s">
+        <v>454</v>
+      </c>
+      <c r="U81" s="13">
         <f t="shared" si="45"/>
-        <v>134.06976045045198</v>
-      </c>
-      <c r="I81" s="13">
-        <f>I$71*$F36</f>
-        <v>6.732888340886352</v>
-      </c>
-      <c r="J81" s="13">
-        <f>J$71*$F36</f>
-        <v>13.742837340358847</v>
-      </c>
-      <c r="K81" s="13">
-        <f t="shared" si="46"/>
-        <v>210.92046242294322</v>
-      </c>
-      <c r="L81" s="13">
-        <f>L$71*$F36</f>
-        <v>3.7406162997355099</v>
-      </c>
-      <c r="N81" s="2">
-        <f t="shared" ref="N81" si="56">I36*100</f>
         <v>0</v>
       </c>
-      <c r="R81" s="110" t="s">
-        <v>457</v>
-      </c>
-      <c r="U81" s="13">
-        <f>C90/C$94*100</f>
+      <c r="V81" s="13">
+        <f t="shared" ref="V81:Z81" si="68">D90/D$94*100</f>
         <v>0</v>
       </c>
-      <c r="V81" s="13">
-        <f t="shared" ref="V81:AD81" si="57">D90/D$94*100</f>
+      <c r="W81" s="13">
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="W81" s="13">
-        <f t="shared" si="57"/>
+      <c r="X81" s="13">
+        <f t="shared" si="68"/>
+        <v>0.15292217782221385</v>
+      </c>
+      <c r="Y81" s="13">
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="X81" s="13">
-        <f t="shared" si="57"/>
-        <v>0.15292217782221385</v>
-      </c>
-      <c r="Y81" s="13">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
       <c r="Z81" s="13">
-        <f t="shared" si="57"/>
+        <f t="shared" si="68"/>
         <v>0.79155977596891625</v>
       </c>
       <c r="AA81" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>6.4147659339548135E-2</v>
       </c>
       <c r="AB81" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.19212923415671709</v>
       </c>
       <c r="AC81" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>1.2453761952678961</v>
       </c>
       <c r="AD81" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>5.1717203758995696E-2</v>
       </c>
     </row>
     <row r="82" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F82" s="13">
-        <f>F$71*$F37</f>
+        <f t="shared" si="52"/>
         <v>2.3682117304623489</v>
       </c>
       <c r="G82" s="13"/>
       <c r="H82" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>45.679612045694284</v>
       </c>
       <c r="I82" s="13">
-        <f>I$71*$F37</f>
+        <f t="shared" si="53"/>
         <v>2.2939977391272368</v>
       </c>
       <c r="J82" s="13">
-        <f>J$71*$F37</f>
+        <f t="shared" si="53"/>
         <v>4.6823942700089853</v>
       </c>
       <c r="K82" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>71.863818236172619</v>
       </c>
       <c r="L82" s="13">
-        <f>L$71*$F37</f>
+        <f t="shared" si="54"/>
         <v>1.2744850204074685</v>
       </c>
       <c r="N82" s="2">
@@ -36208,187 +35963,187 @@
         <v>100</v>
       </c>
       <c r="R82" s="110" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="U82" s="13">
-        <f>C91/C$94*100</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="V82" s="13">
-        <f t="shared" ref="V82:AD82" si="58">D91/D$94*100</f>
+        <f t="shared" ref="V82:Z82" si="69">D91/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W82" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="X82" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v>0.14960153780340887</v>
       </c>
       <c r="Y82" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Z82" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v>0.77437139226426754</v>
       </c>
       <c r="AA82" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>6.2754720213588133E-2</v>
       </c>
       <c r="AB82" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.1879572295932922</v>
       </c>
       <c r="AC82" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>1.2183333811295727</v>
       </c>
       <c r="AD82" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>5.059418668646571E-2</v>
       </c>
     </row>
     <row r="83" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B83" s="110" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F83" s="13">
-        <f>F$71*$F38</f>
+        <f t="shared" si="52"/>
         <v>1.1977083633723378</v>
       </c>
       <c r="G83" s="13"/>
       <c r="H83" s="13">
+        <f t="shared" si="56"/>
+        <v>23.102179876480324</v>
+      </c>
+      <c r="I83" s="13">
+        <f t="shared" si="53"/>
+        <v>1.1601750985219215</v>
+      </c>
+      <c r="J83" s="13">
+        <f t="shared" si="53"/>
+        <v>2.3680917992503945</v>
+      </c>
+      <c r="K83" s="13">
+        <f t="shared" si="57"/>
+        <v>36.344679412819943</v>
+      </c>
+      <c r="L83" s="13">
+        <f t="shared" si="54"/>
+        <v>0.64456287767680998</v>
+      </c>
+      <c r="N83" s="2">
+        <f t="shared" ref="N83:N84" si="70">I38*100</f>
+        <v>100</v>
+      </c>
+      <c r="R83" s="110" t="s">
+        <v>511</v>
+      </c>
+      <c r="U83" s="13">
         <f t="shared" si="45"/>
-        <v>23.102179876480324</v>
-      </c>
-      <c r="I83" s="13">
-        <f>I$71*$F38</f>
-        <v>1.1601750985219215</v>
-      </c>
-      <c r="J83" s="13">
-        <f>J$71*$F38</f>
-        <v>2.3680917992503945</v>
-      </c>
-      <c r="K83" s="13">
-        <f t="shared" si="46"/>
-        <v>36.344679412819943</v>
-      </c>
-      <c r="L83" s="13">
-        <f>L$71*$F38</f>
-        <v>0.64456287767680998</v>
-      </c>
-      <c r="N83" s="2">
-        <f t="shared" ref="N83:N84" si="59">I38*100</f>
-        <v>100</v>
-      </c>
-      <c r="R83" s="110" t="s">
-        <v>514</v>
-      </c>
-      <c r="U83" s="13">
-        <f>C92/C$94*100</f>
         <v>0</v>
       </c>
       <c r="V83" s="13">
-        <f t="shared" ref="V83:AD83" si="60">D92/D$94*100</f>
+        <f t="shared" ref="V83:Z83" si="71">D92/D$94*100</f>
         <v>0</v>
       </c>
       <c r="W83" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X83" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>8.3111965446338212E-2</v>
       </c>
       <c r="Y83" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="Z83" s="13">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>0.43020632903570405</v>
       </c>
       <c r="AA83" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>3.4863733451993388E-2</v>
       </c>
       <c r="AB83" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.10442068310738449</v>
       </c>
       <c r="AC83" s="13">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>0.67685187840531824</v>
       </c>
       <c r="AD83" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>2.8107881492480925E-2</v>
       </c>
     </row>
     <row r="84" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F84" s="13">
-        <f>F$71*$F39</f>
+        <f t="shared" si="52"/>
         <v>3.0428813434354844</v>
       </c>
       <c r="G84" s="13"/>
       <c r="H84" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>58.693079457923922</v>
       </c>
       <c r="I84" s="13">
-        <f>I$71*$F39</f>
+        <f t="shared" si="53"/>
         <v>2.9475248485956382</v>
       </c>
       <c r="J84" s="13">
-        <f>J$71*$F39</f>
+        <f t="shared" si="53"/>
         <v>6.016341353075684</v>
       </c>
       <c r="K84" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>92.336791075769597</v>
       </c>
       <c r="L84" s="13">
-        <f>L$71*$F39</f>
+        <f t="shared" si="54"/>
         <v>1.6375675541176171</v>
       </c>
       <c r="N84" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>100</v>
       </c>
     </row>
     <row r="85" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F85" s="13">
-        <f>F$71*$F40</f>
+        <f t="shared" si="52"/>
         <v>8.2567223096232656</v>
       </c>
       <c r="G85" s="13"/>
       <c r="H85" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>159.26104369012054</v>
       </c>
       <c r="I85" s="13">
-        <f>I$71*$F40</f>
+        <f t="shared" si="53"/>
         <v>7.9979767295466146</v>
       </c>
       <c r="J85" s="13">
-        <f>J$71*$F40</f>
+        <f t="shared" si="53"/>
         <v>16.325072937666537</v>
       </c>
       <c r="K85" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>250.55174909106466</v>
       </c>
       <c r="L85" s="13">
-        <f>L$71*$F40</f>
+        <f t="shared" si="54"/>
         <v>4.4434662517377941</v>
       </c>
       <c r="N85" s="2">
@@ -36400,103 +36155,103 @@
         <v>100</v>
       </c>
       <c r="V85" s="2">
-        <f t="shared" ref="V85:AD85" si="61">SUM(V56:V83)</f>
+        <f t="shared" ref="V85:AD85" si="72">SUM(V56:V83)</f>
         <v>100</v>
       </c>
       <c r="W85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>100</v>
       </c>
       <c r="X85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>99.999999999999986</v>
       </c>
       <c r="Y85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>99.999999999999986</v>
       </c>
       <c r="Z85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>100.00000000000001</v>
       </c>
       <c r="AA85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>99.999999999999943</v>
       </c>
       <c r="AB85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>99.999999999999957</v>
       </c>
       <c r="AC85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>99.999999999999986</v>
       </c>
       <c r="AD85" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>100</v>
       </c>
     </row>
     <row r="86" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F86" s="13">
-        <f>F$71*$F41</f>
+        <f t="shared" si="52"/>
         <v>0.29739329300182427</v>
       </c>
       <c r="G86" s="13"/>
       <c r="H86" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>5.7363157502233415</v>
       </c>
       <c r="I86" s="13">
-        <f>I$71*$F41</f>
+        <f t="shared" si="53"/>
         <v>0.28807371106324103</v>
       </c>
       <c r="J86" s="13">
-        <f>J$71*$F41</f>
+        <f t="shared" si="53"/>
         <v>0.58800175388835829</v>
       </c>
       <c r="K86" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>9.0244538856192218</v>
       </c>
       <c r="L86" s="13">
-        <f>L$71*$F41</f>
+        <f t="shared" si="54"/>
         <v>0.16004620373469608</v>
       </c>
       <c r="N86" s="2">
-        <f t="shared" ref="N86" si="62">I41*100</f>
+        <f t="shared" ref="N86" si="73">I41*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="87" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B87" s="110" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F87" s="13">
-        <f>F$71*$F42</f>
+        <f t="shared" si="52"/>
         <v>0.18441207340044716</v>
       </c>
       <c r="G87" s="13"/>
       <c r="H87" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>3.5570603173348565</v>
       </c>
       <c r="I87" s="13">
-        <f>I$71*$F42</f>
+        <f t="shared" si="53"/>
         <v>0.17863304788453227</v>
       </c>
       <c r="J87" s="13">
-        <f>J$71*$F42</f>
+        <f t="shared" si="53"/>
         <v>0.36461690680087544</v>
       </c>
       <c r="K87" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>5.5960181063785868</v>
       </c>
       <c r="L87" s="13">
-        <f>L$71*$F42</f>
+        <f t="shared" si="54"/>
         <v>9.9243839606041981E-2</v>
       </c>
       <c r="N87" s="2">
@@ -36511,99 +36266,99 @@
     </row>
     <row r="88" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F88" s="13">
-        <f>F$71*$F43</f>
+        <f t="shared" si="52"/>
         <v>2.0490230377827452E-2</v>
       </c>
       <c r="G88" s="13"/>
       <c r="H88" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>0.3952289241483174</v>
       </c>
       <c r="I88" s="13">
-        <f>I$71*$F43</f>
+        <f t="shared" si="53"/>
         <v>1.9848116431614687E-2</v>
       </c>
       <c r="J88" s="13">
-        <f>J$71*$F43</f>
+        <f t="shared" si="53"/>
         <v>4.0512989644541697E-2</v>
       </c>
       <c r="K88" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>0.6217797895976207</v>
       </c>
       <c r="L88" s="13">
-        <f>L$71*$F43</f>
+        <f t="shared" si="54"/>
         <v>1.1027093289560214E-2</v>
       </c>
       <c r="N88" s="2">
-        <f t="shared" ref="N88:N89" si="63">I43*100</f>
+        <f t="shared" ref="N88:N89" si="74">I43*100</f>
         <v>40.587012896078654</v>
       </c>
     </row>
     <row r="89" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B89" s="93" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F89" s="13">
-        <f>F$71*$F44</f>
+        <f t="shared" si="52"/>
         <v>1.6957185762975293</v>
       </c>
       <c r="G89" s="13"/>
       <c r="H89" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>32.708125590115941</v>
       </c>
       <c r="I89" s="13">
-        <f>I$71*$F44</f>
+        <f t="shared" si="53"/>
         <v>1.6425788835456636</v>
       </c>
       <c r="J89" s="13">
-        <f>J$71*$F44</f>
+        <f t="shared" si="53"/>
         <v>3.3527504500846321</v>
       </c>
       <c r="K89" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>51.456890437307393</v>
       </c>
       <c r="L89" s="13">
-        <f>L$71*$F44</f>
+        <f t="shared" si="54"/>
         <v>0.91257377730155609</v>
       </c>
       <c r="N89" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="74"/>
         <v>26.716313113044972</v>
       </c>
     </row>
     <row r="90" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B90" s="162" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F90" s="13">
-        <f>F$71*$F45</f>
+        <f t="shared" si="52"/>
         <v>3.1569817134907492</v>
       </c>
       <c r="G90" s="13"/>
       <c r="H90" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>60.893921794507143</v>
       </c>
       <c r="I90" s="13">
-        <f>I$71*$F45</f>
+        <f t="shared" si="53"/>
         <v>3.0580495907770557</v>
       </c>
       <c r="J90" s="13">
-        <f>J$71*$F45</f>
+        <f t="shared" si="53"/>
         <v>6.2419389683904152</v>
       </c>
       <c r="K90" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>95.799187680287133</v>
       </c>
       <c r="L90" s="13">
-        <f>L$71*$F45</f>
+        <f t="shared" si="54"/>
         <v>1.698972204127519</v>
       </c>
       <c r="N90" s="2">
@@ -36613,69 +36368,69 @@
     </row>
     <row r="91" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F91" s="13">
-        <f>F$71*$F46</f>
+        <f t="shared" si="52"/>
         <v>3.0884291989650889</v>
       </c>
       <c r="G91" s="13"/>
       <c r="H91" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>59.571636194782634</v>
       </c>
       <c r="I91" s="13">
-        <f>I$71*$F46</f>
+        <f t="shared" si="53"/>
         <v>2.9916453451977763</v>
       </c>
       <c r="J91" s="13">
-        <f>J$71*$F46</f>
+        <f t="shared" si="53"/>
         <v>6.1063979198090061</v>
       </c>
       <c r="K91" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>93.718949085006244</v>
       </c>
       <c r="L91" s="13">
-        <f>L$71*$F46</f>
+        <f t="shared" si="54"/>
         <v>1.6620797456744218</v>
       </c>
       <c r="N91" s="2">
-        <f t="shared" ref="N91:N92" si="64">I46*100</f>
+        <f t="shared" ref="N91:N92" si="75">I46*100</f>
         <v>46.986991038291379</v>
       </c>
     </row>
     <row r="92" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F92" s="13">
-        <f>F$71*$F47</f>
+        <f t="shared" si="52"/>
         <v>1.7157939994250484</v>
       </c>
       <c r="G92" s="13"/>
       <c r="H92" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="56"/>
         <v>33.095353441545903</v>
       </c>
       <c r="I92" s="13">
-        <f>I$71*$F47</f>
+        <f t="shared" si="53"/>
         <v>1.6620251917765414</v>
       </c>
       <c r="J92" s="13">
-        <f>J$71*$F47</f>
+        <f t="shared" si="53"/>
         <v>3.3924432887827791</v>
       </c>
       <c r="K92" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="57"/>
         <v>52.06608282500347</v>
       </c>
       <c r="L92" s="13">
-        <f>L$71*$F47</f>
+        <f t="shared" si="54"/>
         <v>0.9233776364857893</v>
       </c>
       <c r="N92" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="75"/>
         <v>46.986991038291379</v>
       </c>
     </row>
@@ -36694,43 +36449,43 @@
         <v>317</v>
       </c>
       <c r="C94" s="12">
-        <f>SUM(C56:C61,C63:C67,C69:C70,C72:C92)</f>
+        <f t="shared" ref="C94:L94" si="76">SUM(C56:C61,C63:C67,C69:C70,C72:C92)</f>
         <v>4683.2228452868276</v>
       </c>
       <c r="D94" s="12">
-        <f>SUM(D56:D61,D63:D67,D69:D70,D72:D92)</f>
+        <f t="shared" si="76"/>
         <v>3588.2395719012102</v>
       </c>
       <c r="E94" s="12">
-        <f>SUM(E56:E61,E63:E67,E69:E70,E72:E92)</f>
+        <f t="shared" si="76"/>
         <v>3648.7073963999328</v>
       </c>
       <c r="F94" s="12">
-        <f>SUM(F56:F61,F63:F67,F69:F70,F72:F92)</f>
+        <f t="shared" si="76"/>
         <v>2064.4367994556237</v>
       </c>
       <c r="G94" s="12">
-        <f>SUM(G56:G61,G63:G67,G69:G70,G72:G92)</f>
+        <f t="shared" si="76"/>
         <v>2073.84</v>
       </c>
       <c r="H94" s="12">
-        <f>SUM(H56:H61,H63:H67,H69:H70,H72:H92)</f>
+        <f t="shared" si="76"/>
         <v>7692.9024999999992</v>
       </c>
       <c r="I94" s="12">
-        <f>SUM(I56:I61,I63:I67,I69:I70,I72:I92)</f>
+        <f t="shared" si="76"/>
         <v>4767.2037019934032</v>
       </c>
       <c r="J94" s="12">
-        <f>SUM(J56:J61,J63:J67,J69:J70,J72:J92)</f>
+        <f t="shared" si="76"/>
         <v>3248.8231141851916</v>
       </c>
       <c r="K94" s="12">
-        <f>SUM(K56:K61,K63:K67,K69:K70,K72:K92)</f>
+        <f t="shared" si="76"/>
         <v>7692.3895000000002</v>
       </c>
       <c r="L94" s="12">
-        <f>SUM(L56:L61,L63:L67,L69:L70,L72:L92)</f>
+        <f t="shared" si="76"/>
         <v>3285.1199999999994</v>
       </c>
     </row>

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="13" r:id="rId1"/>
@@ -57,7 +57,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId13"/>
+    <pivotCache cacheId="0" r:id="rId13"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -14549,7 +14549,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="L3:O43" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0">
@@ -25458,7 +25458,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -25512,30 +25512,38 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <f>D2*1.06</f>
-        <v>1.06</v>
+        <f>D2*1.01^5</f>
+        <v>1.0510100500999999</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2:J2" si="0">E2*1.06</f>
-        <v>1.1236000000000002</v>
+        <f>E2*1.0081^5</f>
+        <v>1.0942711329791557</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1910160000000003</v>
+        <f>F2*1.0061^5</f>
+        <v>1.1280560721959558</v>
       </c>
       <c r="H2" s="1">
-        <f t="shared" si="0"/>
-        <v>1.2624769600000003</v>
+        <f>G2*1.004^5</f>
+        <v>1.1507984060123795</v>
       </c>
       <c r="I2" s="1">
-        <f t="shared" si="0"/>
-        <v>1.3382255776000005</v>
+        <f>H2*1.002^5</f>
+        <v>1.1623525141647169</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" si="0"/>
-        <v>1.4185191122560006</v>
+        <f>I2*1.001^5</f>
+        <v>1.1681759118900195</v>
       </c>
       <c r="K2" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\prod_parameters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="13" r:id="rId1"/>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3605" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="541">
   <si>
     <t>value</t>
   </si>
@@ -1314,9 +1314,6 @@
     <t>Ekvation baserad på tabell ovan</t>
   </si>
   <si>
-    <t>Need these for feed energy requrements</t>
-  </si>
-  <si>
     <t>Total incl. for calves</t>
   </si>
   <si>
@@ -1832,6 +1829,18 @@
   <si>
     <t>share of males slaughtered as steers</t>
   </si>
+  <si>
+    <t>milk kg x 0,25 + fat kg x 12,2 + protein kg x 7,7</t>
+  </si>
+  <si>
+    <t>Hessle (2016)  in Bertilsson (2016)</t>
+  </si>
+  <si>
+    <t>Assumes same as dairy cows</t>
+  </si>
+  <si>
+    <t>Converted from ECM. 2013 kg ECM/cow/year</t>
+  </si>
 </sst>
 </file>
 
@@ -1844,7 +1853,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2145,6 +2154,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2743,7 +2758,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2993,7 +3008,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3037,6 +3051,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="13" fillId="37" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -17275,7 +17293,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L431"/>
+  <dimension ref="A1:O431"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -17292,7 +17310,7 @@
     <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>51</v>
       </c>
@@ -17300,7 +17318,7 @@
         <v>295</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>52</v>
@@ -17330,7 +17348,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="94" t="s">
         <v>297</v>
       </c>
@@ -17346,7 +17364,7 @@
       <c r="K2" s="95"/>
       <c r="L2" s="95"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="97" t="s">
         <v>303</v>
       </c>
@@ -17362,7 +17380,7 @@
       <c r="K3" s="98"/>
       <c r="L3" s="98"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -17380,13 +17398,13 @@
         <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -17407,7 +17425,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -17428,7 +17446,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -17449,7 +17467,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -17470,7 +17488,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -17491,7 +17509,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -17511,7 +17529,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="100" t="s">
         <v>304</v>
       </c>
@@ -17527,52 +17545,65 @@
       <c r="K11" s="101"/>
       <c r="L11" s="101"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
       <c r="H12" t="s">
         <v>43</v>
       </c>
-      <c r="I12" s="111">
-        <v>0</v>
+      <c r="I12" s="2">
+        <f>2013/(0.25+I13/100*12.2+I14/100*7.7)</f>
+        <v>1973.6068081101221</v>
       </c>
       <c r="J12" t="s">
         <v>44</v>
       </c>
-      <c r="K12" s="93" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K12" s="110" t="s">
+        <v>540</v>
+      </c>
+      <c r="L12" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="157">
-        <v>0</v>
+      <c r="I13" s="195">
+        <v>4.1399999999999997</v>
       </c>
       <c r="J13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K13" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
       <c r="H14" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="157">
-        <v>0</v>
+      <c r="I14" s="195">
+        <v>3.44</v>
       </c>
       <c r="J14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>539</v>
+      </c>
+      <c r="O14" s="194" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -17586,7 +17617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -17831,13 +17862,13 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I30" s="93">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -17848,13 +17879,13 @@
         <v>5</v>
       </c>
       <c r="H31" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I31" s="93">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -17994,13 +18025,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I41" s="93">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -18011,13 +18042,13 @@
         <v>5</v>
       </c>
       <c r="H42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I42" s="93">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -18485,15 +18516,15 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H63" s="160" t="s">
+      <c r="H63" s="159" t="s">
         <v>300</v>
       </c>
-      <c r="I63" s="160">
+      <c r="I63" s="159">
         <v>0</v>
       </c>
-      <c r="J63" s="160"/>
-      <c r="K63" s="161" t="s">
-        <v>427</v>
+      <c r="J63" s="159"/>
+      <c r="K63" s="160" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -19134,12 +19165,12 @@
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H99" t="s">
         <v>36</v>
       </c>
-      <c r="I99" s="158">
+      <c r="I99" s="157">
         <v>0</v>
       </c>
       <c r="J99" s="93" t="s">
@@ -19154,7 +19185,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I100" s="13">
         <v>7.708382338966838</v>
@@ -19163,10 +19194,10 @@
         <v>9</v>
       </c>
       <c r="K100" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L100" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -19177,7 +19208,7 @@
         <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I101" s="13">
         <v>14.798145933014354</v>
@@ -19186,10 +19217,10 @@
         <v>9</v>
       </c>
       <c r="K101" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L101" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -19200,7 +19231,7 @@
         <v>5</v>
       </c>
       <c r="H102" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I102" s="13">
         <v>7.708382338966838</v>
@@ -19209,10 +19240,10 @@
         <v>9</v>
       </c>
       <c r="K102" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L102" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -19223,7 +19254,7 @@
         <v>5</v>
       </c>
       <c r="H103" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I103" s="13">
         <v>65.534646274777856</v>
@@ -19232,10 +19263,10 @@
         <v>9</v>
       </c>
       <c r="K103" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L103" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -19429,12 +19460,12 @@
         <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H115" t="s">
         <v>36</v>
       </c>
-      <c r="I115" s="158">
+      <c r="I115" s="157">
         <v>0</v>
       </c>
       <c r="J115" s="93" t="s">
@@ -19449,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I116" s="13">
         <v>2.4579700542883822</v>
@@ -19458,10 +19489,10 @@
         <v>9</v>
       </c>
       <c r="K116" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L116" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -19472,7 +19503,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I117" s="13">
         <v>9.2748685002842954</v>
@@ -19481,10 +19512,10 @@
         <v>9</v>
       </c>
       <c r="K117" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L117" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -19495,7 +19526,7 @@
         <v>5</v>
       </c>
       <c r="H118" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I118" s="13">
         <v>2.4579700542883822</v>
@@ -19504,10 +19535,10 @@
         <v>9</v>
       </c>
       <c r="K118" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L118" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -19518,7 +19549,7 @@
         <v>5</v>
       </c>
       <c r="H119" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I119" s="13">
         <v>35.940115438601644</v>
@@ -19527,10 +19558,10 @@
         <v>9</v>
       </c>
       <c r="K119" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L119" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -19675,7 +19706,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="94" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B129" s="94"/>
       <c r="C129" s="94"/>
@@ -19694,30 +19725,30 @@
         <v>18</v>
       </c>
       <c r="H130" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I130">
         <v>0.50700000000000001</v>
       </c>
       <c r="J130" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L130" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H131" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I131">
         <v>0.47499999999999998</v>
       </c>
       <c r="J131" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L131" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -19725,16 +19756,16 @@
         <v>18</v>
       </c>
       <c r="H132" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I132" s="13">
         <v>5</v>
       </c>
       <c r="J132" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L132" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -19745,20 +19776,20 @@
         <v>18</v>
       </c>
       <c r="H133" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I133" s="13">
         <f>(0.013+0.021+0.038) * 30.4</f>
         <v>2.1888000000000001</v>
       </c>
       <c r="J133" t="s">
+        <v>414</v>
+      </c>
+      <c r="K133" t="s">
         <v>415</v>
       </c>
-      <c r="K133" t="s">
-        <v>416</v>
-      </c>
       <c r="L133" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -19769,31 +19800,31 @@
         <v>18</v>
       </c>
       <c r="H134" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I134" s="13">
         <f>(8 * 7 * 3.6)/100</f>
         <v>2.016</v>
       </c>
       <c r="J134" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K134" t="s">
+        <v>416</v>
+      </c>
+      <c r="L134" t="s">
         <v>417</v>
-      </c>
-      <c r="L134" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H135" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I135" s="1">
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -19804,16 +19835,16 @@
         <v>18</v>
       </c>
       <c r="H136" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I136" s="1">
         <v>1.1100000000000001</v>
       </c>
       <c r="J136" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L136" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -19824,19 +19855,19 @@
         <v>35</v>
       </c>
       <c r="H137" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I137" s="1">
         <v>0.9</v>
       </c>
       <c r="J137" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L137" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -19844,16 +19875,16 @@
         <v>33</v>
       </c>
       <c r="H138" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I138" s="1">
         <v>1.05</v>
       </c>
       <c r="J138" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L138" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -19864,27 +19895,27 @@
         <v>34</v>
       </c>
       <c r="H139" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I139" s="1">
         <v>1.05</v>
       </c>
       <c r="J139" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L139" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H140" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I140" s="13">
         <v>0</v>
       </c>
       <c r="J140" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -19895,16 +19926,16 @@
         <v>18</v>
       </c>
       <c r="H141" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I141" s="13">
         <v>-13.6</v>
       </c>
       <c r="J141" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L141" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -19941,7 +19972,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="94" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B145" s="94"/>
       <c r="C145" s="94"/>
@@ -19958,15 +19989,15 @@
       <c r="L145" s="95"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H146" s="160" t="s">
+      <c r="H146" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I146" s="160">
+      <c r="I146" s="159">
         <v>0</v>
       </c>
-      <c r="J146" s="160"/>
-      <c r="K146" s="160" t="s">
-        <v>427</v>
+      <c r="J146" s="159"/>
+      <c r="K146" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -19996,29 +20027,29 @@
       <c r="F148" s="49"/>
       <c r="G148" s="49"/>
       <c r="H148" s="49"/>
-      <c r="I148" s="163"/>
+      <c r="I148" s="162"/>
       <c r="J148" s="49"/>
       <c r="K148" s="49"/>
       <c r="L148" s="49"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="160" t="s">
+      <c r="A149" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B149" s="160"/>
-      <c r="C149" s="160"/>
-      <c r="D149" s="160" t="s">
+      <c r="B149" s="159"/>
+      <c r="C149" s="159"/>
+      <c r="D149" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="H149" s="160" t="s">
+      <c r="H149" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I149" s="160">
+      <c r="I149" s="159">
         <v>0</v>
       </c>
-      <c r="J149" s="160"/>
-      <c r="K149" s="160" t="s">
-        <v>427</v>
+      <c r="J149" s="159"/>
+      <c r="K149" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -20029,7 +20060,7 @@
         <v>18</v>
       </c>
       <c r="E150" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H150" t="s">
         <v>326</v>
@@ -20038,8 +20069,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E150,Foderstater!$R$56:$R$83,0),MATCH(A150&amp;C150&amp;D150,Foderstater!$U$55:$AD$55,0))</f>
         <v>38.655760943285067</v>
       </c>
-      <c r="J150" s="160"/>
-      <c r="K150" s="160"/>
+      <c r="J150" s="159"/>
+      <c r="K150" s="159"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
@@ -20049,7 +20080,7 @@
         <v>18</v>
       </c>
       <c r="E151" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H151" t="s">
         <v>326</v>
@@ -20058,8 +20089,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E151,Foderstater!$R$56:$R$83,0),MATCH(A151&amp;C151&amp;D151,Foderstater!$U$55:$AD$55,0))</f>
         <v>9.2487848377124262</v>
       </c>
-      <c r="J151" s="160"/>
-      <c r="K151" s="160"/>
+      <c r="J151" s="159"/>
+      <c r="K151" s="159"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
@@ -20069,7 +20100,7 @@
         <v>18</v>
       </c>
       <c r="E152" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H152" t="s">
         <v>326</v>
@@ -20078,8 +20109,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E152,Foderstater!$R$56:$R$83,0),MATCH(A152&amp;C152&amp;D152,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J152" s="160"/>
-      <c r="K152" s="160"/>
+      <c r="J152" s="159"/>
+      <c r="K152" s="159"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
@@ -20089,7 +20120,7 @@
         <v>18</v>
       </c>
       <c r="E153" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H153" t="s">
         <v>326</v>
@@ -20098,8 +20129,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E153,Foderstater!$R$56:$R$83,0),MATCH(A153&amp;C153&amp;D153,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J153" s="160"/>
-      <c r="K153" s="160"/>
+      <c r="J153" s="159"/>
+      <c r="K153" s="159"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
@@ -20109,7 +20140,7 @@
         <v>18</v>
       </c>
       <c r="E154" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H154" t="s">
         <v>326</v>
@@ -20118,8 +20149,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E154,Foderstater!$R$56:$R$83,0),MATCH(A154&amp;C154&amp;D154,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.6959915324547534</v>
       </c>
-      <c r="J154" s="160"/>
-      <c r="K154" s="160"/>
+      <c r="J154" s="159"/>
+      <c r="K154" s="159"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
@@ -20129,7 +20160,7 @@
         <v>18</v>
       </c>
       <c r="E155" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H155" t="s">
         <v>326</v>
@@ -20138,8 +20169,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E155,Foderstater!$R$56:$R$83,0),MATCH(A155&amp;C155&amp;D155,Foderstater!$U$55:$AD$55,0))</f>
         <v>10.178212969682118</v>
       </c>
-      <c r="J155" s="160"/>
-      <c r="K155" s="160"/>
+      <c r="J155" s="159"/>
+      <c r="K155" s="159"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
@@ -20149,7 +20180,7 @@
         <v>18</v>
       </c>
       <c r="E156" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H156" t="s">
         <v>326</v>
@@ -20158,8 +20189,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E156,Foderstater!$R$56:$R$83,0),MATCH(A156&amp;C156&amp;D156,Foderstater!$U$55:$AD$55,0))</f>
         <v>6.522978613065411</v>
       </c>
-      <c r="J156" s="160"/>
-      <c r="K156" s="160"/>
+      <c r="J156" s="159"/>
+      <c r="K156" s="159"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
@@ -20169,7 +20200,7 @@
         <v>18</v>
       </c>
       <c r="E157" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H157" t="s">
         <v>326</v>
@@ -20178,8 +20209,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E157,Foderstater!$R$56:$R$83,0),MATCH(A157&amp;C157&amp;D157,Foderstater!$U$55:$AD$55,0))</f>
         <v>4.992523211434996</v>
       </c>
-      <c r="J157" s="160"/>
-      <c r="K157" s="160"/>
+      <c r="J157" s="159"/>
+      <c r="K157" s="159"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
@@ -20189,7 +20220,7 @@
         <v>18</v>
       </c>
       <c r="E158" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H158" t="s">
         <v>326</v>
@@ -20198,8 +20229,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E158,Foderstater!$R$56:$R$83,0),MATCH(A158&amp;C158&amp;D158,Foderstater!$U$55:$AD$55,0))</f>
         <v>13.174510208769105</v>
       </c>
-      <c r="J158" s="160"/>
-      <c r="K158" s="160"/>
+      <c r="J158" s="159"/>
+      <c r="K158" s="159"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
@@ -20209,7 +20240,7 @@
         <v>18</v>
       </c>
       <c r="E159" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H159" t="s">
         <v>326</v>
@@ -20218,8 +20249,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E159,Foderstater!$R$56:$R$83,0),MATCH(A159&amp;C159&amp;D159,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.7226307320294127</v>
       </c>
-      <c r="J159" s="160"/>
-      <c r="K159" s="160"/>
+      <c r="J159" s="159"/>
+      <c r="K159" s="159"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
@@ -20229,7 +20260,7 @@
         <v>18</v>
       </c>
       <c r="E160" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H160" t="s">
         <v>326</v>
@@ -20238,8 +20269,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E160,Foderstater!$R$56:$R$83,0),MATCH(A160&amp;C160&amp;D160,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J160" s="160"/>
-      <c r="K160" s="160"/>
+      <c r="J160" s="159"/>
+      <c r="K160" s="159"/>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
@@ -20249,7 +20280,7 @@
         <v>18</v>
       </c>
       <c r="E161" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H161" t="s">
         <v>326</v>
@@ -20258,8 +20289,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E161,Foderstater!$R$56:$R$83,0),MATCH(A161&amp;C161&amp;D161,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.15456668608878038</v>
       </c>
-      <c r="J161" s="160"/>
-      <c r="K161" s="160"/>
+      <c r="J161" s="159"/>
+      <c r="K161" s="159"/>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
@@ -20269,7 +20300,7 @@
         <v>18</v>
       </c>
       <c r="E162" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H162" t="s">
         <v>326</v>
@@ -20278,8 +20309,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E162,Foderstater!$R$56:$R$83,0),MATCH(A162&amp;C162&amp;D162,Foderstater!$U$55:$AD$55,0))</f>
         <v>7.9125995025714754E-2</v>
       </c>
-      <c r="J162" s="160"/>
-      <c r="K162" s="160"/>
+      <c r="J162" s="159"/>
+      <c r="K162" s="159"/>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
@@ -20289,7 +20320,7 @@
         <v>18</v>
       </c>
       <c r="E163" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H163" t="s">
         <v>326</v>
@@ -20298,8 +20329,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E163,Foderstater!$R$56:$R$83,0),MATCH(A163&amp;C163&amp;D163,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.22436720268746718</v>
       </c>
-      <c r="J163" s="160"/>
-      <c r="K163" s="160"/>
+      <c r="J163" s="159"/>
+      <c r="K163" s="159"/>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
@@ -20309,7 +20340,7 @@
         <v>18</v>
       </c>
       <c r="E164" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H164" t="s">
         <v>326</v>
@@ -20318,8 +20349,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E164,Foderstater!$R$56:$R$83,0),MATCH(A164&amp;C164&amp;D164,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.6016725715862865</v>
       </c>
-      <c r="J164" s="160"/>
-      <c r="K164" s="160"/>
+      <c r="J164" s="159"/>
+      <c r="K164" s="159"/>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
@@ -20329,7 +20360,7 @@
         <v>18</v>
       </c>
       <c r="E165" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H165" t="s">
         <v>326</v>
@@ -20338,8 +20369,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E165,Foderstater!$R$56:$R$83,0),MATCH(A165&amp;C165&amp;D165,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.73157130621435396</v>
       </c>
-      <c r="J165" s="160"/>
-      <c r="K165" s="160"/>
+      <c r="J165" s="159"/>
+      <c r="K165" s="159"/>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
@@ -20349,7 +20380,7 @@
         <v>18</v>
       </c>
       <c r="E166" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H166" t="s">
         <v>326</v>
@@ -20358,8 +20389,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E166,Foderstater!$R$56:$R$83,0),MATCH(A166&amp;C166&amp;D166,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.7427721260012328</v>
       </c>
-      <c r="J166" s="160"/>
-      <c r="K166" s="160"/>
+      <c r="J166" s="159"/>
+      <c r="K166" s="159"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
@@ -20369,7 +20400,7 @@
         <v>18</v>
       </c>
       <c r="E167" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H167" t="s">
         <v>326</v>
@@ -20378,8 +20409,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E167,Foderstater!$R$56:$R$83,0),MATCH(A167&amp;C167&amp;D167,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.59378904185636427</v>
       </c>
-      <c r="J167" s="160"/>
-      <c r="K167" s="160"/>
+      <c r="J167" s="159"/>
+      <c r="K167" s="159"/>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
@@ -20389,7 +20420,7 @@
         <v>18</v>
       </c>
       <c r="E168" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H168" t="s">
         <v>326</v>
@@ -20398,8 +20429,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E168,Foderstater!$R$56:$R$83,0),MATCH(A168&amp;C168&amp;D168,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.30030511730104892</v>
       </c>
-      <c r="J168" s="160"/>
-      <c r="K168" s="160"/>
+      <c r="J168" s="159"/>
+      <c r="K168" s="159"/>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
@@ -20409,7 +20440,7 @@
         <v>18</v>
       </c>
       <c r="E169" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H169" t="s">
         <v>326</v>
@@ -20418,8 +20449,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E169,Foderstater!$R$56:$R$83,0),MATCH(A169&amp;C169&amp;D169,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.76295103776401596</v>
       </c>
-      <c r="J169" s="160"/>
-      <c r="K169" s="160"/>
+      <c r="J169" s="159"/>
+      <c r="K169" s="159"/>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
@@ -20429,7 +20460,7 @@
         <v>18</v>
       </c>
       <c r="E170" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H170" t="s">
         <v>326</v>
@@ -20438,8 +20469,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E170,Foderstater!$R$56:$R$83,0),MATCH(A170&amp;C170&amp;D170,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.0702334871671719</v>
       </c>
-      <c r="J170" s="160"/>
-      <c r="K170" s="160"/>
+      <c r="J170" s="159"/>
+      <c r="K170" s="159"/>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
@@ -20449,7 +20480,7 @@
         <v>18</v>
       </c>
       <c r="E171" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H171" t="s">
         <v>326</v>
@@ -20467,7 +20498,7 @@
         <v>18</v>
       </c>
       <c r="E172" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H172" t="s">
         <v>326</v>
@@ -20485,7 +20516,7 @@
         <v>18</v>
       </c>
       <c r="E173" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H173" t="s">
         <v>326</v>
@@ -20503,7 +20534,7 @@
         <v>18</v>
       </c>
       <c r="E174" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H174" t="s">
         <v>326</v>
@@ -20521,7 +20552,7 @@
         <v>18</v>
       </c>
       <c r="E175" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H175" t="s">
         <v>326</v>
@@ -20539,7 +20570,7 @@
         <v>18</v>
       </c>
       <c r="E176" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H176" t="s">
         <v>326</v>
@@ -20557,7 +20588,7 @@
         <v>18</v>
       </c>
       <c r="E177" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H177" t="s">
         <v>326</v>
@@ -20568,25 +20599,25 @@
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="160" t="s">
+      <c r="A179" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B179" s="160"/>
-      <c r="C179" s="160" t="s">
-        <v>433</v>
-      </c>
-      <c r="D179" s="160" t="s">
+      <c r="B179" s="159"/>
+      <c r="C179" s="159" t="s">
+        <v>432</v>
+      </c>
+      <c r="D179" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="H179" s="160" t="s">
+      <c r="H179" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I179" s="160">
+      <c r="I179" s="159">
         <v>0</v>
       </c>
-      <c r="J179" s="160"/>
-      <c r="K179" s="160" t="s">
-        <v>427</v>
+      <c r="J179" s="159"/>
+      <c r="K179" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -20594,13 +20625,13 @@
         <v>2</v>
       </c>
       <c r="C180" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D180" t="s">
         <v>18</v>
       </c>
       <c r="E180" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H180" t="s">
         <v>326</v>
@@ -20609,21 +20640,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E180,Foderstater!$R$56:$R$83,0),MATCH(A180&amp;C180&amp;D180,Foderstater!$U$55:$AD$55,0))</f>
         <v>21.053926091496013</v>
       </c>
-      <c r="J180" s="160"/>
-      <c r="K180" s="160"/>
+      <c r="J180" s="159"/>
+      <c r="K180" s="159"/>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>2</v>
       </c>
       <c r="C181" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D181" t="s">
         <v>18</v>
       </c>
       <c r="E181" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H181" t="s">
         <v>326</v>
@@ -20632,21 +20663,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E181,Foderstater!$R$56:$R$83,0),MATCH(A181&amp;C181&amp;D181,Foderstater!$U$55:$AD$55,0))</f>
         <v>9.7648461508611888</v>
       </c>
-      <c r="J181" s="160"/>
-      <c r="K181" s="160"/>
+      <c r="J181" s="159"/>
+      <c r="K181" s="159"/>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>2</v>
       </c>
       <c r="C182" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D182" t="s">
         <v>18</v>
       </c>
       <c r="E182" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H182" t="s">
         <v>326</v>
@@ -20655,21 +20686,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E182,Foderstater!$R$56:$R$83,0),MATCH(A182&amp;C182&amp;D182,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J182" s="160"/>
-      <c r="K182" s="160"/>
+      <c r="J182" s="159"/>
+      <c r="K182" s="159"/>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>2</v>
       </c>
       <c r="C183" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D183" t="s">
         <v>18</v>
       </c>
       <c r="E183" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H183" t="s">
         <v>326</v>
@@ -20678,21 +20709,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E183,Foderstater!$R$56:$R$83,0),MATCH(A183&amp;C183&amp;D183,Foderstater!$U$55:$AD$55,0))</f>
         <v>16.256327113961142</v>
       </c>
-      <c r="J183" s="160"/>
-      <c r="K183" s="160"/>
+      <c r="J183" s="159"/>
+      <c r="K183" s="159"/>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>2</v>
       </c>
       <c r="C184" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D184" t="s">
         <v>18</v>
       </c>
       <c r="E184" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H184" t="s">
         <v>326</v>
@@ -20701,21 +20732,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E184,Foderstater!$R$56:$R$83,0),MATCH(A184&amp;C184&amp;D184,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.6961713262179456</v>
       </c>
-      <c r="J184" s="160"/>
-      <c r="K184" s="160"/>
+      <c r="J184" s="159"/>
+      <c r="K184" s="159"/>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>2</v>
       </c>
       <c r="C185" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D185" t="s">
         <v>18</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H185" t="s">
         <v>326</v>
@@ -20724,21 +20755,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E185,Foderstater!$R$56:$R$83,0),MATCH(A185&amp;C185&amp;D185,Foderstater!$U$55:$AD$55,0))</f>
         <v>10.178891747486265</v>
       </c>
-      <c r="J185" s="160"/>
-      <c r="K185" s="160"/>
+      <c r="J185" s="159"/>
+      <c r="K185" s="159"/>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>2</v>
       </c>
       <c r="C186" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D186" t="s">
         <v>18</v>
       </c>
       <c r="E186" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H186" t="s">
         <v>326</v>
@@ -20747,21 +20778,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E186,Foderstater!$R$56:$R$83,0),MATCH(A186&amp;C186&amp;D186,Foderstater!$U$55:$AD$55,0))</f>
         <v>5.1917347110499525</v>
       </c>
-      <c r="J186" s="160"/>
-      <c r="K186" s="160"/>
+      <c r="J186" s="159"/>
+      <c r="K186" s="159"/>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>2</v>
       </c>
       <c r="C187" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D187" t="s">
         <v>18</v>
       </c>
       <c r="E187" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H187" t="s">
         <v>326</v>
@@ -20770,21 +20801,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E187,Foderstater!$R$56:$R$83,0),MATCH(A187&amp;C187&amp;D187,Foderstater!$U$55:$AD$55,0))</f>
         <v>3.8278564703417133</v>
       </c>
-      <c r="J187" s="160"/>
-      <c r="K187" s="160"/>
+      <c r="J187" s="159"/>
+      <c r="K187" s="159"/>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>2</v>
       </c>
       <c r="C188" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D188" t="s">
         <v>18</v>
       </c>
       <c r="E188" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H188" t="s">
         <v>326</v>
@@ -20793,21 +20824,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E188,Foderstater!$R$56:$R$83,0),MATCH(A188&amp;C188&amp;D188,Foderstater!$U$55:$AD$55,0))</f>
         <v>10.319020213721652</v>
       </c>
-      <c r="J188" s="160"/>
-      <c r="K188" s="160"/>
+      <c r="J188" s="159"/>
+      <c r="K188" s="159"/>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>2</v>
       </c>
       <c r="C189" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D189" t="s">
         <v>18</v>
       </c>
       <c r="E189" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H189" t="s">
         <v>326</v>
@@ -20816,21 +20847,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E189,Foderstater!$R$56:$R$83,0),MATCH(A189&amp;C189&amp;D189,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.1325181060325882</v>
       </c>
-      <c r="J189" s="160"/>
-      <c r="K189" s="160"/>
+      <c r="J189" s="159"/>
+      <c r="K189" s="159"/>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>2</v>
       </c>
       <c r="C190" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D190" t="s">
         <v>18</v>
       </c>
       <c r="E190" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H190" t="s">
         <v>326</v>
@@ -20839,21 +20870,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E190,Foderstater!$R$56:$R$83,0),MATCH(A190&amp;C190&amp;D190,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J190" s="160"/>
-      <c r="K190" s="160"/>
+      <c r="J190" s="159"/>
+      <c r="K190" s="159"/>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>2</v>
       </c>
       <c r="C191" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D191" t="s">
         <v>18</v>
       </c>
       <c r="E191" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H191" t="s">
         <v>326</v>
@@ -20862,21 +20893,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E191,Foderstater!$R$56:$R$83,0),MATCH(A191&amp;C191&amp;D191,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.24318273525305006</v>
       </c>
-      <c r="J191" s="160"/>
-      <c r="K191" s="160"/>
+      <c r="J191" s="159"/>
+      <c r="K191" s="159"/>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>2</v>
       </c>
       <c r="C192" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D192" t="s">
         <v>18</v>
       </c>
       <c r="E192" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H192" t="s">
         <v>326</v>
@@ -20885,21 +20916,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E192,Foderstater!$R$56:$R$83,0),MATCH(A192&amp;C192&amp;D192,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.12449044737182395</v>
       </c>
-      <c r="J192" s="160"/>
-      <c r="K192" s="160"/>
+      <c r="J192" s="159"/>
+      <c r="K192" s="159"/>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>2</v>
       </c>
       <c r="C193" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D193" t="s">
         <v>18</v>
       </c>
       <c r="E193" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H193" t="s">
         <v>326</v>
@@ -20908,21 +20939,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E193,Foderstater!$R$56:$R$83,0),MATCH(A193&amp;C193&amp;D193,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.35300122834537684</v>
       </c>
-      <c r="J193" s="160"/>
-      <c r="K193" s="160"/>
+      <c r="J193" s="159"/>
+      <c r="K193" s="159"/>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>2</v>
       </c>
       <c r="C194" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D194" t="s">
         <v>18</v>
       </c>
       <c r="E194" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H194" t="s">
         <v>326</v>
@@ -20931,21 +20962,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E194,Foderstater!$R$56:$R$83,0),MATCH(A194&amp;C194&amp;D194,Foderstater!$U$55:$AD$55,0))</f>
         <v>4.0932614148678095</v>
       </c>
-      <c r="J194" s="160"/>
-      <c r="K194" s="160"/>
+      <c r="J194" s="159"/>
+      <c r="K194" s="159"/>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>2</v>
       </c>
       <c r="C195" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D195" t="s">
         <v>18</v>
       </c>
       <c r="E195" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H195" t="s">
         <v>326</v>
@@ -20954,21 +20985,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E195,Foderstater!$R$56:$R$83,0),MATCH(A195&amp;C195&amp;D195,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.1509951838888972</v>
       </c>
-      <c r="J195" s="160"/>
-      <c r="K195" s="160"/>
+      <c r="J195" s="159"/>
+      <c r="K195" s="159"/>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>2</v>
       </c>
       <c r="C196" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D196" t="s">
         <v>18</v>
       </c>
       <c r="E196" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H196" t="s">
         <v>326</v>
@@ -20977,21 +21008,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E196,Foderstater!$R$56:$R$83,0),MATCH(A196&amp;C196&amp;D196,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.7419368509998514</v>
       </c>
-      <c r="J196" s="160"/>
-      <c r="K196" s="160"/>
+      <c r="J196" s="159"/>
+      <c r="K196" s="159"/>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>2</v>
       </c>
       <c r="C197" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D197" t="s">
         <v>18</v>
       </c>
       <c r="E197" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H197" t="s">
         <v>326</v>
@@ -21000,21 +21031,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E197,Foderstater!$R$56:$R$83,0),MATCH(A197&amp;C197&amp;D197,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.93421970164371715</v>
       </c>
-      <c r="J197" s="160"/>
-      <c r="K197" s="160"/>
+      <c r="J197" s="159"/>
+      <c r="K197" s="159"/>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>2</v>
       </c>
       <c r="C198" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D198" t="s">
         <v>18</v>
       </c>
       <c r="E198" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H198" t="s">
         <v>326</v>
@@ -21023,21 +21054,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E198,Foderstater!$R$56:$R$83,0),MATCH(A198&amp;C198&amp;D198,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.47247580758644553</v>
       </c>
-      <c r="J198" s="160"/>
-      <c r="K198" s="160"/>
+      <c r="J198" s="159"/>
+      <c r="K198" s="159"/>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>2</v>
       </c>
       <c r="C199" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D199" t="s">
         <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H199" t="s">
         <v>326</v>
@@ -21046,21 +21077,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E199,Foderstater!$R$56:$R$83,0),MATCH(A199&amp;C199&amp;D199,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.2003655180977197</v>
       </c>
-      <c r="J199" s="160"/>
-      <c r="K199" s="160"/>
+      <c r="J199" s="159"/>
+      <c r="K199" s="159"/>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>2</v>
       </c>
       <c r="C200" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D200" t="s">
         <v>18</v>
       </c>
       <c r="E200" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H200" t="s">
         <v>326</v>
@@ -21069,21 +21100,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E200,Foderstater!$R$56:$R$83,0),MATCH(A200&amp;C200&amp;D200,Foderstater!$U$55:$AD$55,0))</f>
         <v>3.2571380985201626</v>
       </c>
-      <c r="J200" s="160"/>
-      <c r="K200" s="160"/>
+      <c r="J200" s="159"/>
+      <c r="K200" s="159"/>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>2</v>
       </c>
       <c r="C201" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D201" t="s">
         <v>18</v>
       </c>
       <c r="E201" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H201" t="s">
         <v>326</v>
@@ -21098,13 +21129,13 @@
         <v>2</v>
       </c>
       <c r="C202" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D202" t="s">
         <v>18</v>
       </c>
       <c r="E202" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H202" t="s">
         <v>326</v>
@@ -21119,13 +21150,13 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D203" t="s">
         <v>18</v>
       </c>
       <c r="E203" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H203" t="s">
         <v>326</v>
@@ -21140,13 +21171,13 @@
         <v>2</v>
       </c>
       <c r="C204" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D204" t="s">
         <v>18</v>
       </c>
       <c r="E204" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H204" t="s">
         <v>326</v>
@@ -21161,13 +21192,13 @@
         <v>2</v>
       </c>
       <c r="C205" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D205" t="s">
         <v>18</v>
       </c>
       <c r="E205" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H205" t="s">
         <v>326</v>
@@ -21182,13 +21213,13 @@
         <v>2</v>
       </c>
       <c r="C206" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D206" t="s">
         <v>18</v>
       </c>
       <c r="E206" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H206" t="s">
         <v>326</v>
@@ -21203,13 +21234,13 @@
         <v>2</v>
       </c>
       <c r="C207" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D207" t="s">
         <v>18</v>
       </c>
       <c r="E207" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H207" t="s">
         <v>326</v>
@@ -21221,7 +21252,7 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="81" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B209" s="48"/>
       <c r="C209" s="48"/>
@@ -21230,27 +21261,27 @@
       <c r="F209" s="49"/>
       <c r="G209" s="49"/>
       <c r="H209" s="49"/>
-      <c r="I209" s="163"/>
+      <c r="I209" s="162"/>
       <c r="J209" s="49"/>
       <c r="K209" s="49"/>
       <c r="L209" s="49"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A210" s="160" t="s">
+      <c r="A210" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B210" s="160"/>
-      <c r="C210" s="160"/>
-      <c r="D210" s="160"/>
-      <c r="H210" s="160" t="s">
+      <c r="B210" s="159"/>
+      <c r="C210" s="159"/>
+      <c r="D210" s="159"/>
+      <c r="H210" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I210" s="160">
+      <c r="I210" s="159">
         <v>0</v>
       </c>
-      <c r="J210" s="160"/>
-      <c r="K210" s="160" t="s">
-        <v>427</v>
+      <c r="J210" s="159"/>
+      <c r="K210" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -21258,7 +21289,7 @@
         <v>2</v>
       </c>
       <c r="E211" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H211" t="s">
         <v>326</v>
@@ -21267,15 +21298,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E211,Foderstater!$R$56:$R$83,0),MATCH(A211&amp;C211&amp;D211,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J211" s="160"/>
-      <c r="K211" s="160"/>
+      <c r="J211" s="159"/>
+      <c r="K211" s="159"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H212" t="s">
         <v>326</v>
@@ -21284,15 +21315,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E212,Foderstater!$R$56:$R$83,0),MATCH(A212&amp;C212&amp;D212,Foderstater!$U$55:$AD$55,0))</f>
         <v>55.413619478612851</v>
       </c>
-      <c r="J212" s="160"/>
-      <c r="K212" s="160"/>
+      <c r="J212" s="159"/>
+      <c r="K212" s="159"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>2</v>
       </c>
       <c r="E213" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H213" t="s">
         <v>326</v>
@@ -21301,15 +21332,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E213,Foderstater!$R$56:$R$83,0),MATCH(A213&amp;C213&amp;D213,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J213" s="160"/>
-      <c r="K213" s="160"/>
+      <c r="J213" s="159"/>
+      <c r="K213" s="159"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>2</v>
       </c>
       <c r="E214" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H214" t="s">
         <v>326</v>
@@ -21318,15 +21349,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E214,Foderstater!$R$56:$R$83,0),MATCH(A214&amp;C214&amp;D214,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J214" s="160"/>
-      <c r="K214" s="160"/>
+      <c r="J214" s="159"/>
+      <c r="K214" s="159"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H215" t="s">
         <v>326</v>
@@ -21335,15 +21366,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E215,Foderstater!$R$56:$R$83,0),MATCH(A215&amp;C215&amp;D215,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J215" s="160"/>
-      <c r="K215" s="160"/>
+      <c r="J215" s="159"/>
+      <c r="K215" s="159"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H216" t="s">
         <v>326</v>
@@ -21352,15 +21383,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E216,Foderstater!$R$56:$R$83,0),MATCH(A216&amp;C216&amp;D216,Foderstater!$U$55:$AD$55,0))</f>
         <v>38.884638191900635</v>
       </c>
-      <c r="J216" s="160"/>
-      <c r="K216" s="160"/>
+      <c r="J216" s="159"/>
+      <c r="K216" s="159"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H217" t="s">
         <v>326</v>
@@ -21369,15 +21400,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E217,Foderstater!$R$56:$R$83,0),MATCH(A217&amp;C217&amp;D217,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.1628177607947425</v>
       </c>
-      <c r="J217" s="160"/>
-      <c r="K217" s="160"/>
+      <c r="J217" s="159"/>
+      <c r="K217" s="159"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>2</v>
       </c>
       <c r="E218" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H218" t="s">
         <v>326</v>
@@ -21386,15 +21417,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E218,Foderstater!$R$56:$R$83,0),MATCH(A218&amp;C218&amp;D218,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.80563895711258293</v>
       </c>
-      <c r="J218" s="160"/>
-      <c r="K218" s="160"/>
+      <c r="J218" s="159"/>
+      <c r="K218" s="159"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H219" t="s">
         <v>326</v>
@@ -21403,15 +21434,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E219,Foderstater!$R$56:$R$83,0),MATCH(A219&amp;C219&amp;D219,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.2520471552888917</v>
       </c>
-      <c r="J219" s="160"/>
-      <c r="K219" s="160"/>
+      <c r="J219" s="159"/>
+      <c r="K219" s="159"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H220" t="s">
         <v>326</v>
@@ -21420,15 +21451,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E220,Foderstater!$R$56:$R$83,0),MATCH(A220&amp;C220&amp;D220,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.46540574926935496</v>
       </c>
-      <c r="J220" s="160"/>
-      <c r="K220" s="160"/>
+      <c r="J220" s="159"/>
+      <c r="K220" s="159"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>2</v>
       </c>
       <c r="E221" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H221" t="s">
         <v>326</v>
@@ -21437,15 +21468,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E221,Foderstater!$R$56:$R$83,0),MATCH(A221&amp;C221&amp;D221,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J221" s="160"/>
-      <c r="K221" s="160"/>
+      <c r="J221" s="159"/>
+      <c r="K221" s="159"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>2</v>
       </c>
       <c r="E222" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H222" t="s">
         <v>326</v>
@@ -21454,15 +21485,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E222,Foderstater!$R$56:$R$83,0),MATCH(A222&amp;C222&amp;D222,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.2526016891559834E-2</v>
       </c>
-      <c r="J222" s="160"/>
-      <c r="K222" s="160"/>
+      <c r="J222" s="159"/>
+      <c r="K222" s="159"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H223" t="s">
         <v>326</v>
@@ -21471,15 +21502,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E223,Foderstater!$R$56:$R$83,0),MATCH(A223&amp;C223&amp;D223,Foderstater!$U$55:$AD$55,0))</f>
         <v>3.6613311294760156E-2</v>
       </c>
-      <c r="J223" s="160"/>
-      <c r="K223" s="160"/>
+      <c r="J223" s="159"/>
+      <c r="K223" s="159"/>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H224" t="s">
         <v>326</v>
@@ -21488,15 +21519,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E224,Foderstater!$R$56:$R$83,0),MATCH(A224&amp;C224&amp;D224,Foderstater!$U$55:$AD$55,0))</f>
         <v>4.6849990217144546E-2</v>
       </c>
-      <c r="J224" s="160"/>
-      <c r="K224" s="160"/>
+      <c r="J224" s="159"/>
+      <c r="K224" s="159"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H225" t="s">
         <v>326</v>
@@ -21505,15 +21536,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E225,Foderstater!$R$56:$R$83,0),MATCH(A225&amp;C225&amp;D225,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.2108384115790605</v>
       </c>
-      <c r="J225" s="160"/>
-      <c r="K225" s="160"/>
+      <c r="J225" s="159"/>
+      <c r="K225" s="159"/>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H226" t="s">
         <v>326</v>
@@ -21522,15 +21553,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E226,Foderstater!$R$56:$R$83,0),MATCH(A226&amp;C226&amp;D226,Foderstater!$U$55:$AD$55,0))</f>
         <v>5.9286219889310578E-2</v>
       </c>
-      <c r="J226" s="160"/>
-      <c r="K226" s="160"/>
+      <c r="J226" s="159"/>
+      <c r="K226" s="159"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>2</v>
       </c>
       <c r="E227" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H227" t="s">
         <v>326</v>
@@ -21539,15 +21570,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E227,Foderstater!$R$56:$R$83,0),MATCH(A227&amp;C227&amp;D227,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.14123349371605412</v>
       </c>
-      <c r="J227" s="160"/>
-      <c r="K227" s="160"/>
+      <c r="J227" s="159"/>
+      <c r="K227" s="159"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>2</v>
       </c>
       <c r="E228" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H228" t="s">
         <v>326</v>
@@ -21556,15 +21587,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E228,Foderstater!$R$56:$R$83,0),MATCH(A228&amp;C228&amp;D228,Foderstater!$U$55:$AD$55,0))</f>
         <v>4.8120405221367048E-2</v>
       </c>
-      <c r="J228" s="160"/>
-      <c r="K228" s="160"/>
+      <c r="J228" s="159"/>
+      <c r="K228" s="159"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>2</v>
       </c>
       <c r="E229" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H229" t="s">
         <v>326</v>
@@ -21573,15 +21604,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E229,Foderstater!$R$56:$R$83,0),MATCH(A229&amp;C229&amp;D229,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.4336595854647348E-2</v>
       </c>
-      <c r="J229" s="160"/>
-      <c r="K229" s="160"/>
+      <c r="J229" s="159"/>
+      <c r="K229" s="159"/>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H230" t="s">
         <v>326</v>
@@ -21590,15 +21621,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E230,Foderstater!$R$56:$R$83,0),MATCH(A230&amp;C230&amp;D230,Foderstater!$U$55:$AD$55,0))</f>
         <v>6.1829219661059011E-2</v>
       </c>
-      <c r="J230" s="160"/>
-      <c r="K230" s="160"/>
+      <c r="J230" s="159"/>
+      <c r="K230" s="159"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H231" t="s">
         <v>326</v>
@@ -21607,15 +21638,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E231,Foderstater!$R$56:$R$83,0),MATCH(A231&amp;C231&amp;D231,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.16777081974076891</v>
       </c>
-      <c r="J231" s="160"/>
-      <c r="K231" s="160"/>
+      <c r="J231" s="159"/>
+      <c r="K231" s="159"/>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>2</v>
       </c>
       <c r="E232" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H232" t="s">
         <v>326</v>
@@ -21630,7 +21661,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H233" t="s">
         <v>326</v>
@@ -21645,7 +21676,7 @@
         <v>2</v>
       </c>
       <c r="E234" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H234" t="s">
         <v>326</v>
@@ -21660,7 +21691,7 @@
         <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H235" t="s">
         <v>326</v>
@@ -21675,7 +21706,7 @@
         <v>2</v>
       </c>
       <c r="E236" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H236" t="s">
         <v>326</v>
@@ -21690,7 +21721,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H237" t="s">
         <v>326</v>
@@ -21705,7 +21736,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H238" t="s">
         <v>326</v>
@@ -21726,29 +21757,29 @@
       <c r="F240" s="49"/>
       <c r="G240" s="49"/>
       <c r="H240" s="49"/>
-      <c r="I240" s="163"/>
+      <c r="I240" s="162"/>
       <c r="J240" s="49"/>
       <c r="K240" s="49"/>
       <c r="L240" s="49"/>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A241" s="160" t="s">
+      <c r="A241" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B241" s="160"/>
-      <c r="C241" s="160"/>
-      <c r="D241" s="160" t="s">
+      <c r="B241" s="159"/>
+      <c r="C241" s="159"/>
+      <c r="D241" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="H241" s="160" t="s">
+      <c r="H241" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I241" s="160">
+      <c r="I241" s="159">
         <v>0</v>
       </c>
-      <c r="J241" s="160"/>
-      <c r="K241" s="160" t="s">
-        <v>427</v>
+      <c r="J241" s="159"/>
+      <c r="K241" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -21759,7 +21790,7 @@
         <v>35</v>
       </c>
       <c r="E242" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H242" t="s">
         <v>326</v>
@@ -21768,8 +21799,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E242,Foderstater!$R$56:$R$83,0),MATCH(A242&amp;C242&amp;D242,Foderstater!$U$55:$AD$55,0))</f>
         <v>65.282988689132509</v>
       </c>
-      <c r="J242" s="160"/>
-      <c r="K242" s="160"/>
+      <c r="J242" s="159"/>
+      <c r="K242" s="159"/>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
@@ -21779,7 +21810,7 @@
         <v>35</v>
       </c>
       <c r="E243" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H243" t="s">
         <v>326</v>
@@ -21788,8 +21819,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E243,Foderstater!$R$56:$R$83,0),MATCH(A243&amp;C243&amp;D243,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J243" s="160"/>
-      <c r="K243" s="160"/>
+      <c r="J243" s="159"/>
+      <c r="K243" s="159"/>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
@@ -21799,7 +21830,7 @@
         <v>35</v>
       </c>
       <c r="E244" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H244" t="s">
         <v>326</v>
@@ -21808,8 +21839,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E244,Foderstater!$R$56:$R$83,0),MATCH(A244&amp;C244&amp;D244,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J244" s="160"/>
-      <c r="K244" s="160"/>
+      <c r="J244" s="159"/>
+      <c r="K244" s="159"/>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
@@ -21819,7 +21850,7 @@
         <v>35</v>
       </c>
       <c r="E245" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H245" t="s">
         <v>326</v>
@@ -21828,8 +21859,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E245,Foderstater!$R$56:$R$83,0),MATCH(A245&amp;C245&amp;D245,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J245" s="160"/>
-      <c r="K245" s="160"/>
+      <c r="J245" s="159"/>
+      <c r="K245" s="159"/>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
@@ -21839,7 +21870,7 @@
         <v>35</v>
       </c>
       <c r="E246" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H246" t="s">
         <v>326</v>
@@ -21848,8 +21879,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E246,Foderstater!$R$56:$R$83,0),MATCH(A246&amp;C246&amp;D246,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J246" s="160"/>
-      <c r="K246" s="160"/>
+      <c r="J246" s="159"/>
+      <c r="K246" s="159"/>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
@@ -21859,7 +21890,7 @@
         <v>35</v>
       </c>
       <c r="E247" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H247" t="s">
         <v>326</v>
@@ -21868,8 +21899,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E247,Foderstater!$R$56:$R$83,0),MATCH(A247&amp;C247&amp;D247,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J247" s="160"/>
-      <c r="K247" s="160"/>
+      <c r="J247" s="159"/>
+      <c r="K247" s="159"/>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
@@ -21879,7 +21910,7 @@
         <v>35</v>
       </c>
       <c r="E248" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H248" t="s">
         <v>326</v>
@@ -21888,8 +21919,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E248,Foderstater!$R$56:$R$83,0),MATCH(A248&amp;C248&amp;D248,Foderstater!$U$55:$AD$55,0))</f>
         <v>7.0130888477159132</v>
       </c>
-      <c r="J248" s="160"/>
-      <c r="K248" s="160"/>
+      <c r="J248" s="159"/>
+      <c r="K248" s="159"/>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
@@ -21899,7 +21930,7 @@
         <v>35</v>
       </c>
       <c r="E249" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H249" t="s">
         <v>326</v>
@@ -21908,8 +21939,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E249,Foderstater!$R$56:$R$83,0),MATCH(A249&amp;C249&amp;D249,Foderstater!$U$55:$AD$55,0))</f>
         <v>5.2164760725210764</v>
       </c>
-      <c r="J249" s="160"/>
-      <c r="K249" s="160"/>
+      <c r="J249" s="159"/>
+      <c r="K249" s="159"/>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
@@ -21919,7 +21950,7 @@
         <v>35</v>
       </c>
       <c r="E250" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H250" t="s">
         <v>326</v>
@@ -21928,8 +21959,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E250,Foderstater!$R$56:$R$83,0),MATCH(A250&amp;C250&amp;D250,Foderstater!$U$55:$AD$55,0))</f>
         <v>13.991446516700695</v>
       </c>
-      <c r="J250" s="160"/>
-      <c r="K250" s="160"/>
+      <c r="J250" s="159"/>
+      <c r="K250" s="159"/>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
@@ -21939,7 +21970,7 @@
         <v>35</v>
       </c>
       <c r="E251" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H251" t="s">
         <v>326</v>
@@ -21948,8 +21979,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E251,Foderstater!$R$56:$R$83,0),MATCH(A251&amp;C251&amp;D251,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.8914579493482573</v>
       </c>
-      <c r="J251" s="160"/>
-      <c r="K251" s="160"/>
+      <c r="J251" s="159"/>
+      <c r="K251" s="159"/>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
@@ -21959,7 +21990,7 @@
         <v>35</v>
       </c>
       <c r="E252" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H252" t="s">
         <v>326</v>
@@ -21968,8 +21999,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E252,Foderstater!$R$56:$R$83,0),MATCH(A252&amp;C252&amp;D252,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J252" s="160"/>
-      <c r="K252" s="160"/>
+      <c r="J252" s="159"/>
+      <c r="K252" s="159"/>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
@@ -21979,7 +22010,7 @@
         <v>35</v>
       </c>
       <c r="E253" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H253" t="s">
         <v>326</v>
@@ -21988,8 +22019,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E253,Foderstater!$R$56:$R$83,0),MATCH(A253&amp;C253&amp;D253,Foderstater!$U$55:$AD$55,0))</f>
         <v>3.7516786382972102E-2</v>
       </c>
-      <c r="J253" s="160"/>
-      <c r="K253" s="160"/>
+      <c r="J253" s="159"/>
+      <c r="K253" s="159"/>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
@@ -21999,7 +22030,7 @@
         <v>35</v>
       </c>
       <c r="E254" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H254" t="s">
         <v>326</v>
@@ -22008,8 +22039,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E254,Foderstater!$R$56:$R$83,0),MATCH(A254&amp;C254&amp;D254,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.4240390174797204</v>
       </c>
-      <c r="J254" s="160"/>
-      <c r="K254" s="160"/>
+      <c r="J254" s="159"/>
+      <c r="K254" s="159"/>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
@@ -22019,7 +22050,7 @@
         <v>35</v>
       </c>
       <c r="E255" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H255" t="s">
         <v>326</v>
@@ -22028,8 +22059,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E255,Foderstater!$R$56:$R$83,0),MATCH(A255&amp;C255&amp;D255,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.38795487532739</v>
       </c>
-      <c r="J255" s="160"/>
-      <c r="K255" s="160"/>
+      <c r="J255" s="159"/>
+      <c r="K255" s="159"/>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
@@ -22039,7 +22070,7 @@
         <v>35</v>
       </c>
       <c r="E256" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H256" t="s">
         <v>326</v>
@@ -22048,8 +22079,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E256,Foderstater!$R$56:$R$83,0),MATCH(A256&amp;C256&amp;D256,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.63148403175686241</v>
       </c>
-      <c r="J256" s="160"/>
-      <c r="K256" s="160"/>
+      <c r="J256" s="159"/>
+      <c r="K256" s="159"/>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
@@ -22059,7 +22090,7 @@
         <v>35</v>
       </c>
       <c r="E257" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H257" t="s">
         <v>326</v>
@@ -22068,8 +22099,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E257,Foderstater!$R$56:$R$83,0),MATCH(A257&amp;C257&amp;D257,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.17756869292902569</v>
       </c>
-      <c r="J257" s="160"/>
-      <c r="K257" s="160"/>
+      <c r="J257" s="159"/>
+      <c r="K257" s="159"/>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
@@ -22079,7 +22110,7 @@
         <v>35</v>
       </c>
       <c r="E258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H258" t="s">
         <v>326</v>
@@ -22088,8 +22119,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E258,Foderstater!$R$56:$R$83,0),MATCH(A258&amp;C258&amp;D258,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.42300971328214537</v>
       </c>
-      <c r="J258" s="160"/>
-      <c r="K258" s="160"/>
+      <c r="J258" s="159"/>
+      <c r="K258" s="159"/>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
@@ -22099,7 +22130,7 @@
         <v>35</v>
       </c>
       <c r="E259" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H259" t="s">
         <v>326</v>
@@ -22108,8 +22139,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E259,Foderstater!$R$56:$R$83,0),MATCH(A259&amp;C259&amp;D259,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.14412586051744264</v>
       </c>
-      <c r="J259" s="160"/>
-      <c r="K259" s="160"/>
+      <c r="J259" s="159"/>
+      <c r="K259" s="159"/>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
@@ -22119,7 +22150,7 @@
         <v>35</v>
       </c>
       <c r="E260" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H260" t="s">
         <v>326</v>
@@ -22128,8 +22159,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E260,Foderstater!$R$56:$R$83,0),MATCH(A260&amp;C260&amp;D260,Foderstater!$U$55:$AD$55,0))</f>
         <v>7.2890758161338512E-2</v>
       </c>
-      <c r="J260" s="160"/>
-      <c r="K260" s="160"/>
+      <c r="J260" s="159"/>
+      <c r="K260" s="159"/>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
@@ -22139,7 +22170,7 @@
         <v>35</v>
       </c>
       <c r="E261" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H261" t="s">
         <v>326</v>
@@ -22148,8 +22179,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E261,Foderstater!$R$56:$R$83,0),MATCH(A261&amp;C261&amp;D261,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.18518525452514792</v>
       </c>
-      <c r="J261" s="160"/>
-      <c r="K261" s="160"/>
+      <c r="J261" s="159"/>
+      <c r="K261" s="159"/>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
@@ -22159,7 +22190,7 @@
         <v>35</v>
       </c>
       <c r="E262" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H262" t="s">
         <v>326</v>
@@ -22168,8 +22199,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E262,Foderstater!$R$56:$R$83,0),MATCH(A262&amp;C262&amp;D262,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.50249189826270002</v>
       </c>
-      <c r="J262" s="160"/>
-      <c r="K262" s="160"/>
+      <c r="J262" s="159"/>
+      <c r="K262" s="159"/>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
@@ -22179,7 +22210,7 @@
         <v>35</v>
       </c>
       <c r="E263" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H263" t="s">
         <v>326</v>
@@ -22197,7 +22228,7 @@
         <v>35</v>
       </c>
       <c r="E264" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H264" t="s">
         <v>326</v>
@@ -22215,7 +22246,7 @@
         <v>35</v>
       </c>
       <c r="E265" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H265" t="s">
         <v>326</v>
@@ -22233,7 +22264,7 @@
         <v>35</v>
       </c>
       <c r="E266" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H266" t="s">
         <v>326</v>
@@ -22251,7 +22282,7 @@
         <v>35</v>
       </c>
       <c r="E267" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H267" t="s">
         <v>326</v>
@@ -22269,7 +22300,7 @@
         <v>35</v>
       </c>
       <c r="E268" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H268" t="s">
         <v>326</v>
@@ -22287,7 +22318,7 @@
         <v>35</v>
       </c>
       <c r="E269" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H269" t="s">
         <v>326</v>
@@ -22298,35 +22329,35 @@
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A270" s="160"/>
-      <c r="B270" s="160"/>
-      <c r="C270" s="160"/>
-      <c r="D270" s="160"/>
-      <c r="H270" s="160"/>
-      <c r="I270" s="160"/>
-      <c r="J270" s="160"/>
-      <c r="K270" s="160"/>
+      <c r="A270" s="159"/>
+      <c r="B270" s="159"/>
+      <c r="C270" s="159"/>
+      <c r="D270" s="159"/>
+      <c r="H270" s="159"/>
+      <c r="I270" s="159"/>
+      <c r="J270" s="159"/>
+      <c r="K270" s="159"/>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A271" s="160" t="s">
+      <c r="A271" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B271" s="160"/>
-      <c r="C271" s="160" t="s">
-        <v>433</v>
-      </c>
-      <c r="D271" s="160" t="s">
+      <c r="B271" s="159"/>
+      <c r="C271" s="159" t="s">
+        <v>432</v>
+      </c>
+      <c r="D271" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="H271" s="160" t="s">
+      <c r="H271" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I271" s="160">
+      <c r="I271" s="159">
         <v>0</v>
       </c>
-      <c r="J271" s="160"/>
-      <c r="K271" s="160" t="s">
-        <v>427</v>
+      <c r="J271" s="159"/>
+      <c r="K271" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -22334,13 +22365,13 @@
         <v>2</v>
       </c>
       <c r="C272" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D272" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E272" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H272" t="s">
         <v>326</v>
@@ -22349,21 +22380,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E272,Foderstater!$R$56:$R$83,0),MATCH(A272&amp;C272&amp;D272,Foderstater!$U$55:$AD$55,0))</f>
         <v>56.862458601207877</v>
       </c>
-      <c r="J272" s="160"/>
-      <c r="K272" s="160"/>
+      <c r="J272" s="159"/>
+      <c r="K272" s="159"/>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>2</v>
       </c>
       <c r="C273" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D273" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E273" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H273" t="s">
         <v>326</v>
@@ -22372,21 +22403,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E273,Foderstater!$R$56:$R$83,0),MATCH(A273&amp;C273&amp;D273,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J273" s="160"/>
-      <c r="K273" s="160"/>
+      <c r="J273" s="159"/>
+      <c r="K273" s="159"/>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>2</v>
       </c>
       <c r="C274" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D274" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E274" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H274" t="s">
         <v>326</v>
@@ -22395,21 +22426,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E274,Foderstater!$R$56:$R$83,0),MATCH(A274&amp;C274&amp;D274,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J274" s="160"/>
-      <c r="K274" s="160"/>
+      <c r="J274" s="159"/>
+      <c r="K274" s="159"/>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>2</v>
       </c>
       <c r="C275" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D275" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E275" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H275" t="s">
         <v>326</v>
@@ -22418,21 +22449,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E275,Foderstater!$R$56:$R$83,0),MATCH(A275&amp;C275&amp;D275,Foderstater!$U$55:$AD$55,0))</f>
         <v>13.271965712059227</v>
       </c>
-      <c r="J275" s="160"/>
-      <c r="K275" s="160"/>
+      <c r="J275" s="159"/>
+      <c r="K275" s="159"/>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>2</v>
       </c>
       <c r="C276" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D276" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E276" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H276" t="s">
         <v>326</v>
@@ -22441,21 +22472,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E276,Foderstater!$R$56:$R$83,0),MATCH(A276&amp;C276&amp;D276,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J276" s="160"/>
-      <c r="K276" s="160"/>
+      <c r="J276" s="159"/>
+      <c r="K276" s="159"/>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>2</v>
       </c>
       <c r="C277" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D277" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E277" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H277" t="s">
         <v>326</v>
@@ -22464,21 +22495,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E277,Foderstater!$R$56:$R$83,0),MATCH(A277&amp;C277&amp;D277,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J277" s="160"/>
-      <c r="K277" s="160"/>
+      <c r="J277" s="159"/>
+      <c r="K277" s="159"/>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>2</v>
       </c>
       <c r="C278" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D278" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E278" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H278" t="s">
         <v>326</v>
@@ -22487,21 +22518,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E278,Foderstater!$R$56:$R$83,0),MATCH(A278&amp;C278&amp;D278,Foderstater!$U$55:$AD$55,0))</f>
         <v>6.6666574064662587</v>
       </c>
-      <c r="J278" s="160"/>
-      <c r="K278" s="160"/>
+      <c r="J278" s="159"/>
+      <c r="K278" s="159"/>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>2</v>
       </c>
       <c r="C279" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D279" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E279" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H279" t="s">
         <v>326</v>
@@ -22510,21 +22541,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E279,Foderstater!$R$56:$R$83,0),MATCH(A279&amp;C279&amp;D279,Foderstater!$U$55:$AD$55,0))</f>
         <v>5.1991702356471148</v>
       </c>
-      <c r="J279" s="160"/>
-      <c r="K279" s="160"/>
+      <c r="J279" s="159"/>
+      <c r="K279" s="159"/>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>2</v>
       </c>
       <c r="C280" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D280" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E280" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H280" t="s">
         <v>326</v>
@@ -22533,21 +22564,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E280,Foderstater!$R$56:$R$83,0),MATCH(A280&amp;C280&amp;D280,Foderstater!$U$55:$AD$55,0))</f>
         <v>13.575306555370148</v>
       </c>
-      <c r="J280" s="160"/>
-      <c r="K280" s="160"/>
+      <c r="J280" s="159"/>
+      <c r="K280" s="159"/>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>2</v>
       </c>
       <c r="C281" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D281" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E281" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H281" t="s">
         <v>326</v>
@@ -22556,21 +22587,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E281,Foderstater!$R$56:$R$83,0),MATCH(A281&amp;C281&amp;D281,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.8054588928679678</v>
       </c>
-      <c r="J281" s="160"/>
-      <c r="K281" s="160"/>
+      <c r="J281" s="159"/>
+      <c r="K281" s="159"/>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>2</v>
       </c>
       <c r="C282" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D282" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E282" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H282" t="s">
         <v>326</v>
@@ -22579,21 +22610,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E282,Foderstater!$R$56:$R$83,0),MATCH(A282&amp;C282&amp;D282,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J282" s="160"/>
-      <c r="K282" s="160"/>
+      <c r="J282" s="159"/>
+      <c r="K282" s="159"/>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>2</v>
       </c>
       <c r="C283" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D283" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E283" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H283" t="s">
         <v>326</v>
@@ -22602,21 +22633,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E283,Foderstater!$R$56:$R$83,0),MATCH(A283&amp;C283&amp;D283,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.0098740539236407E-2</v>
       </c>
-      <c r="J283" s="160"/>
-      <c r="K283" s="160"/>
+      <c r="J283" s="159"/>
+      <c r="K283" s="159"/>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>2</v>
       </c>
       <c r="C284" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D284" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E284" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H284" t="s">
         <v>326</v>
@@ -22625,21 +22656,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E284,Foderstater!$R$56:$R$83,0),MATCH(A284&amp;C284&amp;D284,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.43993732150286113</v>
       </c>
-      <c r="J284" s="160"/>
-      <c r="K284" s="160"/>
+      <c r="J284" s="159"/>
+      <c r="K284" s="159"/>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>2</v>
       </c>
       <c r="C285" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D285" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E285" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H285" t="s">
         <v>326</v>
@@ -22648,21 +22679,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E285,Foderstater!$R$56:$R$83,0),MATCH(A285&amp;C285&amp;D285,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.42734928129407507</v>
       </c>
-      <c r="J285" s="160"/>
-      <c r="K285" s="160"/>
+      <c r="J285" s="159"/>
+      <c r="K285" s="159"/>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>2</v>
       </c>
       <c r="C286" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D286" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E286" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H286" t="s">
         <v>326</v>
@@ -22671,21 +22702,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E286,Foderstater!$R$56:$R$83,0),MATCH(A286&amp;C286&amp;D286,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.16998240004580778</v>
       </c>
-      <c r="J286" s="160"/>
-      <c r="K286" s="160"/>
+      <c r="J286" s="159"/>
+      <c r="K286" s="159"/>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>2</v>
       </c>
       <c r="C287" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D287" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E287" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H287" t="s">
         <v>326</v>
@@ -22694,21 +22725,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E287,Foderstater!$R$56:$R$83,0),MATCH(A287&amp;C287&amp;D287,Foderstater!$U$55:$AD$55,0))</f>
         <v>4.7797808145834932E-2</v>
       </c>
-      <c r="J287" s="160"/>
-      <c r="K287" s="160"/>
+      <c r="J287" s="159"/>
+      <c r="K287" s="159"/>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>2</v>
       </c>
       <c r="C288" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D288" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E288" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H288" t="s">
         <v>326</v>
@@ -22717,21 +22748,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E288,Foderstater!$R$56:$R$83,0),MATCH(A288&amp;C288&amp;D288,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.11386543869738427</v>
       </c>
-      <c r="J288" s="160"/>
-      <c r="K288" s="160"/>
+      <c r="J288" s="159"/>
+      <c r="K288" s="159"/>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>2</v>
       </c>
       <c r="C289" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D289" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E289" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H289" t="s">
         <v>326</v>
@@ -22740,21 +22771,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E289,Foderstater!$R$56:$R$83,0),MATCH(A289&amp;C289&amp;D289,Foderstater!$U$55:$AD$55,0))</f>
         <v>3.879569149399318E-2</v>
       </c>
-      <c r="J289" s="160"/>
-      <c r="K289" s="160"/>
+      <c r="J289" s="159"/>
+      <c r="K289" s="159"/>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>2</v>
       </c>
       <c r="C290" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D290" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E290" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H290" t="s">
         <v>326</v>
@@ -22763,21 +22794,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E290,Foderstater!$R$56:$R$83,0),MATCH(A290&amp;C290&amp;D290,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.9620679843561577E-2</v>
       </c>
-      <c r="J290" s="160"/>
-      <c r="K290" s="160"/>
+      <c r="J290" s="159"/>
+      <c r="K290" s="159"/>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>2</v>
       </c>
       <c r="C291" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D291" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E291" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H291" t="s">
         <v>326</v>
@@ -22786,21 +22817,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E291,Foderstater!$R$56:$R$83,0),MATCH(A291&amp;C291&amp;D291,Foderstater!$U$55:$AD$55,0))</f>
         <v>4.98480285078663E-2</v>
       </c>
-      <c r="J291" s="160"/>
-      <c r="K291" s="160"/>
+      <c r="J291" s="159"/>
+      <c r="K291" s="159"/>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>2</v>
       </c>
       <c r="C292" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D292" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E292" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H292" t="s">
         <v>326</v>
@@ -22809,21 +22840,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E292,Foderstater!$R$56:$R$83,0),MATCH(A292&amp;C292&amp;D292,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.13526039388934941</v>
       </c>
-      <c r="J292" s="160"/>
-      <c r="K292" s="160"/>
+      <c r="J292" s="159"/>
+      <c r="K292" s="159"/>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>2</v>
       </c>
       <c r="C293" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D293" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E293" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H293" t="s">
         <v>326</v>
@@ -22838,13 +22869,13 @@
         <v>2</v>
       </c>
       <c r="C294" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D294" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E294" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H294" t="s">
         <v>326</v>
@@ -22859,13 +22890,13 @@
         <v>2</v>
       </c>
       <c r="C295" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D295" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E295" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H295" t="s">
         <v>326</v>
@@ -22880,13 +22911,13 @@
         <v>2</v>
       </c>
       <c r="C296" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D296" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E296" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H296" t="s">
         <v>326</v>
@@ -22901,13 +22932,13 @@
         <v>2</v>
       </c>
       <c r="C297" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D297" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E297" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H297" t="s">
         <v>326</v>
@@ -22922,13 +22953,13 @@
         <v>2</v>
       </c>
       <c r="C298" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D298" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E298" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H298" t="s">
         <v>326</v>
@@ -22943,13 +22974,13 @@
         <v>2</v>
       </c>
       <c r="C299" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D299" s="110" t="s">
         <v>35</v>
       </c>
       <c r="E299" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H299" t="s">
         <v>326</v>
@@ -22979,36 +23010,36 @@
       <c r="A302" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="B302" s="164"/>
-      <c r="C302" s="164"/>
+      <c r="B302" s="163"/>
+      <c r="C302" s="163"/>
       <c r="D302" s="90"/>
       <c r="E302" s="90"/>
       <c r="F302" s="90"/>
       <c r="G302" s="90"/>
       <c r="H302" s="90"/>
-      <c r="I302" s="165"/>
+      <c r="I302" s="164"/>
       <c r="J302" s="90"/>
       <c r="K302" s="90"/>
       <c r="L302" s="90"/>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A303" s="160" t="s">
+      <c r="A303" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="B303" s="160"/>
-      <c r="C303" s="160"/>
-      <c r="D303" s="160" t="s">
+      <c r="B303" s="159"/>
+      <c r="C303" s="159"/>
+      <c r="D303" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="H303" s="160" t="s">
+      <c r="H303" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I303" s="160">
+      <c r="I303" s="159">
         <v>0</v>
       </c>
-      <c r="J303" s="160"/>
-      <c r="K303" s="160" t="s">
-        <v>427</v>
+      <c r="J303" s="159"/>
+      <c r="K303" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
@@ -23019,7 +23050,7 @@
         <v>18</v>
       </c>
       <c r="E304" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H304" t="s">
         <v>326</v>
@@ -23028,8 +23059,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E304,Foderstater!$R$56:$R$83,0),MATCH(A304&amp;C304&amp;D304,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J304" s="160"/>
-      <c r="K304" s="160"/>
+      <c r="J304" s="159"/>
+      <c r="K304" s="159"/>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
@@ -23039,7 +23070,7 @@
         <v>18</v>
       </c>
       <c r="E305" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H305" t="s">
         <v>326</v>
@@ -23048,8 +23079,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E305,Foderstater!$R$56:$R$83,0),MATCH(A305&amp;C305&amp;D305,Foderstater!$U$55:$AD$55,0))</f>
         <v>16.595954764760993</v>
       </c>
-      <c r="J305" s="160"/>
-      <c r="K305" s="160"/>
+      <c r="J305" s="159"/>
+      <c r="K305" s="159"/>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
@@ -23059,7 +23090,7 @@
         <v>18</v>
       </c>
       <c r="E306" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H306" t="s">
         <v>326</v>
@@ -23068,8 +23099,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E306,Foderstater!$R$56:$R$83,0),MATCH(A306&amp;C306&amp;D306,Foderstater!$U$55:$AD$55,0))</f>
         <v>17.173343787959137</v>
       </c>
-      <c r="J306" s="160"/>
-      <c r="K306" s="160"/>
+      <c r="J306" s="159"/>
+      <c r="K306" s="159"/>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
@@ -23079,7 +23110,7 @@
         <v>18</v>
       </c>
       <c r="E307" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H307" t="s">
         <v>326</v>
@@ -23088,8 +23119,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E307,Foderstater!$R$56:$R$83,0),MATCH(A307&amp;C307&amp;D307,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J307" s="160"/>
-      <c r="K307" s="160"/>
+      <c r="J307" s="159"/>
+      <c r="K307" s="159"/>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
@@ -23099,7 +23130,7 @@
         <v>18</v>
       </c>
       <c r="E308" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H308" t="s">
         <v>326</v>
@@ -23108,8 +23139,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E308,Foderstater!$R$56:$R$83,0),MATCH(A308&amp;C308&amp;D308,Foderstater!$U$55:$AD$55,0))</f>
         <v>17.173343787959137</v>
       </c>
-      <c r="J308" s="160"/>
-      <c r="K308" s="160"/>
+      <c r="J308" s="159"/>
+      <c r="K308" s="159"/>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
@@ -23119,7 +23150,7 @@
         <v>18</v>
       </c>
       <c r="E309" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H309" t="s">
         <v>326</v>
@@ -23128,8 +23159,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E309,Foderstater!$R$56:$R$83,0),MATCH(A309&amp;C309&amp;D309,Foderstater!$U$55:$AD$55,0))</f>
         <v>49.057357659320729</v>
       </c>
-      <c r="J309" s="160"/>
-      <c r="K309" s="160"/>
+      <c r="J309" s="159"/>
+      <c r="K309" s="159"/>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
@@ -23139,7 +23170,7 @@
         <v>18</v>
       </c>
       <c r="E310" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H310" t="s">
         <v>326</v>
@@ -23148,8 +23179,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E310,Foderstater!$R$56:$R$83,0),MATCH(A310&amp;C310&amp;D310,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J310" s="160"/>
-      <c r="K310" s="160"/>
+      <c r="J310" s="159"/>
+      <c r="K310" s="159"/>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
@@ -23159,7 +23190,7 @@
         <v>18</v>
       </c>
       <c r="E311" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H311" t="s">
         <v>326</v>
@@ -23168,8 +23199,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E311,Foderstater!$R$56:$R$83,0),MATCH(A311&amp;C311&amp;D311,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J311" s="160"/>
-      <c r="K311" s="160"/>
+      <c r="J311" s="159"/>
+      <c r="K311" s="159"/>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
@@ -23179,7 +23210,7 @@
         <v>18</v>
       </c>
       <c r="E312" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H312" t="s">
         <v>326</v>
@@ -23188,8 +23219,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E312,Foderstater!$R$56:$R$83,0),MATCH(A312&amp;C312&amp;D312,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J312" s="160"/>
-      <c r="K312" s="160"/>
+      <c r="J312" s="159"/>
+      <c r="K312" s="159"/>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
@@ -23199,7 +23230,7 @@
         <v>18</v>
       </c>
       <c r="E313" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H313" t="s">
         <v>326</v>
@@ -23208,8 +23239,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E313,Foderstater!$R$56:$R$83,0),MATCH(A313&amp;C313&amp;D313,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J313" s="160"/>
-      <c r="K313" s="160"/>
+      <c r="J313" s="159"/>
+      <c r="K313" s="159"/>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
@@ -23219,7 +23250,7 @@
         <v>18</v>
       </c>
       <c r="E314" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H314" t="s">
         <v>326</v>
@@ -23228,8 +23259,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E314,Foderstater!$R$56:$R$83,0),MATCH(A314&amp;C314&amp;D314,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J314" s="160"/>
-      <c r="K314" s="160"/>
+      <c r="J314" s="159"/>
+      <c r="K314" s="159"/>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
@@ -23239,7 +23270,7 @@
         <v>18</v>
       </c>
       <c r="E315" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H315" t="s">
         <v>326</v>
@@ -23248,8 +23279,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E315,Foderstater!$R$56:$R$83,0),MATCH(A315&amp;C315&amp;D315,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J315" s="160"/>
-      <c r="K315" s="160"/>
+      <c r="J315" s="159"/>
+      <c r="K315" s="159"/>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
@@ -23259,7 +23290,7 @@
         <v>18</v>
       </c>
       <c r="E316" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H316" t="s">
         <v>326</v>
@@ -23268,8 +23299,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E316,Foderstater!$R$56:$R$83,0),MATCH(A316&amp;C316&amp;D316,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J316" s="160"/>
-      <c r="K316" s="160"/>
+      <c r="J316" s="159"/>
+      <c r="K316" s="159"/>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
@@ -23279,7 +23310,7 @@
         <v>18</v>
       </c>
       <c r="E317" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H317" t="s">
         <v>326</v>
@@ -23288,8 +23319,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E317,Foderstater!$R$56:$R$83,0),MATCH(A317&amp;C317&amp;D317,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J317" s="160"/>
-      <c r="K317" s="160"/>
+      <c r="J317" s="159"/>
+      <c r="K317" s="159"/>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
@@ -23299,7 +23330,7 @@
         <v>18</v>
       </c>
       <c r="E318" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H318" t="s">
         <v>326</v>
@@ -23308,8 +23339,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E318,Foderstater!$R$56:$R$83,0),MATCH(A318&amp;C318&amp;D318,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J318" s="160"/>
-      <c r="K318" s="160"/>
+      <c r="J318" s="159"/>
+      <c r="K318" s="159"/>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
@@ -23319,7 +23350,7 @@
         <v>18</v>
       </c>
       <c r="E319" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H319" t="s">
         <v>326</v>
@@ -23328,8 +23359,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E319,Foderstater!$R$56:$R$83,0),MATCH(A319&amp;C319&amp;D319,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J319" s="160"/>
-      <c r="K319" s="160"/>
+      <c r="J319" s="159"/>
+      <c r="K319" s="159"/>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
@@ -23339,7 +23370,7 @@
         <v>18</v>
       </c>
       <c r="E320" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H320" t="s">
         <v>326</v>
@@ -23348,8 +23379,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E320,Foderstater!$R$56:$R$83,0),MATCH(A320&amp;C320&amp;D320,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J320" s="160"/>
-      <c r="K320" s="160"/>
+      <c r="J320" s="159"/>
+      <c r="K320" s="159"/>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
@@ -23359,7 +23390,7 @@
         <v>18</v>
       </c>
       <c r="E321" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H321" t="s">
         <v>326</v>
@@ -23368,8 +23399,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E321,Foderstater!$R$56:$R$83,0),MATCH(A321&amp;C321&amp;D321,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J321" s="160"/>
-      <c r="K321" s="160"/>
+      <c r="J321" s="159"/>
+      <c r="K321" s="159"/>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
@@ -23379,7 +23410,7 @@
         <v>18</v>
       </c>
       <c r="E322" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H322" t="s">
         <v>326</v>
@@ -23388,8 +23419,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E322,Foderstater!$R$56:$R$83,0),MATCH(A322&amp;C322&amp;D322,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J322" s="160"/>
-      <c r="K322" s="160"/>
+      <c r="J322" s="159"/>
+      <c r="K322" s="159"/>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
@@ -23399,7 +23430,7 @@
         <v>18</v>
       </c>
       <c r="E323" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H323" t="s">
         <v>326</v>
@@ -23408,8 +23439,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E323,Foderstater!$R$56:$R$83,0),MATCH(A323&amp;C323&amp;D323,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J323" s="160"/>
-      <c r="K323" s="160"/>
+      <c r="J323" s="159"/>
+      <c r="K323" s="159"/>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
@@ -23419,7 +23450,7 @@
         <v>18</v>
       </c>
       <c r="E324" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H324" t="s">
         <v>326</v>
@@ -23428,8 +23459,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E324,Foderstater!$R$56:$R$83,0),MATCH(A324&amp;C324&amp;D324,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J324" s="160"/>
-      <c r="K324" s="160"/>
+      <c r="J324" s="159"/>
+      <c r="K324" s="159"/>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
@@ -23439,7 +23470,7 @@
         <v>18</v>
       </c>
       <c r="E325" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H325" t="s">
         <v>326</v>
@@ -23457,7 +23488,7 @@
         <v>18</v>
       </c>
       <c r="E326" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H326" t="s">
         <v>326</v>
@@ -23475,7 +23506,7 @@
         <v>18</v>
       </c>
       <c r="E327" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H327" t="s">
         <v>326</v>
@@ -23493,7 +23524,7 @@
         <v>18</v>
       </c>
       <c r="E328" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H328" t="s">
         <v>326</v>
@@ -23511,7 +23542,7 @@
         <v>18</v>
       </c>
       <c r="E329" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H329" t="s">
         <v>326</v>
@@ -23529,7 +23560,7 @@
         <v>18</v>
       </c>
       <c r="E330" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H330" t="s">
         <v>326</v>
@@ -23547,7 +23578,7 @@
         <v>18</v>
       </c>
       <c r="E331" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H331" t="s">
         <v>326</v>
@@ -23559,36 +23590,36 @@
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" s="91" t="s">
-        <v>454</v>
-      </c>
-      <c r="B333" s="164"/>
-      <c r="C333" s="164"/>
+        <v>453</v>
+      </c>
+      <c r="B333" s="163"/>
+      <c r="C333" s="163"/>
       <c r="D333" s="90"/>
       <c r="E333" s="90"/>
       <c r="F333" s="90"/>
       <c r="G333" s="90"/>
       <c r="H333" s="90"/>
-      <c r="I333" s="165"/>
+      <c r="I333" s="164"/>
       <c r="J333" s="90"/>
       <c r="K333" s="90"/>
       <c r="L333" s="90"/>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A334" s="160" t="s">
+      <c r="A334" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="B334" s="160"/>
-      <c r="C334" s="160"/>
-      <c r="D334" s="160"/>
-      <c r="H334" s="160" t="s">
+      <c r="B334" s="159"/>
+      <c r="C334" s="159"/>
+      <c r="D334" s="159"/>
+      <c r="H334" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I334" s="160">
+      <c r="I334" s="159">
         <v>0</v>
       </c>
-      <c r="J334" s="160"/>
-      <c r="K334" s="160" t="s">
-        <v>427</v>
+      <c r="J334" s="159"/>
+      <c r="K334" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.25">
@@ -23596,7 +23627,7 @@
         <v>38</v>
       </c>
       <c r="E335" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H335" t="s">
         <v>326</v>
@@ -23605,15 +23636,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E335,Foderstater!$R$56:$R$83,0),MATCH(A335&amp;C335&amp;D335,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J335" s="160"/>
-      <c r="K335" s="160"/>
+      <c r="J335" s="159"/>
+      <c r="K335" s="159"/>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>38</v>
       </c>
       <c r="E336" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H336" t="s">
         <v>326</v>
@@ -23622,15 +23653,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E336,Foderstater!$R$56:$R$83,0),MATCH(A336&amp;C336&amp;D336,Foderstater!$U$55:$AD$55,0))</f>
         <v>69.353683256124697</v>
       </c>
-      <c r="J336" s="160"/>
-      <c r="K336" s="160"/>
+      <c r="J336" s="159"/>
+      <c r="K336" s="159"/>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>38</v>
       </c>
       <c r="E337" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H337" t="s">
         <v>326</v>
@@ -23639,15 +23670,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E337,Foderstater!$R$56:$R$83,0),MATCH(A337&amp;C337&amp;D337,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J337" s="160"/>
-      <c r="K337" s="160"/>
+      <c r="J337" s="159"/>
+      <c r="K337" s="159"/>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>38</v>
       </c>
       <c r="E338" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H338" t="s">
         <v>326</v>
@@ -23656,15 +23687,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E338,Foderstater!$R$56:$R$83,0),MATCH(A338&amp;C338&amp;D338,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J338" s="160"/>
-      <c r="K338" s="160"/>
+      <c r="J338" s="159"/>
+      <c r="K338" s="159"/>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>38</v>
       </c>
       <c r="E339" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H339" t="s">
         <v>326</v>
@@ -23673,15 +23704,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E339,Foderstater!$R$56:$R$83,0),MATCH(A339&amp;C339&amp;D339,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J339" s="160"/>
-      <c r="K339" s="160"/>
+      <c r="J339" s="159"/>
+      <c r="K339" s="159"/>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>38</v>
       </c>
       <c r="E340" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H340" t="s">
         <v>326</v>
@@ -23690,15 +23721,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E340,Foderstater!$R$56:$R$83,0),MATCH(A340&amp;C340&amp;D340,Foderstater!$U$55:$AD$55,0))</f>
         <v>30.646316743875307</v>
       </c>
-      <c r="J340" s="160"/>
-      <c r="K340" s="160"/>
+      <c r="J340" s="159"/>
+      <c r="K340" s="159"/>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>38</v>
       </c>
       <c r="E341" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H341" t="s">
         <v>326</v>
@@ -23707,15 +23738,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E341,Foderstater!$R$56:$R$83,0),MATCH(A341&amp;C341&amp;D341,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J341" s="160"/>
-      <c r="K341" s="160"/>
+      <c r="J341" s="159"/>
+      <c r="K341" s="159"/>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>38</v>
       </c>
       <c r="E342" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H342" t="s">
         <v>326</v>
@@ -23724,15 +23755,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E342,Foderstater!$R$56:$R$83,0),MATCH(A342&amp;C342&amp;D342,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J342" s="160"/>
-      <c r="K342" s="160"/>
+      <c r="J342" s="159"/>
+      <c r="K342" s="159"/>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>38</v>
       </c>
       <c r="E343" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H343" t="s">
         <v>326</v>
@@ -23741,15 +23772,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E343,Foderstater!$R$56:$R$83,0),MATCH(A343&amp;C343&amp;D343,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J343" s="160"/>
-      <c r="K343" s="160"/>
+      <c r="J343" s="159"/>
+      <c r="K343" s="159"/>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>38</v>
       </c>
       <c r="E344" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H344" t="s">
         <v>326</v>
@@ -23758,15 +23789,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E344,Foderstater!$R$56:$R$83,0),MATCH(A344&amp;C344&amp;D344,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J344" s="160"/>
-      <c r="K344" s="160"/>
+      <c r="J344" s="159"/>
+      <c r="K344" s="159"/>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>38</v>
       </c>
       <c r="E345" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H345" t="s">
         <v>326</v>
@@ -23775,15 +23806,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E345,Foderstater!$R$56:$R$83,0),MATCH(A345&amp;C345&amp;D345,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J345" s="160"/>
-      <c r="K345" s="160"/>
+      <c r="J345" s="159"/>
+      <c r="K345" s="159"/>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>38</v>
       </c>
       <c r="E346" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H346" t="s">
         <v>326</v>
@@ -23792,15 +23823,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E346,Foderstater!$R$56:$R$83,0),MATCH(A346&amp;C346&amp;D346,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J346" s="160"/>
-      <c r="K346" s="160"/>
+      <c r="J346" s="159"/>
+      <c r="K346" s="159"/>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>38</v>
       </c>
       <c r="E347" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H347" t="s">
         <v>326</v>
@@ -23809,15 +23840,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E347,Foderstater!$R$56:$R$83,0),MATCH(A347&amp;C347&amp;D347,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J347" s="160"/>
-      <c r="K347" s="160"/>
+      <c r="J347" s="159"/>
+      <c r="K347" s="159"/>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>38</v>
       </c>
       <c r="E348" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H348" t="s">
         <v>326</v>
@@ -23826,15 +23857,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E348,Foderstater!$R$56:$R$83,0),MATCH(A348&amp;C348&amp;D348,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J348" s="160"/>
-      <c r="K348" s="160"/>
+      <c r="J348" s="159"/>
+      <c r="K348" s="159"/>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>38</v>
       </c>
       <c r="E349" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H349" t="s">
         <v>326</v>
@@ -23843,15 +23874,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E349,Foderstater!$R$56:$R$83,0),MATCH(A349&amp;C349&amp;D349,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J349" s="160"/>
-      <c r="K349" s="160"/>
+      <c r="J349" s="159"/>
+      <c r="K349" s="159"/>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>38</v>
       </c>
       <c r="E350" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H350" t="s">
         <v>326</v>
@@ -23860,15 +23891,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E350,Foderstater!$R$56:$R$83,0),MATCH(A350&amp;C350&amp;D350,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J350" s="160"/>
-      <c r="K350" s="160"/>
+      <c r="J350" s="159"/>
+      <c r="K350" s="159"/>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>38</v>
       </c>
       <c r="E351" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H351" t="s">
         <v>326</v>
@@ -23877,15 +23908,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E351,Foderstater!$R$56:$R$83,0),MATCH(A351&amp;C351&amp;D351,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J351" s="160"/>
-      <c r="K351" s="160"/>
+      <c r="J351" s="159"/>
+      <c r="K351" s="159"/>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>38</v>
       </c>
       <c r="E352" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H352" t="s">
         <v>326</v>
@@ -23894,15 +23925,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E352,Foderstater!$R$56:$R$83,0),MATCH(A352&amp;C352&amp;D352,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J352" s="160"/>
-      <c r="K352" s="160"/>
+      <c r="J352" s="159"/>
+      <c r="K352" s="159"/>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>38</v>
       </c>
       <c r="E353" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H353" t="s">
         <v>326</v>
@@ -23911,15 +23942,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E353,Foderstater!$R$56:$R$83,0),MATCH(A353&amp;C353&amp;D353,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J353" s="160"/>
-      <c r="K353" s="160"/>
+      <c r="J353" s="159"/>
+      <c r="K353" s="159"/>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>38</v>
       </c>
       <c r="E354" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H354" t="s">
         <v>326</v>
@@ -23928,15 +23959,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E354,Foderstater!$R$56:$R$83,0),MATCH(A354&amp;C354&amp;D354,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J354" s="160"/>
-      <c r="K354" s="160"/>
+      <c r="J354" s="159"/>
+      <c r="K354" s="159"/>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>38</v>
       </c>
       <c r="E355" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H355" t="s">
         <v>326</v>
@@ -23945,15 +23976,15 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E355,Foderstater!$R$56:$R$83,0),MATCH(A355&amp;C355&amp;D355,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J355" s="160"/>
-      <c r="K355" s="160"/>
+      <c r="J355" s="159"/>
+      <c r="K355" s="159"/>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>38</v>
       </c>
       <c r="E356" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H356" t="s">
         <v>326</v>
@@ -23968,7 +23999,7 @@
         <v>38</v>
       </c>
       <c r="E357" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H357" t="s">
         <v>326</v>
@@ -23983,7 +24014,7 @@
         <v>38</v>
       </c>
       <c r="E358" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H358" t="s">
         <v>326</v>
@@ -23998,7 +24029,7 @@
         <v>38</v>
       </c>
       <c r="E359" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H359" t="s">
         <v>326</v>
@@ -24013,7 +24044,7 @@
         <v>38</v>
       </c>
       <c r="E360" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H360" t="s">
         <v>326</v>
@@ -24028,7 +24059,7 @@
         <v>38</v>
       </c>
       <c r="E361" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H361" t="s">
         <v>326</v>
@@ -24043,7 +24074,7 @@
         <v>38</v>
       </c>
       <c r="E362" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H362" t="s">
         <v>326</v>
@@ -24057,36 +24088,36 @@
       <c r="A364" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="B364" s="164"/>
-      <c r="C364" s="164"/>
+      <c r="B364" s="163"/>
+      <c r="C364" s="163"/>
       <c r="D364" s="90"/>
       <c r="E364" s="90"/>
       <c r="F364" s="90"/>
       <c r="G364" s="90"/>
       <c r="H364" s="90"/>
-      <c r="I364" s="165"/>
+      <c r="I364" s="164"/>
       <c r="J364" s="90"/>
       <c r="K364" s="90"/>
       <c r="L364" s="90"/>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A365" s="160" t="s">
+      <c r="A365" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="B365" s="160"/>
-      <c r="C365" s="160"/>
-      <c r="D365" s="160" t="s">
+      <c r="B365" s="159"/>
+      <c r="C365" s="159"/>
+      <c r="D365" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="H365" s="160" t="s">
+      <c r="H365" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I365" s="160">
+      <c r="I365" s="159">
         <v>0</v>
       </c>
-      <c r="J365" s="160"/>
-      <c r="K365" s="160" t="s">
-        <v>427</v>
+      <c r="J365" s="159"/>
+      <c r="K365" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
@@ -24097,7 +24128,7 @@
         <v>35</v>
       </c>
       <c r="E366" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H366" t="s">
         <v>326</v>
@@ -24106,8 +24137,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E366,Foderstater!$R$56:$R$83,0),MATCH(A366&amp;C366&amp;D366,Foderstater!$U$55:$AD$55,0))</f>
         <v>60.249501023299892</v>
       </c>
-      <c r="J366" s="160"/>
-      <c r="K366" s="160"/>
+      <c r="J366" s="159"/>
+      <c r="K366" s="159"/>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
@@ -24117,7 +24148,7 @@
         <v>35</v>
       </c>
       <c r="E367" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H367" t="s">
         <v>326</v>
@@ -24126,8 +24157,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E367,Foderstater!$R$56:$R$83,0),MATCH(A367&amp;C367&amp;D367,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J367" s="160"/>
-      <c r="K367" s="160"/>
+      <c r="J367" s="159"/>
+      <c r="K367" s="159"/>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
@@ -24137,7 +24168,7 @@
         <v>35</v>
       </c>
       <c r="E368" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H368" t="s">
         <v>326</v>
@@ -24146,8 +24177,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E368,Foderstater!$R$56:$R$83,0),MATCH(A368&amp;C368&amp;D368,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J368" s="160"/>
-      <c r="K368" s="160"/>
+      <c r="J368" s="159"/>
+      <c r="K368" s="159"/>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
@@ -24157,7 +24188,7 @@
         <v>35</v>
       </c>
       <c r="E369" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H369" t="s">
         <v>326</v>
@@ -24166,8 +24197,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E369,Foderstater!$R$56:$R$83,0),MATCH(A369&amp;C369&amp;D369,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J369" s="160"/>
-      <c r="K369" s="160"/>
+      <c r="J369" s="159"/>
+      <c r="K369" s="159"/>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
@@ -24177,7 +24208,7 @@
         <v>35</v>
       </c>
       <c r="E370" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H370" t="s">
         <v>326</v>
@@ -24186,8 +24217,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E370,Foderstater!$R$56:$R$83,0),MATCH(A370&amp;C370&amp;D370,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J370" s="160"/>
-      <c r="K370" s="160"/>
+      <c r="J370" s="159"/>
+      <c r="K370" s="159"/>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
@@ -24197,7 +24228,7 @@
         <v>35</v>
       </c>
       <c r="E371" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H371" t="s">
         <v>326</v>
@@ -24206,8 +24237,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E371,Foderstater!$R$56:$R$83,0),MATCH(A371&amp;C371&amp;D371,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J371" s="160"/>
-      <c r="K371" s="160"/>
+      <c r="J371" s="159"/>
+      <c r="K371" s="159"/>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
@@ -24217,7 +24248,7 @@
         <v>35</v>
       </c>
       <c r="E372" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H372" t="s">
         <v>326</v>
@@ -24226,8 +24257,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E372,Foderstater!$R$56:$R$83,0),MATCH(A372&amp;C372&amp;D372,Foderstater!$U$55:$AD$55,0))</f>
         <v>8.3580433504262022</v>
       </c>
-      <c r="J372" s="160"/>
-      <c r="K372" s="160"/>
+      <c r="J372" s="159"/>
+      <c r="K372" s="159"/>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
@@ -24237,7 +24268,7 @@
         <v>35</v>
       </c>
       <c r="E373" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H373" t="s">
         <v>326</v>
@@ -24246,8 +24277,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E373,Foderstater!$R$56:$R$83,0),MATCH(A373&amp;C373&amp;D373,Foderstater!$U$55:$AD$55,0))</f>
         <v>6.3565169401541155</v>
       </c>
-      <c r="J373" s="160"/>
-      <c r="K373" s="160"/>
+      <c r="J373" s="159"/>
+      <c r="K373" s="159"/>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
@@ -24257,7 +24288,7 @@
         <v>35</v>
       </c>
       <c r="E374" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H374" t="s">
         <v>326</v>
@@ -24266,8 +24297,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E374,Foderstater!$R$56:$R$83,0),MATCH(A374&amp;C374&amp;D374,Foderstater!$U$55:$AD$55,0))</f>
         <v>16.834448704037197</v>
       </c>
-      <c r="J374" s="160"/>
-      <c r="K374" s="160"/>
+      <c r="J374" s="159"/>
+      <c r="K374" s="159"/>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
@@ -24277,7 +24308,7 @@
         <v>35</v>
       </c>
       <c r="E375" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H375" t="s">
         <v>326</v>
@@ -24286,8 +24317,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E375,Foderstater!$R$56:$R$83,0),MATCH(A375&amp;C375&amp;D375,Foderstater!$U$55:$AD$55,0))</f>
         <v>3.4789898578450962</v>
       </c>
-      <c r="J375" s="160"/>
-      <c r="K375" s="160"/>
+      <c r="J375" s="159"/>
+      <c r="K375" s="159"/>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
@@ -24297,7 +24328,7 @@
         <v>35</v>
       </c>
       <c r="E376" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H376" t="s">
         <v>326</v>
@@ -24306,8 +24337,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E376,Foderstater!$R$56:$R$83,0),MATCH(A376&amp;C376&amp;D376,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J376" s="160"/>
-      <c r="K376" s="160"/>
+      <c r="J376" s="159"/>
+      <c r="K376" s="159"/>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
@@ -24317,7 +24348,7 @@
         <v>35</v>
       </c>
       <c r="E377" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H377" t="s">
         <v>326</v>
@@ -24326,8 +24357,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E377,Foderstater!$R$56:$R$83,0),MATCH(A377&amp;C377&amp;D377,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.9860883502482297E-2</v>
       </c>
-      <c r="J377" s="160"/>
-      <c r="K377" s="160"/>
+      <c r="J377" s="159"/>
+      <c r="K377" s="159"/>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
@@ -24337,7 +24368,7 @@
         <v>35</v>
       </c>
       <c r="E378" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H378" t="s">
         <v>326</v>
@@ -24346,8 +24377,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E378,Foderstater!$R$56:$R$83,0),MATCH(A378&amp;C378&amp;D378,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.2676767287415975</v>
       </c>
-      <c r="J378" s="160"/>
-      <c r="K378" s="160"/>
+      <c r="J378" s="159"/>
+      <c r="K378" s="159"/>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
@@ -24357,7 +24388,7 @@
         <v>35</v>
       </c>
       <c r="E379" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H379" t="s">
         <v>326</v>
@@ -24366,8 +24397,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E379,Foderstater!$R$56:$R$83,0),MATCH(A379&amp;C379&amp;D379,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.2321396453293407</v>
       </c>
-      <c r="J379" s="160"/>
-      <c r="K379" s="160"/>
+      <c r="J379" s="159"/>
+      <c r="K379" s="159"/>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
@@ -24377,7 +24408,7 @@
         <v>35</v>
       </c>
       <c r="E380" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H380" t="s">
         <v>326</v>
@@ -24386,8 +24417,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E380,Foderstater!$R$56:$R$83,0),MATCH(A380&amp;C380&amp;D380,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.50261957176929339</v>
       </c>
-      <c r="J380" s="160"/>
-      <c r="K380" s="160"/>
+      <c r="J380" s="159"/>
+      <c r="K380" s="159"/>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
@@ -24397,7 +24428,7 @@
         <v>35</v>
       </c>
       <c r="E381" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H381" t="s">
         <v>326</v>
@@ -24406,8 +24437,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E381,Foderstater!$R$56:$R$83,0),MATCH(A381&amp;C381&amp;D381,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.14133294891292425</v>
       </c>
-      <c r="J381" s="160"/>
-      <c r="K381" s="160"/>
+      <c r="J381" s="159"/>
+      <c r="K381" s="159"/>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
@@ -24417,7 +24448,7 @@
         <v>35</v>
       </c>
       <c r="E382" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H382" t="s">
         <v>326</v>
@@ -24426,8 +24457,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E382,Foderstater!$R$56:$R$83,0),MATCH(A382&amp;C382&amp;D382,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.33668778662955168</v>
       </c>
-      <c r="J382" s="160"/>
-      <c r="K382" s="160"/>
+      <c r="J382" s="159"/>
+      <c r="K382" s="159"/>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
@@ -24437,7 +24468,7 @@
         <v>35</v>
       </c>
       <c r="E383" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H383" t="s">
         <v>326</v>
@@ -24446,8 +24477,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E383,Foderstater!$R$56:$R$83,0),MATCH(A383&amp;C383&amp;D383,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.11471466363546844</v>
       </c>
-      <c r="J383" s="160"/>
-      <c r="K383" s="160"/>
+      <c r="J383" s="159"/>
+      <c r="K383" s="159"/>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
@@ -24457,7 +24488,7 @@
         <v>35</v>
       </c>
       <c r="E384" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H384" t="s">
         <v>326</v>
@@ -24466,8 +24497,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E384,Foderstater!$R$56:$R$83,0),MATCH(A384&amp;C384&amp;D384,Foderstater!$U$55:$AD$55,0))</f>
         <v>5.8016228139711724E-2</v>
       </c>
-      <c r="J384" s="160"/>
-      <c r="K384" s="160"/>
+      <c r="J384" s="159"/>
+      <c r="K384" s="159"/>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
@@ -24477,7 +24508,7 @@
         <v>35</v>
       </c>
       <c r="E385" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H385" t="s">
         <v>326</v>
@@ -24486,8 +24517,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E385,Foderstater!$R$56:$R$83,0),MATCH(A385&amp;C385&amp;D385,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.14739522877318739</v>
       </c>
-      <c r="J385" s="160"/>
-      <c r="K385" s="160"/>
+      <c r="J385" s="159"/>
+      <c r="K385" s="159"/>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
@@ -24497,7 +24528,7 @@
         <v>35</v>
       </c>
       <c r="E386" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H386" t="s">
         <v>326</v>
@@ -24506,8 +24537,8 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E386,Foderstater!$R$56:$R$83,0),MATCH(A386&amp;C386&amp;D386,Foderstater!$U$55:$AD$55,0))</f>
         <v>0.3999503550702303</v>
       </c>
-      <c r="J386" s="160"/>
-      <c r="K386" s="160"/>
+      <c r="J386" s="159"/>
+      <c r="K386" s="159"/>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
@@ -24517,7 +24548,7 @@
         <v>35</v>
       </c>
       <c r="E387" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H387" t="s">
         <v>326</v>
@@ -24535,7 +24566,7 @@
         <v>35</v>
       </c>
       <c r="E388" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H388" t="s">
         <v>326</v>
@@ -24553,7 +24584,7 @@
         <v>35</v>
       </c>
       <c r="E389" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H389" t="s">
         <v>326</v>
@@ -24571,7 +24602,7 @@
         <v>35</v>
       </c>
       <c r="E390" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H390" t="s">
         <v>326</v>
@@ -24589,7 +24620,7 @@
         <v>35</v>
       </c>
       <c r="E391" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H391" t="s">
         <v>326</v>
@@ -24607,7 +24638,7 @@
         <v>35</v>
       </c>
       <c r="E392" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H392" t="s">
         <v>326</v>
@@ -24625,7 +24656,7 @@
         <v>35</v>
       </c>
       <c r="E393" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H393" t="s">
         <v>326</v>
@@ -24636,29 +24667,29 @@
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J394" s="160"/>
-      <c r="K394" s="160"/>
+      <c r="J394" s="159"/>
+      <c r="K394" s="159"/>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A395" s="160" t="s">
+      <c r="A395" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="B395" s="160"/>
-      <c r="C395" s="160" t="s">
-        <v>433</v>
-      </c>
-      <c r="D395" s="160" t="s">
+      <c r="B395" s="159"/>
+      <c r="C395" s="159" t="s">
+        <v>432</v>
+      </c>
+      <c r="D395" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="H395" s="160" t="s">
+      <c r="H395" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I395" s="160">
+      <c r="I395" s="159">
         <v>0</v>
       </c>
-      <c r="J395" s="160"/>
-      <c r="K395" s="160" t="s">
-        <v>427</v>
+      <c r="J395" s="159"/>
+      <c r="K395" s="159" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.25">
@@ -24666,13 +24697,13 @@
         <v>38</v>
       </c>
       <c r="C396" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D396" t="s">
         <v>35</v>
       </c>
       <c r="E396" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H396" t="s">
         <v>326</v>
@@ -24681,21 +24712,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E396,Foderstater!$R$56:$R$83,0),MATCH(A396&amp;C396&amp;D396,Foderstater!$U$55:$AD$55,0))</f>
         <v>56.175982718049596</v>
       </c>
-      <c r="J396" s="160"/>
-      <c r="K396" s="160"/>
+      <c r="J396" s="159"/>
+      <c r="K396" s="159"/>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>38</v>
       </c>
       <c r="C397" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D397" t="s">
         <v>35</v>
       </c>
       <c r="E397" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H397" t="s">
         <v>326</v>
@@ -24704,21 +24735,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E397,Foderstater!$R$56:$R$83,0),MATCH(A397&amp;C397&amp;D397,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J397" s="160"/>
-      <c r="K397" s="160"/>
+      <c r="J397" s="159"/>
+      <c r="K397" s="159"/>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>38</v>
       </c>
       <c r="C398" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D398" t="s">
         <v>35</v>
       </c>
       <c r="E398" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H398" t="s">
         <v>326</v>
@@ -24727,21 +24758,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E398,Foderstater!$R$56:$R$83,0),MATCH(A398&amp;C398&amp;D398,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J398" s="160"/>
-      <c r="K398" s="160"/>
+      <c r="J398" s="159"/>
+      <c r="K398" s="159"/>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>38</v>
       </c>
       <c r="C399" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D399" t="s">
         <v>35</v>
       </c>
       <c r="E399" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H399" t="s">
         <v>326</v>
@@ -24750,21 +24781,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E399,Foderstater!$R$56:$R$83,0),MATCH(A399&amp;C399&amp;D399,Foderstater!$U$55:$AD$55,0))</f>
         <v>13.115765922154072</v>
       </c>
-      <c r="J399" s="160"/>
-      <c r="K399" s="160"/>
+      <c r="J399" s="159"/>
+      <c r="K399" s="159"/>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>38</v>
       </c>
       <c r="C400" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D400" t="s">
         <v>35</v>
       </c>
       <c r="E400" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H400" t="s">
         <v>326</v>
@@ -24773,21 +24804,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E400,Foderstater!$R$56:$R$83,0),MATCH(A400&amp;C400&amp;D400,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J400" s="160"/>
-      <c r="K400" s="160"/>
+      <c r="J400" s="159"/>
+      <c r="K400" s="159"/>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>38</v>
       </c>
       <c r="C401" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D401" t="s">
         <v>35</v>
       </c>
       <c r="E401" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H401" t="s">
         <v>326</v>
@@ -24796,21 +24827,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E401,Foderstater!$R$56:$R$83,0),MATCH(A401&amp;C401&amp;D401,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J401" s="160"/>
-      <c r="K401" s="160"/>
+      <c r="J401" s="159"/>
+      <c r="K401" s="159"/>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>38</v>
       </c>
       <c r="C402" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D402" t="s">
         <v>35</v>
       </c>
       <c r="E402" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H402" t="s">
         <v>326</v>
@@ -24819,21 +24850,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E402,Foderstater!$R$56:$R$83,0),MATCH(A402&amp;C402&amp;D402,Foderstater!$U$55:$AD$55,0))</f>
         <v>6.4239515794862037</v>
       </c>
-      <c r="J402" s="160"/>
-      <c r="K402" s="160"/>
+      <c r="J402" s="159"/>
+      <c r="K402" s="159"/>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>38</v>
       </c>
       <c r="C403" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D403" t="s">
         <v>35</v>
       </c>
       <c r="E403" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H403" t="s">
         <v>326</v>
@@ -24842,21 +24873,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E403,Foderstater!$R$56:$R$83,0),MATCH(A403&amp;C403&amp;D403,Foderstater!$U$55:$AD$55,0))</f>
         <v>5.1013876253121104</v>
       </c>
-      <c r="J403" s="160"/>
-      <c r="K403" s="160"/>
+      <c r="J403" s="159"/>
+      <c r="K403" s="159"/>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>38</v>
       </c>
       <c r="C404" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D404" t="s">
         <v>35</v>
       </c>
       <c r="E404" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H404" t="s">
         <v>326</v>
@@ -24865,21 +24896,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E404,Foderstater!$R$56:$R$83,0),MATCH(A404&amp;C404&amp;D404,Foderstater!$U$55:$AD$55,0))</f>
         <v>13.185764834849451</v>
       </c>
-      <c r="J404" s="160"/>
-      <c r="K404" s="160"/>
+      <c r="J404" s="159"/>
+      <c r="K404" s="159"/>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>38</v>
       </c>
       <c r="C405" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D405" t="s">
         <v>35</v>
       </c>
       <c r="E405" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H405" t="s">
         <v>326</v>
@@ -24888,21 +24919,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E405,Foderstater!$R$56:$R$83,0),MATCH(A405&amp;C405&amp;D405,Foderstater!$U$55:$AD$55,0))</f>
         <v>2.7249566014817326</v>
       </c>
-      <c r="J405" s="160"/>
-      <c r="K405" s="160"/>
+      <c r="J405" s="159"/>
+      <c r="K405" s="159"/>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>38</v>
       </c>
       <c r="C406" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D406" t="s">
         <v>35</v>
       </c>
       <c r="E406" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H406" t="s">
         <v>326</v>
@@ -24911,21 +24942,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E406,Foderstater!$R$56:$R$83,0),MATCH(A406&amp;C406&amp;D406,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J406" s="160"/>
-      <c r="K406" s="160"/>
+      <c r="J406" s="159"/>
+      <c r="K406" s="159"/>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>38</v>
       </c>
       <c r="C407" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D407" t="s">
         <v>35</v>
       </c>
       <c r="E407" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H407" t="s">
         <v>326</v>
@@ -24934,21 +24965,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E407,Foderstater!$R$56:$R$83,0),MATCH(A407&amp;C407&amp;D407,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J407" s="160"/>
-      <c r="K407" s="160"/>
+      <c r="J407" s="159"/>
+      <c r="K407" s="159"/>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>38</v>
       </c>
       <c r="C408" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D408" t="s">
         <v>35</v>
       </c>
       <c r="E408" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H408" t="s">
         <v>326</v>
@@ -24957,21 +24988,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E408,Foderstater!$R$56:$R$83,0),MATCH(A408&amp;C408&amp;D408,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.6787180022812531</v>
       </c>
-      <c r="J408" s="160"/>
-      <c r="K408" s="160"/>
+      <c r="J408" s="159"/>
+      <c r="K408" s="159"/>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>38</v>
       </c>
       <c r="C409" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D409" t="s">
         <v>35</v>
       </c>
       <c r="E409" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H409" t="s">
         <v>326</v>
@@ -24980,21 +25011,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E409,Foderstater!$R$56:$R$83,0),MATCH(A409&amp;C409&amp;D409,Foderstater!$U$55:$AD$55,0))</f>
         <v>1.5934727163855678</v>
       </c>
-      <c r="J409" s="160"/>
-      <c r="K409" s="160"/>
+      <c r="J409" s="159"/>
+      <c r="K409" s="159"/>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>38</v>
       </c>
       <c r="C410" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D410" t="s">
         <v>35</v>
       </c>
       <c r="E410" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H410" t="s">
         <v>326</v>
@@ -25003,21 +25034,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E410,Foderstater!$R$56:$R$83,0),MATCH(A410&amp;C410&amp;D410,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J410" s="160"/>
-      <c r="K410" s="160"/>
+      <c r="J410" s="159"/>
+      <c r="K410" s="159"/>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>38</v>
       </c>
       <c r="C411" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D411" t="s">
         <v>35</v>
       </c>
       <c r="E411" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H411" t="s">
         <v>326</v>
@@ -25026,21 +25057,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E411,Foderstater!$R$56:$R$83,0),MATCH(A411&amp;C411&amp;D411,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J411" s="160"/>
-      <c r="K411" s="160"/>
+      <c r="J411" s="159"/>
+      <c r="K411" s="159"/>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>38</v>
       </c>
       <c r="C412" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D412" t="s">
         <v>35</v>
       </c>
       <c r="E412" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H412" t="s">
         <v>326</v>
@@ -25049,21 +25080,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E412,Foderstater!$R$56:$R$83,0),MATCH(A412&amp;C412&amp;D412,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J412" s="160"/>
-      <c r="K412" s="160"/>
+      <c r="J412" s="159"/>
+      <c r="K412" s="159"/>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>38</v>
       </c>
       <c r="C413" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D413" t="s">
         <v>35</v>
       </c>
       <c r="E413" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H413" t="s">
         <v>326</v>
@@ -25072,21 +25103,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E413,Foderstater!$R$56:$R$83,0),MATCH(A413&amp;C413&amp;D413,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J413" s="160"/>
-      <c r="K413" s="160"/>
+      <c r="J413" s="159"/>
+      <c r="K413" s="159"/>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>38</v>
       </c>
       <c r="C414" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D414" t="s">
         <v>35</v>
       </c>
       <c r="E414" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H414" t="s">
         <v>326</v>
@@ -25095,21 +25126,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E414,Foderstater!$R$56:$R$83,0),MATCH(A414&amp;C414&amp;D414,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J414" s="160"/>
-      <c r="K414" s="160"/>
+      <c r="J414" s="159"/>
+      <c r="K414" s="159"/>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>38</v>
       </c>
       <c r="C415" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D415" t="s">
         <v>35</v>
       </c>
       <c r="E415" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H415" t="s">
         <v>326</v>
@@ -25118,21 +25149,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E415,Foderstater!$R$56:$R$83,0),MATCH(A415&amp;C415&amp;D415,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J415" s="160"/>
-      <c r="K415" s="160"/>
+      <c r="J415" s="159"/>
+      <c r="K415" s="159"/>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>38</v>
       </c>
       <c r="C416" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D416" t="s">
         <v>35</v>
       </c>
       <c r="E416" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H416" t="s">
         <v>326</v>
@@ -25141,21 +25172,21 @@
         <f>INDEX(Foderstater!$U$56:$AD$83,MATCH(E416,Foderstater!$R$56:$R$83,0),MATCH(A416&amp;C416&amp;D416,Foderstater!$U$55:$AD$55,0))</f>
         <v>0</v>
       </c>
-      <c r="J416" s="160"/>
-      <c r="K416" s="160"/>
+      <c r="J416" s="159"/>
+      <c r="K416" s="159"/>
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>38</v>
       </c>
       <c r="C417" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D417" t="s">
         <v>35</v>
       </c>
       <c r="E417" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H417" t="s">
         <v>326</v>
@@ -25170,13 +25201,13 @@
         <v>38</v>
       </c>
       <c r="C418" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D418" t="s">
         <v>35</v>
       </c>
       <c r="E418" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H418" t="s">
         <v>326</v>
@@ -25191,13 +25222,13 @@
         <v>38</v>
       </c>
       <c r="C419" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D419" t="s">
         <v>35</v>
       </c>
       <c r="E419" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H419" t="s">
         <v>326</v>
@@ -25212,13 +25243,13 @@
         <v>38</v>
       </c>
       <c r="C420" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D420" t="s">
         <v>35</v>
       </c>
       <c r="E420" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H420" t="s">
         <v>326</v>
@@ -25233,13 +25264,13 @@
         <v>38</v>
       </c>
       <c r="C421" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D421" t="s">
         <v>35</v>
       </c>
       <c r="E421" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H421" t="s">
         <v>326</v>
@@ -25254,13 +25285,13 @@
         <v>38</v>
       </c>
       <c r="C422" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D422" t="s">
         <v>35</v>
       </c>
       <c r="E422" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H422" t="s">
         <v>326</v>
@@ -25275,13 +25306,13 @@
         <v>38</v>
       </c>
       <c r="C423" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D423" t="s">
         <v>35</v>
       </c>
       <c r="E423" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H423" t="s">
         <v>326</v>
@@ -25292,11 +25323,11 @@
       </c>
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A425" s="159" t="s">
+      <c r="A425" s="158" t="s">
         <v>305</v>
       </c>
-      <c r="B425" s="159"/>
-      <c r="C425" s="159"/>
+      <c r="B425" s="158"/>
+      <c r="C425" s="158"/>
       <c r="D425" s="95"/>
       <c r="E425" s="95"/>
       <c r="F425" s="95"/>
@@ -27838,7 +27869,7 @@
       <c r="D36" s="12"/>
       <c r="E36" s="42"/>
       <c r="M36" s="14" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N36" s="21"/>
       <c r="O36" s="22"/>
@@ -27894,7 +27925,7 @@
       <c r="D37" s="12"/>
       <c r="E37" s="42"/>
       <c r="M37" s="14" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N37" s="21"/>
       <c r="O37" s="22"/>
@@ -31219,7 +31250,7 @@
     </row>
     <row r="94" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="96" spans="2:30" x14ac:dyDescent="0.25">
@@ -31227,10 +31258,10 @@
         <v>316</v>
       </c>
       <c r="F96" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I96" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
@@ -31238,28 +31269,28 @@
         <v>18</v>
       </c>
       <c r="D97" t="s">
+        <v>398</v>
+      </c>
+      <c r="E97" t="s">
         <v>399</v>
-      </c>
-      <c r="E97" t="s">
-        <v>400</v>
       </c>
       <c r="F97" t="s">
         <v>18</v>
       </c>
       <c r="G97" t="s">
+        <v>398</v>
+      </c>
+      <c r="H97" t="s">
         <v>399</v>
-      </c>
-      <c r="H97" t="s">
-        <v>400</v>
       </c>
       <c r="I97" t="s">
         <v>18</v>
       </c>
       <c r="J97" t="s">
+        <v>398</v>
+      </c>
+      <c r="K97" t="s">
         <v>399</v>
-      </c>
-      <c r="K97" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
@@ -31449,7 +31480,7 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" s="155" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C103" s="2">
         <f>AVERAGE(C98:C102)</f>
@@ -31490,7 +31521,7 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D104" s="155" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E104" s="156">
         <f>1/E103</f>
@@ -31548,201 +31579,201 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B2" s="179" t="s">
-        <v>522</v>
-      </c>
-      <c r="C2" s="179" t="s">
-        <v>452</v>
-      </c>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="179"/>
-      <c r="K2" s="179"/>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="179"/>
-      <c r="P2" s="179"/>
-      <c r="Q2" s="179"/>
-      <c r="R2" s="179"/>
-      <c r="S2" s="179"/>
-      <c r="T2" s="179"/>
-      <c r="U2" s="179"/>
-      <c r="V2" s="179"/>
-      <c r="W2" s="179"/>
-      <c r="X2" s="179" t="s">
+      <c r="B2" s="178" t="s">
+        <v>521</v>
+      </c>
+      <c r="C2" s="178" t="s">
+        <v>451</v>
+      </c>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+      <c r="L2" s="178"/>
+      <c r="M2" s="178"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="178"/>
+      <c r="P2" s="178"/>
+      <c r="Q2" s="178"/>
+      <c r="R2" s="178"/>
+      <c r="S2" s="178"/>
+      <c r="T2" s="178"/>
+      <c r="U2" s="178"/>
+      <c r="V2" s="178"/>
+      <c r="W2" s="178"/>
+      <c r="X2" s="178" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y2" s="178"/>
+      <c r="AA2" s="190"/>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B3" s="178"/>
+      <c r="C3" s="83" t="s">
+        <v>450</v>
+      </c>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="83" t="s">
+        <v>470</v>
+      </c>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
+      <c r="O3" s="171"/>
+      <c r="P3" s="171"/>
+      <c r="Q3" s="171"/>
+      <c r="R3" s="83" t="s">
+        <v>471</v>
+      </c>
+      <c r="S3" s="171"/>
+      <c r="T3" s="171"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="171"/>
+      <c r="W3" s="171"/>
+      <c r="X3" s="193" t="s">
         <v>530</v>
       </c>
-      <c r="Y2" s="179"/>
-      <c r="AA2" s="191"/>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B3" s="179"/>
-      <c r="C3" s="83" t="s">
-        <v>451</v>
-      </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
-      <c r="L3" s="83" t="s">
-        <v>471</v>
-      </c>
-      <c r="M3" s="172"/>
-      <c r="N3" s="172"/>
-      <c r="O3" s="172"/>
-      <c r="P3" s="172"/>
-      <c r="Q3" s="172"/>
-      <c r="R3" s="83" t="s">
-        <v>472</v>
-      </c>
-      <c r="S3" s="172"/>
-      <c r="T3" s="172"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="194" t="s">
-        <v>531</v>
-      </c>
       <c r="Y3" s="83"/>
-      <c r="AA3" s="192"/>
+      <c r="AA3" s="191"/>
     </row>
     <row r="4" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B4" s="172"/>
+      <c r="B4" s="171"/>
       <c r="C4" s="101" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D4" s="101"/>
       <c r="E4" s="101"/>
-      <c r="F4" s="169" t="s">
-        <v>455</v>
-      </c>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
+      <c r="F4" s="168" t="s">
+        <v>454</v>
+      </c>
+      <c r="G4" s="168"/>
+      <c r="H4" s="168"/>
       <c r="I4" s="101" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J4" s="101"/>
       <c r="K4" s="101"/>
-      <c r="L4" s="169" t="s">
+      <c r="L4" s="168" t="s">
+        <v>464</v>
+      </c>
+      <c r="M4" s="168"/>
+      <c r="N4" s="168"/>
+      <c r="O4" s="101" t="s">
         <v>465</v>
-      </c>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="101" t="s">
-        <v>466</v>
       </c>
       <c r="P4" s="101"/>
       <c r="Q4" s="101"/>
-      <c r="R4" s="169" t="s">
+      <c r="R4" s="168" t="s">
+        <v>455</v>
+      </c>
+      <c r="S4" s="168"/>
+      <c r="T4" s="168"/>
+      <c r="U4" s="101" t="s">
         <v>456</v>
-      </c>
-      <c r="S4" s="169"/>
-      <c r="T4" s="169"/>
-      <c r="U4" s="101" t="s">
-        <v>457</v>
       </c>
       <c r="V4" s="101"/>
       <c r="W4" s="101"/>
-      <c r="X4" s="169" t="s">
+      <c r="X4" s="168" t="s">
+        <v>526</v>
+      </c>
+      <c r="Y4" s="101" t="s">
+        <v>526</v>
+      </c>
+      <c r="AA4" s="32"/>
+    </row>
+    <row r="5" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="171"/>
+      <c r="C5" s="101" t="s">
+        <v>439</v>
+      </c>
+      <c r="D5" s="101" t="s">
+        <v>440</v>
+      </c>
+      <c r="E5" s="101" t="s">
+        <v>441</v>
+      </c>
+      <c r="F5" s="168" t="s">
+        <v>439</v>
+      </c>
+      <c r="G5" s="168" t="s">
+        <v>440</v>
+      </c>
+      <c r="H5" s="168" t="s">
+        <v>441</v>
+      </c>
+      <c r="I5" s="101" t="s">
+        <v>439</v>
+      </c>
+      <c r="J5" s="101" t="s">
+        <v>440</v>
+      </c>
+      <c r="K5" s="101" t="s">
+        <v>441</v>
+      </c>
+      <c r="L5" s="168" t="s">
+        <v>439</v>
+      </c>
+      <c r="M5" s="168" t="s">
+        <v>440</v>
+      </c>
+      <c r="N5" s="168" t="s">
+        <v>441</v>
+      </c>
+      <c r="O5" s="101" t="s">
+        <v>439</v>
+      </c>
+      <c r="P5" s="101" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q5" s="101" t="s">
+        <v>441</v>
+      </c>
+      <c r="R5" s="168" t="s">
+        <v>439</v>
+      </c>
+      <c r="S5" s="168" t="s">
+        <v>440</v>
+      </c>
+      <c r="T5" s="168" t="s">
+        <v>441</v>
+      </c>
+      <c r="U5" s="101" t="s">
+        <v>439</v>
+      </c>
+      <c r="V5" s="101" t="s">
+        <v>440</v>
+      </c>
+      <c r="W5" s="101" t="s">
+        <v>441</v>
+      </c>
+      <c r="X5" s="168" t="s">
         <v>527</v>
       </c>
-      <c r="Y4" s="101" t="s">
-        <v>527</v>
-      </c>
-      <c r="AA4" s="32"/>
-    </row>
-    <row r="5" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="172"/>
-      <c r="C5" s="101" t="s">
-        <v>440</v>
-      </c>
-      <c r="D5" s="101" t="s">
-        <v>441</v>
-      </c>
-      <c r="E5" s="101" t="s">
-        <v>442</v>
-      </c>
-      <c r="F5" s="169" t="s">
-        <v>440</v>
-      </c>
-      <c r="G5" s="169" t="s">
-        <v>441</v>
-      </c>
-      <c r="H5" s="169" t="s">
-        <v>442</v>
-      </c>
-      <c r="I5" s="101" t="s">
-        <v>440</v>
-      </c>
-      <c r="J5" s="101" t="s">
-        <v>441</v>
-      </c>
-      <c r="K5" s="101" t="s">
-        <v>442</v>
-      </c>
-      <c r="L5" s="169" t="s">
-        <v>440</v>
-      </c>
-      <c r="M5" s="169" t="s">
-        <v>441</v>
-      </c>
-      <c r="N5" s="169" t="s">
-        <v>442</v>
-      </c>
-      <c r="O5" s="101" t="s">
-        <v>440</v>
-      </c>
-      <c r="P5" s="101" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q5" s="101" t="s">
-        <v>442</v>
-      </c>
-      <c r="R5" s="169" t="s">
-        <v>440</v>
-      </c>
-      <c r="S5" s="169" t="s">
-        <v>441</v>
-      </c>
-      <c r="T5" s="169" t="s">
-        <v>442</v>
-      </c>
-      <c r="U5" s="101" t="s">
-        <v>440</v>
-      </c>
-      <c r="V5" s="101" t="s">
-        <v>441</v>
-      </c>
-      <c r="W5" s="101" t="s">
-        <v>442</v>
-      </c>
-      <c r="X5" s="169" t="s">
+      <c r="Y5" s="101" t="s">
         <v>528</v>
       </c>
-      <c r="Y5" s="101" t="s">
-        <v>529</v>
-      </c>
       <c r="AA5" s="32"/>
-      <c r="AF5" s="173" t="s">
-        <v>491</v>
+      <c r="AF5" s="172" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="172" t="s">
-        <v>458</v>
-      </c>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
-      <c r="E6" s="169"/>
+      <c r="B6" s="171" t="s">
+        <v>457</v>
+      </c>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="168"/>
       <c r="F6" s="90">
         <v>1229</v>
       </c>
@@ -31750,9 +31781,9 @@
       <c r="H6" s="90">
         <v>1329</v>
       </c>
-      <c r="I6" s="169"/>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
+      <c r="I6" s="168"/>
+      <c r="J6" s="168"/>
+      <c r="K6" s="168"/>
       <c r="L6" s="90">
         <v>2119</v>
       </c>
@@ -31760,49 +31791,49 @@
       <c r="N6" s="90">
         <v>2130</v>
       </c>
-      <c r="O6" s="169"/>
-      <c r="P6" s="169"/>
-      <c r="Q6" s="169"/>
+      <c r="O6" s="168"/>
+      <c r="P6" s="168"/>
+      <c r="Q6" s="168"/>
       <c r="R6" s="90"/>
       <c r="S6" s="90"/>
       <c r="T6" s="90"/>
-      <c r="U6" s="169"/>
-      <c r="V6" s="169"/>
-      <c r="W6" s="169"/>
-      <c r="X6" s="189">
+      <c r="U6" s="168"/>
+      <c r="V6" s="168"/>
+      <c r="W6" s="168"/>
+      <c r="X6" s="188">
         <v>2973.75</v>
       </c>
-      <c r="Y6" s="190">
+      <c r="Y6" s="189">
         <v>1619.5499999999997</v>
       </c>
       <c r="AA6" s="32"/>
-      <c r="AF6" s="174">
+      <c r="AF6" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B7" s="172" t="s">
-        <v>459</v>
-      </c>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
+      <c r="B7" s="171" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="168"/>
+      <c r="D7" s="168"/>
+      <c r="E7" s="168"/>
       <c r="F7" s="90"/>
       <c r="G7" s="90"/>
       <c r="H7" s="90"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
+      <c r="I7" s="168"/>
+      <c r="J7" s="168"/>
+      <c r="K7" s="168"/>
       <c r="L7" s="90"/>
       <c r="M7" s="90"/>
       <c r="N7" s="90"/>
-      <c r="O7" s="169">
+      <c r="O7" s="168">
         <v>2663</v>
       </c>
-      <c r="P7" s="169">
+      <c r="P7" s="168">
         <v>2561</v>
       </c>
-      <c r="Q7" s="169">
+      <c r="Q7" s="168">
         <v>2690</v>
       </c>
       <c r="R7" s="90">
@@ -31814,255 +31845,255 @@
       <c r="T7" s="90">
         <v>2401</v>
       </c>
-      <c r="U7" s="169">
+      <c r="U7" s="168">
         <v>2506</v>
       </c>
-      <c r="V7" s="169">
+      <c r="V7" s="168">
         <v>2459</v>
       </c>
-      <c r="W7" s="169">
+      <c r="W7" s="168">
         <v>2431</v>
       </c>
-      <c r="X7" s="189">
+      <c r="X7" s="188">
         <v>711.50000000000011</v>
       </c>
-      <c r="Y7" s="190">
+      <c r="Y7" s="189">
         <v>751.1500000000002</v>
       </c>
       <c r="AA7" s="32"/>
-      <c r="AF7" s="174">
+      <c r="AF7" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B8" s="172" t="s">
-        <v>445</v>
-      </c>
-      <c r="C8" s="169">
+      <c r="B8" s="171" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="168">
         <v>659</v>
       </c>
-      <c r="D8" s="169">
+      <c r="D8" s="168">
         <v>1254</v>
       </c>
-      <c r="E8" s="169">
+      <c r="E8" s="168">
         <v>770</v>
       </c>
       <c r="F8" s="90"/>
       <c r="G8" s="90"/>
       <c r="H8" s="90"/>
-      <c r="I8" s="169"/>
-      <c r="J8" s="169">
+      <c r="I8" s="168"/>
+      <c r="J8" s="168">
         <v>1235</v>
       </c>
-      <c r="K8" s="169"/>
+      <c r="K8" s="168"/>
       <c r="L8" s="90"/>
       <c r="M8" s="90"/>
       <c r="N8" s="90"/>
-      <c r="O8" s="169"/>
-      <c r="P8" s="169"/>
-      <c r="Q8" s="169"/>
+      <c r="O8" s="168"/>
+      <c r="P8" s="168"/>
+      <c r="Q8" s="168"/>
       <c r="R8" s="90"/>
       <c r="S8" s="90"/>
       <c r="T8" s="90"/>
-      <c r="U8" s="169"/>
-      <c r="V8" s="169"/>
-      <c r="W8" s="169"/>
+      <c r="U8" s="168"/>
+      <c r="V8" s="168"/>
+      <c r="W8" s="168"/>
       <c r="X8" s="90"/>
-      <c r="Y8" s="169"/>
+      <c r="Y8" s="168"/>
       <c r="AA8" s="32"/>
-      <c r="AF8" s="174">
+      <c r="AF8" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B9" s="172" t="s">
-        <v>460</v>
-      </c>
-      <c r="C9" s="169"/>
-      <c r="D9" s="169"/>
-      <c r="E9" s="169"/>
+      <c r="B9" s="171" t="s">
+        <v>459</v>
+      </c>
+      <c r="C9" s="168"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="168"/>
       <c r="F9" s="90"/>
       <c r="G9" s="90">
         <v>1165</v>
       </c>
       <c r="H9" s="90"/>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="168"/>
+      <c r="J9" s="168"/>
+      <c r="K9" s="168"/>
       <c r="L9" s="90"/>
       <c r="M9" s="90">
         <v>1868</v>
       </c>
       <c r="N9" s="90"/>
-      <c r="O9" s="169"/>
-      <c r="P9" s="169"/>
-      <c r="Q9" s="169"/>
+      <c r="O9" s="168"/>
+      <c r="P9" s="168"/>
+      <c r="Q9" s="168"/>
       <c r="R9" s="90"/>
       <c r="S9" s="90"/>
       <c r="T9" s="90"/>
-      <c r="U9" s="169"/>
-      <c r="V9" s="169"/>
-      <c r="W9" s="169"/>
+      <c r="U9" s="168"/>
+      <c r="V9" s="168"/>
+      <c r="W9" s="168"/>
       <c r="X9" s="90"/>
-      <c r="Y9" s="169"/>
+      <c r="Y9" s="168"/>
       <c r="AA9" s="32"/>
-      <c r="AF9" s="174">
+      <c r="AF9" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B10" s="172" t="s">
-        <v>461</v>
-      </c>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="169"/>
+      <c r="B10" s="171" t="s">
+        <v>460</v>
+      </c>
+      <c r="C10" s="168"/>
+      <c r="D10" s="168"/>
+      <c r="E10" s="168"/>
       <c r="F10" s="90"/>
       <c r="G10" s="90">
         <v>272</v>
       </c>
       <c r="H10" s="90"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
+      <c r="I10" s="168"/>
+      <c r="J10" s="168"/>
+      <c r="K10" s="168"/>
       <c r="L10" s="90"/>
       <c r="M10" s="90">
         <v>436</v>
       </c>
       <c r="N10" s="90"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="169"/>
-      <c r="Q10" s="169"/>
+      <c r="O10" s="168"/>
+      <c r="P10" s="168"/>
+      <c r="Q10" s="168"/>
       <c r="R10" s="90"/>
       <c r="S10" s="90"/>
       <c r="T10" s="90"/>
-      <c r="U10" s="169"/>
-      <c r="V10" s="169"/>
-      <c r="W10" s="169"/>
+      <c r="U10" s="168"/>
+      <c r="V10" s="168"/>
+      <c r="W10" s="168"/>
       <c r="X10" s="90"/>
-      <c r="Y10" s="190">
+      <c r="Y10" s="189">
         <v>1250.5</v>
       </c>
       <c r="AA10" s="32"/>
-      <c r="AF10" s="174">
+      <c r="AF10" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B11" s="172" t="s">
-        <v>446</v>
-      </c>
-      <c r="C11" s="169">
+      <c r="B11" s="171" t="s">
+        <v>445</v>
+      </c>
+      <c r="C11" s="168">
         <v>977</v>
       </c>
-      <c r="D11" s="169"/>
-      <c r="E11" s="169">
+      <c r="D11" s="168"/>
+      <c r="E11" s="168">
         <v>970</v>
       </c>
       <c r="F11" s="90"/>
       <c r="G11" s="90"/>
       <c r="H11" s="90"/>
-      <c r="I11" s="169">
+      <c r="I11" s="168">
         <v>1536</v>
       </c>
-      <c r="J11" s="169"/>
-      <c r="K11" s="169">
+      <c r="J11" s="168"/>
+      <c r="K11" s="168">
         <v>1614</v>
       </c>
       <c r="L11" s="90"/>
       <c r="M11" s="90"/>
       <c r="N11" s="90"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="169"/>
-      <c r="Q11" s="169"/>
+      <c r="O11" s="168"/>
+      <c r="P11" s="168"/>
+      <c r="Q11" s="168"/>
       <c r="R11" s="90"/>
       <c r="S11" s="90"/>
       <c r="T11" s="90"/>
-      <c r="U11" s="169"/>
-      <c r="V11" s="169"/>
-      <c r="W11" s="169"/>
+      <c r="U11" s="168"/>
+      <c r="V11" s="168"/>
+      <c r="W11" s="168"/>
       <c r="X11" s="90"/>
-      <c r="Y11" s="169"/>
+      <c r="Y11" s="168"/>
       <c r="AA11" s="32"/>
-      <c r="AF11" s="174">
+      <c r="AF11" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B12" s="172" t="s">
-        <v>447</v>
-      </c>
-      <c r="C12" s="169"/>
-      <c r="D12" s="169">
+      <c r="B12" s="171" t="s">
+        <v>446</v>
+      </c>
+      <c r="C12" s="168"/>
+      <c r="D12" s="168">
         <v>299</v>
       </c>
-      <c r="E12" s="169"/>
+      <c r="E12" s="168"/>
       <c r="F12" s="90"/>
       <c r="G12" s="90"/>
       <c r="H12" s="90"/>
-      <c r="I12" s="169"/>
-      <c r="J12" s="169">
+      <c r="I12" s="168"/>
+      <c r="J12" s="168">
         <v>139</v>
       </c>
-      <c r="K12" s="169"/>
+      <c r="K12" s="168"/>
       <c r="L12" s="90"/>
       <c r="M12" s="90"/>
       <c r="N12" s="90"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="169"/>
+      <c r="O12" s="168"/>
+      <c r="P12" s="168"/>
+      <c r="Q12" s="168"/>
       <c r="R12" s="90"/>
       <c r="S12" s="90"/>
       <c r="T12" s="90"/>
-      <c r="U12" s="169"/>
-      <c r="V12" s="169"/>
-      <c r="W12" s="169"/>
-      <c r="X12" s="189">
+      <c r="U12" s="168"/>
+      <c r="V12" s="168"/>
+      <c r="W12" s="168"/>
+      <c r="X12" s="188">
         <v>207.4</v>
       </c>
-      <c r="Y12" s="190">
+      <c r="Y12" s="189">
         <v>207.4</v>
       </c>
       <c r="AA12" s="32"/>
-      <c r="AF12" s="174">
+      <c r="AF12" s="173">
         <v>0.85</v>
       </c>
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B13" s="172" t="s">
-        <v>448</v>
-      </c>
-      <c r="C13" s="169">
+      <c r="B13" s="171" t="s">
+        <v>447</v>
+      </c>
+      <c r="C13" s="168">
         <v>1953</v>
       </c>
-      <c r="D13" s="169">
+      <c r="D13" s="168">
         <v>2053</v>
       </c>
-      <c r="E13" s="169">
+      <c r="E13" s="168">
         <v>1806</v>
       </c>
       <c r="F13" s="90"/>
       <c r="G13" s="90"/>
       <c r="H13" s="90"/>
-      <c r="I13" s="169">
+      <c r="I13" s="168">
         <v>1313</v>
       </c>
-      <c r="J13" s="169">
+      <c r="J13" s="168">
         <v>1390</v>
       </c>
-      <c r="K13" s="169">
+      <c r="K13" s="168">
         <v>1235</v>
       </c>
       <c r="L13" s="90"/>
       <c r="M13" s="90"/>
       <c r="N13" s="90"/>
-      <c r="O13" s="169">
+      <c r="O13" s="168">
         <v>1548</v>
       </c>
-      <c r="P13" s="169">
+      <c r="P13" s="168">
         <v>1662</v>
       </c>
-      <c r="Q13" s="169">
+      <c r="Q13" s="168">
         <v>1548</v>
       </c>
       <c r="R13" s="90">
@@ -32074,57 +32105,57 @@
       <c r="T13" s="90">
         <v>951</v>
       </c>
-      <c r="U13" s="169">
+      <c r="U13" s="168">
         <v>926</v>
       </c>
-      <c r="V13" s="169">
+      <c r="V13" s="168">
         <v>978</v>
       </c>
-      <c r="W13" s="169">
+      <c r="W13" s="168">
         <v>924</v>
       </c>
       <c r="X13" s="90"/>
-      <c r="Y13" s="169"/>
+      <c r="Y13" s="168"/>
       <c r="AA13" s="32"/>
-      <c r="AF13" s="174">
+      <c r="AF13" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B14" s="172" t="s">
-        <v>449</v>
-      </c>
-      <c r="C14" s="169">
+      <c r="B14" s="171" t="s">
+        <v>448</v>
+      </c>
+      <c r="C14" s="168">
         <v>345</v>
       </c>
-      <c r="D14" s="169">
+      <c r="D14" s="168">
         <v>362</v>
       </c>
-      <c r="E14" s="169">
+      <c r="E14" s="168">
         <v>319</v>
       </c>
       <c r="F14" s="90"/>
       <c r="G14" s="90"/>
       <c r="H14" s="90"/>
-      <c r="I14" s="169">
+      <c r="I14" s="168">
         <v>232</v>
       </c>
-      <c r="J14" s="169">
+      <c r="J14" s="168">
         <v>245</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="168">
         <v>218</v>
       </c>
       <c r="L14" s="90"/>
       <c r="M14" s="90"/>
       <c r="N14" s="90"/>
-      <c r="O14" s="169">
+      <c r="O14" s="168">
         <v>273</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="168">
         <v>293</v>
       </c>
-      <c r="Q14" s="169">
+      <c r="Q14" s="168">
         <v>273</v>
       </c>
       <c r="R14" s="90">
@@ -32136,33 +32167,33 @@
       <c r="T14" s="90">
         <v>168</v>
       </c>
-      <c r="U14" s="169">
+      <c r="U14" s="168">
         <v>163</v>
       </c>
-      <c r="V14" s="169">
+      <c r="V14" s="168">
         <v>173</v>
       </c>
-      <c r="W14" s="169">
+      <c r="W14" s="168">
         <v>163</v>
       </c>
       <c r="X14" s="90">
         <v>782.99999999999989</v>
       </c>
-      <c r="Y14" s="169">
+      <c r="Y14" s="168">
         <v>782.99999999999989</v>
       </c>
       <c r="AA14" s="32"/>
-      <c r="AF14" s="174">
+      <c r="AF14" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B15" s="172" t="s">
-        <v>462</v>
-      </c>
-      <c r="C15" s="169"/>
-      <c r="D15" s="169"/>
-      <c r="E15" s="169"/>
+      <c r="B15" s="171" t="s">
+        <v>461</v>
+      </c>
+      <c r="C15" s="168"/>
+      <c r="D15" s="168"/>
+      <c r="E15" s="168"/>
       <c r="F15" s="90">
         <v>861</v>
       </c>
@@ -32170,9 +32201,9 @@
         <v>654</v>
       </c>
       <c r="H15" s="90"/>
-      <c r="I15" s="169"/>
-      <c r="J15" s="169"/>
-      <c r="K15" s="169"/>
+      <c r="I15" s="168"/>
+      <c r="J15" s="168"/>
+      <c r="K15" s="168"/>
       <c r="L15" s="90">
         <v>1084</v>
       </c>
@@ -32180,37 +32211,37 @@
         <v>1014</v>
       </c>
       <c r="N15" s="90"/>
-      <c r="O15" s="169">
+      <c r="O15" s="168">
         <v>188</v>
       </c>
-      <c r="P15" s="169">
+      <c r="P15" s="168">
         <v>184</v>
       </c>
-      <c r="Q15" s="169"/>
+      <c r="Q15" s="168"/>
       <c r="R15" s="90"/>
       <c r="S15" s="90"/>
       <c r="T15" s="90"/>
-      <c r="U15" s="169"/>
-      <c r="V15" s="169"/>
-      <c r="W15" s="169"/>
-      <c r="X15" s="189">
+      <c r="U15" s="168"/>
+      <c r="V15" s="168"/>
+      <c r="W15" s="168"/>
+      <c r="X15" s="188">
         <v>1897.2525000000001</v>
       </c>
-      <c r="Y15" s="190">
+      <c r="Y15" s="189">
         <v>1318.7895000000003</v>
       </c>
       <c r="AA15" s="32"/>
-      <c r="AF15" s="174">
+      <c r="AF15" s="173">
         <v>0.87</v>
       </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B16" s="172" t="s">
-        <v>463</v>
-      </c>
-      <c r="C16" s="169"/>
-      <c r="D16" s="169"/>
-      <c r="E16" s="169"/>
+      <c r="B16" s="171" t="s">
+        <v>462</v>
+      </c>
+      <c r="C16" s="168"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
       <c r="F16" s="90">
         <v>68</v>
       </c>
@@ -32218,9 +32249,9 @@
         <v>78</v>
       </c>
       <c r="H16" s="90"/>
-      <c r="I16" s="169"/>
-      <c r="J16" s="169"/>
-      <c r="K16" s="169"/>
+      <c r="I16" s="168"/>
+      <c r="J16" s="168"/>
+      <c r="K16" s="168"/>
       <c r="L16" s="90">
         <v>124</v>
       </c>
@@ -32228,41 +32259,41 @@
         <v>32</v>
       </c>
       <c r="N16" s="90"/>
-      <c r="O16" s="169">
+      <c r="O16" s="168">
         <v>4</v>
       </c>
-      <c r="P16" s="169">
+      <c r="P16" s="168">
         <v>3</v>
       </c>
-      <c r="Q16" s="169"/>
+      <c r="Q16" s="168"/>
       <c r="R16" s="90"/>
       <c r="S16" s="90"/>
       <c r="T16" s="90"/>
-      <c r="U16" s="169"/>
-      <c r="V16" s="169"/>
-      <c r="W16" s="169"/>
+      <c r="U16" s="168"/>
+      <c r="V16" s="168"/>
+      <c r="W16" s="168"/>
       <c r="X16" s="90"/>
-      <c r="Y16" s="169"/>
+      <c r="Y16" s="168"/>
       <c r="AA16" s="32"/>
-      <c r="AF16" s="174">
+      <c r="AF16" s="173">
         <v>0.87</v>
       </c>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B17" s="172" t="s">
-        <v>464</v>
-      </c>
-      <c r="C17" s="169"/>
-      <c r="D17" s="169"/>
-      <c r="E17" s="169"/>
+      <c r="B17" s="171" t="s">
+        <v>463</v>
+      </c>
+      <c r="C17" s="168"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
       <c r="F17" s="90"/>
       <c r="G17" s="90"/>
       <c r="H17" s="90">
         <v>991</v>
       </c>
-      <c r="I17" s="169"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="169"/>
+      <c r="I17" s="168"/>
+      <c r="J17" s="168"/>
+      <c r="K17" s="168"/>
       <c r="L17" s="90">
         <v>80</v>
       </c>
@@ -32272,43 +32303,43 @@
       <c r="N17" s="90">
         <v>1279</v>
       </c>
-      <c r="O17" s="169">
+      <c r="O17" s="168">
         <v>119</v>
       </c>
-      <c r="P17" s="169">
+      <c r="P17" s="168">
         <v>119</v>
       </c>
-      <c r="Q17" s="169">
+      <c r="Q17" s="168">
         <v>294</v>
       </c>
       <c r="R17" s="90"/>
       <c r="S17" s="90"/>
       <c r="T17" s="90"/>
-      <c r="U17" s="169"/>
-      <c r="V17" s="169"/>
-      <c r="W17" s="169"/>
+      <c r="U17" s="168"/>
+      <c r="V17" s="168"/>
+      <c r="W17" s="168"/>
       <c r="X17" s="90">
         <v>1120</v>
       </c>
-      <c r="Y17" s="169">
+      <c r="Y17" s="168">
         <v>1762</v>
       </c>
       <c r="AA17" s="32"/>
-      <c r="AF17" s="174">
+      <c r="AF17" s="173">
         <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B18" s="172" t="s">
-        <v>450</v>
-      </c>
-      <c r="C18" s="169">
+      <c r="B18" s="171" t="s">
+        <v>449</v>
+      </c>
+      <c r="C18" s="168">
         <v>34</v>
       </c>
-      <c r="D18" s="169">
+      <c r="D18" s="168">
         <v>34</v>
       </c>
-      <c r="E18" s="169">
+      <c r="E18" s="168">
         <v>34</v>
       </c>
       <c r="F18" s="90">
@@ -32320,13 +32351,13 @@
       <c r="H18" s="90">
         <v>14</v>
       </c>
-      <c r="I18" s="169">
+      <c r="I18" s="168">
         <v>33</v>
       </c>
-      <c r="J18" s="169">
+      <c r="J18" s="168">
         <v>33</v>
       </c>
-      <c r="K18" s="169">
+      <c r="K18" s="168">
         <v>33</v>
       </c>
       <c r="L18" s="90">
@@ -32338,13 +32369,13 @@
       <c r="N18" s="90">
         <v>21</v>
       </c>
-      <c r="O18" s="169">
+      <c r="O18" s="168">
         <v>35</v>
       </c>
-      <c r="P18" s="169">
+      <c r="P18" s="168">
         <v>35</v>
       </c>
-      <c r="Q18" s="169">
+      <c r="Q18" s="168">
         <v>35</v>
       </c>
       <c r="R18" s="90">
@@ -32356,1003 +32387,1003 @@
       <c r="T18" s="90">
         <v>24</v>
       </c>
-      <c r="U18" s="169">
+      <c r="U18" s="168">
         <v>26</v>
       </c>
-      <c r="V18" s="169">
+      <c r="V18" s="168">
         <v>26</v>
       </c>
-      <c r="W18" s="169">
+      <c r="W18" s="168">
         <v>26</v>
       </c>
       <c r="X18" s="90"/>
-      <c r="Y18" s="169"/>
+      <c r="Y18" s="168"/>
       <c r="AA18" s="32"/>
-      <c r="AF18" s="174">
+      <c r="AF18" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B19" s="172" t="s">
+      <c r="B19" s="171" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="171">
+      <c r="C19" s="170">
         <f t="shared" ref="C19:K19" si="0">SUM(C6:C18)</f>
         <v>3968</v>
       </c>
-      <c r="D19" s="171">
+      <c r="D19" s="170">
         <f t="shared" si="0"/>
         <v>4002</v>
       </c>
-      <c r="E19" s="171">
+      <c r="E19" s="170">
         <f t="shared" si="0"/>
         <v>3899</v>
       </c>
-      <c r="F19" s="170">
+      <c r="F19" s="169">
         <f t="shared" si="0"/>
         <v>2170</v>
       </c>
-      <c r="G19" s="170">
+      <c r="G19" s="169">
         <f t="shared" si="0"/>
         <v>2181</v>
       </c>
-      <c r="H19" s="170">
+      <c r="H19" s="169">
         <f t="shared" si="0"/>
         <v>2334</v>
       </c>
-      <c r="I19" s="171">
+      <c r="I19" s="170">
         <f t="shared" si="0"/>
         <v>3114</v>
       </c>
-      <c r="J19" s="171">
+      <c r="J19" s="170">
         <f t="shared" si="0"/>
         <v>3042</v>
       </c>
-      <c r="K19" s="171">
+      <c r="K19" s="170">
         <f t="shared" si="0"/>
         <v>3100</v>
       </c>
-      <c r="L19" s="170">
+      <c r="L19" s="169">
         <f t="shared" ref="L19:Y19" si="1">SUM(L6:L18)</f>
         <v>3429</v>
       </c>
-      <c r="M19" s="170">
+      <c r="M19" s="169">
         <f t="shared" si="1"/>
         <v>3451</v>
       </c>
-      <c r="N19" s="170">
+      <c r="N19" s="169">
         <f t="shared" si="1"/>
         <v>3430</v>
       </c>
-      <c r="O19" s="171">
+      <c r="O19" s="170">
         <f t="shared" si="1"/>
         <v>4830</v>
       </c>
-      <c r="P19" s="171">
+      <c r="P19" s="170">
         <f t="shared" si="1"/>
         <v>4857</v>
       </c>
-      <c r="Q19" s="171">
+      <c r="Q19" s="170">
         <f t="shared" si="1"/>
         <v>4840</v>
       </c>
-      <c r="R19" s="170">
+      <c r="R19" s="169">
         <f t="shared" si="1"/>
         <v>3691</v>
       </c>
-      <c r="S19" s="170">
+      <c r="S19" s="169">
         <f t="shared" si="1"/>
         <v>3699</v>
       </c>
-      <c r="T19" s="170">
+      <c r="T19" s="169">
         <f t="shared" si="1"/>
         <v>3544</v>
       </c>
-      <c r="U19" s="171">
+      <c r="U19" s="170">
         <f t="shared" si="1"/>
         <v>3621</v>
       </c>
-      <c r="V19" s="171">
+      <c r="V19" s="170">
         <f t="shared" si="1"/>
         <v>3636</v>
       </c>
-      <c r="W19" s="171">
+      <c r="W19" s="170">
         <f t="shared" si="1"/>
         <v>3544</v>
       </c>
-      <c r="X19" s="170">
+      <c r="X19" s="169">
         <f t="shared" si="1"/>
         <v>7692.9025000000001</v>
       </c>
-      <c r="Y19" s="171">
+      <c r="Y19" s="170">
         <f t="shared" si="1"/>
         <v>7692.3894999999993</v>
       </c>
-      <c r="AA19" s="193"/>
+      <c r="AA19" s="192"/>
     </row>
     <row r="21" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B21" s="172" t="s">
-        <v>468</v>
-      </c>
-      <c r="C21" s="185">
+      <c r="B21" s="171" t="s">
+        <v>467</v>
+      </c>
+      <c r="C21" s="184">
         <v>103131</v>
       </c>
-      <c r="D21" s="185">
+      <c r="D21" s="184">
         <v>40386</v>
       </c>
-      <c r="E21" s="185">
+      <c r="E21" s="184">
         <v>21929</v>
       </c>
-      <c r="F21" s="166"/>
-      <c r="G21" s="166"/>
-      <c r="H21" s="166"/>
-      <c r="I21" s="166"/>
-      <c r="J21" s="166"/>
-      <c r="K21" s="166"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="166"/>
-      <c r="N21" s="166"/>
-      <c r="O21" s="166"/>
-      <c r="P21" s="166"/>
-      <c r="Q21" s="166"/>
-      <c r="R21" s="166"/>
-      <c r="S21" s="166"/>
-      <c r="T21" s="166"/>
-      <c r="U21" s="166"/>
-      <c r="V21" s="166"/>
-      <c r="W21" s="166"/>
-      <c r="X21" s="166"/>
-      <c r="Y21" s="166"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
+      <c r="H21" s="165"/>
+      <c r="I21" s="165"/>
+      <c r="J21" s="165"/>
+      <c r="K21" s="165"/>
+      <c r="L21" s="165"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="165"/>
+      <c r="O21" s="165"/>
+      <c r="P21" s="165"/>
+      <c r="Q21" s="165"/>
+      <c r="R21" s="165"/>
+      <c r="S21" s="165"/>
+      <c r="T21" s="165"/>
+      <c r="U21" s="165"/>
+      <c r="V21" s="165"/>
+      <c r="W21" s="165"/>
+      <c r="X21" s="165"/>
+      <c r="Y21" s="165"/>
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B22" s="172" t="s">
-        <v>467</v>
-      </c>
-      <c r="C22" s="185">
+      <c r="B22" s="171" t="s">
+        <v>466</v>
+      </c>
+      <c r="C22" s="184">
         <v>87632</v>
       </c>
-      <c r="D22" s="185">
+      <c r="D22" s="184">
         <v>21961</v>
       </c>
-      <c r="E22" s="185">
+      <c r="E22" s="184">
         <v>15238</v>
       </c>
-      <c r="F22" s="166"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="166"/>
-      <c r="J22" s="166"/>
-      <c r="K22" s="166"/>
-      <c r="L22" s="166"/>
-      <c r="M22" s="166"/>
-      <c r="N22" s="166"/>
-      <c r="O22" s="166"/>
-      <c r="P22" s="166"/>
-      <c r="Q22" s="166"/>
-      <c r="R22" s="166"/>
-      <c r="S22" s="166"/>
-      <c r="T22" s="166"/>
-      <c r="U22" s="166"/>
-      <c r="V22" s="166"/>
-      <c r="W22" s="166"/>
-      <c r="X22" s="166"/>
-      <c r="Y22" s="166"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="165"/>
+      <c r="H22" s="165"/>
+      <c r="I22" s="165"/>
+      <c r="J22" s="165"/>
+      <c r="K22" s="165"/>
+      <c r="L22" s="165"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="165"/>
+      <c r="O22" s="165"/>
+      <c r="P22" s="165"/>
+      <c r="Q22" s="165"/>
+      <c r="R22" s="165"/>
+      <c r="S22" s="165"/>
+      <c r="T22" s="165"/>
+      <c r="U22" s="165"/>
+      <c r="V22" s="165"/>
+      <c r="W22" s="165"/>
+      <c r="X22" s="165"/>
+      <c r="Y22" s="165"/>
     </row>
     <row r="24" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B24" s="179" t="s">
-        <v>519</v>
+      <c r="B24" s="178" t="s">
+        <v>518</v>
       </c>
       <c r="C24" s="83" t="s">
-        <v>525</v>
-      </c>
-      <c r="D24" s="172"/>
-      <c r="E24" s="172"/>
-      <c r="F24" s="172"/>
-      <c r="G24" s="172"/>
-      <c r="H24" s="172"/>
-      <c r="I24" s="172"/>
-      <c r="M24" s="179" t="s">
-        <v>519</v>
+        <v>524</v>
+      </c>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
+      <c r="H24" s="171"/>
+      <c r="I24" s="171"/>
+      <c r="M24" s="178" t="s">
+        <v>518</v>
       </c>
       <c r="N24" s="83"/>
       <c r="O24" s="83"/>
       <c r="P24" s="83" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q24" s="172"/>
-      <c r="R24" s="172"/>
-      <c r="S24" s="172"/>
-      <c r="T24" s="172"/>
-      <c r="U24" s="172"/>
+        <v>523</v>
+      </c>
+      <c r="Q24" s="171"/>
+      <c r="R24" s="171"/>
+      <c r="S24" s="171"/>
+      <c r="T24" s="171"/>
+      <c r="U24" s="171"/>
     </row>
     <row r="25" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B25" s="179" t="s">
-        <v>492</v>
-      </c>
-      <c r="C25" s="169"/>
-      <c r="D25" s="169" t="s">
+      <c r="B25" s="178" t="s">
         <v>491</v>
+      </c>
+      <c r="C25" s="168"/>
+      <c r="D25" s="168" t="s">
+        <v>490</v>
       </c>
       <c r="E25" s="101"/>
       <c r="F25" s="101" t="s">
+        <v>490</v>
+      </c>
+      <c r="G25" s="168"/>
+      <c r="H25" s="168" t="s">
+        <v>489</v>
+      </c>
+      <c r="I25" s="101" t="s">
+        <v>487</v>
+      </c>
+      <c r="M25" s="178" t="s">
         <v>491</v>
       </c>
-      <c r="G25" s="169"/>
-      <c r="H25" s="169" t="s">
-        <v>490</v>
-      </c>
-      <c r="I25" s="101" t="s">
-        <v>488</v>
-      </c>
-      <c r="M25" s="179" t="s">
-        <v>492</v>
-      </c>
-      <c r="N25" s="172"/>
-      <c r="O25" s="172"/>
-      <c r="P25" s="169" t="s">
+      <c r="N25" s="171"/>
+      <c r="O25" s="171"/>
+      <c r="P25" s="168" t="s">
         <v>303</v>
       </c>
-      <c r="Q25" s="169" t="s">
-        <v>490</v>
+      <c r="Q25" s="168" t="s">
+        <v>489</v>
       </c>
       <c r="R25" s="101" t="s">
         <v>304</v>
       </c>
       <c r="S25" s="101" t="s">
-        <v>490</v>
-      </c>
-      <c r="T25" s="169" t="s">
+        <v>489</v>
+      </c>
+      <c r="T25" s="168" t="s">
         <v>316</v>
       </c>
-      <c r="U25" s="169" t="s">
-        <v>526</v>
+      <c r="U25" s="168" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="26" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B26" s="83" t="s">
-        <v>473</v>
-      </c>
-      <c r="C26" s="169" t="s">
+        <v>472</v>
+      </c>
+      <c r="C26" s="168" t="s">
         <v>303</v>
       </c>
-      <c r="D26" s="169" t="s">
-        <v>490</v>
+      <c r="D26" s="168" t="s">
+        <v>489</v>
       </c>
       <c r="E26" s="101" t="s">
         <v>304</v>
       </c>
       <c r="F26" s="101" t="s">
+        <v>489</v>
+      </c>
+      <c r="G26" s="168" t="s">
+        <v>316</v>
+      </c>
+      <c r="H26" s="168" t="s">
+        <v>525</v>
+      </c>
+      <c r="I26" s="101" t="s">
+        <v>488</v>
+      </c>
+      <c r="K26" s="172" t="s">
         <v>490</v>
       </c>
-      <c r="G26" s="169" t="s">
-        <v>316</v>
-      </c>
-      <c r="H26" s="169" t="s">
-        <v>526</v>
-      </c>
-      <c r="I26" s="101" t="s">
-        <v>489</v>
-      </c>
-      <c r="K26" s="173" t="s">
-        <v>491</v>
-      </c>
-      <c r="M26" s="172" t="s">
-        <v>518</v>
-      </c>
-      <c r="N26" s="172"/>
-      <c r="O26" s="172"/>
+      <c r="M26" s="171" t="s">
+        <v>517</v>
+      </c>
+      <c r="N26" s="171"/>
+      <c r="O26" s="171"/>
       <c r="P26" s="92">
         <f>T26*U26</f>
         <v>77812.622155690478</v>
       </c>
-      <c r="Q26" s="175">
+      <c r="Q26" s="174">
         <f>P26/SUM(P$26:P$29)</f>
         <v>0.23414263671133728</v>
       </c>
-      <c r="R26" s="176">
+      <c r="R26" s="175">
         <f>T26-P26</f>
         <v>47594.13899404119</v>
       </c>
-      <c r="S26" s="177">
+      <c r="S26" s="176">
         <f>R26/SUM(R$26:R$29)</f>
         <v>0.23414263671133731</v>
       </c>
       <c r="T26" s="92">
         <v>125406.76114973167</v>
       </c>
-      <c r="U26" s="186">
+      <c r="U26" s="185">
         <v>0.62048187388225973</v>
       </c>
     </row>
     <row r="27" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B27" s="172" t="s">
-        <v>474</v>
+      <c r="B27" s="171" t="s">
+        <v>473</v>
       </c>
       <c r="C27" s="92">
         <f>G27*H27</f>
         <v>8000.2142902474725</v>
       </c>
-      <c r="D27" s="175">
+      <c r="D27" s="174">
         <f>C27*$K27/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
         <v>1.0616664694902623E-2</v>
       </c>
-      <c r="E27" s="176">
+      <c r="E27" s="175">
         <f>G27-C27</f>
         <v>631.319043085864</v>
       </c>
-      <c r="F27" s="177">
+      <c r="F27" s="176">
         <f>E27*$K27/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
         <v>4.6660442363229675E-3</v>
       </c>
       <c r="G27" s="92">
         <v>8631.5333333333365</v>
       </c>
-      <c r="H27" s="186">
+      <c r="H27" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I27" s="177">
+      <c r="I27" s="176">
         <v>0.27270318402958632</v>
       </c>
-      <c r="K27" s="174">
+      <c r="K27" s="173">
         <v>0.87</v>
       </c>
-      <c r="M27" s="172" t="s">
-        <v>515</v>
-      </c>
-      <c r="N27" s="172"/>
-      <c r="O27" s="172"/>
+      <c r="M27" s="171" t="s">
+        <v>514</v>
+      </c>
+      <c r="N27" s="171"/>
+      <c r="O27" s="171"/>
       <c r="P27" s="92">
         <f t="shared" ref="P27:P29" si="2">T27*U27</f>
         <v>61792.549779753324</v>
       </c>
-      <c r="Q27" s="175">
+      <c r="Q27" s="174">
         <f>P27/SUM(P$26:P$29)</f>
         <v>0.18593732139754057</v>
       </c>
-      <c r="R27" s="176">
+      <c r="R27" s="175">
         <f t="shared" ref="R27:R29" si="3">T27-P27</f>
         <v>37795.451708713757</v>
       </c>
-      <c r="S27" s="177">
+      <c r="S27" s="176">
         <f>R27/SUM(R$26:R$29)</f>
         <v>0.18593732139754063</v>
       </c>
       <c r="T27" s="92">
         <v>99588.001488467082</v>
       </c>
-      <c r="U27" s="186">
+      <c r="U27" s="185">
         <v>0.62048187388225973</v>
       </c>
     </row>
     <row r="28" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B28" s="172" t="s">
-        <v>518</v>
+      <c r="B28" s="171" t="s">
+        <v>517</v>
       </c>
       <c r="C28" s="92">
         <f t="shared" ref="C28:C33" si="4">G28*H28</f>
         <v>38739.785795838885</v>
       </c>
-      <c r="D28" s="175">
+      <c r="D28" s="174">
         <f t="shared" ref="D28:D33" si="5">C28*K28/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
         <v>5.140953744803383E-2</v>
       </c>
-      <c r="E28" s="176">
+      <c r="E28" s="175">
         <f t="shared" ref="E28:E33" si="6">G28-C28</f>
         <v>23695.214204161115</v>
       </c>
-      <c r="F28" s="177">
+      <c r="F28" s="176">
         <f t="shared" ref="F28:F33" si="7">E28*$K28/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
         <v>0.17513002162161409</v>
       </c>
       <c r="G28" s="92">
         <v>62435</v>
       </c>
-      <c r="H28" s="186">
+      <c r="H28" s="185">
         <v>0.62048187388225973</v>
       </c>
-      <c r="I28" s="177">
+      <c r="I28" s="176">
         <v>0</v>
       </c>
-      <c r="K28" s="174">
+      <c r="K28" s="173">
         <v>0.87</v>
       </c>
-      <c r="M28" s="172" t="s">
-        <v>517</v>
-      </c>
-      <c r="N28" s="172"/>
-      <c r="O28" s="172"/>
+      <c r="M28" s="171" t="s">
+        <v>516</v>
+      </c>
+      <c r="N28" s="171"/>
+      <c r="O28" s="171"/>
       <c r="P28" s="92">
         <f t="shared" si="2"/>
         <v>159717.72580047889</v>
       </c>
-      <c r="Q28" s="175">
+      <c r="Q28" s="174">
         <f>P28/SUM(P$26:P$29)</f>
         <v>0.48059978461640451</v>
       </c>
-      <c r="R28" s="176">
+      <c r="R28" s="175">
         <f t="shared" si="3"/>
         <v>97691.446849722182</v>
       </c>
-      <c r="S28" s="177">
+      <c r="S28" s="176">
         <f>R28/SUM(R$26:R$29)</f>
         <v>0.48059978461640457</v>
       </c>
       <c r="T28" s="92">
         <v>257409.17265020107</v>
       </c>
-      <c r="U28" s="186">
+      <c r="U28" s="185">
         <v>0.62048187388225973</v>
       </c>
     </row>
     <row r="29" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B29" s="172" t="s">
-        <v>515</v>
+      <c r="B29" s="171" t="s">
+        <v>514</v>
       </c>
       <c r="C29" s="92">
         <f t="shared" si="4"/>
         <v>21059.030703189121</v>
       </c>
-      <c r="D29" s="175">
+      <c r="D29" s="174">
         <f t="shared" si="5"/>
         <v>2.7946334893549748E-2</v>
       </c>
-      <c r="E29" s="176">
+      <c r="E29" s="175">
         <f t="shared" si="6"/>
         <v>12880.769296810882</v>
       </c>
-      <c r="F29" s="177">
+      <c r="F29" s="176">
         <f t="shared" si="7"/>
         <v>9.5201055623180236E-2</v>
       </c>
       <c r="G29" s="92">
         <v>33939.800000000003</v>
       </c>
-      <c r="H29" s="186">
+      <c r="H29" s="185">
         <v>0.62048187388225973</v>
       </c>
-      <c r="I29" s="177">
+      <c r="I29" s="176">
         <v>0</v>
       </c>
-      <c r="K29" s="174">
+      <c r="K29" s="173">
         <v>0.87</v>
       </c>
-      <c r="M29" s="172" t="s">
-        <v>516</v>
-      </c>
-      <c r="N29" s="172"/>
-      <c r="O29" s="172"/>
+      <c r="M29" s="171" t="s">
+        <v>515</v>
+      </c>
+      <c r="N29" s="171"/>
+      <c r="O29" s="171"/>
       <c r="P29" s="92">
         <f t="shared" si="2"/>
         <v>33007.100971752872</v>
       </c>
-      <c r="Q29" s="175">
+      <c r="Q29" s="174">
         <f>P29/SUM(P$26:P$29)</f>
         <v>9.9320257274717494E-2</v>
       </c>
-      <c r="R29" s="176">
+      <c r="R29" s="175">
         <f t="shared" si="3"/>
         <v>20188.81394713511</v>
       </c>
-      <c r="S29" s="177">
+      <c r="S29" s="176">
         <f>R29/SUM(R$26:R$29)</f>
         <v>9.9320257274717508E-2</v>
       </c>
       <c r="T29" s="92">
         <v>53195.914918887982</v>
       </c>
-      <c r="U29" s="186">
+      <c r="U29" s="185">
         <v>0.62048187388225973</v>
       </c>
     </row>
     <row r="30" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B30" s="172" t="s">
-        <v>517</v>
+      <c r="B30" s="171" t="s">
+        <v>516</v>
       </c>
       <c r="C30" s="92">
         <f t="shared" si="4"/>
         <v>68413.87639421731</v>
       </c>
-      <c r="D30" s="175">
+      <c r="D30" s="174">
         <f t="shared" si="5"/>
         <v>9.0788466384123717E-2</v>
       </c>
-      <c r="E30" s="176">
+      <c r="E30" s="175">
         <f t="shared" si="6"/>
         <v>41845.390272449687</v>
       </c>
-      <c r="F30" s="177">
+      <c r="F30" s="176">
         <f t="shared" si="7"/>
         <v>0.30927697213608885</v>
       </c>
       <c r="G30" s="92">
         <v>110259.266666667</v>
       </c>
-      <c r="H30" s="186">
+      <c r="H30" s="185">
         <v>0.62048187388225973</v>
       </c>
-      <c r="I30" s="177">
+      <c r="I30" s="176">
         <v>0</v>
       </c>
-      <c r="K30" s="174">
+      <c r="K30" s="173">
         <v>0.87</v>
       </c>
     </row>
     <row r="31" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B31" s="172" t="s">
-        <v>516</v>
+      <c r="B31" s="171" t="s">
+        <v>515</v>
       </c>
       <c r="C31" s="92">
         <f t="shared" si="4"/>
         <v>14138.341343739448</v>
       </c>
-      <c r="D31" s="175">
+      <c r="D31" s="174">
         <f t="shared" si="5"/>
         <v>1.8762251102641098E-2</v>
       </c>
-      <c r="E31" s="176">
+      <c r="E31" s="175">
         <f t="shared" si="6"/>
         <v>8647.7253229272501</v>
       </c>
-      <c r="F31" s="177">
+      <c r="F31" s="176">
         <f t="shared" si="7"/>
         <v>6.3914861023542546E-2</v>
       </c>
       <c r="G31" s="92">
         <v>22786.066666666698</v>
       </c>
-      <c r="H31" s="186">
+      <c r="H31" s="185">
         <v>0.62048187388225973</v>
       </c>
-      <c r="I31" s="177">
+      <c r="I31" s="176">
         <v>0</v>
       </c>
-      <c r="K31" s="174">
+      <c r="K31" s="173">
         <v>0.87</v>
       </c>
     </row>
     <row r="32" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B32" s="172" t="s">
-        <v>520</v>
+      <c r="B32" s="171" t="s">
+        <v>519</v>
       </c>
       <c r="C32" s="92">
         <f t="shared" si="4"/>
         <v>4095.4809354661024</v>
       </c>
-      <c r="D32" s="175">
+      <c r="D32" s="174">
         <f t="shared" si="5"/>
         <v>5.4348979013241839E-3</v>
       </c>
-      <c r="E32" s="176">
+      <c r="E32" s="175">
         <f t="shared" si="6"/>
         <v>323.18573120056726</v>
       </c>
-      <c r="F32" s="177">
+      <c r="F32" s="176">
         <f t="shared" si="7"/>
         <v>2.3886479187435693E-3</v>
       </c>
       <c r="G32" s="92">
         <v>4418.6666666666697</v>
       </c>
-      <c r="H32" s="186">
+      <c r="H32" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I32" s="177">
+      <c r="I32" s="176">
         <v>0</v>
       </c>
-      <c r="K32" s="174">
+      <c r="K32" s="173">
         <v>0.87</v>
       </c>
-      <c r="M32" s="179" t="s">
-        <v>519</v>
+      <c r="M32" s="178" t="s">
+        <v>518</v>
       </c>
       <c r="N32" s="83"/>
       <c r="O32" s="83"/>
       <c r="P32" s="83" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q32" s="172"/>
-      <c r="R32" s="172"/>
-      <c r="S32" s="172"/>
-      <c r="T32" s="172"/>
-      <c r="U32" s="172"/>
+        <v>522</v>
+      </c>
+      <c r="Q32" s="171"/>
+      <c r="R32" s="171"/>
+      <c r="S32" s="171"/>
+      <c r="T32" s="171"/>
+      <c r="U32" s="171"/>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B33" s="172" t="s">
-        <v>521</v>
+      <c r="B33" s="171" t="s">
+        <v>520</v>
       </c>
       <c r="C33" s="92">
         <f t="shared" si="4"/>
         <v>11613.017957647857</v>
       </c>
-      <c r="D33" s="175">
+      <c r="D33" s="174">
         <f t="shared" si="5"/>
         <v>1.5411026914932346E-2</v>
       </c>
-      <c r="E33" s="176">
+      <c r="E33" s="175">
         <f t="shared" si="6"/>
         <v>916.415375685443</v>
       </c>
-      <c r="F33" s="177">
+      <c r="F33" s="176">
         <f t="shared" si="7"/>
         <v>6.7731755102676929E-3</v>
       </c>
       <c r="G33" s="92">
         <v>12529.4333333333</v>
       </c>
-      <c r="H33" s="186">
+      <c r="H33" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I33" s="177">
+      <c r="I33" s="176">
         <v>0</v>
       </c>
-      <c r="K33" s="174">
+      <c r="K33" s="173">
         <v>0.87</v>
       </c>
-      <c r="M33" s="179" t="s">
-        <v>492</v>
-      </c>
-      <c r="N33" s="172"/>
-      <c r="O33" s="172"/>
-      <c r="P33" s="169" t="s">
+      <c r="M33" s="178" t="s">
+        <v>491</v>
+      </c>
+      <c r="N33" s="171"/>
+      <c r="O33" s="171"/>
+      <c r="P33" s="168" t="s">
         <v>303</v>
       </c>
-      <c r="Q33" s="169" t="s">
-        <v>490</v>
+      <c r="Q33" s="168" t="s">
+        <v>489</v>
       </c>
       <c r="R33" s="101" t="s">
         <v>304</v>
       </c>
       <c r="S33" s="101" t="s">
-        <v>490</v>
-      </c>
-      <c r="T33" s="169" t="s">
+        <v>489</v>
+      </c>
+      <c r="T33" s="168" t="s">
         <v>316</v>
       </c>
-      <c r="U33" s="169" t="s">
-        <v>526</v>
+      <c r="U33" s="168" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B34" s="172" t="s">
-        <v>480</v>
+      <c r="B34" s="171" t="s">
+        <v>479</v>
       </c>
       <c r="C34" s="92">
         <f t="shared" ref="C34:C47" si="8">G34*H34</f>
         <v>125972.18626629541</v>
       </c>
-      <c r="D34" s="175">
+      <c r="D34" s="174">
         <f t="shared" ref="D34:D47" si="9">C34*K34/SUMPRODUCT(C$27:C$47,$K$27:$K$47)</f>
         <v>0.1787001199119426</v>
       </c>
-      <c r="E34" s="176">
+      <c r="E34" s="175">
         <f t="shared" ref="E34:E47" si="10">G34-C34</f>
         <v>9940.8137337045919</v>
       </c>
-      <c r="F34" s="177">
+      <c r="F34" s="176">
         <f t="shared" ref="F34:F47" si="11">E34*$K34/SUMPRODUCT(E$27:E$47,$K$27:$K$47)</f>
         <v>7.8539041074329657E-2</v>
       </c>
       <c r="G34" s="92">
         <v>135913</v>
       </c>
-      <c r="H34" s="186">
+      <c r="H34" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I34" s="177">
+      <c r="I34" s="176">
         <v>0.19883912083302038</v>
       </c>
-      <c r="K34" s="174">
+      <c r="K34" s="173">
         <v>0.93</v>
       </c>
-      <c r="M34" s="172" t="s">
-        <v>520</v>
-      </c>
-      <c r="N34" s="172"/>
-      <c r="O34" s="172"/>
+      <c r="M34" s="171" t="s">
+        <v>519</v>
+      </c>
+      <c r="N34" s="171"/>
+      <c r="O34" s="171"/>
       <c r="P34" s="92">
         <f t="shared" ref="P34:P35" si="12">T34*U34</f>
         <v>18331.527857478479</v>
       </c>
-      <c r="Q34" s="175">
+      <c r="Q34" s="174">
         <f>P34/SUM(P$34:P$35)</f>
         <v>0.51302572087399856</v>
       </c>
-      <c r="R34" s="176">
+      <c r="R34" s="175">
         <f t="shared" ref="R34:R35" si="13">T34-P34</f>
         <v>11212.490475854818</v>
       </c>
-      <c r="S34" s="177">
+      <c r="S34" s="176">
         <f>R34/SUM(R$34:R$35)</f>
         <v>0.51302572087399856</v>
       </c>
       <c r="T34" s="92">
         <v>29544.018333333297</v>
       </c>
-      <c r="U34" s="186">
+      <c r="U34" s="185">
         <v>0.62048187388225973</v>
       </c>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B35" s="172" t="s">
-        <v>475</v>
+      <c r="B35" s="171" t="s">
+        <v>474</v>
       </c>
       <c r="C35" s="92">
         <f t="shared" si="8"/>
         <v>36603.206384229525</v>
       </c>
-      <c r="D35" s="175">
+      <c r="D35" s="174">
         <f t="shared" si="9"/>
         <v>5.024916723664883E-2</v>
       </c>
-      <c r="E35" s="176">
+      <c r="E35" s="175">
         <f t="shared" si="10"/>
         <v>2888.4602824371759</v>
       </c>
-      <c r="F35" s="177">
+      <c r="F35" s="176">
         <f t="shared" si="11"/>
         <v>2.2084604148529564E-2</v>
       </c>
       <c r="G35" s="92">
         <v>39491.666666666701</v>
       </c>
-      <c r="H35" s="186">
+      <c r="H35" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I35" s="177">
+      <c r="I35" s="176">
         <v>0</v>
       </c>
-      <c r="K35" s="174">
+      <c r="K35" s="173">
         <v>0.9</v>
       </c>
-      <c r="M35" s="172" t="s">
-        <v>521</v>
-      </c>
-      <c r="N35" s="172"/>
-      <c r="O35" s="172"/>
+      <c r="M35" s="171" t="s">
+        <v>520</v>
+      </c>
+      <c r="N35" s="171"/>
+      <c r="O35" s="171"/>
       <c r="P35" s="92">
         <f t="shared" si="12"/>
         <v>17400.653028596018</v>
       </c>
-      <c r="Q35" s="175">
+      <c r="Q35" s="174">
         <f>P35/SUM(P$34:P$35)</f>
         <v>0.48697427912600155</v>
       </c>
-      <c r="R35" s="176">
+      <c r="R35" s="175">
         <f t="shared" si="13"/>
         <v>10643.120304737324</v>
       </c>
-      <c r="S35" s="177">
+      <c r="S35" s="176">
         <f>R35/SUM(R$34:R$35)</f>
         <v>0.48697427912600144</v>
       </c>
       <c r="T35" s="92">
         <v>28043.773333333342</v>
       </c>
-      <c r="U35" s="186">
+      <c r="U35" s="185">
         <v>0.62048187388225973</v>
       </c>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B36" s="172" t="s">
-        <v>476</v>
+      <c r="B36" s="171" t="s">
+        <v>475</v>
       </c>
       <c r="C36" s="92">
         <f t="shared" si="8"/>
         <v>90204.110729731736</v>
       </c>
-      <c r="D36" s="175">
+      <c r="D36" s="174">
         <f t="shared" si="9"/>
         <v>0.11970514325933213</v>
       </c>
-      <c r="E36" s="176">
+      <c r="E36" s="175">
         <f t="shared" si="10"/>
         <v>7118.2559369349037</v>
       </c>
-      <c r="F36" s="177">
+      <c r="F36" s="176">
         <f t="shared" si="11"/>
         <v>5.2610637127081708E-2</v>
       </c>
       <c r="G36" s="92">
         <v>97322.36666666664</v>
       </c>
-      <c r="H36" s="186">
+      <c r="H36" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I36" s="177">
+      <c r="I36" s="176">
         <v>0</v>
       </c>
-      <c r="K36" s="174">
+      <c r="K36" s="173">
         <v>0.87</v>
       </c>
       <c r="T36" s="32"/>
-      <c r="U36" s="188"/>
+      <c r="U36" s="187"/>
       <c r="V36" s="32"/>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B37" s="172" t="s">
-        <v>477</v>
+      <c r="B37" s="171" t="s">
+        <v>476</v>
       </c>
       <c r="C37" s="92">
         <f t="shared" si="8"/>
         <v>29382.974831585889</v>
       </c>
-      <c r="D37" s="175">
+      <c r="D37" s="174">
         <f t="shared" si="9"/>
         <v>4.0785367897941328E-2</v>
       </c>
-      <c r="E37" s="176">
+      <c r="E37" s="175">
         <f t="shared" si="10"/>
         <v>2318.69183508071</v>
       </c>
-      <c r="F37" s="177">
+      <c r="F37" s="176">
         <f t="shared" si="11"/>
         <v>1.7925246419233029E-2</v>
       </c>
       <c r="G37" s="92">
         <v>31701.666666666599</v>
       </c>
-      <c r="H37" s="186">
+      <c r="H37" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I37" s="177">
+      <c r="I37" s="176">
         <v>1</v>
       </c>
-      <c r="K37" s="174">
+      <c r="K37" s="173">
         <v>0.91</v>
       </c>
       <c r="T37" s="32"/>
-      <c r="U37" s="188"/>
+      <c r="U37" s="187"/>
       <c r="V37" s="32"/>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B38" s="172" t="s">
-        <v>478</v>
+      <c r="B38" s="171" t="s">
+        <v>477</v>
       </c>
       <c r="C38" s="92">
         <f t="shared" si="8"/>
         <v>15543.487097124786</v>
       </c>
-      <c r="D38" s="175">
+      <c r="D38" s="174">
         <f t="shared" si="9"/>
         <v>2.0626946318286005E-2</v>
       </c>
-      <c r="E38" s="176">
+      <c r="E38" s="175">
         <f t="shared" si="10"/>
         <v>1226.5795695418474</v>
       </c>
-      <c r="F38" s="177">
+      <c r="F38" s="176">
         <f t="shared" si="11"/>
         <v>9.0655819645120948E-3</v>
       </c>
       <c r="G38" s="92">
         <v>16770.066666666633</v>
       </c>
-      <c r="H38" s="186">
+      <c r="H38" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I38" s="177">
+      <c r="I38" s="176">
         <v>1</v>
       </c>
-      <c r="K38" s="174">
+      <c r="K38" s="173">
         <v>0.87</v>
       </c>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B39" s="172" t="s">
-        <v>479</v>
+      <c r="B39" s="171" t="s">
+        <v>478</v>
       </c>
       <c r="C39" s="92">
         <f t="shared" si="8"/>
         <v>39489.568868500683</v>
       </c>
-      <c r="D39" s="175">
+      <c r="D39" s="174">
         <f t="shared" si="9"/>
         <v>5.2404535230289213E-2</v>
       </c>
-      <c r="E39" s="176">
+      <c r="E39" s="175">
         <f t="shared" si="10"/>
         <v>3116.2311314993494</v>
       </c>
-      <c r="F39" s="177">
+      <c r="F39" s="176">
         <f t="shared" si="11"/>
         <v>2.3031892462976329E-2</v>
       </c>
       <c r="G39" s="92">
         <v>42605.800000000032</v>
       </c>
-      <c r="H39" s="186">
+      <c r="H39" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I39" s="177">
+      <c r="I39" s="176">
         <v>1</v>
       </c>
-      <c r="K39" s="174">
+      <c r="K39" s="173">
         <v>0.87</v>
       </c>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B40" s="172" t="s">
-        <v>481</v>
+      <c r="B40" s="171" t="s">
+        <v>480</v>
       </c>
       <c r="C40" s="92">
         <f t="shared" si="8"/>
         <v>103581.4047798645</v>
       </c>
-      <c r="D40" s="175">
+      <c r="D40" s="174">
         <f t="shared" si="9"/>
         <v>0.14219736043760764</v>
       </c>
-      <c r="E40" s="176">
+      <c r="E40" s="175">
         <f t="shared" si="10"/>
         <v>8173.8952201354987</v>
       </c>
-      <c r="F40" s="177">
+      <c r="F40" s="176">
         <f t="shared" si="11"/>
         <v>6.2496009166494983E-2</v>
       </c>
       <c r="G40" s="92">
         <v>111755.3</v>
       </c>
-      <c r="H40" s="186">
+      <c r="H40" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I40" s="177">
+      <c r="I40" s="176">
         <v>0.60570716705655525</v>
       </c>
-      <c r="K40" s="174">
+      <c r="K40" s="173">
         <v>0.9</v>
       </c>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B41" s="172" t="s">
-        <v>482</v>
+      <c r="B41" s="171" t="s">
+        <v>481</v>
       </c>
       <c r="C41" s="92">
         <f t="shared" si="8"/>
         <v>3649.7235506071347</v>
       </c>
-      <c r="D41" s="175">
+      <c r="D41" s="174">
         <f t="shared" si="9"/>
         <v>5.1217104912708407E-3</v>
       </c>
-      <c r="E41" s="176">
+      <c r="E41" s="175">
         <f t="shared" si="10"/>
         <v>288.0097827262025</v>
       </c>
-      <c r="F41" s="177">
+      <c r="F41" s="176">
         <f t="shared" si="11"/>
         <v>2.2510014589971318E-3</v>
       </c>
       <c r="G41" s="92">
         <v>3937.7333333333372</v>
       </c>
-      <c r="H41" s="186">
+      <c r="H41" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I41" s="177">
+      <c r="I41" s="176">
         <v>1</v>
       </c>
-      <c r="K41" s="174">
+      <c r="K41" s="173">
         <v>0.92</v>
       </c>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B42" s="172" t="s">
-        <v>486</v>
+      <c r="B42" s="171" t="s">
+        <v>485</v>
       </c>
       <c r="C42" s="92">
         <f t="shared" si="8"/>
         <v>2313.4678513921531</v>
       </c>
-      <c r="D42" s="175">
+      <c r="D42" s="174">
         <f t="shared" si="9"/>
         <v>3.175946711906122E-3</v>
       </c>
-      <c r="E42" s="176">
+      <c r="E42" s="175">
         <f t="shared" si="10"/>
         <v>182.56214860784985</v>
       </c>
-      <c r="F42" s="177">
+      <c r="F42" s="176">
         <f t="shared" si="11"/>
         <v>1.3958345936152176E-3</v>
       </c>
@@ -33360,33 +33391,33 @@
         <f>2773.36666666667*0.9</f>
         <v>2496.0300000000029</v>
       </c>
-      <c r="H42" s="186">
+      <c r="H42" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I42" s="177">
+      <c r="I42" s="176">
         <v>0.40587012896078656</v>
       </c>
-      <c r="K42" s="174">
+      <c r="K42" s="173">
         <v>0.9</v>
       </c>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B43" s="172" t="s">
-        <v>487</v>
+      <c r="B43" s="171" t="s">
+        <v>486</v>
       </c>
       <c r="C43" s="92">
         <f t="shared" si="8"/>
         <v>257.05198348801702</v>
       </c>
-      <c r="D43" s="175">
+      <c r="D43" s="174">
         <f t="shared" si="9"/>
         <v>3.5288296798956909E-4</v>
       </c>
-      <c r="E43" s="176">
+      <c r="E43" s="175">
         <f t="shared" si="10"/>
         <v>20.284683178649971</v>
       </c>
-      <c r="F43" s="177">
+      <c r="F43" s="176">
         <f t="shared" si="11"/>
         <v>1.5509273262391299E-4</v>
       </c>
@@ -33394,99 +33425,99 @@
         <f>2773.36666666667*0.1</f>
         <v>277.33666666666699</v>
       </c>
-      <c r="H43" s="186">
+      <c r="H43" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I43" s="177">
+      <c r="I43" s="176">
         <v>0.40587012896078656</v>
       </c>
-      <c r="K43" s="174">
+      <c r="K43" s="173">
         <v>0.9</v>
       </c>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B44" s="172" t="s">
-        <v>483</v>
+      <c r="B44" s="171" t="s">
+        <v>482</v>
       </c>
       <c r="C44" s="92">
         <f t="shared" si="8"/>
         <v>19145.662781409661</v>
       </c>
-      <c r="D44" s="175">
+      <c r="D44" s="174">
         <f t="shared" si="9"/>
         <v>2.9203683562603517E-2</v>
       </c>
-      <c r="E44" s="176">
+      <c r="E44" s="175">
         <f t="shared" si="10"/>
         <v>1510.837218590339</v>
       </c>
-      <c r="F44" s="177">
+      <c r="F44" s="176">
         <f t="shared" si="11"/>
         <v>1.2835074223650576E-2</v>
       </c>
       <c r="G44" s="92">
         <v>20656.5</v>
       </c>
-      <c r="H44" s="186">
+      <c r="H44" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I44" s="177">
+      <c r="I44" s="176">
         <v>0.2671631311304497</v>
       </c>
-      <c r="K44" s="174">
+      <c r="K44" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B45" s="172" t="s">
-        <v>484</v>
+      <c r="B45" s="171" t="s">
+        <v>483</v>
       </c>
       <c r="C45" s="92">
         <f t="shared" si="8"/>
         <v>35644.185384547847</v>
       </c>
-      <c r="D45" s="175">
+      <c r="D45" s="174">
         <f t="shared" si="9"/>
         <v>5.4369573030809949E-2</v>
       </c>
-      <c r="E45" s="176">
+      <c r="E45" s="175">
         <f t="shared" si="10"/>
         <v>2812.7812821188563</v>
       </c>
-      <c r="F45" s="177">
+      <c r="F45" s="176">
         <f t="shared" si="11"/>
         <v>2.3895530297152162E-2</v>
       </c>
       <c r="G45" s="92">
         <v>38456.966666666704</v>
       </c>
-      <c r="H45" s="186">
+      <c r="H45" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I45" s="177">
+      <c r="I45" s="176">
         <v>0.14385536511797675</v>
       </c>
-      <c r="K45" s="174">
+      <c r="K45" s="173">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B46" s="172" t="s">
-        <v>494</v>
+      <c r="B46" s="171" t="s">
+        <v>493</v>
       </c>
       <c r="C46" s="92">
         <f t="shared" si="8"/>
         <v>38744.652296118176</v>
       </c>
-      <c r="D46" s="175">
+      <c r="D46" s="174">
         <f t="shared" si="9"/>
         <v>5.3188960888198779E-2</v>
       </c>
-      <c r="E46" s="176">
+      <c r="E46" s="175">
         <f t="shared" si="10"/>
         <v>3057.4477038818441</v>
       </c>
-      <c r="F46" s="177">
+      <c r="F46" s="176">
         <f t="shared" si="11"/>
         <v>2.3376649024956703E-2</v>
       </c>
@@ -33494,33 +33525,33 @@
         <f>69670.1666666667*0.6</f>
         <v>41802.10000000002</v>
       </c>
-      <c r="H46" s="186">
+      <c r="H46" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I46" s="177">
+      <c r="I46" s="176">
         <v>0.46986991038291381</v>
       </c>
-      <c r="K46" s="174">
+      <c r="K46" s="173">
         <v>0.9</v>
       </c>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B47" s="172" t="s">
-        <v>493</v>
+      <c r="B47" s="171" t="s">
+        <v>492</v>
       </c>
       <c r="C47" s="92">
         <f t="shared" si="8"/>
         <v>25829.768197412119</v>
       </c>
-      <c r="D47" s="175">
+      <c r="D47" s="174">
         <f t="shared" si="9"/>
         <v>2.9549422715665987E-2</v>
       </c>
-      <c r="E47" s="176">
+      <c r="E47" s="175">
         <f t="shared" si="10"/>
         <v>2038.2984692545615</v>
       </c>
-      <c r="F47" s="177">
+      <c r="F47" s="176">
         <f t="shared" si="11"/>
         <v>1.2987027236087049E-2</v>
       </c>
@@ -33528,40 +33559,40 @@
         <f>69670.1666666667*0.4</f>
         <v>27868.06666666668</v>
       </c>
-      <c r="H47" s="186">
+      <c r="H47" s="185">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I47" s="177">
+      <c r="I47" s="176">
         <v>0.46986991038291381</v>
       </c>
-      <c r="K47" s="174">
+      <c r="K47" s="173">
         <v>0.75</v>
       </c>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B48" s="180" t="s">
-        <v>485</v>
-      </c>
-      <c r="C48" s="181">
+      <c r="B48" s="179" t="s">
+        <v>484</v>
+      </c>
+      <c r="C48" s="180">
         <v>692.67262049750991</v>
       </c>
-      <c r="D48" s="182"/>
-      <c r="E48" s="183">
+      <c r="D48" s="181"/>
+      <c r="E48" s="182">
         <v>54.660712835823112</v>
       </c>
-      <c r="F48" s="184"/>
+      <c r="F48" s="183"/>
       <c r="G48" s="92"/>
-      <c r="H48" s="187">
+      <c r="H48" s="186">
         <v>0.92685899263716798</v>
       </c>
-      <c r="I48" s="184">
+      <c r="I48" s="183">
         <v>0.15455308043620117</v>
       </c>
-      <c r="K48" s="178"/>
+      <c r="K48" s="177"/>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C52" t="s">
         <v>38</v>
@@ -33596,24 +33627,24 @@
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G53" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K53" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L53" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="N53" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
@@ -33646,12 +33677,12 @@
         <v>35</v>
       </c>
       <c r="N54" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U55" s="110" t="str">
         <f>C52&amp;C53&amp;C54</f>
@@ -33696,7 +33727,7 @@
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
@@ -33731,7 +33762,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" s="110" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="U56" s="13">
         <f t="shared" ref="U56:U61" si="15">C56/C$94*100</f>
@@ -33776,7 +33807,7 @@
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C57" s="12">
         <f>SUMPRODUCT(C8:E8,C22:E22)/SUM(C22:E22)*AF8</f>
@@ -33810,7 +33841,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="110" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="U57" s="13">
         <f t="shared" si="15"/>
@@ -33855,7 +33886,7 @@
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C58" s="12">
         <f>SUMPRODUCT(C11:E11,C22:E22)/SUM(C22:E22)*AF11</f>
@@ -33873,7 +33904,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="110" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="U58" s="13">
         <f t="shared" si="15"/>
@@ -33918,7 +33949,7 @@
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C59" s="12"/>
       <c r="D59" s="12"/>
@@ -33943,7 +33974,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="110" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U59" s="13">
         <f t="shared" si="15"/>
@@ -33988,7 +34019,7 @@
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C60" s="12">
         <f>SUMPRODUCT(C11:E11,C22:E22)/SUM(C22:E22)*AF11</f>
@@ -34012,7 +34043,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="110" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="U60" s="13">
         <f t="shared" si="15"/>
@@ -34057,7 +34088,7 @@
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C61" s="12">
         <f>SUMPRODUCT(C13:E13,C22:E22)/SUM(C22:E22)*AF13+SUMPRODUCT(C14:E14,C22:E22)/SUM(C22:E22)*AF14</f>
@@ -34090,7 +34121,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="110" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="U61" s="13">
         <f t="shared" si="15"/>
@@ -34136,12 +34167,12 @@
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="155"/>
       <c r="B62" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="C62" s="167"/>
-      <c r="D62" s="167"/>
-      <c r="E62" s="167"/>
-      <c r="F62" s="167">
+        <v>496</v>
+      </c>
+      <c r="C62" s="166"/>
+      <c r="D62" s="166"/>
+      <c r="E62" s="166"/>
+      <c r="F62" s="166">
         <f>(F15*C$22+H15*E$22)/(C$22+E$22)*AF15</f>
         <v>638.11123009623793</v>
       </c>
@@ -34153,15 +34184,15 @@
         <f>X15</f>
         <v>1897.2525000000001</v>
       </c>
-      <c r="I62" s="167">
+      <c r="I62" s="166">
         <f>SUMPRODUCT(O15:Q15,C$21:E$21)/SUM(C$21:E$21)*AF15</f>
         <v>141.0314981323211</v>
       </c>
-      <c r="J62" s="167">
+      <c r="J62" s="166">
         <f>(L15*C$21+N15*E$21)/(C$21+E$21)*AF15</f>
         <v>777.71296561650411</v>
       </c>
-      <c r="K62" s="167">
+      <c r="K62" s="166">
         <f>Y15</f>
         <v>1318.7895000000003</v>
       </c>
@@ -34172,7 +34203,7 @@
       <c r="N62" s="72"/>
       <c r="Q62" s="72"/>
       <c r="R62" s="110" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="U62" s="13">
         <f>(C63+C73)/C$94*100</f>
@@ -34216,8 +34247,8 @@
       </c>
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B63" s="168" t="s">
-        <v>396</v>
+      <c r="B63" s="167" t="s">
+        <v>395</v>
       </c>
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
@@ -34255,7 +34286,7 @@
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="110" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U63" s="13">
         <f>(C64+C74)/C$94*100</f>
@@ -34299,8 +34330,8 @@
       </c>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B64" s="168" t="s">
-        <v>514</v>
+      <c r="B64" s="167" t="s">
+        <v>513</v>
       </c>
       <c r="C64" s="12"/>
       <c r="D64" s="12"/>
@@ -34338,7 +34369,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" s="110" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U64" s="13">
         <f>(C65+C75)/C$94*100</f>
@@ -34382,8 +34413,8 @@
       </c>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B65" s="168" t="s">
-        <v>430</v>
+      <c r="B65" s="167" t="s">
+        <v>429</v>
       </c>
       <c r="C65" s="12"/>
       <c r="D65" s="12"/>
@@ -34421,7 +34452,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="110" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="U65" s="13">
         <f>(C66+C76)/C$94*100</f>
@@ -34465,8 +34496,8 @@
       </c>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B66" s="168" t="s">
-        <v>470</v>
+      <c r="B66" s="167" t="s">
+        <v>469</v>
       </c>
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
@@ -34504,7 +34535,7 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" s="110" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="U66" s="13">
         <f>C67/C$94*100</f>
@@ -34549,7 +34580,7 @@
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B67" s="110" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C67" s="12"/>
       <c r="D67" s="12"/>
@@ -34565,7 +34596,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="110" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="U67" s="13">
         <f>C72/C$94*100</f>
@@ -34611,12 +34642,12 @@
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="155"/>
       <c r="B68" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="C68" s="167"/>
-      <c r="D68" s="167"/>
-      <c r="E68" s="167"/>
-      <c r="F68" s="167">
+        <v>497</v>
+      </c>
+      <c r="C68" s="166"/>
+      <c r="D68" s="166"/>
+      <c r="E68" s="166"/>
+      <c r="F68" s="166">
         <f>(F16*C$22+H16*E$22)/(C$22+E$22)*AF16</f>
         <v>50.396705745115192</v>
       </c>
@@ -34624,15 +34655,15 @@
         <f>G16*AF16</f>
         <v>67.86</v>
       </c>
-      <c r="I68" s="167">
+      <c r="I68" s="166">
         <f>SUMPRODUCT(O16:Q16,C$21:E$21)/SUM(C$21:E$21)*AF16</f>
         <v>2.8063739226091897</v>
       </c>
-      <c r="J68" s="167">
+      <c r="J68" s="166">
         <f>(L16*C$21+N16*E$21)/(C$21+E$21)*AF16</f>
         <v>88.963475771629618</v>
       </c>
-      <c r="K68" s="167"/>
+      <c r="K68" s="166"/>
       <c r="L68" s="72">
         <f>M16*AF16</f>
         <v>27.84</v>
@@ -34640,7 +34671,7 @@
       <c r="N68" s="72"/>
       <c r="Q68" s="72"/>
       <c r="R68" s="110" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="U68" s="13">
         <f>(C69+C77)/C$94*100</f>
@@ -34684,8 +34715,8 @@
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B69" s="168" t="s">
-        <v>469</v>
+      <c r="B69" s="167" t="s">
+        <v>468</v>
       </c>
       <c r="C69" s="12"/>
       <c r="D69" s="12"/>
@@ -34716,7 +34747,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="110" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U69" s="13">
         <f>(C70+C78)/C$94*100</f>
@@ -34760,8 +34791,8 @@
       </c>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B70" s="168" t="s">
-        <v>503</v>
+      <c r="B70" s="167" t="s">
+        <v>502</v>
       </c>
       <c r="C70" s="12"/>
       <c r="D70" s="12"/>
@@ -34792,7 +34823,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="110" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="U70" s="13">
         <f t="shared" ref="U70:U83" si="45">C79/C$94*100</f>
@@ -34837,12 +34868,12 @@
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="C71" s="167"/>
-      <c r="D71" s="167"/>
-      <c r="E71" s="167"/>
-      <c r="F71" s="167">
+        <v>495</v>
+      </c>
+      <c r="C71" s="166"/>
+      <c r="D71" s="166"/>
+      <c r="E71" s="166"/>
+      <c r="F71" s="166">
         <f>(F17*C$22+H17*E$22)/(C$22+E$22)*AF17</f>
         <v>132.11599300087491</v>
       </c>
@@ -34851,15 +34882,15 @@
         <f>X17</f>
         <v>1120</v>
       </c>
-      <c r="I71" s="167">
+      <c r="I71" s="166">
         <f>SUMPRODUCT(O17:Q17,C$21:E$21)/SUM(C$21:E$21)*AF17</f>
         <v>127.97579935447216</v>
       </c>
-      <c r="J71" s="167">
+      <c r="J71" s="166">
         <f>(L17*C$21+N17*E$21)/(C$21+E$21)*AF17</f>
         <v>261.21784663361586</v>
       </c>
-      <c r="K71" s="167">
+      <c r="K71" s="166">
         <f>Y17</f>
         <v>1762</v>
       </c>
@@ -34870,7 +34901,7 @@
       <c r="N71" s="72"/>
       <c r="Q71" s="72"/>
       <c r="R71" s="110" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U71" s="13">
         <f t="shared" si="45"/>
@@ -34915,7 +34946,7 @@
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F72" s="13">
         <f t="shared" ref="F72:F92" si="52">F$71*$F27</f>
@@ -34947,7 +34978,7 @@
         <v>27.270318402958633</v>
       </c>
       <c r="R72" s="110" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U72" s="13">
         <f t="shared" si="45"/>
@@ -34991,8 +35022,8 @@
       </c>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B73" s="168" t="s">
-        <v>396</v>
+      <c r="B73" s="167" t="s">
+        <v>395</v>
       </c>
       <c r="F73" s="13">
         <f t="shared" si="52"/>
@@ -35023,7 +35054,7 @@
         <v>0</v>
       </c>
       <c r="R73" s="110" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="U73" s="13">
         <f t="shared" si="45"/>
@@ -35067,8 +35098,8 @@
       </c>
     </row>
     <row r="74" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B74" s="168" t="s">
-        <v>514</v>
+      <c r="B74" s="167" t="s">
+        <v>513</v>
       </c>
       <c r="F74" s="13">
         <f t="shared" si="52"/>
@@ -35099,7 +35130,7 @@
         <v>0</v>
       </c>
       <c r="R74" s="110" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="U74" s="13">
         <f t="shared" si="45"/>
@@ -35143,8 +35174,8 @@
       </c>
     </row>
     <row r="75" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B75" s="168" t="s">
-        <v>430</v>
+      <c r="B75" s="167" t="s">
+        <v>429</v>
       </c>
       <c r="F75" s="13">
         <f t="shared" si="52"/>
@@ -35175,7 +35206,7 @@
         <v>0</v>
       </c>
       <c r="R75" s="110" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U75" s="13">
         <f t="shared" si="45"/>
@@ -35219,8 +35250,8 @@
       </c>
     </row>
     <row r="76" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B76" s="168" t="s">
-        <v>470</v>
+      <c r="B76" s="167" t="s">
+        <v>469</v>
       </c>
       <c r="F76" s="13">
         <f t="shared" si="52"/>
@@ -35251,7 +35282,7 @@
         <v>0</v>
       </c>
       <c r="R76" s="110" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U76" s="13">
         <f t="shared" si="45"/>
@@ -35295,8 +35326,8 @@
       </c>
     </row>
     <row r="77" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B77" s="168" t="s">
-        <v>469</v>
+      <c r="B77" s="167" t="s">
+        <v>468</v>
       </c>
       <c r="F77" s="13">
         <f t="shared" si="52"/>
@@ -35327,7 +35358,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="110" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="U77" s="13">
         <f t="shared" si="45"/>
@@ -35371,8 +35402,8 @@
       </c>
     </row>
     <row r="78" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B78" s="168" t="s">
-        <v>503</v>
+      <c r="B78" s="167" t="s">
+        <v>502</v>
       </c>
       <c r="F78" s="13">
         <f t="shared" si="52"/>
@@ -35403,7 +35434,7 @@
         <v>0</v>
       </c>
       <c r="R78" s="110" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U78" s="13">
         <f t="shared" si="45"/>
@@ -35448,7 +35479,7 @@
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F79" s="13">
         <f t="shared" si="52"/>
@@ -35480,7 +35511,7 @@
         <v>19.88391208330204</v>
       </c>
       <c r="R79" s="110" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="U79" s="13">
         <f t="shared" si="45"/>
@@ -35525,7 +35556,7 @@
     </row>
     <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F80" s="13">
         <f t="shared" si="52"/>
@@ -35557,7 +35588,7 @@
         <v>0</v>
       </c>
       <c r="R80" s="110" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="U80" s="13">
         <f t="shared" si="45"/>
@@ -35602,7 +35633,7 @@
     </row>
     <row r="81" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B81" s="93" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F81" s="13">
         <f t="shared" si="52"/>
@@ -35634,7 +35665,7 @@
         <v>0</v>
       </c>
       <c r="R81" s="110" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="U81" s="13">
         <f t="shared" si="45"/>
@@ -35679,7 +35710,7 @@
     </row>
     <row r="82" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F82" s="13">
         <f t="shared" si="52"/>
@@ -35711,7 +35742,7 @@
         <v>100</v>
       </c>
       <c r="R82" s="110" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U82" s="13">
         <f t="shared" si="45"/>
@@ -35756,7 +35787,7 @@
     </row>
     <row r="83" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B83" s="110" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F83" s="13">
         <f t="shared" si="52"/>
@@ -35788,7 +35819,7 @@
         <v>100</v>
       </c>
       <c r="R83" s="110" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="U83" s="13">
         <f t="shared" si="45"/>
@@ -35833,7 +35864,7 @@
     </row>
     <row r="84" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F84" s="13">
         <f t="shared" si="52"/>
@@ -35867,7 +35898,7 @@
     </row>
     <row r="85" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F85" s="13">
         <f t="shared" si="52"/>
@@ -35941,7 +35972,7 @@
     </row>
     <row r="86" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F86" s="13">
         <f t="shared" si="52"/>
@@ -35975,7 +36006,7 @@
     </row>
     <row r="87" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B87" s="110" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F87" s="13">
         <f t="shared" si="52"/>
@@ -36014,7 +36045,7 @@
     </row>
     <row r="88" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F88" s="13">
         <f t="shared" si="52"/>
@@ -36048,7 +36079,7 @@
     </row>
     <row r="89" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B89" s="93" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F89" s="13">
         <f t="shared" si="52"/>
@@ -36081,8 +36112,8 @@
       </c>
     </row>
     <row r="90" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B90" s="162" t="s">
-        <v>453</v>
+      <c r="B90" s="161" t="s">
+        <v>452</v>
       </c>
       <c r="F90" s="13">
         <f t="shared" si="52"/>
@@ -36116,7 +36147,7 @@
     </row>
     <row r="91" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F91" s="13">
         <f t="shared" si="52"/>
@@ -36150,7 +36181,7 @@
     </row>
     <row r="92" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F92" s="13">
         <f t="shared" si="52"/>
@@ -36183,13 +36214,13 @@
       </c>
     </row>
     <row r="93" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C93" s="167"/>
-      <c r="D93" s="167"/>
-      <c r="E93" s="167"/>
-      <c r="F93" s="167"/>
-      <c r="I93" s="167"/>
-      <c r="J93" s="167"/>
-      <c r="K93" s="167"/>
+      <c r="C93" s="166"/>
+      <c r="D93" s="166"/>
+      <c r="E93" s="166"/>
+      <c r="F93" s="166"/>
+      <c r="I93" s="166"/>
+      <c r="J93" s="166"/>
+      <c r="K93" s="166"/>
       <c r="N93" s="6"/>
     </row>
     <row r="94" spans="2:30" x14ac:dyDescent="0.25">

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="541">
   <si>
     <t>value</t>
   </si>
@@ -20602,7 +20602,9 @@
       <c r="A179" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B179" s="159"/>
+      <c r="B179" s="159" t="s">
+        <v>1</v>
+      </c>
       <c r="C179" s="159" t="s">
         <v>432</v>
       </c>
@@ -20624,6 +20626,9 @@
       <c r="A180" t="s">
         <v>2</v>
       </c>
+      <c r="B180" t="s">
+        <v>1</v>
+      </c>
       <c r="C180" t="s">
         <v>432</v>
       </c>
@@ -20647,6 +20652,9 @@
       <c r="A181" t="s">
         <v>2</v>
       </c>
+      <c r="B181" t="s">
+        <v>1</v>
+      </c>
       <c r="C181" t="s">
         <v>432</v>
       </c>
@@ -20670,6 +20678,9 @@
       <c r="A182" t="s">
         <v>2</v>
       </c>
+      <c r="B182" t="s">
+        <v>1</v>
+      </c>
       <c r="C182" t="s">
         <v>432</v>
       </c>
@@ -20693,6 +20704,9 @@
       <c r="A183" t="s">
         <v>2</v>
       </c>
+      <c r="B183" t="s">
+        <v>1</v>
+      </c>
       <c r="C183" t="s">
         <v>432</v>
       </c>
@@ -20716,6 +20730,9 @@
       <c r="A184" t="s">
         <v>2</v>
       </c>
+      <c r="B184" t="s">
+        <v>1</v>
+      </c>
       <c r="C184" t="s">
         <v>432</v>
       </c>
@@ -20739,6 +20756,9 @@
       <c r="A185" t="s">
         <v>2</v>
       </c>
+      <c r="B185" t="s">
+        <v>1</v>
+      </c>
       <c r="C185" t="s">
         <v>432</v>
       </c>
@@ -20762,6 +20782,9 @@
       <c r="A186" t="s">
         <v>2</v>
       </c>
+      <c r="B186" t="s">
+        <v>1</v>
+      </c>
       <c r="C186" t="s">
         <v>432</v>
       </c>
@@ -20785,6 +20808,9 @@
       <c r="A187" t="s">
         <v>2</v>
       </c>
+      <c r="B187" t="s">
+        <v>1</v>
+      </c>
       <c r="C187" t="s">
         <v>432</v>
       </c>
@@ -20808,6 +20834,9 @@
       <c r="A188" t="s">
         <v>2</v>
       </c>
+      <c r="B188" t="s">
+        <v>1</v>
+      </c>
       <c r="C188" t="s">
         <v>432</v>
       </c>
@@ -20831,6 +20860,9 @@
       <c r="A189" t="s">
         <v>2</v>
       </c>
+      <c r="B189" t="s">
+        <v>1</v>
+      </c>
       <c r="C189" t="s">
         <v>432</v>
       </c>
@@ -20854,6 +20886,9 @@
       <c r="A190" t="s">
         <v>2</v>
       </c>
+      <c r="B190" t="s">
+        <v>1</v>
+      </c>
       <c r="C190" t="s">
         <v>432</v>
       </c>
@@ -20877,6 +20912,9 @@
       <c r="A191" t="s">
         <v>2</v>
       </c>
+      <c r="B191" t="s">
+        <v>1</v>
+      </c>
       <c r="C191" t="s">
         <v>432</v>
       </c>
@@ -20900,6 +20938,9 @@
       <c r="A192" t="s">
         <v>2</v>
       </c>
+      <c r="B192" t="s">
+        <v>1</v>
+      </c>
       <c r="C192" t="s">
         <v>432</v>
       </c>
@@ -20923,6 +20964,9 @@
       <c r="A193" t="s">
         <v>2</v>
       </c>
+      <c r="B193" t="s">
+        <v>1</v>
+      </c>
       <c r="C193" t="s">
         <v>432</v>
       </c>
@@ -20946,6 +20990,9 @@
       <c r="A194" t="s">
         <v>2</v>
       </c>
+      <c r="B194" t="s">
+        <v>1</v>
+      </c>
       <c r="C194" t="s">
         <v>432</v>
       </c>
@@ -20969,6 +21016,9 @@
       <c r="A195" t="s">
         <v>2</v>
       </c>
+      <c r="B195" t="s">
+        <v>1</v>
+      </c>
       <c r="C195" t="s">
         <v>432</v>
       </c>
@@ -20992,6 +21042,9 @@
       <c r="A196" t="s">
         <v>2</v>
       </c>
+      <c r="B196" t="s">
+        <v>1</v>
+      </c>
       <c r="C196" t="s">
         <v>432</v>
       </c>
@@ -21015,6 +21068,9 @@
       <c r="A197" t="s">
         <v>2</v>
       </c>
+      <c r="B197" t="s">
+        <v>1</v>
+      </c>
       <c r="C197" t="s">
         <v>432</v>
       </c>
@@ -21038,6 +21094,9 @@
       <c r="A198" t="s">
         <v>2</v>
       </c>
+      <c r="B198" t="s">
+        <v>1</v>
+      </c>
       <c r="C198" t="s">
         <v>432</v>
       </c>
@@ -21061,6 +21120,9 @@
       <c r="A199" t="s">
         <v>2</v>
       </c>
+      <c r="B199" t="s">
+        <v>1</v>
+      </c>
       <c r="C199" t="s">
         <v>432</v>
       </c>
@@ -21084,6 +21146,9 @@
       <c r="A200" t="s">
         <v>2</v>
       </c>
+      <c r="B200" t="s">
+        <v>1</v>
+      </c>
       <c r="C200" t="s">
         <v>432</v>
       </c>
@@ -21107,6 +21172,9 @@
       <c r="A201" t="s">
         <v>2</v>
       </c>
+      <c r="B201" t="s">
+        <v>1</v>
+      </c>
       <c r="C201" t="s">
         <v>432</v>
       </c>
@@ -21128,6 +21196,9 @@
       <c r="A202" t="s">
         <v>2</v>
       </c>
+      <c r="B202" t="s">
+        <v>1</v>
+      </c>
       <c r="C202" t="s">
         <v>432</v>
       </c>
@@ -21149,6 +21220,9 @@
       <c r="A203" t="s">
         <v>2</v>
       </c>
+      <c r="B203" t="s">
+        <v>1</v>
+      </c>
       <c r="C203" t="s">
         <v>432</v>
       </c>
@@ -21170,6 +21244,9 @@
       <c r="A204" t="s">
         <v>2</v>
       </c>
+      <c r="B204" t="s">
+        <v>1</v>
+      </c>
       <c r="C204" t="s">
         <v>432</v>
       </c>
@@ -21191,6 +21268,9 @@
       <c r="A205" t="s">
         <v>2</v>
       </c>
+      <c r="B205" t="s">
+        <v>1</v>
+      </c>
       <c r="C205" t="s">
         <v>432</v>
       </c>
@@ -21212,6 +21292,9 @@
       <c r="A206" t="s">
         <v>2</v>
       </c>
+      <c r="B206" t="s">
+        <v>1</v>
+      </c>
       <c r="C206" t="s">
         <v>432</v>
       </c>
@@ -21232,6 +21315,9 @@
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>2</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1</v>
       </c>
       <c r="C207" t="s">
         <v>432</v>
@@ -22342,7 +22428,9 @@
       <c r="A271" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B271" s="159"/>
+      <c r="B271" s="159" t="s">
+        <v>1</v>
+      </c>
       <c r="C271" s="159" t="s">
         <v>432</v>
       </c>
@@ -22364,6 +22452,9 @@
       <c r="A272" t="s">
         <v>2</v>
       </c>
+      <c r="B272" t="s">
+        <v>1</v>
+      </c>
       <c r="C272" t="s">
         <v>432</v>
       </c>
@@ -22387,6 +22478,9 @@
       <c r="A273" t="s">
         <v>2</v>
       </c>
+      <c r="B273" t="s">
+        <v>1</v>
+      </c>
       <c r="C273" t="s">
         <v>432</v>
       </c>
@@ -22410,6 +22504,9 @@
       <c r="A274" t="s">
         <v>2</v>
       </c>
+      <c r="B274" t="s">
+        <v>1</v>
+      </c>
       <c r="C274" t="s">
         <v>432</v>
       </c>
@@ -22433,6 +22530,9 @@
       <c r="A275" t="s">
         <v>2</v>
       </c>
+      <c r="B275" t="s">
+        <v>1</v>
+      </c>
       <c r="C275" t="s">
         <v>432</v>
       </c>
@@ -22456,6 +22556,9 @@
       <c r="A276" t="s">
         <v>2</v>
       </c>
+      <c r="B276" t="s">
+        <v>1</v>
+      </c>
       <c r="C276" t="s">
         <v>432</v>
       </c>
@@ -22479,6 +22582,9 @@
       <c r="A277" t="s">
         <v>2</v>
       </c>
+      <c r="B277" t="s">
+        <v>1</v>
+      </c>
       <c r="C277" t="s">
         <v>432</v>
       </c>
@@ -22502,6 +22608,9 @@
       <c r="A278" t="s">
         <v>2</v>
       </c>
+      <c r="B278" t="s">
+        <v>1</v>
+      </c>
       <c r="C278" t="s">
         <v>432</v>
       </c>
@@ -22525,6 +22634,9 @@
       <c r="A279" t="s">
         <v>2</v>
       </c>
+      <c r="B279" t="s">
+        <v>1</v>
+      </c>
       <c r="C279" t="s">
         <v>432</v>
       </c>
@@ -22548,6 +22660,9 @@
       <c r="A280" t="s">
         <v>2</v>
       </c>
+      <c r="B280" t="s">
+        <v>1</v>
+      </c>
       <c r="C280" t="s">
         <v>432</v>
       </c>
@@ -22571,6 +22686,9 @@
       <c r="A281" t="s">
         <v>2</v>
       </c>
+      <c r="B281" t="s">
+        <v>1</v>
+      </c>
       <c r="C281" t="s">
         <v>432</v>
       </c>
@@ -22594,6 +22712,9 @@
       <c r="A282" t="s">
         <v>2</v>
       </c>
+      <c r="B282" t="s">
+        <v>1</v>
+      </c>
       <c r="C282" t="s">
         <v>432</v>
       </c>
@@ -22617,6 +22738,9 @@
       <c r="A283" t="s">
         <v>2</v>
       </c>
+      <c r="B283" t="s">
+        <v>1</v>
+      </c>
       <c r="C283" t="s">
         <v>432</v>
       </c>
@@ -22640,6 +22764,9 @@
       <c r="A284" t="s">
         <v>2</v>
       </c>
+      <c r="B284" t="s">
+        <v>1</v>
+      </c>
       <c r="C284" t="s">
         <v>432</v>
       </c>
@@ -22663,6 +22790,9 @@
       <c r="A285" t="s">
         <v>2</v>
       </c>
+      <c r="B285" t="s">
+        <v>1</v>
+      </c>
       <c r="C285" t="s">
         <v>432</v>
       </c>
@@ -22686,6 +22816,9 @@
       <c r="A286" t="s">
         <v>2</v>
       </c>
+      <c r="B286" t="s">
+        <v>1</v>
+      </c>
       <c r="C286" t="s">
         <v>432</v>
       </c>
@@ -22709,6 +22842,9 @@
       <c r="A287" t="s">
         <v>2</v>
       </c>
+      <c r="B287" t="s">
+        <v>1</v>
+      </c>
       <c r="C287" t="s">
         <v>432</v>
       </c>
@@ -22732,6 +22868,9 @@
       <c r="A288" t="s">
         <v>2</v>
       </c>
+      <c r="B288" t="s">
+        <v>1</v>
+      </c>
       <c r="C288" t="s">
         <v>432</v>
       </c>
@@ -22755,6 +22894,9 @@
       <c r="A289" t="s">
         <v>2</v>
       </c>
+      <c r="B289" t="s">
+        <v>1</v>
+      </c>
       <c r="C289" t="s">
         <v>432</v>
       </c>
@@ -22778,6 +22920,9 @@
       <c r="A290" t="s">
         <v>2</v>
       </c>
+      <c r="B290" t="s">
+        <v>1</v>
+      </c>
       <c r="C290" t="s">
         <v>432</v>
       </c>
@@ -22801,6 +22946,9 @@
       <c r="A291" t="s">
         <v>2</v>
       </c>
+      <c r="B291" t="s">
+        <v>1</v>
+      </c>
       <c r="C291" t="s">
         <v>432</v>
       </c>
@@ -22824,6 +22972,9 @@
       <c r="A292" t="s">
         <v>2</v>
       </c>
+      <c r="B292" t="s">
+        <v>1</v>
+      </c>
       <c r="C292" t="s">
         <v>432</v>
       </c>
@@ -22847,6 +22998,9 @@
       <c r="A293" t="s">
         <v>2</v>
       </c>
+      <c r="B293" t="s">
+        <v>1</v>
+      </c>
       <c r="C293" t="s">
         <v>432</v>
       </c>
@@ -22868,6 +23022,9 @@
       <c r="A294" t="s">
         <v>2</v>
       </c>
+      <c r="B294" t="s">
+        <v>1</v>
+      </c>
       <c r="C294" t="s">
         <v>432</v>
       </c>
@@ -22889,6 +23046,9 @@
       <c r="A295" t="s">
         <v>2</v>
       </c>
+      <c r="B295" t="s">
+        <v>1</v>
+      </c>
       <c r="C295" t="s">
         <v>432</v>
       </c>
@@ -22910,6 +23070,9 @@
       <c r="A296" t="s">
         <v>2</v>
       </c>
+      <c r="B296" t="s">
+        <v>1</v>
+      </c>
       <c r="C296" t="s">
         <v>432</v>
       </c>
@@ -22931,6 +23094,9 @@
       <c r="A297" t="s">
         <v>2</v>
       </c>
+      <c r="B297" t="s">
+        <v>1</v>
+      </c>
       <c r="C297" t="s">
         <v>432</v>
       </c>
@@ -22952,6 +23118,9 @@
       <c r="A298" t="s">
         <v>2</v>
       </c>
+      <c r="B298" t="s">
+        <v>1</v>
+      </c>
       <c r="C298" t="s">
         <v>432</v>
       </c>
@@ -22972,6 +23141,9 @@
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>2</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1</v>
       </c>
       <c r="C299" t="s">
         <v>432</v>
@@ -24674,7 +24846,9 @@
       <c r="A395" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="B395" s="159"/>
+      <c r="B395" s="159" t="s">
+        <v>1</v>
+      </c>
       <c r="C395" s="159" t="s">
         <v>432</v>
       </c>
@@ -24696,6 +24870,9 @@
       <c r="A396" t="s">
         <v>38</v>
       </c>
+      <c r="B396" t="s">
+        <v>1</v>
+      </c>
       <c r="C396" t="s">
         <v>432</v>
       </c>
@@ -24719,6 +24896,9 @@
       <c r="A397" t="s">
         <v>38</v>
       </c>
+      <c r="B397" t="s">
+        <v>1</v>
+      </c>
       <c r="C397" t="s">
         <v>432</v>
       </c>
@@ -24742,6 +24922,9 @@
       <c r="A398" t="s">
         <v>38</v>
       </c>
+      <c r="B398" t="s">
+        <v>1</v>
+      </c>
       <c r="C398" t="s">
         <v>432</v>
       </c>
@@ -24765,6 +24948,9 @@
       <c r="A399" t="s">
         <v>38</v>
       </c>
+      <c r="B399" t="s">
+        <v>1</v>
+      </c>
       <c r="C399" t="s">
         <v>432</v>
       </c>
@@ -24788,6 +24974,9 @@
       <c r="A400" t="s">
         <v>38</v>
       </c>
+      <c r="B400" t="s">
+        <v>1</v>
+      </c>
       <c r="C400" t="s">
         <v>432</v>
       </c>
@@ -24811,6 +25000,9 @@
       <c r="A401" t="s">
         <v>38</v>
       </c>
+      <c r="B401" t="s">
+        <v>1</v>
+      </c>
       <c r="C401" t="s">
         <v>432</v>
       </c>
@@ -24834,6 +25026,9 @@
       <c r="A402" t="s">
         <v>38</v>
       </c>
+      <c r="B402" t="s">
+        <v>1</v>
+      </c>
       <c r="C402" t="s">
         <v>432</v>
       </c>
@@ -24857,6 +25052,9 @@
       <c r="A403" t="s">
         <v>38</v>
       </c>
+      <c r="B403" t="s">
+        <v>1</v>
+      </c>
       <c r="C403" t="s">
         <v>432</v>
       </c>
@@ -24880,6 +25078,9 @@
       <c r="A404" t="s">
         <v>38</v>
       </c>
+      <c r="B404" t="s">
+        <v>1</v>
+      </c>
       <c r="C404" t="s">
         <v>432</v>
       </c>
@@ -24903,6 +25104,9 @@
       <c r="A405" t="s">
         <v>38</v>
       </c>
+      <c r="B405" t="s">
+        <v>1</v>
+      </c>
       <c r="C405" t="s">
         <v>432</v>
       </c>
@@ -24926,6 +25130,9 @@
       <c r="A406" t="s">
         <v>38</v>
       </c>
+      <c r="B406" t="s">
+        <v>1</v>
+      </c>
       <c r="C406" t="s">
         <v>432</v>
       </c>
@@ -24949,6 +25156,9 @@
       <c r="A407" t="s">
         <v>38</v>
       </c>
+      <c r="B407" t="s">
+        <v>1</v>
+      </c>
       <c r="C407" t="s">
         <v>432</v>
       </c>
@@ -24972,6 +25182,9 @@
       <c r="A408" t="s">
         <v>38</v>
       </c>
+      <c r="B408" t="s">
+        <v>1</v>
+      </c>
       <c r="C408" t="s">
         <v>432</v>
       </c>
@@ -24995,6 +25208,9 @@
       <c r="A409" t="s">
         <v>38</v>
       </c>
+      <c r="B409" t="s">
+        <v>1</v>
+      </c>
       <c r="C409" t="s">
         <v>432</v>
       </c>
@@ -25018,6 +25234,9 @@
       <c r="A410" t="s">
         <v>38</v>
       </c>
+      <c r="B410" t="s">
+        <v>1</v>
+      </c>
       <c r="C410" t="s">
         <v>432</v>
       </c>
@@ -25041,6 +25260,9 @@
       <c r="A411" t="s">
         <v>38</v>
       </c>
+      <c r="B411" t="s">
+        <v>1</v>
+      </c>
       <c r="C411" t="s">
         <v>432</v>
       </c>
@@ -25064,6 +25286,9 @@
       <c r="A412" t="s">
         <v>38</v>
       </c>
+      <c r="B412" t="s">
+        <v>1</v>
+      </c>
       <c r="C412" t="s">
         <v>432</v>
       </c>
@@ -25087,6 +25312,9 @@
       <c r="A413" t="s">
         <v>38</v>
       </c>
+      <c r="B413" t="s">
+        <v>1</v>
+      </c>
       <c r="C413" t="s">
         <v>432</v>
       </c>
@@ -25110,6 +25338,9 @@
       <c r="A414" t="s">
         <v>38</v>
       </c>
+      <c r="B414" t="s">
+        <v>1</v>
+      </c>
       <c r="C414" t="s">
         <v>432</v>
       </c>
@@ -25133,6 +25364,9 @@
       <c r="A415" t="s">
         <v>38</v>
       </c>
+      <c r="B415" t="s">
+        <v>1</v>
+      </c>
       <c r="C415" t="s">
         <v>432</v>
       </c>
@@ -25156,6 +25390,9 @@
       <c r="A416" t="s">
         <v>38</v>
       </c>
+      <c r="B416" t="s">
+        <v>1</v>
+      </c>
       <c r="C416" t="s">
         <v>432</v>
       </c>
@@ -25179,6 +25416,9 @@
       <c r="A417" t="s">
         <v>38</v>
       </c>
+      <c r="B417" t="s">
+        <v>1</v>
+      </c>
       <c r="C417" t="s">
         <v>432</v>
       </c>
@@ -25200,6 +25440,9 @@
       <c r="A418" t="s">
         <v>38</v>
       </c>
+      <c r="B418" t="s">
+        <v>1</v>
+      </c>
       <c r="C418" t="s">
         <v>432</v>
       </c>
@@ -25221,6 +25464,9 @@
       <c r="A419" t="s">
         <v>38</v>
       </c>
+      <c r="B419" t="s">
+        <v>1</v>
+      </c>
       <c r="C419" t="s">
         <v>432</v>
       </c>
@@ -25242,6 +25488,9 @@
       <c r="A420" t="s">
         <v>38</v>
       </c>
+      <c r="B420" t="s">
+        <v>1</v>
+      </c>
       <c r="C420" t="s">
         <v>432</v>
       </c>
@@ -25263,6 +25512,9 @@
       <c r="A421" t="s">
         <v>38</v>
       </c>
+      <c r="B421" t="s">
+        <v>1</v>
+      </c>
       <c r="C421" t="s">
         <v>432</v>
       </c>
@@ -25284,6 +25536,9 @@
       <c r="A422" t="s">
         <v>38</v>
       </c>
+      <c r="B422" t="s">
+        <v>1</v>
+      </c>
       <c r="C422" t="s">
         <v>432</v>
       </c>
@@ -25304,6 +25559,9 @@
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>38</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1</v>
       </c>
       <c r="C423" t="s">
         <v>432</v>

--- a/data/prod_parameters/CattleHerd.xlsx
+++ b/data/prod_parameters/CattleHerd.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3715" uniqueCount="543">
   <si>
     <t>value</t>
   </si>
@@ -1840,6 +1840,12 @@
   </si>
   <si>
     <t>Converted from ECM. 2013 kg ECM/cow/year</t>
+  </si>
+  <si>
+    <t>Ahlgren et al. (2022) Miljöpåverkan av svensk nöt- och lammköttsproduktion</t>
+  </si>
+  <si>
+    <t>Växa Husdjursstatistik 2020, tab 32</t>
   </si>
 </sst>
 </file>
@@ -17926,6 +17932,7 @@
         <v>6</v>
       </c>
       <c r="I35">
+        <f>(27.5+28.4+27.6+29.9+30)/5</f>
         <v>28.68</v>
       </c>
       <c r="J35" t="s">
@@ -17933,6 +17940,9 @@
       </c>
       <c r="K35" t="s">
         <v>7</v>
+      </c>
+      <c r="L35" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -18578,6 +18588,9 @@
       <c r="K66" t="s">
         <v>10</v>
       </c>
+      <c r="L66" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -18598,6 +18611,9 @@
       <c r="K67" t="s">
         <v>22</v>
       </c>
+      <c r="L67" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -18618,6 +18634,9 @@
       <c r="K68" t="s">
         <v>24</v>
       </c>
+      <c r="L68" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -18638,6 +18657,9 @@
       <c r="K69" t="s">
         <v>22</v>
       </c>
+      <c r="L69" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -18658,6 +18680,9 @@
       <c r="K70" t="s">
         <v>24</v>
       </c>
+      <c r="L70" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -18678,6 +18703,9 @@
       <c r="K71" t="s">
         <v>28</v>
       </c>
+      <c r="L71" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -18698,6 +18726,9 @@
       <c r="K72" t="s">
         <v>24</v>
       </c>
+      <c r="L72" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -18718,6 +18749,9 @@
       <c r="K73" t="s">
         <v>28</v>
       </c>
+      <c r="L73" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
@@ -18737,6 +18771,9 @@
       </c>
       <c r="K74" t="s">
         <v>24</v>
+      </c>
+      <c r="L74" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -18774,6 +18811,9 @@
       <c r="K76" t="s">
         <v>10</v>
       </c>
+      <c r="L76" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -18794,6 +18834,9 @@
       <c r="K77" t="s">
         <v>22</v>
       </c>
+      <c r="L77" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -18814,6 +18857,9 @@
       <c r="K78" t="s">
         <v>39</v>
       </c>
+      <c r="L78" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
@@ -18834,6 +18880,9 @@
       <c r="K79" t="s">
         <v>22</v>
       </c>
+      <c r="L79" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -18854,6 +18903,9 @@
       <c r="K80" t="s">
         <v>39</v>
       </c>
+      <c r="L80" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -18874,6 +18926,9 @@
       <c r="K81" t="s">
         <v>28</v>
       </c>
+      <c r="L81" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
@@ -18894,6 +18949,9 @@
       <c r="K82" t="s">
         <v>39</v>
       </c>
+      <c r="L82" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
@@ -18914,6 +18972,9 @@
       <c r="K83" t="s">
         <v>28</v>
       </c>
+      <c r="L83" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -18933,6 +18994,9 @@
       </c>
       <c r="K84" t="s">
         <v>39</v>
+      </c>
+      <c r="L84" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
